--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Herbs" sheetId="2" state="visible" r:id="rId2"/>
@@ -13,7 +10,6 @@
     <sheet name="NPC" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -37,8 +33,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -81,20 +75,8 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
@@ -126,10 +108,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0"/>
     <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -444,8 +425,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -7323,7 +7302,7 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>A healthy pulse is neither too high nor too low, thick nor thin, wide nor narrow. It beats four to five times per breath.</t>
+          <t>A healthy pulse has neither increased nor decreased amplitude, neither a thicker nor thinner pulse line, and neither broader nor narrower pulse width. Its pulse frequency is four to five beats per breath.</t>
         </is>
       </c>
     </row>
@@ -7358,8 +7337,8 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Peak height reflects the state of Qi;
-higher peaks indicate stronger Qi stagnation, while lower peaks indicate greater Qi deficiency.</t>
+          <t>Amplitude reflects the state of Qi;
+increased amplitude indicates greater Qi stagnation, while decreased amplitude indicates greater Qi deficiency.</t>
         </is>
       </c>
     </row>
@@ -7394,8 +7373,8 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Line thickness reflects the state of blood;
-thicker lines indicate more blood stasis, while thinner lines indicate greater blood deficiency.</t>
+          <t>Pulse-line thickness reflects the state of Blood;
+a thicker pulse line indicates greater blood stasis, while a thinner pulse line indicates greater blood deficiency.</t>
         </is>
       </c>
     </row>
@@ -7430,8 +7409,8 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Pulse width reflects dampness and dryness;
-a wider pulse indicates more dampness, while a narrower pulse indicates more dryness.</t>
+          <t>Pulse width reflects Dampness and Dryness;
+broader pulse width indicates greater Dampness, while narrower pulse width indicates greater Dryness.</t>
         </is>
       </c>
     </row>
@@ -7466,8 +7445,8 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>The number of pulse peaks felt per breath reflects cold and heat;
-more beats indicate greater heat, while fewer indicate greater cold.</t>
+          <t>Pulse frequency reflects Cold and Heat;
+higher pulse frequency indicates greater Heat, while lower pulse frequency indicates greater Cold.</t>
         </is>
       </c>
     </row>
@@ -20026,7 +20005,7 @@
 [Pathogenesis] Cold constrains the exterior, closes the pores and inhibits defensive Yang.
 [Symptoms] Aversion to cold with fever, aching of the head and body, no sweating, and wheezing.
 [Pulse]
-Floating pulse (Exterior): high peak, slow rate
+Floating pulse (Exterior): increased amplitude, lower pulse frequency
 [Standard formula] Ephedra Decoction</t>
         </is>
       </c>
@@ -20070,7 +20049,7 @@
 [Pathogenesis] Wind-Cold invades the exterior; defensive Qi fails to secure the surface, allowing nutritive Yin to escape.
 [Symptoms] Aversion to wind with fever, headache, clear nasal discharge, and sweating.
 [Pulse]
-Floating pulse (Exterior): low peak, slow rate
+Floating pulse (Exterior): decreased amplitude, lower pulse frequency
 [Standard formula] Cinnamon Twig Decoction</t>
         </is>
       </c>
@@ -20114,7 +20093,7 @@
 [Pathogenesis] Wind-Heat invades the Lung and defensive level, disrupting defensive Qi and the Lung's clearing and descending functions.
 [Symptoms] Pronounced fever, a red and swollen throat, and thick yellow phlegm and nasal discharge.
 [Pulse]
-Floating pulse (Exterior): rapid rate
+Floating pulse (Exterior): higher pulse frequency
 [Standard formula] Honeysuckle and Forsythia Powder</t>
         </is>
       </c>
@@ -20158,7 +20137,7 @@
 [Pathogenesis] Warm and dry influences in early autumn invade the Lung and defensive level, impairing the Lung's moistening function.
 [Symptoms] Fever with aversion to wind; dry mouth and nose, dry throat and thirst, a dry cough with little phlegm, and thick yellow phlegm or nasal discharge.
 [Pulse]
-Floating pulse (Exterior): rapid rate, narrow wave
+Floating pulse (Exterior): higher pulse frequency, narrower pulse width
 [Standard formula] Mulberry Leaf and Apricot Kernel Decoction</t>
         </is>
       </c>
@@ -20202,7 +20181,7 @@
 [Pathogenesis] As cold sets in during late autumn, Dryness together with Wind-Cold invades the Lung and defensive level.
 [Symptoms] Aversion to cold with fever, a blocked nose with clear discharge, a dry cough with little phlegm, dry throat and lips, and dry skin.
 [Pulse]
-Floating pulse (Exterior): slow rate, narrow wave
+Floating pulse (Exterior): lower pulse frequency, narrower pulse width
 [Standard formula] Apricot Kernel and Perilla Leaf Powder</t>
         </is>
       </c>
@@ -20246,7 +20225,7 @@
 [Pathogenesis] An inherently weak constitution or prolonged illness depletes Lung Qi. Defensive Qi fails to secure the surface; loose pores weaken protection and containment.
 [Symptoms] Spontaneous sweating even at rest, worse with activity; frequent colds, aversion to wind and cold, and catching cold easily; a pale complexion, shortness of breath, fatigue, and little inclination to speak; loose pores and frequent sensitivity to wind.
 [Pulse]
-Floating pulse (Exterior): low peak
+Floating pulse (Exterior): decreased amplitude
 [Standard formula] Jade Windscreen Powder</t>
         </is>
       </c>
@@ -20290,7 +20269,7 @@
 [Pathogenesis] Wind-Cold-Damp obstructs the channels, with Cold predominating. Cold contracts and congeals; blocked Qi and blood cause severe pain.
 [Symptoms] Severe, fixed pain in the limbs and joints; worse with cold and relieved by warmth; restricted joint movement and local sensitivity to cold.
 [Pulse]
-Floating pulse (Exterior): slightly high peak, markedly slow rate, slightly broad wave
+Floating pulse (Exterior): slightly increased amplitude, markedly lower pulse frequency, slightly broader pulse width
 [Standard formula] Aconite Decoction</t>
         </is>
       </c>
@@ -20334,7 +20313,7 @@
 [Pathogenesis] Wind-Damp-Heat invades the channels and joints, or Wind-Cold-Damp stagnates and turns to Heat. Qi and blood become congested, obstructing the channels.
 [Symptoms] Red, swollen, burning joints with severe pain; hot and tender to touch, somewhat relieved by cold; fever, thirst, and irritability; restricted movement of the limbs.
 [Pulse]
-Floating pulse (Exterior): slightly high peak, rapid rate, slightly broad wave
+Floating pulse (Exterior): slightly increased amplitude, higher pulse frequency, slightly broader pulse width
 [Standard formula] White Tiger Decoction with Cinnamon Twig</t>
         </is>
       </c>
@@ -20380,7 +20359,7 @@
 [Symptoms] Heavy, aching joints, as though wrapped; fixed pain, skin numbness, and heavy limbs; joint swelling and restricted movement.
 Worse in rainy or humid weather.
 [Pulse]
-Floating pulse (Exterior): slightly high peak, slightly slow rate, markedly broad wave
+Floating pulse (Exterior): slightly increased amplitude, slightly lower pulse frequency, markedly broader pulse width
 [Standard formula] Coix Seed Decoction</t>
         </is>
       </c>
@@ -20424,7 +20403,7 @@
 [Pathogenesis] Wind-Cold-Damp invades the channels, with Wind predominating. Wind moves readily and causes shifting symptoms.
 [Symptoms] Aching joints and limbs with pain that shifts from place to place throughout the body.
 [Pulse]
-Floating pulse (Exterior): markedly high peak, slightly slow rate, slightly broad wave
+Floating pulse (Exterior): markedly increased amplitude, slightly lower pulse frequency, slightly broader pulse width
 [Standard formula] Saposhnikovia Decoction</t>
         </is>
       </c>
@@ -20468,7 +20447,7 @@
 [Pathogenesis] Pathogenic Heat congests the Lung, impairing its dispersing and descending functions; Qi becomes blocked and rises against its normal flow.
 [Symptoms] Forceful coughing and wheezing with chest tightness; thick, sticky yellow phlegm that is hard to expectorate; fever, thirst, and sore throat; flaring nostrils, relatively dry stools, and yellow urine.
 [Pulse]
-Right cun (Lung): rapid rate
+Right cun (Lung): higher pulse frequency
 [Standard formula] Ephedra, Apricot Kernel, Gypsum and Licorice Decoction</t>
         </is>
       </c>
@@ -20512,7 +20491,7 @@
 [Pathogenesis] Insufficient Lung Qi weakens its dispersing and descending functions and fails to secure the exterior.
 [Symptoms] Weak coughing and wheezing, shortness of breath and reluctance to speak, worse with activity; a weak voice and fatigue; spontaneous sweating, aversion to wind, and frequent colds; scant, thin, clear phlegm.
 [Pulse]
-Right cun (Lung): low peak
+Right cun (Lung): decreased amplitude
 [Standard formula] Lung-Tonifying Decoction</t>
         </is>
       </c>
@@ -20556,7 +20535,7 @@
 [Pathogenesis] When the Spleen fails to transform and transport, Phlegm-Damp forms internally and accumulates in the Lung, impairing its dispersing and descending functions.
 [Symptoms] A cough with abundant white, sticky phlegm that is easy to bring up; chest tightness, wheezing, and rattling phlegm in the throat; heavy limbs and a bland taste without thirst.
 [Pulse]
-Right cun (Lung): broad wave
+Right cun (Lung): broader pulse width
 [Standard formula] Two-Cured Decoction</t>
         </is>
       </c>
@@ -20600,7 +20579,7 @@
 [Pathogenesis] Depleted Lung Yin gives rise to deficiency Fire; the Lung loses moisture and cannot perform its clearing function.
 [Symptoms] A dry cough without phlegm, or a little sticky phlegm that is hard to bring up; dry throat and mouth with hoarseness; tidal fever, night sweats, and heat in the palms, soles, and chest; flushed cheekbones and weight loss.
 [Pulse]
-Right cun (Lung): thin wave, rapid rate, narrow wave
+Right cun (Lung): thinner pulse line, higher pulse frequency, narrower pulse width
 [Standard formula] Adenophora and Ophiopogon Decoction</t>
         </is>
       </c>
@@ -20644,7 +20623,7 @@
 [Pathogenesis] Pathogenic Heat enters the interior and scorches fluids into Phlegm. Phlegm and Heat combine and congest the Lung, impairing its dispersing and descending functions.
 [Symptoms] Coughing and wheezing with abundant, thick yellow phlegm that is difficult to bring up; chest tightness and pain, sometimes with flaring nostrils; fever, thirst, irritability, constipation, and yellow urine.
 [Pulse]
-Right cun (Lung): rapid rate, broad wave
+Right cun (Lung): higher pulse frequency, broader pulse width
 [Standard formula] Clear Qi and Transform Phlegm Pill</t>
         </is>
       </c>
@@ -20689,8 +20668,8 @@
 [Pathogenesis] Cold constrains the exterior while Heat is trapped inside, producing a mixed Cold-Heat pattern.
 [Symptoms] Aversion to cold without sweating, dry mouth and sore throat, generalized aches and chills, together with irritability and a sensation of internal heat.
 [Pulse]
-Floating pulse (Exterior): slow rate
-Right cun (Lung): rapid rate
+Floating pulse (Exterior): lower pulse frequency
+Right cun (Lung): higher pulse frequency
 [Standard formula] Great Azure Dragon Decoction</t>
         </is>
       </c>
@@ -20735,8 +20714,8 @@
 [Pathogenesis] External Wind-Cold constrains the surface. Retained fluid within the Lung combines with exterior Cold, obstructing Lung Qi.
 [Symptoms] Aversion to cold with fever, coughing and wheezing; copious thin, clear phlegm, chest fullness and tightness, and facial swelling.
 [Pulse]
-Floating pulse (Exterior): slow rate
-Right cun (Lung): broad wave
+Floating pulse (Exterior): lower pulse frequency
+Right cun (Lung): broader pulse width
 [Standard formula] Minor Azure Dragon Decoction</t>
         </is>
       </c>
@@ -20780,7 +20759,7 @@
 [Pathogenesis] Poor diet, overwork or prolonged illness depletes the Spleen. Middle Qi becomes weak and the Spleen cannot transform and transport properly.
 [Symptoms] Poor appetite and abdominal bloating, especially after meals; fatigue, weakness, little inclination to speak and tired limbs; a sallow complexion with weight loss or swelling; loose stools.
 [Pulse]
-Right guan (Spleen): low peak
+Right guan (Spleen): decreased amplitude
 [Standard formula] Four Gentlemen Decoction</t>
         </is>
       </c>
@@ -20824,7 +20803,7 @@
 [Pathogenesis] External Dampness, or frequent cold, raw and rich foods, causes Dampness to accumulate. It constrains Spleen Yang and impairs transformation and transport; this is an excess pattern.
 [Symptoms] Fullness in the upper abdomen and poor appetite; nausea, a sticky feeling in the mouth and a bland taste without thirst; a heavy head and body, aching limbs and drowsiness; loose, unsatisfying stools.
 [Pulse]
-Right guan (Spleen): broad wave
+Right guan (Spleen): broader pulse width
 [Standard formula] Calm the Stomach Powder</t>
         </is>
       </c>
@@ -20868,7 +20847,7 @@
 [Pathogenesis] Longstanding Spleen Qi deficiency weakens Spleen Yang. Deficiency Cold develops and the Spleen can no longer transform or digest food effectively.
 [Symptoms] Poor appetite and cold abdominal pain relieved by warmth and pressure; thin, loose stools, sometimes with undigested food; aversion to cold, cold limbs and fatigue; a bland taste without thirst and a pale or sallow complexion; possibly swelling or copious, thin, clear vaginal discharge.
 [Pulse]
-Right guan (Spleen): low peak, slow rate, broad wave
+Right guan (Spleen): decreased amplitude, lower pulse frequency, broader pulse width
 [Standard formula] Regulate the Middle Pill</t>
         </is>
       </c>
@@ -20912,7 +20891,7 @@
 [Pathogenesis] Underlying Spleen Qi deficiency weakens transformation and transport, causing fluids to accumulate as Dampness.
 [Symptoms] Poor appetite and abdominal fullness, worse after eating; fatigue, little inclination to speak and heavy limbs; loose stools or diarrhea with a sticky, unsatisfying feeling; a sallow complexion, sometimes with swelling or copious thin, clear vaginal discharge.
 [Pulse]
-Right guan (Spleen): low peak, broad wave
+Right guan (Spleen): decreased amplitude, broader pulse width
 [Standard formula] Ginseng, Poria and Atractylodes Powder</t>
         </is>
       </c>
@@ -20957,8 +20936,8 @@
 [Pathogenesis] External Wind-Cold constrains the surface while dietary injury and Dampness obstruct the middle burner: Wind-Cold outside and Damp stagnation inside.
 [Symptoms] External Wind-Cold: aversion to cold with fever, headache and heavy body, no sweating, and a blocked nose with clear discharge; internal Damp stagnation: chest fullness, abdominal distension and pain, nausea, vomiting, bowel sounds and diarrhea; chills and fever with both vomiting and diarrhea, a heavy body and chest tightness.
 [Pulse]
-Floating pulse (Exterior): slow rate
-Right guan (Spleen): broad wave
+Floating pulse (Exterior): lower pulse frequency
+Right guan (Spleen): broader pulse width
 [Standard formula] Patchouli Qi-Rectifying Powder</t>
         </is>
       </c>
@@ -21002,7 +20981,7 @@
 [Pathogenesis] In a person with underlying Yang deficiency, Cold congeals and obstructs the Heart vessels. Chest Yang is weakened; the constricted vessels cannot carry blood freely, causing pain.
 [Symptoms] Sudden, severe chest pain, worse with cold and relieved by warmth; chest tightness, shortness of breath and palpitations; aversion to cold, cold limbs, a pale face, and bluish lips and nails.
 [Pulse]
-Left cun (Heart): slow rate
+Left cun (Heart): lower pulse frequency
 [Standard formula] Chinese Angelica Decoction for Frigid Extremities</t>
         </is>
       </c>
@@ -21046,7 +21025,7 @@
 [Pathogenesis] Heart Fire blazes internally, disturbing the mind and scorching the vessels; the Fire also descends to the Small Intestine.
 [Symptoms] Heat and agitation in the chest, palpitations, insomnia and irritability; painful mouth and tongue sores and a red, sore tongue tip; dry mouth, bitter taste, a flushed face and red eyes; scant, red urine with burning, difficult urination.
 [Pulse]
-Left cun (Heart): rapid rate
+Left cun (Heart): higher pulse frequency
 [Standard formula] Guide Out the Red Powder</t>
         </is>
       </c>
@@ -21090,7 +21069,7 @@
 [Pathogenesis] Turbid Phlegm-Damp clouds the Heart orifices and disrupts awareness. Emotional constraint and weak Spleen transport may generate Phlegm that rises to disturb the mind.
 [Symptoms] Confusion or mental dullness, depression and an indifferent expression; muttering, unusual behavior or reduced awareness; rattling phlegm in the throat, chest tightness, copious phlegm and clouded consciousness; in severe cases, sudden collapse and unconsciousness.
 [Pulse]
-Left cun (Heart): broad wave
+Left cun (Heart): broader pulse width
 [Standard formula] Scour Phlegm Decoction</t>
         </is>
       </c>
@@ -21134,7 +21113,7 @@
 [Pathogenesis] Insufficient Heart Qi weakens its ability to propel blood and fails to nourish the mind.
 [Symptoms] Palpitations, worse with activity; shortness of breath, chest tightness and fatigue; spontaneous sweating and a pale complexion.
 [Pulse]
-Left cun (Heart): low peak
+Left cun (Heart): decreased amplitude
 [Standard formula] Nourish the Heart Decoction</t>
         </is>
       </c>
@@ -21178,7 +21157,7 @@
 [Pathogenesis] Blood stasis blocks the Heart vessels, impedes the circulation of Qi and blood, and deprives the Heart of nourishment. Obstruction causes pain.
 [Symptoms] Chest and Heart pain, palpitations, chest tightness, shortness of breath and breathlessness when lying down; a dull complexion and bluish lips and nails.
 [Pulse]
-Left cun (Heart): thick wave
+Left cun (Heart): thicker pulse line
 [Standard formula] Drive Out Stasis in the Mansion of Blood Decoction</t>
         </is>
       </c>
@@ -21222,7 +21201,7 @@
 [Pathogenesis] Depleted Heart Yin fails to nourish the mind, while deficiency Fire disturbs it internally.
 [Symptoms] Palpitations and unease; restlessness, insomnia and frequent waking from dreams; heat in the palms, soles and chest, tidal fever and night sweats; dry mouth and throat with flushed cheekbones.
 [Pulse]
-Left cun (Heart): thin wave, rapid rate, narrow wave
+Left cun (Heart): thinner pulse line, higher pulse frequency, narrower pulse width
 [Standard formula] Heavenly Emperor's Heart-Tonifying Elixir</t>
         </is>
       </c>
@@ -21266,7 +21245,7 @@
 [Pathogenesis] Insufficient Heart Yang cannot warm or propel effectively, giving rise to internal deficiency Cold.
 [Symptoms] Palpitations and unease; chest tightness and shortness of breath, worse with cold; aversion to cold and cool limbs; a pale complexion, fatigue and spontaneous sweating.
 [Pulse]
-Left cun (Heart): low peak, slow rate
+Left cun (Heart): decreased amplitude, lower pulse frequency
 [Standard formula] Cinnamon Twig and Licorice Decoction</t>
         </is>
       </c>
@@ -21310,7 +21289,7 @@
 [Pathogenesis] Stagnant Phlegm turns into Fire. Phlegm and Fire combine and rise to disturb the Heart and mind, causing agitation.
 [Symptoms] Restlessness, insomnia, agitation and irritability; disturbing dreams, being easily startled, sometimes incoherent speech or inappropriate laughing and crying; chest fullness, a bitter taste and copious thick, yellow phlegm.
 [Pulse]
-Left cun (Heart): rapid rate, broad wave
+Left cun (Heart): higher pulse frequency, broader pulse width
 [Standard formula] Coptis Warm-Gallbladder Decoction</t>
         </is>
       </c>
@@ -21355,8 +21334,8 @@
 [Pathogenesis] Overthinking, overwork, prolonged illness or blood loss weakens the Spleen. Insufficient production of Qi and blood depletes Heart blood, leaving the mind unnourished; this is a deficiency of both Qi and blood.
 [Symptoms] Palpitations, insomnia with vivid dreams, forgetfulness and dizziness; poor appetite, bloating, loose stools and fatigue; a sallow or pale complexion and tired limbs; in women, scant pale menstrual flow or prolonged spotting.
 [Pulse]
-Left cun (Heart): thin wave
-Right guan (Spleen): low peak
+Left cun (Heart): thinner pulse line
+Right guan (Spleen): decreased amplitude
 [Standard formula] Restore the Spleen Decoction</t>
         </is>
       </c>
@@ -21400,7 +21379,7 @@
 [Pathogenesis] Constrained Liver Qi turns to Fire, or intense anger injures the Liver. Liver Fire blazes and Qi and Fire rise; this is an excess Heat pattern.
 [Symptoms] Dizziness with a distending headache, a flushed face, red eyes and irritability; bitter and dry mouth, ringing in the ears or hearing loss, and burning pain along the ribs; insomnia and vivid dreams, possibly agitation; vomiting blood or nosebleeds.
 [Pulse]
-Left guan (Liver): rapid rate
+Left guan (Liver): higher pulse frequency
 [Standard formula] Gentian Decoction to Drain the Liver</t>
         </is>
       </c>
@@ -21444,7 +21423,7 @@
 [Pathogenesis] External Cold congeals in the Liver channel, constricting its vessels, obstructing Qi and blood, and suppressing Yang. This is an excess Cold pattern.
 [Symptoms] Cold pain in the lower abdomen; dragging, cold pain in the testicles or hernia pain; pain at the top of the head, aversion to cold, preference for warmth, relief with warmth and worsening with cold; icy limbs and a pale, bluish complexion.
 [Pulse]
-Left guan (Liver): slow rate
+Left guan (Liver): lower pulse frequency
 [Standard formula] Warm the Liver Decoction</t>
         </is>
       </c>
@@ -21488,7 +21467,7 @@
 [Pathogenesis] Emotional frustration impairs the Liver's free flow, causing Qi to stagnate and the channels to become obstructed.
 [Symptoms] Moving, distending pain in the chest, flanks, breasts or lower abdomen; low mood, irritability and frequent sighing; a lump sensation in the throat, chest tightness and belching; irregular or painful menstruation.
 [Pulse]
-Left guan (Liver): high peak
+Left guan (Liver): increased amplitude
 [Standard formula] Bupleurum Liver-Soothing Powder</t>
         </is>
       </c>
@@ -21532,7 +21511,7 @@
 [Pathogenesis] Insufficient Liver blood fails to nourish the sinews, eyes, nails and mind.
 [Symptoms] Dizziness, reduced vision and blurred sight; dry, brittle nails, numb limbs and muscle cramps; a pale or sallow complexion and pale lips and tongue; scant, pale menstruation or even absence of periods; restless sleep, vivid dreams and being easily startled.
 [Pulse]
-Left guan (Liver): thin wave
+Left guan (Liver): thinner pulse line
 [Standard formula] Four-Substance Decoction</t>
         </is>
       </c>
@@ -21576,7 +21555,7 @@
 [Pathogenesis] Impaired free flow of Liver Qi slows the blood. Blood stasis obstructs the Liver vessels.
 [Symptoms] Dry, rough skin, bruising and fine red spider-like markings; stabbing, distending pain along the ribs, low mood and pain that worsens after anger.
 [Pulse]
-Left guan (Liver): thick wave
+Left guan (Liver): thicker pulse line
 [Standard formula] Drive Out Blood Stasis Below the Diaphragm Decoction</t>
         </is>
       </c>
@@ -21620,7 +21599,7 @@
 [Pathogenesis] Emotional strain generating Fire or prolonged illness depletes Liver Yin. Deficiency Fire arises, leaving the head, eyes and sinews unnourished.
 [Symptoms] Dizziness, tinnitus, dry eyes and blurred vision; a faint burning pain in the flanks and heat in the palms, soles and chest; tidal fever, night sweats, dry mouth and throat, and facial flushing; restless or twitching hands and feet with muscle cramps.
 [Pulse]
-Left guan (Liver): thin wave, rapid rate, narrow wave
+Left guan (Liver): thinner pulse line, higher pulse frequency, narrower pulse width
 [Standard formula] Linking Decoction</t>
         </is>
       </c>
@@ -21664,7 +21643,7 @@
 [Pathogenesis] Liver and Kidney Yin deficiency cannot restrain Yang. Liver Yang rises excessively to disturb the head and eyes: deficiency at the root, excess in the manifestation.
 [Symptoms] Dizziness, tinnitus, a distending headache, a flushed face and red eyes; irritability, insomnia, vivid dreams and aching lower back and knees; a heavy head, light feeling in the feet and unsteady walking.
 [Pulse]
-Left guan (Liver): high peak, rapid rate
+Left guan (Liver): increased amplitude, higher pulse frequency
 [Standard formula] Uncaria Powder</t>
         </is>
       </c>
@@ -21709,8 +21688,8 @@
 [Pathogenesis] Emotional distress constrains Liver Qi, so Wood overacts on Earth. A weakened Spleen fails to transport properly, and Liver Qi overwhelms it.
 [Symptoms] Distending pain in the chest and flanks, frequent sighing, low mood and irritability; abdominal fullness, belching and poor appetite; abdominal pain with diarrhea, relieved after a bowel movement; poor appetite, bowel sounds and frequent passing of gas.
 [Pulse]
-Left guan (Liver): high peak
-Right guan (Spleen): low peak
+Left guan (Liver): increased amplitude
+Right guan (Spleen): decreased amplitude
 [Standard formula] Free and Easy Wanderer Powder</t>
         </is>
       </c>
@@ -21755,8 +21734,8 @@
 [Pathogenesis] Chronic coughing or wheezing, aging or overwork depletes Kidney Qi. The lower source cannot secure and draw down Lung Qi, which rises. This is deficiency wheezing involving both Lung and Kidney, without an obvious excess pathogen.
 [Symptoms] Chronic wheezing with a short inhalation and long exhalation, worse with exertion; shortness of breath and shallow inhalation; weak or aching lower back and knees with fatigue; sometimes spontaneous sweating and a weak voice.
 [Pulse]
-Right cun (Lung): low peak
-Right chi (Kidney Yang): low peak
+Right cun (Lung): decreased amplitude
+Right chi (Kidney Yang): decreased amplitude
 [Standard formula] Ginseng and Gecko Powder</t>
         </is>
       </c>
@@ -21801,8 +21780,8 @@
 [Pathogenesis] Prolonged illness, excessive sexual activity or too many warming and drying substances depletes Kidney Yin. Deficiency Fire arises and nourishment is lost.
 [Symptoms] Aching lower back and knees, dizziness, tinnitus and forgetfulness; tidal fever, night sweats, heat in the palms, soles and chest, and dry mouth and throat; in men, nocturnal emissions or premature ejaculation; in women, scant or absent periods or abnormal uterine bleeding; weight loss, insomnia and vivid dreams.
 [Pulse]
-Right chi (Kidney Yang): rapid rate
-Left chi (Kidney Yin): thin wave, narrow wave
+Right chi (Kidney Yang): higher pulse frequency
+Left chi (Kidney Yin): thinner pulse line, narrower pulse width
 [Standard formula] Six-Ingredient Rehmannia Pill</t>
         </is>
       </c>
@@ -21847,8 +21826,8 @@
 [Pathogenesis] Aging, prolonged illness or sexual overexertion depletes Kidney Yang. The Fire of the Gate of Life weakens, impairing warmth and fluid transformation.
 [Symptoms] Cold, aching and weak lower back and knees; aversion to cold and cold limbs, especially the legs; listlessness and a pale or dark complexion; copious clear urine, frequent urination at night and bed-wetting; in men, erectile dysfunction or premature ejaculation; in women, infertility associated with a cold uterus or thin, clear vaginal discharge; prolonged loose stools, undigested food or diarrhea before dawn.
 [Pulse]
-Right chi (Kidney Yang): low peak, slow rate
-Left chi (Kidney Yin): broad wave
+Right chi (Kidney Yang): decreased amplitude, lower pulse frequency
+Left chi (Kidney Yin): broader pulse width
 [Standard formula] Kidney Qi Pill from the Golden Cabinet</t>
         </is>
       </c>
@@ -21894,9 +21873,9 @@
 [Pathogenesis] Deficient Kidney Yang cannot transform fluids. Water and Dampness accumulate and overflow into the skin.
 [Symptoms] Swelling throughout the body, worse below the waist and leaving an indentation when pressed; cold, aching and weak lower back and knees with aversion to cold and cold limbs; scant or difficult urination; palpitations, shortness of breath, wheezing or coughing with watery phlegm; a pale or grayish complexion.
 [Pulse]
-Right guan (Spleen): broad wave
-Right chi (Kidney Yang): low peak, slow rate
-Left chi (Kidney Yin): broad wave
+Right guan (Spleen): broader pulse width
+Right chi (Kidney Yang): decreased amplitude, lower pulse frequency
+Left chi (Kidney Yin): broader pulse width
 [Standard formula] True Warrior Decoction</t>
         </is>
       </c>
@@ -21943,8 +21922,8 @@
 [Symptoms] In children, the 'five delays and five weaknesses': late standing, walking, speech, hair growth and tooth eruption; delayed fontanelle closure, impaired intellectual development and short stature.
 In adults, poor nourishment of the brain may cause dizziness, tinnitus, forgetfulness, insomnia and slowed thinking; early aging may cause hair loss, loose teeth or prematurely gray hair. Poor nourishment of the bones can cause weak lower back, knees and legs. Reproductive deficiency may cause low sperm count or infertility in men, and absent periods or infertility in women.
 [Pulse]
-Right chi (Kidney Yang): low peak
-Left chi (Kidney Yin): thin wave
+Right chi (Kidney Yang): decreased amplitude
+Left chi (Kidney Yin): thinner pulse line
 [Standard formula] Restore the Left Pill</t>
         </is>
       </c>
@@ -21989,8 +21968,8 @@
 [Pathogenesis] Chronic illness, aging or sexual overexertion depletes Kidney Qi, weakening its ability to store and secure. This is mainly a deficiency pattern without marked Cold or Heat.
 [Symptoms] Aching and weak lower back and knees, fatigue and tinnitus; frequent, copious clear urination, nighttime urination, bed-wetting or incontinence; in men, involuntary semen leakage or premature ejaculation; in women, copious thin, clear vaginal discharge or recurrent signs of threatened miscarriage.
 [Pulse]
-Right chi (Kidney Yang): low peak
-Left chi (Kidney Yin): broad wave
+Right chi (Kidney Yang): decreased amplitude
+Left chi (Kidney Yin): broader pulse width
 [Standard formula] Metal Lock Pill to Secure the Essence</t>
         </is>
       </c>
@@ -22036,9 +22015,9 @@
 [Pathogenesis] Qi and blood gather in the Chong and Ren vessels to nourish the fetus. Maternal Qi and blood sustain fetal growth: the Kidney supports its formation and the Spleen its nourishment.
 [Symptoms] Nausea and vomiting, sometimes immediately after eating, aversion to greasy foods, dizziness and fatigue.
 [Pulse]
-Right guan (Spleen): broad wave
-Right chi (Kidney Yang): high peak
-Left chi (Kidney Yin): thick wave
+Right guan (Spleen): broader pulse width
+Right chi (Kidney Yang): increased amplitude
+Left chi (Kidney Yin): thicker pulse line
 [Standard formula] Mount Tai Rock-Solid Powder</t>
         </is>
       </c>
@@ -22084,9 +22063,9 @@
 [Pathogenesis] Insufficient Kidney Yin fails to nourish the Heart, while excessive Heart Fire cannot descend to the Kidney. Water and Fire fail to balance, disturbing Yin and Yang. Overwork, chronic illness or emotional constraint turning to Fire may contribute; this is generally Yin deficiency with exuberant Fire.
 [Symptoms] Heart Fire above: restlessness, insomnia, frequent waking from dreams, palpitations and mouth sores; Kidney Yin deficiency below: aching lower back and knees, dizziness, tinnitus, tidal fever, night sweats and heat in the palms, soles and chest; troubled sleep with vivid dreams and persistent weakness in the lower back and knees.
 [Pulse]
-Left cun (Heart): rapid rate
-Left chi (Kidney Yin): thin wave, narrow wave
-Right chi (Kidney Yang): rapid rate
+Left cun (Heart): higher pulse frequency
+Left chi (Kidney Yin): thinner pulse line, narrower pulse width
+Right chi (Kidney Yang): higher pulse frequency
 [Standard formula] Coptis and Donkey-Hide Gelatin Decoction</t>
         </is>
       </c>
@@ -22133,10 +22112,10 @@
 [Pathogenesis] An external warm pathogen enters the interior and blazes at the Qi level. Internal Heat rises as the body's defenses struggle against it; this is an excess Heat pattern.
 [Symptoms] Intense fever with aversion to heat rather than cold; profuse sweating as Heat forces fluids outward; intense thirst with a preference for cold drinks; a surging, large pulse.
 [Pulse]
-Floating pulse (Exterior): slightly high peak, slightly rapid rate, slightly narrow wave
-Left cun (Heart): slightly high peak, slightly rapid rate, slightly narrow wave
-Right cun (Lung): markedly high peak, markedly rapid rate, markedly narrow wave
-Right guan (Spleen): markedly high peak, markedly rapid rate, markedly narrow wave
+Floating pulse (Exterior): slightly increased amplitude, slightly higher pulse frequency, slightly narrower pulse width
+Left cun (Heart): slightly increased amplitude, slightly higher pulse frequency, slightly narrower pulse width
+Right cun (Lung): markedly increased amplitude, markedly higher pulse frequency, markedly narrower pulse width
+Right guan (Spleen): markedly increased amplitude, markedly higher pulse frequency, markedly narrower pulse width
 [Standard formula] White Tiger Decoction</t>
         </is>
       </c>

--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="UI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Herbs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Formulas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Diseases" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herbs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseases" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -227,7 +227,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="NPCTranslations" displayName="NPCTranslations" ref="A1:C301" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="NPCTranslations" displayName="NPCTranslations" ref="A1:C302" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" name="keys"/>
     <tableColumn id="2" name="zh_CN"/>
@@ -24497,7 +24497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:C302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -29622,6 +29622,23 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" s="7" t="inlineStr">
+        <is>
+          <t>UI_NPC_GENERIC_SYMPTOM</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>身体不适</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>feeling unwell</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -227,7 +227,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="NPCTranslations" displayName="NPCTranslations" ref="A1:C301" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="NPCTranslations" displayName="NPCTranslations" ref="A1:C302" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" name="keys"/>
     <tableColumn id="2" name="zh_CN"/>
@@ -24497,7 +24497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:C302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -29622,6 +29622,23 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" s="7" t="inlineStr">
+        <is>
+          <t>UI_NPC_GENERIC_SYMPTOM</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>身体不适</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>feeling unwell</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="1" r:id="Rcc7faca4d2804505"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herbs" sheetId="2" r:id="R59f9f37c60f949bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulas" sheetId="3" r:id="R60113a5d37f7430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseases" sheetId="4" r:id="Re4cf8377f62f4731"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="5" r:id="R3fa422ffeb114371"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story" sheetId="6" r:id="R2af6877d69ee46b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="1" r:id="Rbf1c24fa136d4b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herbs" sheetId="2" r:id="R7a4932fafb6c49c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulas" sheetId="3" r:id="Rf56dac6e6ee64a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseases" sheetId="4" r:id="R97bfef86e40542c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="5" r:id="R5c0927361f794e72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story" sheetId="6" r:id="Rabdd4f0a83e548e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JapaneseSearch" sheetId="7" r:id="R84fc555ec4c4433d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -37,8 +38,13 @@
       <x:sz val="9"/>
       <x:name val="宋体"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -75,6 +81,11 @@
         <x:fgColor rgb="FFF3E5F5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE8F5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -84,7 +95,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -108,6 +119,8 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="常规" xfId="0"/>
@@ -10622,7 +10635,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf12337c2a94446df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84fa755a95494b78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17653,7 +17666,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30c77a796abc4137"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcd59084af7549cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20802,7 +20815,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R205450fa00a944a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbdfd52cd6c543af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25592,7 +25605,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0ad206c32534ba1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe511aef2e7f40a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31048,7 +31061,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88de05afe48d4c1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6137b79ba644478"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46743,4 +46756,2453 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="48" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="10" t="str">
+        <x:v>keys</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="str">
+        <x:v>zh_CN</x:v>
+      </x:c>
+      <x:c r="C1" s="10" t="str">
+        <x:v>ja_kana</x:v>
+      </x:c>
+      <x:c r="D1" s="10" t="str">
+        <x:v>ja_romaji</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SI_ZHEN</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>四诊</x:v>
+      </x:c>
+      <x:c r="C2" t="str"/>
+      <x:c r="D2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BA_GANG_BIAN_ZHENG</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>八纲辨证</x:v>
+      </x:c>
+      <x:c r="C3" t="str"/>
+      <x:c r="D3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YIN_YANG</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>阴阳</x:v>
+      </x:c>
+      <x:c r="C4" t="str"/>
+      <x:c r="D4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BIAO_LI</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>表里</x:v>
+      </x:c>
+      <x:c r="C5" t="str"/>
+      <x:c r="D5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HAN_RE</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>寒热</x:v>
+      </x:c>
+      <x:c r="C6" t="str"/>
+      <x:c r="D6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XU_SHI</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>虚实</x:v>
+      </x:c>
+      <x:c r="C7" t="str"/>
+      <x:c r="D7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WU_XING</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>五行</x:v>
+      </x:c>
+      <x:c r="C8" t="str"/>
+      <x:c r="D8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZANG_XIANG</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>藏象</x:v>
+      </x:c>
+      <x:c r="C9" t="str"/>
+      <x:c r="D9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>肝</x:v>
+      </x:c>
+      <x:c r="C10" t="str"/>
+      <x:c r="D10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIN</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>心</x:v>
+      </x:c>
+      <x:c r="C11" t="str"/>
+      <x:c r="D11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_PI</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>脾</x:v>
+      </x:c>
+      <x:c r="C12" t="str"/>
+      <x:c r="D12" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FEI</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>肺</x:v>
+      </x:c>
+      <x:c r="C13" t="str"/>
+      <x:c r="D13" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHEN</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>肾</x:v>
+      </x:c>
+      <x:c r="C14" t="str"/>
+      <x:c r="D14" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_QI</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>气</x:v>
+      </x:c>
+      <x:c r="C15" t="str"/>
+      <x:c r="D15" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XUE</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>血</x:v>
+      </x:c>
+      <x:c r="C16" t="str"/>
+      <x:c r="D16" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JIN</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>津</x:v>
+      </x:c>
+      <x:c r="C17" t="str"/>
+      <x:c r="D17" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YE</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>液</x:v>
+      </x:c>
+      <x:c r="C18" t="str"/>
+      <x:c r="D18" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WAI_GAN_LIU_XIE</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>外感六邪</x:v>
+      </x:c>
+      <x:c r="C19" t="str"/>
+      <x:c r="D19" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FENG_XIE</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>风邪</x:v>
+      </x:c>
+      <x:c r="C20" t="str"/>
+      <x:c r="D20" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HAN_XIE</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>寒邪</x:v>
+      </x:c>
+      <x:c r="C21" t="str"/>
+      <x:c r="D21" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHU_XIE</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>暑邪</x:v>
+      </x:c>
+      <x:c r="C22" t="str"/>
+      <x:c r="D22" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHI_XIE</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>湿邪</x:v>
+      </x:c>
+      <x:c r="C23" t="str"/>
+      <x:c r="D23" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZAO_XIE</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>燥邪</x:v>
+      </x:c>
+      <x:c r="C24" t="str"/>
+      <x:c r="D24" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_RE_XIE</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>热邪</x:v>
+      </x:c>
+      <x:c r="C25" t="str"/>
+      <x:c r="D25" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_QI_QING_NEI_SHANG</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>七情内伤</x:v>
+      </x:c>
+      <x:c r="C26" t="str"/>
+      <x:c r="D26" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XI</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>喜</x:v>
+      </x:c>
+      <x:c r="C27" t="str"/>
+      <x:c r="D27" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_NU</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>怒</x:v>
+      </x:c>
+      <x:c r="C28" t="str"/>
+      <x:c r="D28" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YOU</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>忧</x:v>
+      </x:c>
+      <x:c r="C29" t="str"/>
+      <x:c r="D29" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SI</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>思</x:v>
+      </x:c>
+      <x:c r="C30" t="str"/>
+      <x:c r="D30" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BEI</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>悲</x:v>
+      </x:c>
+      <x:c r="C31" t="str"/>
+      <x:c r="D31" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_KONG</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>恐</x:v>
+      </x:c>
+      <x:c r="C32" t="str"/>
+      <x:c r="D32" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JING</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>惊</x:v>
+      </x:c>
+      <x:c r="C33" t="str"/>
+      <x:c r="D33" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BAI_SHAO</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>白芍</x:v>
+      </x:c>
+      <x:c r="C34" t="str"/>
+      <x:c r="D34" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BAI_ZHI</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>白芷</x:v>
+      </x:c>
+      <x:c r="C35" t="str"/>
+      <x:c r="D35" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BAI_ZHU</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>白术</x:v>
+      </x:c>
+      <x:c r="C36" t="str"/>
+      <x:c r="D36" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BAI_ZI_REN</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>柏子仁</x:v>
+      </x:c>
+      <x:c r="C37" t="str"/>
+      <x:c r="D37" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BAN_XIA</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>半夏</x:v>
+      </x:c>
+      <x:c r="C38" t="str"/>
+      <x:c r="D38" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BEI_MU</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>贝母</x:v>
+      </x:c>
+      <x:c r="C39" t="str"/>
+      <x:c r="D39" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BIAN_DOU</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>扁豆</x:v>
+      </x:c>
+      <x:c r="C40" t="str"/>
+      <x:c r="D40" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BO_HE</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>薄荷</x:v>
+      </x:c>
+      <x:c r="C41" t="str"/>
+      <x:c r="D41" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CANG_ZHU</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>苍术</x:v>
+      </x:c>
+      <x:c r="C42" t="str"/>
+      <x:c r="D42" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CHAI_HU</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>柴胡</x:v>
+      </x:c>
+      <x:c r="C43" t="str"/>
+      <x:c r="D43" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CHE_QIAN_ZI</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>车前子</x:v>
+      </x:c>
+      <x:c r="C44" t="str"/>
+      <x:c r="D44" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CHEN_PI</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>陈皮</x:v>
+      </x:c>
+      <x:c r="C45" t="str"/>
+      <x:c r="D45" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CHEN_XIANG</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>沉香</x:v>
+      </x:c>
+      <x:c r="C46" t="str"/>
+      <x:c r="D46" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CHI_SHAO</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>赤芍</x:v>
+      </x:c>
+      <x:c r="C47" t="str"/>
+      <x:c r="D47" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CHUAN_LIAN_ZI</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>川楝子</x:v>
+      </x:c>
+      <x:c r="C48" t="str"/>
+      <x:c r="D48" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CHUAN_XIONG</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>川芎</x:v>
+      </x:c>
+      <x:c r="C49" t="str"/>
+      <x:c r="D49" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DA_FU_PI</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>大腹皮</x:v>
+      </x:c>
+      <x:c r="C50" t="str"/>
+      <x:c r="D50" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DA_ZAO</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>大枣</x:v>
+      </x:c>
+      <x:c r="C51" t="str"/>
+      <x:c r="D51" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DAN_DOU_CHI</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>淡豆豉</x:v>
+      </x:c>
+      <x:c r="C52" t="str"/>
+      <x:c r="D52" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DAN_NAN_XING</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>胆南星</x:v>
+      </x:c>
+      <x:c r="C53" t="str"/>
+      <x:c r="D53" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DAN_PI</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>丹皮</x:v>
+      </x:c>
+      <x:c r="C54" t="str"/>
+      <x:c r="D54" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DAN_SHEN</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>丹参</x:v>
+      </x:c>
+      <x:c r="C55" t="str"/>
+      <x:c r="D55" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DANG_GUI</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>当归</x:v>
+      </x:c>
+      <x:c r="C56" t="str"/>
+      <x:c r="D56" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DU_HUO</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>独活</x:v>
+      </x:c>
+      <x:c r="C57" t="str"/>
+      <x:c r="D57" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_E_JIAO</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>阿胶</x:v>
+      </x:c>
+      <x:c r="C58" t="str"/>
+      <x:c r="D58" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FANG_FENG</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>防风</x:v>
+      </x:c>
+      <x:c r="C59" t="str"/>
+      <x:c r="D59" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FENG_MI</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>蜂蜜</x:v>
+      </x:c>
+      <x:c r="C60" t="str"/>
+      <x:c r="D60" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FU_LING</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>茯苓</x:v>
+      </x:c>
+      <x:c r="C61" t="str"/>
+      <x:c r="D61" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FU_SHEN</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>茯神</x:v>
+      </x:c>
+      <x:c r="C62" t="str"/>
+      <x:c r="D62" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FU_ZI</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>附子</x:v>
+      </x:c>
+      <x:c r="C63" t="str"/>
+      <x:c r="D63" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_CAO</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>甘草</x:v>
+      </x:c>
+      <x:c r="C64" t="str"/>
+      <x:c r="D64" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_JIANG</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>干姜</x:v>
+      </x:c>
+      <x:c r="C65" t="str"/>
+      <x:c r="D65" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GE_GEN</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>葛根</x:v>
+      </x:c>
+      <x:c r="C66" t="str"/>
+      <x:c r="D66" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GE_JIE</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>蛤蚧</x:v>
+      </x:c>
+      <x:c r="C67" t="str"/>
+      <x:c r="D67" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GOU_QI_ZI</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>枸杞子</x:v>
+      </x:c>
+      <x:c r="C68" t="str"/>
+      <x:c r="D68" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GOU_TENG</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>钩藤</x:v>
+      </x:c>
+      <x:c r="C69" t="str"/>
+      <x:c r="D69" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GUA_LOU_REN</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>瓜蒌仁</x:v>
+      </x:c>
+      <x:c r="C70" t="str"/>
+      <x:c r="D70" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GUI_BAN_JIAO</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>龟板胶</x:v>
+      </x:c>
+      <x:c r="C71" t="str"/>
+      <x:c r="D71" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GUI_ZHI</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>桂枝</x:v>
+      </x:c>
+      <x:c r="C72" t="str"/>
+      <x:c r="D72" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HONG_HUA</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>红花</x:v>
+      </x:c>
+      <x:c r="C73" t="str"/>
+      <x:c r="D73" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HOU_PO</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>厚朴</x:v>
+      </x:c>
+      <x:c r="C74" t="str"/>
+      <x:c r="D74" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HUANG_LIAN</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>黄连</x:v>
+      </x:c>
+      <x:c r="C75" t="str"/>
+      <x:c r="D75" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HUANG_QI</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>黄芪</x:v>
+      </x:c>
+      <x:c r="C76" t="str"/>
+      <x:c r="D76" t="str"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HUANG_QIN</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>黄芩</x:v>
+      </x:c>
+      <x:c r="C77" t="str"/>
+      <x:c r="D77" t="str"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HUI_XIANG</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>茴香</x:v>
+      </x:c>
+      <x:c r="C78" t="str"/>
+      <x:c r="D78" t="str"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HUO_XIANG</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>藿香</x:v>
+      </x:c>
+      <x:c r="C79" t="str"/>
+      <x:c r="D79" t="str"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JI_ZI_HUANG</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>鸡子黄</x:v>
+      </x:c>
+      <x:c r="C80" t="str"/>
+      <x:c r="D80" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JIE_GENG</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>桔梗</x:v>
+      </x:c>
+      <x:c r="C81" t="str"/>
+      <x:c r="D81" t="str"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JIN_YIN_HUA</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>金银花</x:v>
+      </x:c>
+      <x:c r="C82" t="str"/>
+      <x:c r="D82" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JING_JIE</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>荆芥</x:v>
+      </x:c>
+      <x:c r="C83" t="str"/>
+      <x:c r="D83" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JING_MI</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>粳米</x:v>
+      </x:c>
+      <x:c r="C84" t="str"/>
+      <x:c r="D84" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JU_HUA</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>菊花</x:v>
+      </x:c>
+      <x:c r="C85" t="str"/>
+      <x:c r="D85" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LI_PI</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>梨皮</x:v>
+      </x:c>
+      <x:c r="C86" t="str"/>
+      <x:c r="D86" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LIAN_QIAO</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>连翘</x:v>
+      </x:c>
+      <x:c r="C87" t="str"/>
+      <x:c r="D87" t="str"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LIAN_XU</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>莲须</x:v>
+      </x:c>
+      <x:c r="C88" t="str"/>
+      <x:c r="D88" t="str"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LIAN_ZI</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>莲子</x:v>
+      </x:c>
+      <x:c r="C89" t="str"/>
+      <x:c r="D89" t="str"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LONG_DAN_CAO</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>龙胆草</x:v>
+      </x:c>
+      <x:c r="C90" t="str"/>
+      <x:c r="D90" t="str"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LONG_GU</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>龙骨</x:v>
+      </x:c>
+      <x:c r="C91" t="str"/>
+      <x:c r="D91" t="str"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LONG_YAN</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>龙眼</x:v>
+      </x:c>
+      <x:c r="C92" t="str"/>
+      <x:c r="D92" t="str"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LU_GEN</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>芦根</x:v>
+      </x:c>
+      <x:c r="C93" t="str"/>
+      <x:c r="D93" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LU_JIAO_JIAO</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>鹿角胶</x:v>
+      </x:c>
+      <x:c r="C94" t="str"/>
+      <x:c r="D94" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_MA_HUANG</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>麻黄</x:v>
+      </x:c>
+      <x:c r="C95" t="str"/>
+      <x:c r="D95" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_MAI_MEN_DONG</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>麦门冬</x:v>
+      </x:c>
+      <x:c r="C96" t="str"/>
+      <x:c r="D96" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_MU_LI</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>牡蛎</x:v>
+      </x:c>
+      <x:c r="C97" t="str"/>
+      <x:c r="D97" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_MU_TONG</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>木通</x:v>
+      </x:c>
+      <x:c r="C98" t="str"/>
+      <x:c r="D98" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_MU_XIANG</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>木香</x:v>
+      </x:c>
+      <x:c r="C99" t="str"/>
+      <x:c r="D99" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_NIU_BANG_ZI</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>牛蒡子</x:v>
+      </x:c>
+      <x:c r="C100" t="str"/>
+      <x:c r="D100" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_NIU_XI</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>牛膝</x:v>
+      </x:c>
+      <x:c r="C101" t="str"/>
+      <x:c r="D101" t="str"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_NUO_MI</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>糯米</x:v>
+      </x:c>
+      <x:c r="C102" t="str"/>
+      <x:c r="D102" t="str"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_QIAN_HU</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>前胡</x:v>
+      </x:c>
+      <x:c r="C103" t="str"/>
+      <x:c r="D103" t="str"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_QIAN_SHI</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>芡实</x:v>
+      </x:c>
+      <x:c r="C104" t="str"/>
+      <x:c r="D104" t="str"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_QIANG_HUO</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>羌活</x:v>
+      </x:c>
+      <x:c r="C105" t="str"/>
+      <x:c r="D105" t="str"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_QIN_JIAO</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>秦艽</x:v>
+      </x:c>
+      <x:c r="C106" t="str"/>
+      <x:c r="D106" t="str"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_REN_SHEN</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>人参</x:v>
+      </x:c>
+      <x:c r="C107" t="str"/>
+      <x:c r="D107" t="str"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ROU_GUI</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>肉桂</x:v>
+      </x:c>
+      <x:c r="C108" t="str"/>
+      <x:c r="D108" t="str"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SANG_BAI_PI</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>桑白皮</x:v>
+      </x:c>
+      <x:c r="C109" t="str"/>
+      <x:c r="D109" t="str"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SANG_YE</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>桑叶</x:v>
+      </x:c>
+      <x:c r="C110" t="str"/>
+      <x:c r="D110" t="str"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHA_REN</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>砂仁</x:v>
+      </x:c>
+      <x:c r="C111" t="str"/>
+      <x:c r="D111" t="str"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHA_SHEN</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>沙参</x:v>
+      </x:c>
+      <x:c r="C112" t="str"/>
+      <x:c r="D112" t="str"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHA_YUAN_ZI</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>沙苑子</x:v>
+      </x:c>
+      <x:c r="C113" t="str"/>
+      <x:c r="D113" t="str"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHAN_YAO</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>山药</x:v>
+      </x:c>
+      <x:c r="C114" t="str"/>
+      <x:c r="D114" t="str"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHAN_ZHU_YU</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>山茱萸</x:v>
+      </x:c>
+      <x:c r="C115" t="str"/>
+      <x:c r="D115" t="str"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHENG_DI_HUANG</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>生地黄</x:v>
+      </x:c>
+      <x:c r="C116" t="str"/>
+      <x:c r="D116" t="str"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHENG_JIANG</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>生姜</x:v>
+      </x:c>
+      <x:c r="C117" t="str"/>
+      <x:c r="D117" t="str"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHI_CHANG_PU</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>石菖蒲</x:v>
+      </x:c>
+      <x:c r="C118" t="str"/>
+      <x:c r="D118" t="str"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHI_GAO</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>石膏</x:v>
+      </x:c>
+      <x:c r="C119" t="str"/>
+      <x:c r="D119" t="str"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHU_DI_HUANG</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>熟地黄</x:v>
+      </x:c>
+      <x:c r="C120" t="str"/>
+      <x:c r="D120" t="str"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SU_YE</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>苏叶</x:v>
+      </x:c>
+      <x:c r="C121" t="str"/>
+      <x:c r="D121" t="str"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SUAN_ZAO_REN</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>酸枣仁</x:v>
+      </x:c>
+      <x:c r="C122" t="str"/>
+      <x:c r="D122" t="str"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TAO_REN</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>桃仁</x:v>
+      </x:c>
+      <x:c r="C123" t="str"/>
+      <x:c r="D123" t="str"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TIAN_HUA_FEN</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>天花粉</x:v>
+      </x:c>
+      <x:c r="C124" t="str"/>
+      <x:c r="D124" t="str"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TIAN_MEN_DONG</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>天门冬</x:v>
+      </x:c>
+      <x:c r="C125" t="str"/>
+      <x:c r="D125" t="str"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TU_SI_ZI</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>菟丝子</x:v>
+      </x:c>
+      <x:c r="C126" t="str"/>
+      <x:c r="D126" t="str"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WU_LING_ZHI</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>五灵脂</x:v>
+      </x:c>
+      <x:c r="C127" t="str"/>
+      <x:c r="D127" t="str"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WU_TOU</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>乌头</x:v>
+      </x:c>
+      <x:c r="C128" t="str"/>
+      <x:c r="D128" t="str"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WU_WEI_ZI</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>五味子</x:v>
+      </x:c>
+      <x:c r="C129" t="str"/>
+      <x:c r="D129" t="str"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WU_YAO</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>乌药</x:v>
+      </x:c>
+      <x:c r="C130" t="str"/>
+      <x:c r="D130" t="str"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XI_XIN</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>细辛</x:v>
+      </x:c>
+      <x:c r="C131" t="str"/>
+      <x:c r="D131" t="str"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIANG_FU</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>香附</x:v>
+      </x:c>
+      <x:c r="C132" t="str"/>
+      <x:c r="D132" t="str"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XING_REN</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>杏仁</x:v>
+      </x:c>
+      <x:c r="C133" t="str"/>
+      <x:c r="D133" t="str"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XU_DUAN</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>续断</x:v>
+      </x:c>
+      <x:c r="C134" t="str"/>
+      <x:c r="D134" t="str"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XUAN_SHEN</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>玄参</x:v>
+      </x:c>
+      <x:c r="C135" t="str"/>
+      <x:c r="D135" t="str"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YAN_HU_SUO</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>延胡索</x:v>
+      </x:c>
+      <x:c r="C136" t="str"/>
+      <x:c r="D136" t="str"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YI_YI_REN</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>薏苡仁</x:v>
+      </x:c>
+      <x:c r="C137" t="str"/>
+      <x:c r="D137" t="str"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YU_ZHU</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>玉竹</x:v>
+      </x:c>
+      <x:c r="C138" t="str"/>
+      <x:c r="D138" t="str"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YUAN_ZHI</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>远志</x:v>
+      </x:c>
+      <x:c r="C139" t="str"/>
+      <x:c r="D139" t="str"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZE_XIE</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>泽泻</x:v>
+      </x:c>
+      <x:c r="C140" t="str"/>
+      <x:c r="D140" t="str"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZHI_KE</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>枳壳</x:v>
+      </x:c>
+      <x:c r="C141" t="str"/>
+      <x:c r="D141" t="str"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZHI_MU</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>知母</x:v>
+      </x:c>
+      <x:c r="C142" t="str"/>
+      <x:c r="D142" t="str"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZHI_SHI</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>枳实</x:v>
+      </x:c>
+      <x:c r="C143" t="str"/>
+      <x:c r="D143" t="str"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZHI_ZI</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>栀子</x:v>
+      </x:c>
+      <x:c r="C144" t="str"/>
+      <x:c r="D144" t="str"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZHU_RU</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>竹茹</x:v>
+      </x:c>
+      <x:c r="C145" t="str"/>
+      <x:c r="D145" t="str"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZHU_YE</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>竹叶</x:v>
+      </x:c>
+      <x:c r="C146" t="str"/>
+      <x:c r="D146" t="str"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZI_WAN</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>紫菀</x:v>
+      </x:c>
+      <x:c r="C147" t="str"/>
+      <x:c r="D147" t="str"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_MA_HUANG_TANG</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>麻黄汤</x:v>
+      </x:c>
+      <x:c r="C148" t="str"/>
+      <x:c r="D148" t="str"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GUI_ZHI_TANG</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>桂枝汤</x:v>
+      </x:c>
+      <x:c r="C149" t="str"/>
+      <x:c r="D149" t="str"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YIN_QIAO_SAN</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>银翘散</x:v>
+      </x:c>
+      <x:c r="C150" t="str"/>
+      <x:c r="D150" t="str"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SANG_XING_TANG</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>桑杏汤</x:v>
+      </x:c>
+      <x:c r="C151" t="str"/>
+      <x:c r="D151" t="str"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XING_SU_SAN</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>杏苏散</x:v>
+      </x:c>
+      <x:c r="C152" t="str"/>
+      <x:c r="D152" t="str"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YU_PING_FENG_SAN</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>玉屏风散</x:v>
+      </x:c>
+      <x:c r="C153" t="str"/>
+      <x:c r="D153" t="str"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WU_TOU_TANG</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>乌头汤</x:v>
+      </x:c>
+      <x:c r="C154" t="str"/>
+      <x:c r="D154" t="str"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BAI_HU_GUI_ZHI_TANG</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>白虎桂枝汤</x:v>
+      </x:c>
+      <x:c r="C155" t="str"/>
+      <x:c r="D155" t="str"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YI_YI_REN_TANG</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>薏苡仁汤</x:v>
+      </x:c>
+      <x:c r="C156" t="str"/>
+      <x:c r="D156" t="str"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FANG_FENG_TANG</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>防风汤</x:v>
+      </x:c>
+      <x:c r="C157" t="str"/>
+      <x:c r="D157" t="str"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_MA_XING_SHI_GAN_TANG</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>麻杏石甘汤</x:v>
+      </x:c>
+      <x:c r="C158" t="str"/>
+      <x:c r="D158" t="str"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BU_FEI_TANG</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>补肺汤</x:v>
+      </x:c>
+      <x:c r="C159" t="str"/>
+      <x:c r="D159" t="str"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ER_CHEN_TANG</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>二陈汤</x:v>
+      </x:c>
+      <x:c r="C160" t="str"/>
+      <x:c r="D160" t="str"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHA_SHEN_MAI_DONG_TANG</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>沙参麦冬汤</x:v>
+      </x:c>
+      <x:c r="C161" t="str"/>
+      <x:c r="D161" t="str"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_QING_QI_HUA_TAN_WAN</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>清气化痰丸</x:v>
+      </x:c>
+      <x:c r="C162" t="str"/>
+      <x:c r="D162" t="str"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DA_QING_LONG_TANG</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>大青龙汤</x:v>
+      </x:c>
+      <x:c r="C163" t="str"/>
+      <x:c r="D163" t="str"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIAO_QING_LONG_TANG</x:v>
+      </x:c>
+      <x:c r="B164" t="str">
+        <x:v>小青龙汤</x:v>
+      </x:c>
+      <x:c r="C164" t="str"/>
+      <x:c r="D164" t="str"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SI_JUN_ZI_TANG</x:v>
+      </x:c>
+      <x:c r="B165" t="str">
+        <x:v>四君子汤</x:v>
+      </x:c>
+      <x:c r="C165" t="str"/>
+      <x:c r="D165" t="str"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_PING_WEI_SAN</x:v>
+      </x:c>
+      <x:c r="B166" t="str">
+        <x:v>平胃散</x:v>
+      </x:c>
+      <x:c r="C166" t="str"/>
+      <x:c r="D166" t="str"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LI_ZHONG_WAN</x:v>
+      </x:c>
+      <x:c r="B167" t="str">
+        <x:v>理中丸</x:v>
+      </x:c>
+      <x:c r="C167" t="str"/>
+      <x:c r="D167" t="str"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHEN_LING_BAI_ZHU_SAN</x:v>
+      </x:c>
+      <x:c r="B168" t="str">
+        <x:v>参苓白术散</x:v>
+      </x:c>
+      <x:c r="C168" t="str"/>
+      <x:c r="D168" t="str"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HUO_XIANG_ZHENG_QI_SAN</x:v>
+      </x:c>
+      <x:c r="B169" t="str">
+        <x:v>藿香正气散</x:v>
+      </x:c>
+      <x:c r="C169" t="str"/>
+      <x:c r="D169" t="str"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DANG_GUI_SI_NI_TANG</x:v>
+      </x:c>
+      <x:c r="B170" t="str">
+        <x:v>当归四逆汤</x:v>
+      </x:c>
+      <x:c r="C170" t="str"/>
+      <x:c r="D170" t="str"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DAO_CHI_SAN</x:v>
+      </x:c>
+      <x:c r="B171" t="str">
+        <x:v>导赤散</x:v>
+      </x:c>
+      <x:c r="C171" t="str"/>
+      <x:c r="D171" t="str"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_DI_TAN_TANG</x:v>
+      </x:c>
+      <x:c r="B172" t="str">
+        <x:v>涤痰汤</x:v>
+      </x:c>
+      <x:c r="C172" t="str"/>
+      <x:c r="D172" t="str"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YANG_XIN_TANG</x:v>
+      </x:c>
+      <x:c r="B173" t="str">
+        <x:v>养心汤</x:v>
+      </x:c>
+      <x:c r="C173" t="str"/>
+      <x:c r="D173" t="str"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XUE_FU_ZHU_YU_TANG</x:v>
+      </x:c>
+      <x:c r="B174" t="str">
+        <x:v>血府逐瘀汤</x:v>
+      </x:c>
+      <x:c r="C174" t="str"/>
+      <x:c r="D174" t="str"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TIAN_WANG_BU_XIN_DAN</x:v>
+      </x:c>
+      <x:c r="B175" t="str">
+        <x:v>天王补心丹</x:v>
+      </x:c>
+      <x:c r="C175" t="str"/>
+      <x:c r="D175" t="str"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GUI_ZHI_GAN_CAO_TANG</x:v>
+      </x:c>
+      <x:c r="B176" t="str">
+        <x:v>桂枝甘草汤</x:v>
+      </x:c>
+      <x:c r="C176" t="str"/>
+      <x:c r="D176" t="str"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HUANG_LIAN_WEN_DAN_TANG</x:v>
+      </x:c>
+      <x:c r="B177" t="str">
+        <x:v>黄连温胆汤</x:v>
+      </x:c>
+      <x:c r="C177" t="str"/>
+      <x:c r="D177" t="str"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GUI_PI_TANG</x:v>
+      </x:c>
+      <x:c r="B178" t="str">
+        <x:v>归脾汤</x:v>
+      </x:c>
+      <x:c r="C178" t="str"/>
+      <x:c r="D178" t="str"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LONG_DAN_XIE_GAN_TANG</x:v>
+      </x:c>
+      <x:c r="B179" t="str">
+        <x:v>龙胆泻肝汤</x:v>
+      </x:c>
+      <x:c r="C179" t="str"/>
+      <x:c r="D179" t="str"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_NUAN_GAN_JIAN</x:v>
+      </x:c>
+      <x:c r="B180" t="str">
+        <x:v>暖肝煎</x:v>
+      </x:c>
+      <x:c r="C180" t="str"/>
+      <x:c r="D180" t="str"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_CHAI_HU_SHU_GAN_SAN</x:v>
+      </x:c>
+      <x:c r="B181" t="str">
+        <x:v>柴胡疏肝散</x:v>
+      </x:c>
+      <x:c r="C181" t="str"/>
+      <x:c r="D181" t="str"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SI_WU_TANG</x:v>
+      </x:c>
+      <x:c r="B182" t="str">
+        <x:v>四物汤</x:v>
+      </x:c>
+      <x:c r="C182" t="str"/>
+      <x:c r="D182" t="str"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GE_XIA_ZHU_YU_TANG</x:v>
+      </x:c>
+      <x:c r="B183" t="str">
+        <x:v>膈下逐瘀汤</x:v>
+      </x:c>
+      <x:c r="C183" t="str"/>
+      <x:c r="D183" t="str"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_YI_GUAN_JIAN</x:v>
+      </x:c>
+      <x:c r="B184" t="str">
+        <x:v>一贯煎</x:v>
+      </x:c>
+      <x:c r="C184" t="str"/>
+      <x:c r="D184" t="str"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GOU_TENG_SAN</x:v>
+      </x:c>
+      <x:c r="B185" t="str">
+        <x:v>钩藤散</x:v>
+      </x:c>
+      <x:c r="C185" t="str"/>
+      <x:c r="D185" t="str"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIAO_YAO_SAN</x:v>
+      </x:c>
+      <x:c r="B186" t="str">
+        <x:v>逍遥散</x:v>
+      </x:c>
+      <x:c r="C186" t="str"/>
+      <x:c r="D186" t="str"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_REN_SHEN_GE_JIE_SAN</x:v>
+      </x:c>
+      <x:c r="B187" t="str">
+        <x:v>人参蛤蚧散</x:v>
+      </x:c>
+      <x:c r="C187" t="str"/>
+      <x:c r="D187" t="str"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LIU_WEI_DI_HUANG_WAN</x:v>
+      </x:c>
+      <x:c r="B188" t="str">
+        <x:v>六味地黄丸</x:v>
+      </x:c>
+      <x:c r="C188" t="str"/>
+      <x:c r="D188" t="str"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JIN_GUI_SHEN_QI_WAN</x:v>
+      </x:c>
+      <x:c r="B189" t="str">
+        <x:v>金匮肾气丸</x:v>
+      </x:c>
+      <x:c r="C189" t="str"/>
+      <x:c r="D189" t="str"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZHEN_WU_TANG</x:v>
+      </x:c>
+      <x:c r="B190" t="str">
+        <x:v>真武汤</x:v>
+      </x:c>
+      <x:c r="C190" t="str"/>
+      <x:c r="D190" t="str"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZUO_GUI_WAN</x:v>
+      </x:c>
+      <x:c r="B191" t="str">
+        <x:v>左归丸</x:v>
+      </x:c>
+      <x:c r="C191" t="str"/>
+      <x:c r="D191" t="str"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_JIN_SUO_GU_JING_WAN</x:v>
+      </x:c>
+      <x:c r="B192" t="str">
+        <x:v>金锁固精丸</x:v>
+      </x:c>
+      <x:c r="C192" t="str"/>
+      <x:c r="D192" t="str"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TAI_SHAN_PAN_SHI_SAN</x:v>
+      </x:c>
+      <x:c r="B193" t="str">
+        <x:v>泰山磐石散</x:v>
+      </x:c>
+      <x:c r="C193" t="str"/>
+      <x:c r="D193" t="str"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HUANG_LIAN_E_JIAO_TANG</x:v>
+      </x:c>
+      <x:c r="B194" t="str">
+        <x:v>黄连阿胶汤</x:v>
+      </x:c>
+      <x:c r="C194" t="str"/>
+      <x:c r="D194" t="str"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BAI_HU_TANG</x:v>
+      </x:c>
+      <x:c r="B195" t="str">
+        <x:v>白虎汤</x:v>
+      </x:c>
+      <x:c r="C195" t="str"/>
+      <x:c r="D195" t="str"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FENG_HAN_BIAO_SHI_ZHENG</x:v>
+      </x:c>
+      <x:c r="B196" t="str">
+        <x:v>风寒表实证</x:v>
+      </x:c>
+      <x:c r="C196" t="str"/>
+      <x:c r="D196" t="str"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FENG_HAN_BIAO_XU_ZHENG</x:v>
+      </x:c>
+      <x:c r="B197" t="str">
+        <x:v>风寒表虚证</x:v>
+      </x:c>
+      <x:c r="C197" t="str"/>
+      <x:c r="D197" t="str"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FENG_RE_BIAO_ZHENG</x:v>
+      </x:c>
+      <x:c r="B198" t="str">
+        <x:v>风热表证</x:v>
+      </x:c>
+      <x:c r="C198" t="str"/>
+      <x:c r="D198" t="str"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WEN_ZAO_ZHENG</x:v>
+      </x:c>
+      <x:c r="B199" t="str">
+        <x:v>温燥证</x:v>
+      </x:c>
+      <x:c r="C199" t="str"/>
+      <x:c r="D199" t="str"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_LIANG_ZAO_ZHENG</x:v>
+      </x:c>
+      <x:c r="B200" t="str">
+        <x:v>凉燥证</x:v>
+      </x:c>
+      <x:c r="C200" t="str"/>
+      <x:c r="D200" t="str"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WEI_QI_XU</x:v>
+      </x:c>
+      <x:c r="B201" t="str">
+        <x:v>卫气虚</x:v>
+      </x:c>
+      <x:c r="C201" t="str"/>
+      <x:c r="D201" t="str"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TONG_BI</x:v>
+      </x:c>
+      <x:c r="B202" t="str">
+        <x:v>痛痹</x:v>
+      </x:c>
+      <x:c r="C202" t="str"/>
+      <x:c r="D202" t="str"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_RE_BI</x:v>
+      </x:c>
+      <x:c r="B203" t="str">
+        <x:v>热痹</x:v>
+      </x:c>
+      <x:c r="C203" t="str"/>
+      <x:c r="D203" t="str"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_ZHUO_BI</x:v>
+      </x:c>
+      <x:c r="B204" t="str">
+        <x:v>着痹</x:v>
+      </x:c>
+      <x:c r="C204" t="str"/>
+      <x:c r="D204" t="str"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XING_BI</x:v>
+      </x:c>
+      <x:c r="B205" t="str">
+        <x:v>行痹</x:v>
+      </x:c>
+      <x:c r="C205" t="str"/>
+      <x:c r="D205" t="str"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FEI_RE_YONG_SHENG</x:v>
+      </x:c>
+      <x:c r="B206" t="str">
+        <x:v>肺热壅盛</x:v>
+      </x:c>
+      <x:c r="C206" t="str"/>
+      <x:c r="D206" t="str"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FEI_QI_XU</x:v>
+      </x:c>
+      <x:c r="B207" t="str">
+        <x:v>肺气虚</x:v>
+      </x:c>
+      <x:c r="C207" t="str"/>
+      <x:c r="D207" t="str"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TAN_SHI_ZU_FEI</x:v>
+      </x:c>
+      <x:c r="B208" t="str">
+        <x:v>痰湿阻肺</x:v>
+      </x:c>
+      <x:c r="C208" t="str"/>
+      <x:c r="D208" t="str"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_FEI_YIN_XU</x:v>
+      </x:c>
+      <x:c r="B209" t="str">
+        <x:v>肺阴虚</x:v>
+      </x:c>
+      <x:c r="C209" t="str"/>
+      <x:c r="D209" t="str"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TAN_RE_YONG_FEI</x:v>
+      </x:c>
+      <x:c r="B210" t="str">
+        <x:v>痰热壅肺</x:v>
+      </x:c>
+      <x:c r="C210" t="str"/>
+      <x:c r="D210" t="str"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BIAO_HAN_LI_RE</x:v>
+      </x:c>
+      <x:c r="B211" t="str">
+        <x:v>表寒里热</x:v>
+      </x:c>
+      <x:c r="C211" t="str"/>
+      <x:c r="D211" t="str"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_BIAO_HAN_LI_YIN</x:v>
+      </x:c>
+      <x:c r="B212" t="str">
+        <x:v>表寒里饮</x:v>
+      </x:c>
+      <x:c r="C212" t="str"/>
+      <x:c r="D212" t="str"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_PI_QI_XU</x:v>
+      </x:c>
+      <x:c r="B213" t="str">
+        <x:v>脾气虚</x:v>
+      </x:c>
+      <x:c r="C213" t="str"/>
+      <x:c r="D213" t="str"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHI_SHENG_KUN_PI</x:v>
+      </x:c>
+      <x:c r="B214" t="str">
+        <x:v>湿盛困脾</x:v>
+      </x:c>
+      <x:c r="C214" t="str"/>
+      <x:c r="D214" t="str"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_PI_YANG_XU</x:v>
+      </x:c>
+      <x:c r="B215" t="str">
+        <x:v>脾阳虚</x:v>
+      </x:c>
+      <x:c r="C215" t="str"/>
+      <x:c r="D215" t="str"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_PI_XU_SHI_SHENG</x:v>
+      </x:c>
+      <x:c r="B216" t="str">
+        <x:v>脾虚湿盛</x:v>
+      </x:c>
+      <x:c r="C216" t="str"/>
+      <x:c r="D216" t="str"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_WAI_GAN_FENG_HAN_NEI_SHANG_SHI_ZHI</x:v>
+      </x:c>
+      <x:c r="B217" t="str">
+        <x:v>外感风寒，内伤湿滞</x:v>
+      </x:c>
+      <x:c r="C217" t="str"/>
+      <x:c r="D217" t="str"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HAN_NING_XIN_MAI</x:v>
+      </x:c>
+      <x:c r="B218" t="str">
+        <x:v>寒凝心脉</x:v>
+      </x:c>
+      <x:c r="C218" t="str"/>
+      <x:c r="D218" t="str"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIN_HUO_KANG_SHENG</x:v>
+      </x:c>
+      <x:c r="B219" t="str">
+        <x:v>心火亢盛</x:v>
+      </x:c>
+      <x:c r="C219" t="str"/>
+      <x:c r="D219" t="str"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TAN_MI_XIN_QIAO</x:v>
+      </x:c>
+      <x:c r="B220" t="str">
+        <x:v>痰迷心窍</x:v>
+      </x:c>
+      <x:c r="C220" t="str"/>
+      <x:c r="D220" t="str"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIN_QI_XU</x:v>
+      </x:c>
+      <x:c r="B221" t="str">
+        <x:v>心气虚</x:v>
+      </x:c>
+      <x:c r="C221" t="str"/>
+      <x:c r="D221" t="str"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIN_MAI_YU_ZU</x:v>
+      </x:c>
+      <x:c r="B222" t="str">
+        <x:v>心脉瘀阻</x:v>
+      </x:c>
+      <x:c r="C222" t="str"/>
+      <x:c r="D222" t="str"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIN_YIN_XU</x:v>
+      </x:c>
+      <x:c r="B223" t="str">
+        <x:v>心阴虚</x:v>
+      </x:c>
+      <x:c r="C223" t="str"/>
+      <x:c r="D223" t="str"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIN_YANG_XU</x:v>
+      </x:c>
+      <x:c r="B224" t="str">
+        <x:v>心阳虚</x:v>
+      </x:c>
+      <x:c r="C224" t="str"/>
+      <x:c r="D224" t="str"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_TAN_HUO_RAO_XIN</x:v>
+      </x:c>
+      <x:c r="B225" t="str">
+        <x:v>痰火扰心</x:v>
+      </x:c>
+      <x:c r="C225" t="str"/>
+      <x:c r="D225" t="str"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIN_PI_LIANG_XU</x:v>
+      </x:c>
+      <x:c r="B226" t="str">
+        <x:v>心脾两虚</x:v>
+      </x:c>
+      <x:c r="C226" t="str"/>
+      <x:c r="D226" t="str"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_HUO_SHANG_YAN</x:v>
+      </x:c>
+      <x:c r="B227" t="str">
+        <x:v>肝火上炎</x:v>
+      </x:c>
+      <x:c r="C227" t="str"/>
+      <x:c r="D227" t="str"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_HAN_ZHI_GAN_MAI</x:v>
+      </x:c>
+      <x:c r="B228" t="str">
+        <x:v>寒滞肝脉</x:v>
+      </x:c>
+      <x:c r="C228" t="str"/>
+      <x:c r="D228" t="str"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_QI_YU_JIE</x:v>
+      </x:c>
+      <x:c r="B229" t="str">
+        <x:v>肝气郁结</x:v>
+      </x:c>
+      <x:c r="C229" t="str"/>
+      <x:c r="D229" t="str"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_XUE_XU</x:v>
+      </x:c>
+      <x:c r="B230" t="str">
+        <x:v>肝血虚</x:v>
+      </x:c>
+      <x:c r="C230" t="str"/>
+      <x:c r="D230" t="str"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_XUE_YU_ZHI</x:v>
+      </x:c>
+      <x:c r="B231" t="str">
+        <x:v>肝血瘀滞</x:v>
+      </x:c>
+      <x:c r="C231" t="str"/>
+      <x:c r="D231" t="str"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_YIN_XU</x:v>
+      </x:c>
+      <x:c r="B232" t="str">
+        <x:v>肝阴虚</x:v>
+      </x:c>
+      <x:c r="C232" t="str"/>
+      <x:c r="D232" t="str"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_YANG_SHANG_KANG</x:v>
+      </x:c>
+      <x:c r="B233" t="str">
+        <x:v>肝阳上亢</x:v>
+      </x:c>
+      <x:c r="C233" t="str"/>
+      <x:c r="D233" t="str"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_GAN_PI_BU_HE</x:v>
+      </x:c>
+      <x:c r="B234" t="str">
+        <x:v>肝脾不和</x:v>
+      </x:c>
+      <x:c r="C234" t="str"/>
+      <x:c r="D234" t="str"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHEN_BU_NA_QI</x:v>
+      </x:c>
+      <x:c r="B235" t="str">
+        <x:v>肾不纳气</x:v>
+      </x:c>
+      <x:c r="C235" t="str"/>
+      <x:c r="D235" t="str"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHEN_YIN_XU</x:v>
+      </x:c>
+      <x:c r="B236" t="str">
+        <x:v>肾阴虚</x:v>
+      </x:c>
+      <x:c r="C236" t="str"/>
+      <x:c r="D236" t="str"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHEN_YANG_XU</x:v>
+      </x:c>
+      <x:c r="B237" t="str">
+        <x:v>肾阳虚</x:v>
+      </x:c>
+      <x:c r="C237" t="str"/>
+      <x:c r="D237" t="str"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHEN_XU_SHUI_FAN</x:v>
+      </x:c>
+      <x:c r="B238" t="str">
+        <x:v>肾虚水泛</x:v>
+      </x:c>
+      <x:c r="C238" t="str"/>
+      <x:c r="D238" t="str"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHEN_JING_BU_ZU</x:v>
+      </x:c>
+      <x:c r="B239" t="str">
+        <x:v>肾精不足</x:v>
+      </x:c>
+      <x:c r="C239" t="str"/>
+      <x:c r="D239" t="str"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_SHEN_QI_BU_GU</x:v>
+      </x:c>
+      <x:c r="B240" t="str">
+        <x:v>肾气不固</x:v>
+      </x:c>
+      <x:c r="C240" t="str"/>
+      <x:c r="D240" t="str"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_REN_SHEN_DISEASE</x:v>
+      </x:c>
+      <x:c r="B241" t="str">
+        <x:v>妊娠</x:v>
+      </x:c>
+      <x:c r="C241" t="str"/>
+      <x:c r="D241" t="str"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_XIN_SHEN_BU_JIAO</x:v>
+      </x:c>
+      <x:c r="B242" t="str">
+        <x:v>心肾不交</x:v>
+      </x:c>
+      <x:c r="C242" t="str"/>
+      <x:c r="D242" t="str"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" t="str">
+        <x:v>UI_BOOK_ENTRY_TITLE_QI_FEN_RE_SHENG</x:v>
+      </x:c>
+      <x:c r="B243" t="str">
+        <x:v>气分热盛</x:v>
+      </x:c>
+      <x:c r="C243" t="str"/>
+      <x:c r="D243" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -27096,6 +27096,11 @@
           <t>Tea Master</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>茶博士</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -27113,6 +27118,11 @@
           <t>Oh, thank you very much, Doctor.</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>先生、本当にありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -27130,6 +27140,11 @@
           <t>I feel even worse...</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>前より具合が悪くなりました……</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -27147,6 +27162,11 @@
           <t>Chen Second</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>陳二</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -27164,6 +27184,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -27181,6 +27206,11 @@
           <t>Mm... ow...</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>うう……痛い……</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -27198,6 +27228,11 @@
           <t>Chen Granny</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>陳婆</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -27215,6 +27250,11 @@
           <t>Thank you so much, Doctor.</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>先生、本当にありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -27232,6 +27272,11 @@
           <t>Something doesn't feel right...</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>どうも様子がおかしい……</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -27249,6 +27294,11 @@
           <t>Chen Headmaster</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>陳山長</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -27266,6 +27316,11 @@
           <t>Doctor, your skill is remarkable. I feel restored.</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>先生の腕は本当に見事です。</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -27283,6 +27338,11 @@
           <t>You call yourself a physician with skills like that?!</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>腕もないくせに医者を名乗るな！</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -27300,6 +27360,11 @@
           <t>Du Second Sister-in-law</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>杜二嫂</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -27317,6 +27382,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>先生、本当にありがとうございます。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -27334,6 +27404,11 @@
           <t>Ow... ow...</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>あいたた……あいたた……</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -27351,6 +27426,11 @@
           <t>Feng Army Protector</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>馮军保</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -27368,6 +27448,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。だいぶ楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -27385,6 +27470,11 @@
           <t>Hmm... that's strange...</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>あれ……おかしいな……</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -27402,6 +27492,11 @@
           <t>Gao Elegant Lotus</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>高秀蓮</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -27419,6 +27514,11 @@
           <t>I feel much better. Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>だいぶ楽になりました。先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -27436,6 +27536,11 @@
           <t>Ow... ow...</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>あいたた……あいたた……</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -27453,6 +27558,11 @@
           <t>Han Shopkeeper</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>韓店主</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
@@ -27470,6 +27580,11 @@
           <t>Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -27487,6 +27602,11 @@
           <t>Doctor, why am I still not getting better?</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>先生、どうしてまだ治らないんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -27504,6 +27624,11 @@
           <t>He Third Sister</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>賀三姐</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -27521,6 +27646,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -27538,6 +27668,11 @@
           <t>Do you actually know how to treat people?</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>本当に診察できるんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -27555,6 +27690,11 @@
           <t>He Cook</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>何料理長</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
@@ -27572,6 +27712,11 @@
           <t>Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -27589,6 +27734,11 @@
           <t>I still feel awful...</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>まだとてもつらい……</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
@@ -27606,6 +27756,11 @@
           <t>Hua Brocade Maiden</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>華錦娘</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
@@ -27623,6 +27778,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。だいぶ楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
@@ -27640,6 +27800,11 @@
           <t>What kind of medicine did you give me...?</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>これはいったい何の薬ですか……</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -27657,6 +27822,11 @@
           <t>Hua Rue</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>花芸</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
@@ -27674,6 +27844,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -27691,6 +27866,11 @@
           <t>Huh? I feel strange...</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>えっ？　なんだか変な感じがします……</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
@@ -27708,6 +27888,11 @@
           <t>Huang Little Ox</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>黄牛児</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -27725,6 +27910,11 @@
           <t>Thank you so much, Doctor.</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>先生、本当にありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
@@ -27742,6 +27932,11 @@
           <t>Something doesn't feel right...</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>どうも様子がおかしい……</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
@@ -27759,6 +27954,11 @@
           <t>Huang Autumn Chrysanthemum</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>黄秋菊</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
@@ -27776,6 +27976,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
@@ -27793,6 +27998,11 @@
           <t>I still feel awful...</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>まだとてもつらい……</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
@@ -27810,6 +28020,11 @@
           <t>Ji Cloud Maiden</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>季雲娘</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -27827,6 +28042,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
@@ -27844,6 +28064,11 @@
           <t>Mm... ow...</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>うう……痛い……</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -27861,6 +28086,11 @@
           <t>Jiang Little Boat</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>蔣船児</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
@@ -27878,6 +28108,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
@@ -27895,6 +28130,11 @@
           <t>Mm... ow...</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>うう……痛い……</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
@@ -27912,6 +28152,11 @@
           <t>Jiang Moon Maiden</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>姜月娘</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
@@ -27929,6 +28174,11 @@
           <t>Your skill is impressive, Doctor. Thank you.</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>先生の腕は見事ですね。ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
@@ -27946,6 +28196,11 @@
           <t>Huh? I feel strange...</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>えっ？　なんだか変な感じがします……</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -27963,6 +28218,11 @@
           <t>Li Dog Egg</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>李狗蛋</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
@@ -27980,6 +28240,11 @@
           <t>Thank you so much, Doctor.</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>先生、本当にありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="17" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -27997,6 +28262,11 @@
           <t>Mm... ow...</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>うう……痛い……</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
@@ -28014,6 +28284,11 @@
           <t>Li Near Noble</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>李近卿</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -28031,6 +28306,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
@@ -28048,6 +28328,11 @@
           <t>Doctor, why am I still not getting better?</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>先生、どうしてまだ治らないんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
@@ -28065,6 +28350,11 @@
           <t>Li Fourth</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
@@ -28082,6 +28372,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。だいぶ楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
@@ -28099,6 +28394,11 @@
           <t>Doctor, why am I still not getting better?</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>先生、どうしてまだ治らないんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
@@ -28116,6 +28416,11 @@
           <t>Li Squire</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>李員外</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
@@ -28133,6 +28438,11 @@
           <t>Mm, very good. Your medical skill is impressive.</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>うむ、素晴らしい。見事な腕前だ。</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
@@ -28150,6 +28460,11 @@
           <t>You quack! You're nothing but a fraud!</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>このやぶ医者め、よくも騙したな！</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="17" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
@@ -28167,6 +28482,11 @@
           <t>Lin Clever Maiden</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>林巧娘</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
@@ -28184,6 +28504,11 @@
           <t>Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
@@ -28201,6 +28526,11 @@
           <t>Something doesn't feel right...</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>どうも様子がおかしい……</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
@@ -28218,6 +28548,11 @@
           <t>Liu Eldest</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>劉大</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
@@ -28235,6 +28570,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
@@ -28252,6 +28592,11 @@
           <t>Something doesn't feel right...</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>どうも様子がおかしい……</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
@@ -28269,6 +28614,11 @@
           <t>Liu Fortune</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>劉福</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
@@ -28286,6 +28636,11 @@
           <t>Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
@@ -28303,6 +28658,11 @@
           <t>Uh... something's not right.</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>あれ……おかしいな。</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
@@ -28320,6 +28680,11 @@
           <t>Liu Elder</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>劉太公</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
@@ -28337,6 +28702,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
@@ -28354,6 +28724,11 @@
           <t>Cough, cough... ow...</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……あいたた……</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="17" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
@@ -28371,6 +28746,11 @@
           <t>Liu Midwife</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>劉産婆</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
@@ -28388,6 +28768,11 @@
           <t>Oh, thank you, Doctor! You're a marvelous physician!</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます！　本当に名医ですね！</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="17" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
@@ -28405,6 +28790,11 @@
           <t>Hmm, something's not right...</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>あれ、おかしいな……</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
@@ -28422,6 +28812,11 @@
           <t>Liu Little Oriole</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>柳鶯児</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
@@ -28439,6 +28834,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。だいぶ良くなりました。</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
@@ -28456,6 +28856,11 @@
           <t>Hmm... that's strange...</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>あれ……おかしいな……</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="17" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
@@ -28473,6 +28878,11 @@
           <t>Lü Matriarch</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>呂太君</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
@@ -28490,6 +28900,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>若先生、ありがとうございます。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -28507,6 +28922,11 @@
           <t>Something doesn't feel right...</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……これは何の薬なんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -28524,6 +28944,11 @@
           <t>Ma Long Wind</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>馬長风</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="17" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -28541,6 +28966,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
@@ -28558,6 +28988,11 @@
           <t>What kind of medicine did you give me...?</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>これはいったい何の薬ですか……</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="17" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -28575,6 +29010,11 @@
           <t>Qian No Leak</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>銭不漏</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
@@ -28592,6 +29032,11 @@
           <t>Thanks.</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ありがとう。</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -28609,6 +29054,11 @@
           <t>What medicine is this? I'll report you to the authorities!</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>これは何の薬だ！　役所に訴えてやる！</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="17" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
@@ -28626,6 +29076,11 @@
           <t>Qin Third Lady</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>秦三娘</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="17" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
@@ -28643,6 +29098,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。だいぶ楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
@@ -28660,6 +29120,11 @@
           <t>Ow... ow...</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>あいたた……あいたた……</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="17" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -28677,6 +29142,11 @@
           <t>Shen Noble</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>沈貴</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
@@ -28694,6 +29164,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>どうもありがとう。</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
@@ -28711,6 +29186,11 @@
           <t>Do you actually know how to treat people?</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>本当に診察できるんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
@@ -28728,6 +29208,11 @@
           <t>Shi Daring</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>石敢</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
@@ -28745,6 +29230,11 @@
           <t>Oh, thank you so much. I feel much better.</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>本当にありがとうございます。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
@@ -28762,6 +29252,11 @@
           <t>Hmm... that's strange...</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>あれ……おかしいな……</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="17" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -28779,6 +29274,11 @@
           <t>Shi Reborn</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>史更生</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
@@ -28796,6 +29296,11 @@
           <t>I feel much better. Thank you so much, Doctor.</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ずいぶん良くなりました。先生、本当にありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="17" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
@@ -28813,6 +29318,11 @@
           <t>What medicine did you give me...?</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>いったい何の薬を出したんですか……</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="17" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
@@ -28830,6 +29340,11 @@
           <t>Su Embroidered Lotus</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>蘇繍荷</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="17" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
@@ -28847,6 +29362,11 @@
           <t>I feel much better. Thank you so much, Doctor.</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ずいぶん良くなりました。先生、本当にありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
@@ -28864,6 +29384,11 @@
           <t>Cough, cough... I feel terrible.</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……つらい……</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="17" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
@@ -28881,6 +29406,11 @@
           <t>Sun Little Craftsman</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>孫匠児</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="17" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
@@ -28898,6 +29428,11 @@
           <t>Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="17" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
@@ -28915,6 +29450,11 @@
           <t>Uh... something's not right.</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>あれ……おかしいな。</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="17" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
@@ -28932,6 +29472,11 @@
           <t>Sun Little Sister</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>孫小妹</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="17" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -28949,6 +29494,11 @@
           <t>Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="17" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
@@ -28966,6 +29516,11 @@
           <t>Cough, cough... I feel terrible.</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……つらい……</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="17" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
@@ -28983,6 +29538,11 @@
           <t>Tian Spring Vine</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>田春萝</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="17" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
@@ -29000,6 +29560,11 @@
           <t>I feel much better. Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>だいぶ楽になりました。先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="17" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
@@ -29017,6 +29582,11 @@
           <t>Huh? I feel strange...</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>えっ？　なんだか変な感じがします……</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="17" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
@@ -29034,6 +29604,11 @@
           <t>Wang Court Attendant</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>王朝奉</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="17" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
@@ -29051,6 +29626,11 @@
           <t>I feel much better. Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>楽になりました。先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="17" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
@@ -29068,6 +29648,11 @@
           <t>What medicine did you give me...?</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>いったい何の薬を出したんですか……</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="17" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -29085,6 +29670,11 @@
           <t>Wang Sister-in-law</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>王おばさん</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="17" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
@@ -29102,6 +29692,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="17" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
@@ -29119,6 +29714,11 @@
           <t>Ow... ow...</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>あいたた……あいたた……</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="17" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
@@ -29136,6 +29736,11 @@
           <t>Wang Old Madam</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>王老夫人</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="17" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -29153,6 +29758,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>先生、本当にありがとうございます。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="17" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
@@ -29170,6 +29780,11 @@
           <t>Cough, cough... ow...</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……あいたた……</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="17" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
@@ -29187,6 +29802,11 @@
           <t>Wang Fifth</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="17" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
@@ -29204,6 +29824,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="17" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -29221,6 +29846,11 @@
           <t>I still feel awful...</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>まだとてもつらい……</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="17" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
@@ -29238,6 +29868,11 @@
           <t>Wang Distant Mountain</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>王遠山</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="17" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
@@ -29255,6 +29890,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。だいぶ良くなりました。</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="17" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
@@ -29272,6 +29912,11 @@
           <t>Uh... something's not right.</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>あれ……おかしいな。</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="17" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
@@ -29289,6 +29934,11 @@
           <t>Wei Bigfoot</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>魏大脚</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
@@ -29306,6 +29956,11 @@
           <t>Thank you for your trouble, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="17" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
@@ -29323,6 +29978,11 @@
           <t>I feel even worse...</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>前より具合が悪くなりました……</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
@@ -29340,6 +30000,11 @@
           <t>Wu Constable</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>呉班頭</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="17" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
@@ -29357,6 +30022,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="17" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
@@ -29374,6 +30044,11 @@
           <t>Damn it, what did you make me take?</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ちくしょう、何を飲ませたんだ？</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="17" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
@@ -29391,6 +30066,11 @@
           <t>Xu Fourth Aunt</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>徐四姑</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="17" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
@@ -29408,6 +30088,11 @@
           <t>Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="17" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
@@ -29425,6 +30110,11 @@
           <t>What is this medicine? Are you trying to kill me?</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>何の薬よ？　私を殺す気？</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="17" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
@@ -29442,6 +30132,11 @@
           <t>Xu Fragrant Lady</t>
         </is>
       </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>許香君</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="17" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
@@ -29459,6 +30154,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。だいぶ良くなりました。</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="17" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
@@ -29476,6 +30176,11 @@
           <t>What kind of medicine did you give me...?</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>これはいったい何の薬ですか……</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="17" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
@@ -29493,6 +30198,11 @@
           <t>Yan Constable</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>厳捕頭</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="17" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
@@ -29510,6 +30220,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>楽になりました。先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="17" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -29527,6 +30242,11 @@
           <t>Mm... ow...</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>うう……痛い……</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="17" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
@@ -29544,6 +30264,11 @@
           <t>Yan Granny</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>厳婆</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="17" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -29561,6 +30286,11 @@
           <t>I feel much better. Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>だいぶ楽になりました。先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="17" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
@@ -29578,6 +30308,11 @@
           <t>Cough, cough... ow...</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……あいたた……</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="17" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
@@ -29595,6 +30330,11 @@
           <t>Yang Scholar</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>楊秀才</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="17" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
@@ -29612,6 +30352,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="17" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
@@ -29629,6 +30374,11 @@
           <t>What kind of medicine did you give me...?</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>これはいったい何の薬ですか……</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="17" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
@@ -29646,6 +30396,11 @@
           <t>Yao Shopkeeper</t>
         </is>
       </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>姚店主</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="17" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
@@ -29663,6 +30418,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="17" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
@@ -29680,6 +30440,11 @@
           <t>Doctor, why am I still not getting better?</t>
         </is>
       </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>先生、どうしてまだ治らないんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="17" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
@@ -29697,6 +30462,11 @@
           <t>Ye River Boat</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>葉江舟</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
@@ -29714,6 +30484,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="17" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
@@ -29731,6 +30506,11 @@
           <t>Cough, cough... I feel terrible.</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……つらい……</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="17" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
@@ -29748,6 +30528,11 @@
           <t>You Graceful Maiden</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>尤秀姑</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="17" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
@@ -29765,6 +30550,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。だいぶ楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="17" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
@@ -29782,6 +30572,11 @@
           <t>Mm... ow...</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>うう……痛い……</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="17" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
@@ -29799,6 +30594,11 @@
           <t>Zhang Third</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>張三</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="17" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
@@ -29816,6 +30616,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="17" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
@@ -29833,6 +30638,11 @@
           <t>Hmm... that's strange...</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>あれ……おかしいな……</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="17" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
@@ -29850,6 +30660,11 @@
           <t>Zhang Butcher</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>張屠</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="17" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
@@ -29867,6 +30682,11 @@
           <t>Ha! Thank you very much.</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ははは、本当にありがとう。</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="17" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
@@ -29884,6 +30704,11 @@
           <t>Damn it, why do I feel so strange?</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ちくしょう、なんだか変な感じがする。</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="17" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
@@ -29901,6 +30726,11 @@
           <t>Zhang Jade Branch</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>張玉枝</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="17" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
@@ -29918,6 +30748,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>先生、本当にありがとうございます。楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="17" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
@@ -29935,6 +30770,11 @@
           <t>Huh? I feel strange...</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>えっ？　なんだか変な感じがします……</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="17" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
@@ -29952,6 +30792,11 @@
           <t>Zhao Sixth</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>趙六</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="17" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
@@ -29969,6 +30814,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="17" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
@@ -29986,6 +30836,11 @@
           <t>I still feel awful...</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>まだとてもつらい……</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="17" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
@@ -30003,6 +30858,11 @@
           <t>Zhao Matchmaker</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>趙仲人</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="17" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
@@ -30020,6 +30880,11 @@
           <t>Oh, thank you, Doctor! You're a marvelous physician!</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます！　本当に名医ですね！</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="17" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
@@ -30037,6 +30902,11 @@
           <t>Hmm, something's not right...</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>あれ、おかしいな……</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="17" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
@@ -30054,6 +30924,11 @@
           <t>Zheng Second Sister</t>
         </is>
       </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>鄭二姐</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="17" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
@@ -30071,6 +30946,11 @@
           <t>Thank you, Doctor. I feel much better.</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>先生、お世話になりました。ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="17" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
@@ -30088,6 +30968,11 @@
           <t>Hmm... that's strange...</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>あれ……おかしいな……</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="17" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
@@ -30105,6 +30990,11 @@
           <t>Zhou Hearth Peace</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>周炉安</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="17" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
@@ -30122,6 +31012,11 @@
           <t>Thank you, Doctor.</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="17" customHeight="1">
       <c r="A181" s="7" t="inlineStr">
@@ -30139,6 +31034,11 @@
           <t>Doctor, why am I still not getting better?</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>先生、どうしてまだ治らないんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="17" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
@@ -30156,6 +31056,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="17" customHeight="1">
       <c r="A183" s="7" t="inlineStr">
@@ -30173,6 +31078,11 @@
           <t>Would you kindly examine me, Doctor?</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>先生、診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="17" customHeight="1">
       <c r="A184" s="7" t="inlineStr">
@@ -30190,6 +31100,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="17" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
@@ -30207,6 +31122,11 @@
           <t>Could you take a look?</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="17" customHeight="1">
       <c r="A186" s="7" t="inlineStr">
@@ -30224,6 +31144,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="17" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
@@ -30241,6 +31166,11 @@
           <t>Please, have a look at me quickly.</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>早く診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="17" customHeight="1">
       <c r="A188" s="7" t="inlineStr">
@@ -30258,6 +31188,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="17" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
@@ -30275,6 +31210,11 @@
           <t>Would you kindly take a look?</t>
         </is>
       </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="17" customHeight="1">
       <c r="A190" s="7" t="inlineStr">
@@ -30292,6 +31232,11 @@
           <t>Doctor, for the past couple of days I've been</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="17" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
@@ -30309,6 +31254,11 @@
           <t>Could you please examine me?</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="17" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
@@ -30326,6 +31276,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="17" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
@@ -30343,6 +31298,11 @@
           <t>Please, could you take a look?</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="17" customHeight="1">
       <c r="A194" s="7" t="inlineStr">
@@ -30360,6 +31320,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="17" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
@@ -30377,6 +31342,11 @@
           <t>Would you mind taking a look?</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="17" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
@@ -30394,6 +31364,11 @@
           <t>Doctor, for the past couple of days I've been</t>
         </is>
       </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="17" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
@@ -30411,6 +31386,11 @@
           <t>Would you kindly take a look?</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="17" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
@@ -30428,6 +31408,11 @@
           <t>For the past couple of days, I've been</t>
         </is>
       </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="17" customHeight="1">
       <c r="A199" s="7" t="inlineStr">
@@ -30445,6 +31430,11 @@
           <t>Please take a look and see what's wrong.</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>診察をお願いします。</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="17" customHeight="1">
       <c r="A200" s="7" t="inlineStr">
@@ -30462,6 +31452,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="17" customHeight="1">
       <c r="A201" s="7" t="inlineStr">
@@ -30479,6 +31474,11 @@
           <t>Doctor, please have a look at me quickly.</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>先生、早く診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="17" customHeight="1">
       <c r="A202" s="7" t="inlineStr">
@@ -30496,6 +31496,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="17" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
@@ -30513,6 +31518,11 @@
           <t>Would you kindly examine me, Doctor?</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>先生、私を診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="17" customHeight="1">
       <c r="A204" s="7" t="inlineStr">
@@ -30530,6 +31540,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="17" customHeight="1">
       <c r="A205" s="7" t="inlineStr">
@@ -30547,6 +31562,11 @@
           <t>Doctor, would you please take a look?</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>先生、どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="17" customHeight="1">
       <c r="A206" s="7" t="inlineStr">
@@ -30564,6 +31584,11 @@
           <t>Oh dear, Doctor, I've been</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>あいたた……先生、私は</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="17" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
@@ -30581,6 +31606,11 @@
           <t>Please have a look at me quickly.</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>早く診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="17" customHeight="1">
       <c r="A208" s="7" t="inlineStr">
@@ -30598,6 +31628,11 @@
           <t>For the past couple of days, I've been</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="17" customHeight="1">
       <c r="A209" s="7" t="inlineStr">
@@ -30615,6 +31650,11 @@
           <t>Please take a look at me.</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>娘を診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="17" customHeight="1">
       <c r="A210" s="7" t="inlineStr">
@@ -30632,6 +31672,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="17" customHeight="1">
       <c r="A211" s="7" t="inlineStr">
@@ -30649,6 +31694,11 @@
           <t>Would you mind examining me?</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>私を診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="17" customHeight="1">
       <c r="A212" s="7" t="inlineStr">
@@ -30666,6 +31716,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="17" customHeight="1">
       <c r="A213" s="7" t="inlineStr">
@@ -30683,6 +31738,11 @@
           <t>Have a look at me, please.</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="17" customHeight="1">
       <c r="A214" s="7" t="inlineStr">
@@ -30700,6 +31760,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="17" customHeight="1">
       <c r="A215" s="7" t="inlineStr">
@@ -30717,6 +31782,11 @@
           <t>Doctor, would you kindly take a look?</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>先生、診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="17" customHeight="1">
       <c r="A216" s="7" t="inlineStr">
@@ -30734,6 +31804,11 @@
           <t>Doctor, these past couple of days I've been</t>
         </is>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="17" customHeight="1">
       <c r="A217" s="7" t="inlineStr">
@@ -30751,6 +31826,11 @@
           <t>Please take a look at me.</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="17" customHeight="1">
       <c r="A218" s="7" t="inlineStr">
@@ -30768,6 +31848,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="17" customHeight="1">
       <c r="A219" s="7" t="inlineStr">
@@ -30785,6 +31870,11 @@
           <t>Doctor, please take a look.</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>先生、どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="17" customHeight="1">
       <c r="A220" s="7" t="inlineStr">
@@ -30802,6 +31892,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="17" customHeight="1">
       <c r="A221" s="7" t="inlineStr">
@@ -30819,6 +31914,11 @@
           <t>Could you please see what's wrong?</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>どうか診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="17" customHeight="1">
       <c r="A222" s="7" t="inlineStr">
@@ -30836,6 +31936,11 @@
           <t>Young doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>若い先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="17" customHeight="1">
       <c r="A223" s="7" t="inlineStr">
@@ -30853,6 +31958,11 @@
           <t>Take a look at me, young doctor.</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>わしを診てくれ。</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="17" customHeight="1">
       <c r="A224" s="7" t="inlineStr">
@@ -30870,6 +31980,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="17" customHeight="1">
       <c r="A225" s="7" t="inlineStr">
@@ -30887,6 +32002,11 @@
           <t>Would you kindly examine me, Doctor?</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>先生、私を診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="17" customHeight="1">
       <c r="A226" s="7" t="inlineStr">
@@ -30904,6 +32024,11 @@
           <t>Doctor, these past couple of days I've been</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="17" customHeight="1">
       <c r="A227" s="7" t="inlineStr">
@@ -30921,6 +32046,11 @@
           <t>Could you please see what's wrong with me?</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="17" customHeight="1">
       <c r="A228" s="7" t="inlineStr">
@@ -30938,6 +32068,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="17" customHeight="1">
       <c r="A229" s="7" t="inlineStr">
@@ -30955,6 +32090,11 @@
           <t>Have a look at me, please.</t>
         </is>
       </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="17" customHeight="1">
       <c r="A230" s="7" t="inlineStr">
@@ -30972,6 +32112,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="17" customHeight="1">
       <c r="A231" s="7" t="inlineStr">
@@ -30989,6 +32134,11 @@
           <t>Would you mind taking a look?</t>
         </is>
       </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>診察をお願いします。</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="17" customHeight="1">
       <c r="A232" s="7" t="inlineStr">
@@ -31006,6 +32156,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="17" customHeight="1">
       <c r="A233" s="7" t="inlineStr">
@@ -31023,6 +32178,11 @@
           <t>Please have a look at me.</t>
         </is>
       </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="17" customHeight="1">
       <c r="A234" s="7" t="inlineStr">
@@ -31040,6 +32200,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="17" customHeight="1">
       <c r="A235" s="7" t="inlineStr">
@@ -31057,6 +32222,11 @@
           <t>Please take a look at me.</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>娘を診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="17" customHeight="1">
       <c r="A236" s="7" t="inlineStr">
@@ -31074,6 +32244,11 @@
           <t>Young doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>若先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="17" customHeight="1">
       <c r="A237" s="7" t="inlineStr">
@@ -31091,6 +32266,11 @@
           <t>Have a look at me, would you?</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="17" customHeight="1">
       <c r="A238" s="7" t="inlineStr">
@@ -31108,6 +32288,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="17" customHeight="1">
       <c r="A239" s="7" t="inlineStr">
@@ -31125,6 +32310,11 @@
           <t>Would you mind having a look?</t>
         </is>
       </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>診察をお願いします。</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="17" customHeight="1">
       <c r="A240" s="7" t="inlineStr">
@@ -31142,6 +32332,11 @@
           <t>Lately, I've been</t>
         </is>
       </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>最近、</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="17" customHeight="1">
       <c r="A241" s="7" t="inlineStr">
@@ -31159,6 +32354,11 @@
           <t>Quickly—please take a look at me.</t>
         </is>
       </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>早く、早く診てくれ。</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="17" customHeight="1">
       <c r="A242" s="7" t="inlineStr">
@@ -31176,6 +32376,11 @@
           <t>Ahem... Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="17" customHeight="1">
       <c r="A243" s="7" t="inlineStr">
@@ -31193,6 +32398,11 @@
           <t>Would you kindly take a look?</t>
         </is>
       </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="17" customHeight="1">
       <c r="A244" s="7" t="inlineStr">
@@ -31210,6 +32420,11 @@
           <t>Oh dear... I've been</t>
         </is>
       </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>あいたた……私は</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="17" customHeight="1">
       <c r="A245" s="7" t="inlineStr">
@@ -31227,6 +32442,11 @@
           <t>Please have a look at me quickly.</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>早く診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="17" customHeight="1">
       <c r="A246" s="7" t="inlineStr">
@@ -31244,6 +32464,11 @@
           <t>Ahem... Doctor, these past couple of days I've been</t>
         </is>
       </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="17" customHeight="1">
       <c r="A247" s="7" t="inlineStr">
@@ -31261,6 +32486,11 @@
           <t>Please, have a look at me quickly.</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>早く診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="17" customHeight="1">
       <c r="A248" s="7" t="inlineStr">
@@ -31278,6 +32508,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="17" customHeight="1">
       <c r="A249" s="7" t="inlineStr">
@@ -31295,6 +32530,11 @@
           <t>Please have a look.</t>
         </is>
       </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="17" customHeight="1">
       <c r="A250" s="7" t="inlineStr">
@@ -31312,6 +32552,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="17" customHeight="1">
       <c r="A251" s="7" t="inlineStr">
@@ -31329,6 +32574,11 @@
           <t>Would you mind examining me?</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>私を診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="17" customHeight="1">
       <c r="A252" s="7" t="inlineStr">
@@ -31346,6 +32596,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="17" customHeight="1">
       <c r="A253" s="7" t="inlineStr">
@@ -31363,6 +32618,11 @@
           <t>Please, could you take a look?</t>
         </is>
       </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="17" customHeight="1">
       <c r="A254" s="7" t="inlineStr">
@@ -31380,6 +32640,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="17" customHeight="1">
       <c r="A255" s="7" t="inlineStr">
@@ -31397,6 +32662,11 @@
           <t>Please take a look and see what's wrong.</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>診察をお願いします。</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="17" customHeight="1">
       <c r="A256" s="7" t="inlineStr">
@@ -31414,6 +32684,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="17" customHeight="1">
       <c r="A257" s="7" t="inlineStr">
@@ -31431,6 +32706,11 @@
           <t>Please take a look.</t>
         </is>
       </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="17" customHeight="1">
       <c r="A258" s="7" t="inlineStr">
@@ -31448,6 +32728,11 @@
           <t>Ahem... Lately, I've been</t>
         </is>
       </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……最近、</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="17" customHeight="1">
       <c r="A259" s="7" t="inlineStr">
@@ -31465,6 +32750,11 @@
           <t>Would you take a look at me, Doctor?</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>わしを診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="17" customHeight="1">
       <c r="A260" s="7" t="inlineStr">
@@ -31482,6 +32772,11 @@
           <t>Doctor, these past couple of days I've been</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="17" customHeight="1">
       <c r="A261" s="7" t="inlineStr">
@@ -31499,6 +32794,11 @@
           <t>Could you have a look at me?</t>
         </is>
       </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="17" customHeight="1">
       <c r="A262" s="7" t="inlineStr">
@@ -31516,6 +32816,11 @@
           <t>Doctor, these past couple of days I've been</t>
         </is>
       </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="17" customHeight="1">
       <c r="A263" s="7" t="inlineStr">
@@ -31533,6 +32838,11 @@
           <t>Would you kindly take a look?</t>
         </is>
       </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="17" customHeight="1">
       <c r="A264" s="7" t="inlineStr">
@@ -31550,6 +32860,11 @@
           <t>Doctor, for the past couple of days I've been</t>
         </is>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="17" customHeight="1">
       <c r="A265" s="7" t="inlineStr">
@@ -31567,6 +32882,11 @@
           <t>Have a look at me, please.</t>
         </is>
       </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="17" customHeight="1">
       <c r="A266" s="7" t="inlineStr">
@@ -31584,6 +32904,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="17" customHeight="1">
       <c r="A267" s="7" t="inlineStr">
@@ -31601,6 +32926,11 @@
           <t>Please take a look and see what's wrong.</t>
         </is>
       </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>診察をお願いします。</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="17" customHeight="1">
       <c r="A268" s="7" t="inlineStr">
@@ -31618,6 +32948,11 @@
           <t>Oh dear... These past couple of days I've been</t>
         </is>
       </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>あいたた……この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="17" customHeight="1">
       <c r="A269" s="7" t="inlineStr">
@@ -31635,6 +32970,11 @@
           <t>Would you mind taking a look?</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="17" customHeight="1">
       <c r="A270" s="7" t="inlineStr">
@@ -31652,6 +32992,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="17" customHeight="1">
       <c r="A271" s="7" t="inlineStr">
@@ -31669,6 +33014,11 @@
           <t>Please, have a look at me quickly.</t>
         </is>
       </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>早く診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="17" customHeight="1">
       <c r="A272" s="7" t="inlineStr">
@@ -31686,6 +33036,11 @@
           <t>Lately, I've been</t>
         </is>
       </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>最近、</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="17" customHeight="1">
       <c r="A273" s="7" t="inlineStr">
@@ -31703,6 +33058,11 @@
           <t>Please have a look at me quickly.</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>早く診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="17" customHeight="1">
       <c r="A274" s="7" t="inlineStr">
@@ -31720,6 +33080,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="17" customHeight="1">
       <c r="A275" s="7" t="inlineStr">
@@ -31737,6 +33102,11 @@
           <t>Doctor, would you kindly examine me?</t>
         </is>
       </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>先生、どうか私を診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="17" customHeight="1">
       <c r="A276" s="7" t="inlineStr">
@@ -31754,6 +33124,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="17" customHeight="1">
       <c r="A277" s="7" t="inlineStr">
@@ -31771,6 +33146,11 @@
           <t>Doctor, please take a look.</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>先生、どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="17" customHeight="1">
       <c r="A278" s="7" t="inlineStr">
@@ -31788,6 +33168,11 @@
           <t>Doctor, these past couple of days I've been</t>
         </is>
       </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="17" customHeight="1">
       <c r="A279" s="7" t="inlineStr">
@@ -31805,6 +33190,11 @@
           <t>Please, could you take a look?</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="17" customHeight="1">
       <c r="A280" s="7" t="inlineStr">
@@ -31822,6 +33212,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="17" customHeight="1">
       <c r="A281" s="7" t="inlineStr">
@@ -31839,6 +33234,11 @@
           <t>Please have a look.</t>
         </is>
       </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="17" customHeight="1">
       <c r="A282" s="7" t="inlineStr">
@@ -31856,6 +33256,11 @@
           <t>Doctor, for the past couple of days I've been</t>
         </is>
       </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="17" customHeight="1">
       <c r="A283" s="7" t="inlineStr">
@@ -31873,6 +33278,11 @@
           <t>Please take a look.</t>
         </is>
       </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="17" customHeight="1">
       <c r="A284" s="7" t="inlineStr">
@@ -31890,6 +33300,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="17" customHeight="1">
       <c r="A285" s="7" t="inlineStr">
@@ -31907,6 +33322,11 @@
           <t>Would you kindly examine me, Doctor?</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>先生、診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="17" customHeight="1">
       <c r="A286" s="7" t="inlineStr">
@@ -31924,6 +33344,11 @@
           <t>These past few days, I've been</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="17" customHeight="1">
       <c r="A287" s="7" t="inlineStr">
@@ -31941,6 +33366,11 @@
           <t>Doctor, please take a look at me.</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>先生、どうか診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="17" customHeight="1">
       <c r="A288" s="7" t="inlineStr">
@@ -31958,6 +33388,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="17" customHeight="1">
       <c r="A289" s="7" t="inlineStr">
@@ -31975,6 +33410,11 @@
           <t>Could you take a look?</t>
         </is>
       </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="17" customHeight="1">
       <c r="A290" s="7" t="inlineStr">
@@ -31992,6 +33432,11 @@
           <t>Oh dear, Doctor, I've been</t>
         </is>
       </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>あいたた……先生、私は</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="17" customHeight="1">
       <c r="A291" s="7" t="inlineStr">
@@ -32009,6 +33454,11 @@
           <t>Please, have a look at me quickly.</t>
         </is>
       </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>早く診てください。</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="17" customHeight="1">
       <c r="A292" s="7" t="inlineStr">
@@ -32026,6 +33476,11 @@
           <t>Doctor, for the past couple of days I've been</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>先生、この二日ほど、</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="17" customHeight="1">
       <c r="A293" s="7" t="inlineStr">
@@ -32043,6 +33498,11 @@
           <t>Could you please see what's wrong?</t>
         </is>
       </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>どうか診ていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="17" customHeight="1">
       <c r="A294" s="7" t="inlineStr">
@@ -32060,6 +33520,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="17" customHeight="1">
       <c r="A295" s="7" t="inlineStr">
@@ -32077,6 +33542,11 @@
           <t>Would you mind taking a look?</t>
         </is>
       </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>診察をお願いします。</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="17" customHeight="1">
       <c r="A296" s="7" t="inlineStr">
@@ -32094,6 +33564,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="17" customHeight="1">
       <c r="A297" s="7" t="inlineStr">
@@ -32111,6 +33586,11 @@
           <t>Would you kindly take a look?</t>
         </is>
       </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>診ていただけますか。</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="17" customHeight="1">
       <c r="A298" s="7" t="inlineStr">
@@ -32128,6 +33608,11 @@
           <t>Doctor, lately I've been</t>
         </is>
       </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>先生、最近、</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="17" customHeight="1">
       <c r="A299" s="7" t="inlineStr">
@@ -32145,6 +33630,11 @@
           <t>Would you mind taking a look?</t>
         </is>
       </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>診察をお願いします。</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="17" customHeight="1">
       <c r="A300" s="7" t="inlineStr">
@@ -32162,6 +33652,11 @@
           <t>Doctor, these past few days I've been</t>
         </is>
       </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>先生、ここ数日、</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="17" customHeight="1">
       <c r="A301" s="7" t="inlineStr">
@@ -32179,6 +33674,11 @@
           <t>Would you mind taking a look?</t>
         </is>
       </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>診察をお願いします。</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
@@ -32194,6 +33694,11 @@
       <c r="C302" s="2" t="inlineStr">
         <is>
           <t>feeling unwell</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>体調が優れません</t>
         </is>
       </c>
     </row>
@@ -32255,7 +33760,11 @@
           <t>Years passed in the blink of an eye…</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>それから長い年月が流れた……</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32273,7 +33782,11 @@
           <t>Li Dongbi traveled far and wide to study medicinal plants and collect specimens. Drawing on more than 800 books, he revised his manuscript three times before finally completing it: 52 volumes describing 1,892 medicinal substances and 11,096 prescriptions, with 1,109 illustrations and roughly 1.9 million Chinese characters.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>李東璧は各地を実地調査し、標本を集め、800種を超える書物を参照した。原稿を三度書き直し、ついに著作を完成させた。全52巻、収録した薬は1892種、処方は11096方、挿絵は1109点、文字数は約190万字に及ぶ。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32313,7 +33826,11 @@
           <t>At last… it's finished.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ようやく完成した……</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32353,7 +33870,11 @@
           <t>You old man…</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>あなた……</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32393,7 +33914,11 @@
           <t>Father, this extraordinary book of yours must be published, so people everywhere can put it to use.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>父上、この世にまたとない大著は、ぜひ出版してください。天下の人々の役に立つはずです。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32433,7 +33958,11 @@
           <t>Master Li, pardon the intrusion. I am Hu Chenglong, a bookseller. I hear you have a book you wish to have printed?</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>李先生、お邪魔いたします。書肆を営む胡承竜と申します。版木を彫って出版したい本があると伺いましたが？</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32473,7 +34002,11 @@
           <t>Thank you for coming in person, Master Hu. I do indeed have a medical book I would like you to publish.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>胡殿、わざわざお越しいただき恐縮です。確かに医学書の刊行をお願いしたいのです。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32491,7 +34024,11 @@
           <t>Hu Chenglong briefly examined the manuscript.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>胡承竜は書物の内容をひととおり確かめた。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32531,7 +34068,11 @@
           <t>What a remarkable work, Master Li! It brings together the finest medical knowledge of past and present.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>いやはや、先生の大著には感服いたしました。古今の医学書を集大成した一冊ですな。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32571,7 +34112,11 @@
           <t>You flatter me, Master Hu. When might you begin carving the printing blocks?</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>お褒めにあずかり恐縮です。版木の彫刻はいつ始められますか？</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -32611,7 +34156,11 @@
           <t>Master Li, I had best speak frankly.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>はあ……先生には正直に申し上げましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -32651,7 +34200,11 @@
           <t>Your book is a treasure for physicians, but readers these days want heroic tales and romances. I fear it would not sell even if we printed it.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>確かに医家にとっては宝ですが、今の世で好まれるのは英雄譚や恋物語。刊行しても売れないでしょう。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -32691,7 +34244,11 @@
           <t>Besides, your manuscript runs to millions of characters and contains a great many illustrations.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>しかも、これだけの大著には何百万もの文字と大量の挿絵があります。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -32731,7 +34288,11 @@
           <t>At the market rate of one qian of silver per hundred characters, plus ink, paper, wood and binding, I estimate that an initial run of twenty sets would cost two thousand taels of silver.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>相場どおり百字につき銀一銭として、墨、紙、木材、製本の費用も加えると、初版二十組だけで銀二千両はかかるでしょう。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -32771,7 +34332,11 @@
           <t>It is an excellent book, but I cannot run my business at a loss.</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>良書であるのは間違いありませんが、こちらも赤字の商売はできません。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -32811,7 +34376,11 @@
           <t>If you can pay to print it yourself, I will charge you only the bare cost. I would earn nothing from it. What do you say?</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>先生が自費で印刷なさるなら、私も利益を取らず、最低限の実費で引き受けます。いかがでしょう？</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -32851,7 +34420,11 @@
           <t>Two thousand taels… Where could I possibly find that much silver?</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>二千両……そんな大金をどこから用意すれば……</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -32891,7 +34464,11 @@
           <t>Take your time to consider it, Master Li. I shall take my leave.</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>どうぞゆっくりお考えください。私はこれで失礼します。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -32931,7 +34508,11 @@
           <t>Father, how did the meeting with the bookseller go today?</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>父上、今日の書肆との話し合いはどうでしたか？</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -32971,7 +34552,11 @@
           <t>He says it will cost two thousand taels of silver to carve the blocks and print the book…</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>版木を彫って刊行するには銀二千両が必要だそうだ……</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -33011,7 +34596,11 @@
           <t>Two thousand taels? That much?</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>二千両？　そんなにかかるのですか！</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -33051,7 +34640,11 @@
           <t>If it cannot be published, I fear the book will be lost within a few years…</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>はあ……出版できなければ、この書もそう遠くないうちに失われるだろう……</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -33091,7 +34684,11 @@
           <t>I have failed you, Father. I cannot help shoulder this burden…</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>息子の力が足りず、父上のお役に立てません……</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -33131,7 +34728,11 @@
           <t>Do not say that. You have accomplished more than anyone else in this family.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>何を言う。お前は我が家で一番の出世頭だ。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -33171,7 +34772,11 @@
           <t>You are an honest official, a rare bright light in government. We are all proud of you. We will find another way to publish the book.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>お前は清廉な役人として、一家の誇りだ。この書のことは、また方法を考えよう。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -33211,7 +34816,11 @@
           <t>Dear, your mentor Master Gu is an old family friend of Wang Shizhen, the leading man of letters today. If Wang wrote a preface for your book, scholars everywhere would seek it out. Surely a bookseller would then agree to publish it.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>あなたの恩師である顧先生は、今の文壇の第一人者、王世貞先生と古いお知り合いでしょう。王先生に序文を書いていただければ、名を慕って多くの人が読み、出版を引き受ける書肆も現れるはずです。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -33251,7 +34860,11 @@
           <t>Ah, my dear, you have done it! What a fine idea!</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>さすがはお前だ。いい考えだ、実にいい。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -33291,7 +34904,11 @@
           <t>I will go to Taicang tomorrow and visit Master Wang!</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>明日、私が太倉へ行って王先生を訪ねます！</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -33331,7 +34948,11 @@
           <t>Father, I am back. Master Wang has written a preface for your book.</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>父上、ただいま戻りました。王先生が序文を書いてくださいました。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -33389,7 +35010,11 @@
           <t>Wonderful.</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>それは素晴らしい。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -33429,7 +35054,11 @@
           <t>I also spoke to Hu Chenglong. He has agreed to contribute to the publication. Some of your former patients, along with our relatives and friends, are willing to help as well. We need only raise another six hundred taels to publish the book.</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>胡承竜にも会いました。出版費用を出してくれるそうです。父上が治療した患者や親戚、友人にも援助を申し出てくれた人がいます。あと六百両集めれば刊行できます。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -33469,7 +35098,11 @@
           <t>Six hundred is still a great deal of money, but at least there is hope now…</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>六百両も小さな額ではないが、ようやく希望が見えた……</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -33487,7 +35120,11 @@
           <t>Li Dongbi died in the twenty-first year of the Wanli reign, aged seventy-six…</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>万暦二十一年、李東璧は七十六歳で世を去った……</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -33505,7 +35142,11 @@
           <t>In the twenty-fourth year of Wanli, the medical book to which he had devoted his life was finally printed…</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>万暦二十四年、生涯をかけて書き上げた医学書が、ついに版木を彫って刊行された……</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -33563,7 +35204,11 @@
           <t>Dongbi, we can no longer keep this clinic open. Let us pack our things and return to our hometown in the countryside…</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>東璧、この診療所はもう続けられないわ。荷物をまとめて故郷の村へ帰りましょう……</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -33581,7 +35226,11 @@
           <t>The clinic was forced to close after falling into financial difficulty.</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>経営難のため、診療所は閉鎖を余儀なくされた。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -33621,7 +35270,11 @@
           <t>Li Dongbi, someone has accused you of practicing medicine without skill and deceiving your patients. Come with us to the magistrate's office.</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>李東璧、お前の医術が未熟で、人を騙していると訴えがあった。役所まで来てもらうぞ。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -33661,7 +35314,11 @@
           <t>I am innocent! I have been wronged!</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>濡れ衣です！　無実です！</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -33701,7 +35358,11 @@
           <t>Enough talk. Move!</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>黙れ、早く歩け！</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -33719,7 +35380,11 @@
           <t>Li Dongbi was found responsible for a patient's death, flogged forty times and forbidden to practice medicine ever again.</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>李東璧は診療中の過失によって人を死なせた罪で、杖刑四十回を受け、生涯医業を禁じられた。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -33737,7 +35402,11 @@
           <t>Li Dongbi died in the twenty-first year of the Wanli reign, aged seventy-six…</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>万暦二十一年、李東璧は七十六歳で世を去った……</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -33755,7 +35424,11 @@
           <t>Sadly, the medical book he had spent a lifetime writing was never preserved…</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>残念ながら、生涯をかけて編纂した医学書は、後世に残らなかった……</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -33773,7 +35446,11 @@
           <t>The examination results are posted in Wuchang Prefecture, in the nineteenth year of the Jiajing reign.</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>明の嘉靖十九年、武昌府の合格者掲示場。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -33813,7 +35490,11 @@
           <t>Master, the young master's name is not on the list.</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>旦那様、合格者の中に若旦那のお名前がありません。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -33853,7 +35534,11 @@
           <t>Ah… I failed again…</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>はあ……また落ちたか……</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -33893,7 +35578,11 @@
           <t>Look again, more carefully.</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>もう一度よく見てくれ。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -33933,7 +35622,11 @@
           <t>I have checked several times. His name really is not there…</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>何度も確かめましたが、やはり若旦那のお名前はありません……</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -33973,7 +35666,11 @@
           <t>Three attempts, and still no success in the provincial examination. Father, perhaps I am simply not made for scholarship…</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>三度受けても郷試に受かりません。父上、私には学問が向いていないようです……</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -34013,7 +35710,11 @@
           <t>Do not talk like that. Old Fan from the next village spent most of his life taking the lower examinations. He was over fifty when he finally earned his first degree, and later he passed the provincial examination too. You are still young.</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>何を言う。隣村の范じいさんは、半生を費やして童試を受け、五十を過ぎてようやく秀才になった。その後は挙人にもなったぞ。お前はまだまだこれからだ。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -34053,7 +35754,11 @@
           <t>I think I would rather study medicine with you. I simply cannot get the hang of those examination essays…</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>それなら、父上について医術を学びたいです。科挙の文章はどうにも身につきません……</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -34093,7 +35798,11 @@
           <t>A career in medicine offers nothing like the prospects of an official post. I have practiced all my life. The work is hard, the pay is poor, and if a treatment goes badly, people look down on you.</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>医者より役人のほうが将来があるだろう。わしは生涯医者をやってきたが、苦労の割に稼げず、治療がうまくいかなければ非難される。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -34133,7 +35842,11 @@
           <t>But I truly love studying herbs, prescriptions and the old texts. I would do it even if I earned nothing.</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>それでも薬材や処方を調べ、古い書物を考証するのが好きなのです。儲からなくても構いません。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -34173,7 +35886,11 @@
           <t>Ah… Very well. Thousands pursue an official title through the examinations, but how many ever obtain one? Dongbi, if you truly wish to become a physician, then from today we shall begin with the Inner Canon and the materia medica.</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>はあ……それもよかろう。科挙を受ける者は数知れぬが、功名を得られる者はわずかだ。東璧、本当に医の道へ進みたいなら、今日から父と『内経』『本草』を学ぼう。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -34191,7 +35908,11 @@
           <t>Li Dongbi passed his first examination at fourteen, but failed the provincial examination three times over the next nine years. With little desire for an official career, he decided to study medicine under his father.</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>李東璧は十四歳で秀才となったが、その後九年間に三度の郷試で落第した。もとより科挙に心を向けていなかった彼は、父について医術を学ぶ決意をした。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -34209,7 +35930,11 @@
           <t>One year later…</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>一年後……</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -34249,7 +35974,11 @@
           <t>Ephedra and cinnamon twig work together to induce sweating and dispel cold, treating an exterior excess pattern without sweat. Ephedra and apricot kernel help the lungs diffuse and descend qi, treating wheezing caused by cold obstructing the lungs…</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>麻黄と桂枝を併用すれば、発汗と散寒の働きが強まり、表実で汗の出ない症に適する。麻黄と杏仁を組み合わせれば、肺気の宣発と下降を整え、寒邪が肺を塞ぐ喘ぎを治す……</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -34289,7 +36018,11 @@
           <t>Husband, dinner is ready. Come and eat.</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>あなた、夕食ができましたよ。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -34329,7 +36062,11 @@
           <t>Coming, coming.</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>今行くよ。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -34369,7 +36106,11 @@
           <t>Dongbi, did you understand everything I taught you today?</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>東璧、昼間教えたことは理解できたか？</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -34409,7 +36150,11 @@
           <t>Yes. I have watched you treat patients for years, so I already know a little of how it works.</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>はい。普段から父上の診療を見て、少しは心得ていました。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -34449,7 +36194,11 @@
           <t>The most important thing in medicine is to build experience. After dinner, review what I have taught you these past few days. Tomorrow morning, you will accompany me on my rounds.</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>医術で大切なのは積み重ねだ。夕食の後は、この数日教えたことを復習しなさい。明朝はわしと一緒に往診に行くぞ。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -34489,7 +36238,11 @@
           <t>Oh, wonderful!</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>やった、ありがとうございます！</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -34529,7 +36282,11 @@
           <t>From today on, you will treat patients yourself. Remember what I taught you: first take the pulse to understand the nature of the illness, then identify the pattern and diagnose the condition before writing a prescription. If you forget a pulse pattern or formula, consult your notes.</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>今日からお前も正式に患者を診る。教えたことを忘れるな。まず脈を診て病の性質を確かめ、弁証によって病を判断し、それに合う処方を出す。脈や処方を忘れたら、手控えを読み返しなさい。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -34569,7 +36326,11 @@
           <t>Now then, your patient is waiting. Go on.</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>患者が待っている。さあ、行きなさい。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -34609,7 +36370,11 @@
           <t>Brother Yanwen, it has been too long. I hope you are well.</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>言聞殿、お変わりありませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -34649,7 +36414,11 @@
           <t>Ah, Brother Riyan! Forgive me for not greeting you sooner.</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>これは日岩殿。お迎えもせず失礼しました。</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -34689,7 +36458,11 @@
           <t>How has Dongbi been lately?</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>東璧は近頃どうしていますか？</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -34729,7 +36502,11 @@
           <t>He has studied medicine with me for over a year and can already see patients on his own. He learns quickly, too. Now that he helps run the clinic, I have more time to rest.</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>もう一年余り医術を学び、今では一人で診療できるようになりました。覚えも早く、診療所を任せられるので、わしも少し楽になりましたよ。</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -34769,7 +36546,11 @@
           <t>Master Gu, it is an honor to see you.</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>顧先生、ご無沙汰しております。</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -34809,7 +36590,11 @@
           <t>As it happens, I have not felt well these past few days. Dongbi, would you examine me?</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ちょうどこの数日、体調が優れぬ。東璧、診てくれるか。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -34849,7 +36634,11 @@
           <t>Master, you have a deficiency of heart yang. Please rest and avoid overwork. I will prepare your medicine.</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>先生は心陽虚の症です。休息を取り、働きすぎないようにしてください。すぐに薬を用意します。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -34889,7 +36678,11 @@
           <t>Most people believe the examinations and an official post are the only proper path. You have recognized your true calling, carried on your family's medicine and chosen to help others. That is rare indeed.</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>世間では科挙に受かって官職に就くことだけが正道と思われている。お前は自分の心を見つめ、家の医術を継いで人々を救う道を選んだ。立派なことだ。</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -34929,7 +36722,11 @@
           <t>I was a poor student. I have let you down, Master…</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>私は不出来な弟子で、先生の教えに背いてしまいました……</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -34969,7 +36766,11 @@
           <t>You were my favorite pupil then, and you still are.</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>お前は昔も今も、わしの一番の弟子だ。</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -35009,7 +36810,11 @@
           <t>The examinations are not the only path in life. I am glad you have found one that suits you.</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>人生の道は科挙だけではない。自分に合った道を見つけたことを、師として嬉しく思う。</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -35049,7 +36854,11 @@
           <t>Thank you for your guidance, Master. I will honor your teaching by improving my medical skills.</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>先生の教えに感謝します。医術を磨き、ご恩に報います。</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -35089,7 +36898,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -35129,7 +36942,11 @@
           <t>Master! Forgive me for not welcoming you sooner.</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>先生、いらしていたのですか。お迎えもせず失礼しました。</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -35169,7 +36986,11 @@
           <t>Dongbi, the court has ordered me to take up a post in Fujian. I came to see you and your father before I leave.</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>東璧よ、朝廷から福建への赴任を命じられた。発つ前に、お前と父上に会いに来たのだ。</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -35209,7 +37030,11 @@
           <t>Please, have a seat, Master. I will make you some tea.</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>先生、お掛けください。お茶をお淹れします。</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -35249,7 +37074,11 @@
           <t>Well, how have you been? How are your medical studies coming along?</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>うむ、最近はどうだ。医術の勉強は進んでいるか？</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -35289,7 +37118,11 @@
           <t>As I have practiced and studied, I have found that the materia medica has been expanded and revised many times since the Divine Farmer's Classic. Errors and omissions concerning herbs and prescriptions are beyond counting. A mistaken formula can harm several people; a mistaken herb can harm countless more.</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>診療と読書を続けるうちに、『神農本草経』以降の本草書には、度重なる増補や改訂によって薬材や処方の抜け、誤りが数えきれないほどあると気づきました。処方を一つ誤れば数人を害し、薬を一つ取り違えれば多くの命に関わります。</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -35329,7 +37162,11 @@
           <t>I want to check the old texts, recover what was lost, correct their mistakes and write a new medical book for future generations.</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>古い典籍を照合し、欠けた部分を補い、誤りを正して、後世に役立つ医学書を新たに編みたいのです。</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -35369,7 +37206,11 @@
           <t>A fine ambition, Dongbi. A fine ambition indeed.</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>うむ、よい考えだ、東璧。</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -35409,7 +37250,11 @@
           <t>The Song scholar Zhang Zai wrote: “Establish a heart for Heaven and Earth; secure a life for the people; carry forward the lost learning of the sages; and bring peace to all generations.”</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>宋の儒者、張載には四句の教えがある。「天地のために心を立て、生民のために命を立て、往聖のために絶学を継ぎ、万世のために太平を開く」。</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -35449,7 +37294,11 @@
           <t>If you complete this book, you will truly help secure a life for the people and carry forward the learning of the sages.</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>この書を書き上げれば、まさしく人々のために道を示し、先人の学問を後世へ伝えることになる。</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -35489,7 +37338,11 @@
           <t>Secure a life for the people, and carry forward the learning of the sages… I will remember that.</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>「生民のために命を立て、往聖のために絶学を継ぐ」……心に刻みます。</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -35507,7 +37360,11 @@
           <t>Knock, knock… Knock, knock, knock, knock…</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>トントン……トントントントン……</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">

--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -1966,6 +1966,14 @@
 Return to the main menu?</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>現在の段階はまだ完了していません。
+メインメニューに戻ると、保存していない進行状況は失われます。
+「保存して戻る」を選ぶと、先に%sに保存します。
+メインメニューに戻りますか？</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
@@ -1989,6 +1997,14 @@
 Quit the game?</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>現在の段階はまだ完了していません。
+ゲームを終了すると、保存していない進行状況は失われます。
+「保存して終了」を選ぶと、先に%sに保存します。
+ゲームを終了しますか？</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
@@ -2010,6 +2026,13 @@
 Return to the main menu?</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>現在の段階はまだ完了していません。
+メインメニューに戻った場合、次回は最新のオートセーブから再開します。
+メインメニューに戻りますか？</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -2031,6 +2054,13 @@
 Quit the game?</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>現在の段階はまだ完了していません。
+ゲームを終了すると、保存していない進行状況は失われます。
+終了しますか？</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
@@ -2050,6 +2080,12 @@
 Try Save and Return again, or Return to Main Menu to discard unsaved progress.</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>保存に失敗したため、メインメニューには戻りませんでした。
+「保存して戻る」を再試行するか、「メインメニューに戻る」で未保存の進行状況を破棄してください。</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
@@ -2069,6 +2105,12 @@
 Try Save and Quit again, or Quit Game to discard unsaved progress.</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>保存に失敗したため、ゲームは終了しませんでした。
+「保存して終了」を再試行するか、「ゲームを終了」で未保存の進行状況を破棄してください。</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
@@ -2086,6 +2128,11 @@
           <t>Existing Save</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>セーブデータあり</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
@@ -2103,6 +2150,11 @@
           <t>Corrupt Save</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>破損したセーブデータ</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
@@ -2120,6 +2172,11 @@
           <t>Load Failed</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>読み込み失敗</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
@@ -2161,6 +2218,12 @@
 If you have health concerns, consult a qualified doctor and follow the advice of a licensed medical institution. The characters, events, and story are fictional. Any resemblance to real people or events is coincidental.</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>本作はフィクションであり、娯楽を目的としています。ゲーム中の医学知識、診断や治療の内容は正確でない場合があり、現実の医療判断には使用できません。これを根拠に自己診断、服薬、治療を行わないでください。
+健康上の問題がある場合は医師に相談し、正規の医療機関の助言に従ってください。登場人物、出来事、物語はすべて架空のものです。実在のものと類似していても偶然です。</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
@@ -2266,6 +2329,11 @@
           <t>Rep 0 · Novice</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>名声：0　見習い</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="17" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
@@ -2283,6 +2351,11 @@
           <t>Money: 0 liang 0 wen</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>所持金：0両 0文</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
@@ -2498,6 +2571,11 @@
           <t>%s %s · %s</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>%s%s年%s</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
@@ -2559,6 +2637,11 @@
           <t>%s %s · %s</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>%s %s・%s</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
@@ -2598,6 +2681,11 @@
           <t>Infamous</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>悪名高い</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
@@ -2615,6 +2703,11 @@
           <t>Criticized</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>評判が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="3" t="inlineStr">
@@ -2632,6 +2725,11 @@
           <t>Novice</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>見習い</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="17" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
@@ -2649,6 +2747,11 @@
           <t>Apprentice</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>駆け出し</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
@@ -2666,6 +2769,11 @@
           <t>Skilled</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>熟練</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="17" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
@@ -2683,6 +2791,11 @@
           <t>Master</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>名医</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="17" customHeight="1">
       <c r="A104" s="3" t="inlineStr">
@@ -2700,6 +2813,11 @@
           <t>Legend</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>伝説の名医</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="17" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
@@ -2717,6 +2835,11 @@
           <t>Rep %d · %s</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>名声：%d　%s</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
@@ -2732,6 +2855,11 @@
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Rep %d/%d · %s</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>名声：%d/%d　%s</t>
         </is>
       </c>
     </row>
@@ -5979,6 +6107,11 @@
           <t>Search conditions</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>病名を検索</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="17" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
@@ -5996,6 +6129,11 @@
           <t>Search formulas</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>処方を検索</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="17" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
@@ -6013,6 +6151,11 @@
           <t>Search herbs</t>
         </is>
       </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>薬材を検索</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="17" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
@@ -6030,6 +6173,11 @@
           <t>Select a condition</t>
         </is>
       </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>左側の疾病を選択してください</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="17" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
@@ -6047,6 +6195,11 @@
           <t>Select a formula</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>左側の処方を選択してください</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="17" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
@@ -6064,6 +6217,11 @@
           <t>Select an herb</t>
         </is>
       </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>左側の薬材を選択してください</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="17" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
@@ -6081,6 +6239,11 @@
           <t>Previous</t>
         </is>
       </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>前のページ</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="17" customHeight="1">
       <c r="A258" s="3" t="inlineStr">
@@ -6098,6 +6261,11 @@
           <t>Next</t>
         </is>
       </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>次のページ</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="17" customHeight="1">
       <c r="A259" s="3" t="inlineStr">
@@ -6115,6 +6283,11 @@
           <t>Read Books</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>読書</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="17" customHeight="1">
       <c r="A260" s="3" t="inlineStr">
@@ -6132,6 +6305,11 @@
           <t>Search unlocked entries in all available books.</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>閲覧可能な医学書にある、解放済みの項目をすべて検索します。</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="17" customHeight="1">
       <c r="A261" s="3" t="inlineStr">
@@ -6149,6 +6327,11 @@
           <t>Search all unlocked entries...</t>
         </is>
       </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>解放済みの項目を検索……</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="17" customHeight="1">
       <c r="A262" s="3" t="inlineStr">
@@ -6166,6 +6349,11 @@
           <t>Medical Books</t>
         </is>
       </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>医学書一覧</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="17" customHeight="1">
       <c r="A263" s="3" t="inlineStr">
@@ -6183,6 +6371,11 @@
           <t>Entries</t>
         </is>
       </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>項目一覧</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="17" customHeight="1">
       <c r="A264" s="3" t="inlineStr">
@@ -6200,6 +6393,11 @@
           <t>Choose a book to read tonight.</t>
         </is>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>今夜読む医学書を選んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="17" customHeight="1">
       <c r="A265" s="3" t="inlineStr">
@@ -6217,6 +6415,11 @@
           <t>Choose a book to view.</t>
         </is>
       </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>閲覧する医学書を選んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="17" customHeight="1">
       <c r="A266" s="3" t="inlineStr">
@@ -6234,6 +6437,11 @@
           <t xml:space="preserve">  [Matches: %d]</t>
         </is>
       </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【一致%d】</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="17" customHeight="1">
       <c r="A267" s="3" t="inlineStr">
@@ -6251,6 +6459,11 @@
           <t xml:space="preserve">  [New: %d]</t>
         </is>
       </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【新着%d】</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="17" customHeight="1">
       <c r="A268" s="3" t="inlineStr">
@@ -6268,6 +6481,11 @@
           <t>Found %d matching entries</t>
         </is>
       </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>一致する項目が %d 件見つかりました</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="17" customHeight="1">
       <c r="A269" s="3" t="inlineStr">
@@ -6285,6 +6503,11 @@
           <t>%d newly unlocked entries are available</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>新しく解放された項目が %d 件あります</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="17" customHeight="1">
       <c r="A270" s="3" t="inlineStr">
@@ -6302,6 +6525,11 @@
           <t>Search "%s": %d unlocked entries found; "%s" has %d matches.</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>「%s」の検索結果：解放済みの項目が合計 %d 件。現在の『%s』には %d 件あります。</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="17" customHeight="1">
       <c r="A271" s="3" t="inlineStr">
@@ -6319,6 +6547,11 @@
           <t>"%s" has no unlocked entries yet.</t>
         </is>
       </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>『%s』には現在、解放済みの項目がありません。</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="17" customHeight="1">
       <c r="A272" s="3" t="inlineStr">
@@ -6336,6 +6569,11 @@
           <t>"%s" has %d unlocked entries, including %d unread.</t>
         </is>
       </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>『%s』には解放済みの項目が %d 件あり、うち %d 件は未読です。</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="17" customHeight="1">
       <c r="A273" s="3" t="inlineStr">
@@ -6353,6 +6591,11 @@
           <t>"%s" has %d unlocked entries.</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>『%s』には解放済みの項目が %d 件あります。</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="17" customHeight="1">
       <c r="A274" s="3" t="inlineStr">
@@ -6370,6 +6613,11 @@
           <t>No books are available to view.</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>閲覧できる医学書がありません。</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="17" customHeight="1">
       <c r="A275" s="3" t="inlineStr">
@@ -6387,6 +6635,11 @@
           <t>No unlocked entries match "%s".</t>
         </is>
       </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>「%s」に一致する解放済みの項目は見つかりませんでした。</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="17" customHeight="1">
       <c r="A276" s="3" t="inlineStr">
@@ -6404,6 +6657,11 @@
           <t xml:space="preserve">  [New]</t>
         </is>
       </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【新着】</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="17" customHeight="1">
       <c r="A277" s="3" t="inlineStr">
@@ -6421,6 +6679,11 @@
           <t>Newly unlocked; not yet read</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>新しく解放された未読の項目</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="17" customHeight="1">
       <c r="A278" s="3" t="inlineStr">
@@ -6438,6 +6701,11 @@
           <t>No text available</t>
         </is>
       </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>本文はありません</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="17" customHeight="1">
       <c r="A279" s="3" t="inlineStr">
@@ -6455,6 +6723,11 @@
           <t>This entry is locked. Meet its unlock requirements first.</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>この項目はまだ解放されていません。先に解放条件を満たしてください。</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="17" customHeight="1">
       <c r="A280" s="3" t="inlineStr">
@@ -6472,6 +6745,11 @@
           <t>Entry read.</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>閲覧済みの項目です。</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="17" customHeight="1">
       <c r="A281" s="3" t="inlineStr">
@@ -6489,6 +6767,11 @@
           <t>View Pulse</t>
         </is>
       </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>脈を確認</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="17" customHeight="1">
       <c r="A282" s="3" t="inlineStr">
@@ -6506,6 +6789,11 @@
           <t>Select an unlocked condition from the entries first.</t>
         </is>
       </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>まず項目一覧から解放済みの疾病を選んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="17" customHeight="1">
       <c r="A283" s="3" t="inlineStr">
@@ -6523,6 +6811,11 @@
           <t>View left and right pulse patterns for %s to practice at night.</t>
         </is>
       </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>『%s』の左右の脈を確認し、夜間の練習に使います。</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="17" customHeight="1">
       <c r="A284" s="3" t="inlineStr">
@@ -6540,6 +6833,11 @@
           <t>Select a condition entry before viewing its pulse.</t>
         </is>
       </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>脈を確認する前に、疾病の項目を選んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="17" customHeight="1">
       <c r="A285" s="3" t="inlineStr">
@@ -6557,6 +6855,11 @@
           <t>Pulse practice window is unavailable.</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>脈診の練習画面が見つかりません。</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="17" customHeight="1">
       <c r="A286" s="3" t="inlineStr">
@@ -6574,6 +6877,11 @@
           <t>Pulse Practice - %s</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>脈診の練習・%s</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="17" customHeight="1">
       <c r="A287" s="3" t="inlineStr">
@@ -6591,6 +6899,11 @@
           <t>Treatments</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>診療記録</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="17" customHeight="1">
       <c r="A288" s="3" t="inlineStr">
@@ -6608,6 +6921,11 @@
           <t>Accounts</t>
         </is>
       </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>収支明細</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="17" customHeight="1">
       <c r="A289" s="3" t="inlineStr">
@@ -6625,6 +6943,11 @@
           <t>Statistics</t>
         </is>
       </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>統計</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="17" customHeight="1">
       <c r="A290" s="3" t="inlineStr">
@@ -6642,6 +6965,11 @@
           <t>Formula Presets</t>
         </is>
       </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>定型処方</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="17" customHeight="1">
       <c r="A291" s="3" t="inlineStr">
@@ -6659,6 +6987,11 @@
           <t>Treatment Dates</t>
         </is>
       </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>診療日</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="17" customHeight="1">
       <c r="A292" s="3" t="inlineStr">
@@ -6676,6 +7009,11 @@
           <t>Account Dates</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>記帳日</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="17" customHeight="1">
       <c r="A293" s="3" t="inlineStr">
@@ -6693,6 +7031,11 @@
           <t>Patients Treated</t>
         </is>
       </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>診療した患者</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="17" customHeight="1">
       <c r="A294" s="3" t="inlineStr">
@@ -6710,6 +7053,11 @@
           <t>Successful Treatments</t>
         </is>
       </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>治療成功</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="17" customHeight="1">
       <c r="A295" s="3" t="inlineStr">
@@ -6727,6 +7075,11 @@
           <t>Miraculous Recoveries</t>
         </is>
       </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>妙手回春</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="17" customHeight="1">
       <c r="A296" s="3" t="inlineStr">
@@ -6744,6 +7097,11 @@
           <t>Failed Treatments</t>
         </is>
       </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>治療失敗</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="17" customHeight="1">
       <c r="A297" s="3" t="inlineStr">
@@ -6761,6 +7119,11 @@
           <t>Success Rate</t>
         </is>
       </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>成功率</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="17" customHeight="1">
       <c r="A298" s="3" t="inlineStr">
@@ -6778,6 +7141,11 @@
           <t>Total Income</t>
         </is>
       </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>総収入</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="17" customHeight="1">
       <c r="A299" s="3" t="inlineStr">
@@ -6795,6 +7163,11 @@
           <t>Total Expenses</t>
         </is>
       </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>総支出</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="17" customHeight="1">
       <c r="A300" s="3" t="inlineStr">
@@ -6812,6 +7185,11 @@
           <t>Profit</t>
         </is>
       </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>利益</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="17" customHeight="1">
       <c r="A301" s="3" t="inlineStr">
@@ -6829,6 +7207,11 @@
           <t>Formula Mastery</t>
         </is>
       </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>処方の熟練度</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="17" customHeight="1">
       <c r="A302" s="3" t="inlineStr">
@@ -6846,6 +7229,11 @@
           <t>0 people</t>
         </is>
       </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>0人</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="17" customHeight="1">
       <c r="A303" s="3" t="inlineStr">
@@ -6863,6 +7251,11 @@
           <t>0 liang 0 wen</t>
         </is>
       </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>0両0文</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="17" customHeight="1">
       <c r="A304" s="3" t="inlineStr">
@@ -6880,6 +7273,11 @@
           <t>[color=#c6ae83]No treatments recorded yet. After your first treatment, patients, conditions, standard formulas, diagnoses and prescriptions will be saved here by day.[/color]</t>
         </is>
       </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>[color=#c6ae83]診療記録はまだありません。診療を終えると、患者・疾病・標準処方・診断・処方が日ごとに記録されます。[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="17" customHeight="1">
       <c r="A305" s="3" t="inlineStr">
@@ -6897,6 +7295,11 @@
           <t>[font_size=24][color=#e3b66b]%s · Treatments[/color][/font_size]</t>
         </is>
       </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>[font_size=24][color=#e3b66b]%s・診療記録[/color][/font_size]</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="17" customHeight="1">
       <c r="A306" s="3" t="inlineStr">
@@ -6916,6 +7319,12 @@
 [color=#c6ae83]No treatments recorded today.[/color]</t>
         </is>
       </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+[color=#c6ae83]この日の記録はありません。[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="17" customHeight="1">
       <c r="A307" s="3" t="inlineStr">
@@ -6933,6 +7342,11 @@
           <t>Successful</t>
         </is>
       </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="17" customHeight="1">
       <c r="A308" s="3" t="inlineStr">
@@ -6950,6 +7364,11 @@
           <t>Not Cured</t>
         </is>
       </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>未治癒</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="17" customHeight="1">
       <c r="A309" s="3" t="inlineStr">
@@ -6967,6 +7386,11 @@
           <t>Unknown Patient</t>
         </is>
       </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>不明な患者</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="17" customHeight="1">
       <c r="A310" s="3" t="inlineStr">
@@ -6984,6 +7408,11 @@
           <t>Not Recorded</t>
         </is>
       </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>記録なし</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="17" customHeight="1">
       <c r="A311" s="3" t="inlineStr">
@@ -7001,6 +7430,11 @@
           <t>Patient condition: [color=#e3d1aa]%s[/color]</t>
         </is>
       </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>患者の病名：[color=#e3d1aa]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="17" customHeight="1">
       <c r="A312" s="3" t="inlineStr">
@@ -7018,6 +7452,11 @@
           <t>Standard formula: [color=#e3d1aa]%s[/color]</t>
         </is>
       </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>標準処方：[color=#e3d1aa]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="17" customHeight="1">
       <c r="A313" s="3" t="inlineStr">
@@ -7035,6 +7474,11 @@
           <t>Diagnosis: [color=#e3d1aa]%s[/color]</t>
         </is>
       </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>診断：[color=#e3d1aa]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="17" customHeight="1">
       <c r="A314" s="3" t="inlineStr">
@@ -7052,6 +7496,11 @@
           <t>Prescription: [color=#e3d1aa]%s[/color]</t>
         </is>
       </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>処方：[color=#e3d1aa]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="17" customHeight="1">
       <c r="A315" s="3" t="inlineStr">
@@ -7069,6 +7518,11 @@
           <t>(Empty prescription)</t>
         </is>
       </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>（処方なし）</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="17" customHeight="1">
       <c r="A316" s="3" t="inlineStr">
@@ -7086,6 +7540,11 @@
           <t xml:space="preserve">; </t>
         </is>
       </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>；</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="17" customHeight="1">
       <c r="A317" s="3" t="inlineStr">
@@ -7103,6 +7562,11 @@
           <t>[color=#c6ae83]Accounts are recorded from %s onward.[/color]</t>
         </is>
       </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>[color=#c6ae83]収支の記録は%sから始まります。[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="17" customHeight="1">
       <c r="A318" s="3" t="inlineStr">
@@ -7120,6 +7584,11 @@
           <t>[color=#c6ae83]No accounts are available for %s.[/color]</t>
         </is>
       </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>[color=#c6ae83]%sの収支データはありません。[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="17" customHeight="1">
       <c r="A319" s="3" t="inlineStr">
@@ -7137,6 +7606,11 @@
           <t>[font_size=24][color=#e3b66b]%s · Accounts[/color][/font_size]</t>
         </is>
       </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>[font_size=24][color=#e3b66b]%s・収支明細[/color][/font_size]</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="17" customHeight="1">
       <c r="A320" s="3" t="inlineStr">
@@ -7154,6 +7628,11 @@
           <t>[color=#c6ae83]Today is not settled yet. Expenses are recorded when night begins.[/color]</t>
         </is>
       </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>[color=#c6ae83]この日の決算はまだです。夜になると支出が計上されます。[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="17" customHeight="1">
       <c r="A321" s="3" t="inlineStr">
@@ -7173,6 +7652,12 @@
 [b]Income[/b]</t>
         </is>
       </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+[b]収入[/b]</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="17" customHeight="1">
       <c r="A322" s="3" t="inlineStr">
@@ -7192,6 +7677,12 @@
 [b]Expenses[/b]</t>
         </is>
       </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+[b]支出[/b]</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="17" customHeight="1">
       <c r="A323" s="3" t="inlineStr">
@@ -7209,6 +7700,11 @@
           <t>Consultation Fees</t>
         </is>
       </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>診察料</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="17" customHeight="1">
       <c r="A324" s="3" t="inlineStr">
@@ -7226,6 +7722,11 @@
           <t>Herb Sales</t>
         </is>
       </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>薬材収入</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="17" customHeight="1">
       <c r="A325" s="3" t="inlineStr">
@@ -7243,6 +7744,11 @@
           <t>Patient Gifts</t>
         </is>
       </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>患者からの謝礼</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="17" customHeight="1">
       <c r="A326" s="3" t="inlineStr">
@@ -7260,6 +7766,11 @@
           <t>Li Jianzhong's Salary</t>
         </is>
       </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>李建中の俸禄</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="17" customHeight="1">
       <c r="A327" s="3" t="inlineStr">
@@ -7277,6 +7788,11 @@
           <t>Li Yanwen's Income</t>
         </is>
       </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>李言聞の収入</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="17" customHeight="1">
       <c r="A328" s="3" t="inlineStr">
@@ -7294,6 +7810,11 @@
           <t>Land Rent</t>
         </is>
       </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>地代</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="17" customHeight="1">
       <c r="A329" s="3" t="inlineStr">
@@ -7311,6 +7832,11 @@
           <t>Chenpi and Banxia Wages</t>
         </is>
       </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>陳皮と半夏の給金</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="17" customHeight="1">
       <c r="A330" s="3" t="inlineStr">
@@ -7328,6 +7854,11 @@
           <t>Food</t>
         </is>
       </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>食費</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="17" customHeight="1">
       <c r="A331" s="3" t="inlineStr">
@@ -7345,6 +7876,11 @@
           <t>Social Gifts</t>
         </is>
       </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>贈答費</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="17" customHeight="1">
       <c r="A332" s="3" t="inlineStr">
@@ -7362,6 +7898,11 @@
           <t>Medical Books</t>
         </is>
       </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>医学書の購入</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="17" customHeight="1">
       <c r="A333" s="3" t="inlineStr">
@@ -7379,6 +7920,11 @@
           <t>Coal</t>
         </is>
       </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>石炭</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="17" customHeight="1">
       <c r="A334" s="3" t="inlineStr">
@@ -7396,6 +7942,11 @@
           <t>Cloth and Winter Clothes</t>
         </is>
       </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>衣服と綿入れ</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="17" customHeight="1">
       <c r="A335" s="3" t="inlineStr">
@@ -7413,6 +7964,11 @@
           <t>House Repairs</t>
         </is>
       </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>家屋の修繕</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="17" customHeight="1">
       <c r="A336" s="3" t="inlineStr">
@@ -7430,6 +7986,11 @@
           <t>Ancestral Rites</t>
         </is>
       </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>墓参りと先祖供養</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="17" customHeight="1">
       <c r="A337" s="3" t="inlineStr">
@@ -7447,6 +8008,11 @@
           <t>Spoiled Herbs</t>
         </is>
       </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>薬材のカビ</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="17" customHeight="1">
       <c r="A338" s="3" t="inlineStr">
@@ -7464,6 +8030,11 @@
           <t>Summer Tax</t>
         </is>
       </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>夏の税</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="17" customHeight="1">
       <c r="A339" s="3" t="inlineStr">
@@ -7481,6 +8052,11 @@
           <t>Autumn Tax</t>
         </is>
       </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>秋の税</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="17" customHeight="1">
       <c r="A340" s="3" t="inlineStr">
@@ -7498,6 +8074,11 @@
           <t>Total Income: [color=#9fe29f]%s[/color]</t>
         </is>
       </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>収入合計：[color=#9fe29f]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="17" customHeight="1">
       <c r="A341" s="3" t="inlineStr">
@@ -7515,6 +8096,11 @@
           <t>Total Expenses: [color=#f0a0a0]%s[/color]</t>
         </is>
       </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>支出合計：[color=#f0a0a0]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="17" customHeight="1">
       <c r="A342" s="3" t="inlineStr">
@@ -7534,6 +8120,12 @@
 Today's Change: [color=#e3b66b]%s[/color]</t>
         </is>
       </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+本日の増減：[color=#e3b66b]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="17" customHeight="1">
       <c r="A343" s="3" t="inlineStr">
@@ -7551,6 +8143,11 @@
           <t>%s: [color=%s]%s[/color]</t>
         </is>
       </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>%s：[color=%s]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="17" customHeight="1">
       <c r="A344" s="3" t="inlineStr">
@@ -7568,6 +8165,11 @@
           <t>%s%d liang %d wen</t>
         </is>
       </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>%s%d両%d文</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="17" customHeight="1">
       <c r="A345" s="3" t="inlineStr">
@@ -7585,6 +8187,11 @@
           <t>Date Unknown</t>
         </is>
       </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>日付不明</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="17" customHeight="1">
       <c r="A346" s="3" t="inlineStr">
@@ -7602,6 +8209,11 @@
           <t>%d people</t>
         </is>
       </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>%d人</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="17" customHeight="1">
       <c r="A347" s="3" t="inlineStr">
@@ -7619,6 +8231,11 @@
           <t xml:space="preserve">  · Unlocked</t>
         </is>
       </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・解放済み</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="17" customHeight="1">
       <c r="A348" s="3" t="inlineStr">
@@ -7636,6 +8253,11 @@
           <t>[color=#c6ae83]No formula data available.[/color]</t>
         </is>
       </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>[color=#c6ae83]処方データはありません。[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="17" customHeight="1">
       <c r="A349" s="3" t="inlineStr">
@@ -7653,6 +8275,11 @@
           <t>Unlocked: ready to use while prescribing</t>
         </is>
       </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>解放済み：処方時にワンクリックで使用できます</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="17" customHeight="1">
       <c r="A350" s="3" t="inlineStr">
@@ -7670,6 +8297,11 @@
           <t>Locked: earn 5 Miraculous Recovery results with this formula</t>
         </is>
       </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>未解放：この処方で「妙手回春」を5回達成すると解放されます</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="17" customHeight="1">
       <c r="A351" s="3" t="inlineStr">
@@ -7689,6 +8321,12 @@
 Mastery: %d / 5</t>
         </is>
       </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+達成回数：%d / 5</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="17" customHeight="1">
       <c r="A352" s="3" t="inlineStr">
@@ -7706,6 +8344,11 @@
           <t>Status: [color=%s]%s[/color]</t>
         </is>
       </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>状態：[color=%s]%s[/color]</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="17" customHeight="1">
       <c r="A353" s="3" t="inlineStr">
@@ -7725,6 +8368,12 @@
 Standard Formula Ingredients:</t>
         </is>
       </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+標準処方の構成：</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="17" customHeight="1">
       <c r="A354" s="3" t="inlineStr">
@@ -7742,6 +8391,11 @@
           <t>(No ingredient data)</t>
         </is>
       </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>（構成データなし）</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="17" customHeight="1">
       <c r="A355" s="3" t="inlineStr">
@@ -7759,6 +8413,11 @@
           <t>%s (%s)</t>
         </is>
       </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>%s（%s）</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="17" customHeight="1">
       <c r="A356" s="3" t="inlineStr">
@@ -7776,6 +8435,11 @@
           <t>Some entries are unread. Read them before resting.</t>
         </is>
       </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>未読の項目があります。休む前に読んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="17" customHeight="1">
       <c r="A357" s="3" t="inlineStr">
@@ -7793,6 +8457,11 @@
           <t>Dialogue appears here</t>
         </is>
       </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>人物の会話が表示されます</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="17" customHeight="1">
       <c r="A358" s="3" t="inlineStr">
@@ -7810,6 +8479,11 @@
           <t>Pulse (F1)</t>
         </is>
       </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>脈診(F1)</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="17" customHeight="1">
       <c r="A359" s="3" t="inlineStr">
@@ -7827,6 +8501,11 @@
           <t>Prescribe (F2)</t>
         </is>
       </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>処方(F2)</t>
+        </is>
+      </c>
     </row>
     <row r="360" ht="17" customHeight="1">
       <c r="A360" s="3" t="inlineStr">
@@ -7844,6 +8523,11 @@
           <t>Records (F3)</t>
         </is>
       </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>診療記録(F3)</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="17" customHeight="1">
       <c r="A361" s="3" t="inlineStr">
@@ -7861,6 +8545,11 @@
           <t>Click / Space: Continue · Hold Enter: Skip Story</t>
         </is>
       </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>クリック / スペース：続ける、Enter：物語をスキップ</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="17" customHeight="1">
       <c r="A362" s="3" t="inlineStr">
@@ -7878,6 +8567,11 @@
           <t>Subtitles appear here</t>
         </is>
       </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>場面の字幕が表示されます</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="17" customHeight="1">
       <c r="A363" s="3" t="inlineStr">
@@ -7895,6 +8589,11 @@
           <t>Click / Space: Continue · Hold Enter: Skip Story</t>
         </is>
       </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>クリック / スペース：続ける、Enter長押し：物語をスキップ</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="17" customHeight="1">
       <c r="A364" s="3" t="inlineStr">
@@ -7912,6 +8611,11 @@
           <t>Treatment</t>
         </is>
       </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>診療</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="17" customHeight="1">
       <c r="A365" s="3" t="inlineStr">
@@ -7929,6 +8633,11 @@
           <t>Choose a treatment action.</t>
         </is>
       </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>診療項目を選んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="17" customHeight="1">
       <c r="A366" s="3" t="inlineStr">
@@ -7946,6 +8655,11 @@
           <t>Treatment Notice</t>
         </is>
       </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>診療のヒント</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="17" customHeight="1">
       <c r="A367" s="3" t="inlineStr">
@@ -7963,6 +8677,11 @@
           <t>Clinic returned an invalid treatment result.</t>
         </is>
       </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Clinic から無効な診療結果が返されました。</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="17" customHeight="1">
       <c r="A368" s="3" t="inlineStr">
@@ -7980,6 +8699,11 @@
           <t>Could not submit the prescription.</t>
         </is>
       </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>処方を提出できませんでした。</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="17" customHeight="1">
       <c r="A369" s="3" t="inlineStr">
@@ -7997,6 +8721,11 @@
           <t>Notice text</t>
         </is>
       </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>ヒントの内容</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="17" customHeight="1">
       <c r="A370" s="3" t="inlineStr">
@@ -8014,6 +8743,11 @@
           <t>%s: %s</t>
         </is>
       </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>%s：%s</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="17" customHeight="1">
       <c r="A371" s="3" t="inlineStr">
@@ -8031,6 +8765,11 @@
           <t>(None)</t>
         </is>
       </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>（なし）</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="17" customHeight="1">
       <c r="A372" s="3" t="inlineStr">
@@ -8048,6 +8787,11 @@
           <t>(Standard formula not found)</t>
         </is>
       </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>（標準処方が見つかりません）</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="17" customHeight="1">
       <c r="A373" s="3" t="inlineStr">
@@ -8065,6 +8809,11 @@
           <t>No condition selected</t>
         </is>
       </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>病名を選択していません</t>
+        </is>
+      </c>
     </row>
     <row r="374" ht="17" customHeight="1">
       <c r="A374" s="3" t="inlineStr">
@@ -8082,6 +8831,11 @@
           <t>Formula Preset</t>
         </is>
       </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>定型処方</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="17" customHeight="1">
       <c r="A375" s="3" t="inlineStr">
@@ -8099,6 +8853,11 @@
           <t>Formula Preset: %s</t>
         </is>
       </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>定型処方：%s</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="17" customHeight="1">
       <c r="A376" s="3" t="inlineStr">
@@ -8116,6 +8875,11 @@
           <t>Game Guide</t>
         </is>
       </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>遊び方</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="17" customHeight="1">
       <c r="A377" s="3" t="inlineStr">
@@ -8133,6 +8897,11 @@
           <t>← / →: Pages    Esc: Close</t>
         </is>
       </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>← / → ページ切り替え    Esc 閉じる</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="17" customHeight="1">
       <c r="A378" s="3" t="inlineStr">
@@ -8150,6 +8919,11 @@
           <t>Previous</t>
         </is>
       </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>前へ</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="17" customHeight="1">
       <c r="A379" s="3" t="inlineStr">
@@ -8167,6 +8941,11 @@
           <t>Next</t>
         </is>
       </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>次へ</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="17" customHeight="1">
       <c r="A380" s="3" t="inlineStr">
@@ -8184,6 +8963,11 @@
           <t>Finish</t>
         </is>
       </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="17" customHeight="1">
       <c r="A381" s="3" t="inlineStr">
@@ -8201,6 +8985,11 @@
           <t>No guide pages yet</t>
         </is>
       </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>説明はありません</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="17" customHeight="1">
       <c r="A382" s="3" t="inlineStr">
@@ -8218,6 +9007,11 @@
           <t>Add TutorialSlideData to Day Slides in the Inspector.</t>
         </is>
       </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Inspector の Day Slides に TutorialSlideData を追加してください。</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="17" customHeight="1">
       <c r="A383" s="3" t="inlineStr">
@@ -8235,6 +9029,11 @@
           <t>Add TutorialSlideData to Slides in the Inspector.</t>
         </is>
       </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Inspector の Slides に TutorialSlideData を追加してください。</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="17" customHeight="1">
       <c r="A384" s="3" t="inlineStr">
@@ -8252,6 +9051,11 @@
           <t>No TutorialSlideData is set for this guide page.</t>
         </is>
       </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>このチュートリアルページには TutorialSlideData が設定されていません。</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="17" customHeight="1">
       <c r="A385" s="3" t="inlineStr">
@@ -8269,6 +9073,11 @@
           <t>Night</t>
         </is>
       </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="17" customHeight="1">
       <c r="A386" s="3" t="inlineStr">
@@ -8286,6 +9095,11 @@
           <t>At night, click the books (F1) to read, the medical records (F2) to review entries, or the oil lamp (F3) to rest and begin the next day.</t>
         </is>
       </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>夜は書物(F1)をクリックして読書、診療記録(F2)で記録の確認、灯火(F3)で休んで翌日へ進みます。</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="17" customHeight="1">
       <c r="A387" s="3" t="inlineStr">
@@ -8303,6 +9117,11 @@
           <t>Reading</t>
         </is>
       </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>読書</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="17" customHeight="1">
       <c r="A388" s="3" t="inlineStr">
@@ -8320,6 +9139,11 @@
           <t>Read medical classics in the reading window. The Yellow Emperor's Inner Canon explains the foundations of traditional Chinese medicine and serves as a reference.</t>
         </is>
       </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>読書画面では医学書を読めます。『黄帝内経』には東洋医学の基礎理論が記されており、参考にできます。</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="17" customHeight="1">
       <c r="A389" s="3" t="inlineStr">
@@ -8337,6 +9161,11 @@
           <t>Herbs</t>
         </is>
       </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>薬材</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="17" customHeight="1">
       <c r="A390" s="3" t="inlineStr">
@@ -8354,6 +9183,11 @@
           <t>The Divine Farmer's Classic of Materia Medica records information about medicinal herbs and serves as a reference.</t>
         </is>
       </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>『神農本草経』には薬材に関する情報が記されています。参考にしてください。</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="17" customHeight="1">
       <c r="A391" s="3" t="inlineStr">
@@ -8371,6 +9205,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>疾病</t>
+        </is>
+      </c>
     </row>
     <row r="392" ht="17" customHeight="1">
       <c r="A392" s="3" t="inlineStr">
@@ -8388,6 +9227,11 @@
           <t>The Treatise on the Origins and Manifestations of Various Diseases records information about diseases. In the game, diagnose conditions from pulse readings and treat them with standard formulas.</t>
         </is>
       </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>『諸病源候論』には疾病に関する情報が記されています。ゲームでは脈から疾病を判断し、標準処方で治療します。</t>
+        </is>
+      </c>
     </row>
     <row r="393" ht="17" customHeight="1">
       <c r="A393" s="3" t="inlineStr">
@@ -8405,6 +9249,11 @@
           <t>Formulas</t>
         </is>
       </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>処方</t>
+        </is>
+      </c>
     </row>
     <row r="394" ht="17" customHeight="1">
       <c r="A394" s="3" t="inlineStr">
@@ -8422,6 +9271,11 @@
           <t>Other medical books list various formulas. During the day, enter their herbs in the prescription window to treat patients.</t>
         </is>
       </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>ほかの医学書にはさまざまな処方が載っています。昼間は処方画面で構成薬材を入力し、患者に薬を出します。</t>
+        </is>
+      </c>
     </row>
     <row r="395" ht="17" customHeight="1">
       <c r="A395" s="3" t="inlineStr">
@@ -8439,6 +9293,11 @@
           <t>Pulse Readings</t>
         </is>
       </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>脈</t>
+        </is>
+      </c>
     </row>
     <row r="396" ht="17" customHeight="1">
       <c r="A396" s="3" t="inlineStr">
@@ -8456,6 +9315,11 @@
           <t>Select a disease entry in the Treatise on the Origins and Manifestations of Various Diseases, then click 'View Pulse' in the lower right to examine its pulse.</t>
         </is>
       </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>『諸病源候論』で疾病の項目を選び、右下の「脈を確認」を押すと、その病の脈を観察できます。</t>
+        </is>
+      </c>
     </row>
     <row r="397" ht="17" customHeight="1">
       <c r="A397" s="3" t="inlineStr">
@@ -8473,6 +9337,11 @@
           <t>Pulse Readings</t>
         </is>
       </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>脈</t>
+        </is>
+      </c>
     </row>
     <row r="398" ht="17" customHeight="1">
       <c r="A398" s="3" t="inlineStr">
@@ -8490,6 +9359,11 @@
           <t>A healthy pulse has neither increased nor decreased amplitude, neither a thicker nor thinner pulse line, and neither broader nor narrower pulse width. Its pulse frequency is four to five beats per breath.</t>
         </is>
       </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>健康な脈は高すぎず低すぎず、太すぎず細すぎず、広すぎず狭すぎず、呼吸一回につき四～五回打ちます。</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="17" customHeight="1">
       <c r="A399" s="3" t="inlineStr">
@@ -8507,6 +9381,11 @@
           <t>Qi</t>
         </is>
       </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>気</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="17" customHeight="1">
       <c r="A400" s="3" t="inlineStr">
@@ -8526,6 +9405,12 @@
 increased amplitude indicates greater Qi stagnation, while decreased amplitude indicates greater Qi deficiency.</t>
         </is>
       </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>波の峰の高さは気の状態を表します。
+峰が高いほど気滞が強く、低いほど気虚が強くなります。</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="17" customHeight="1">
       <c r="A401" s="3" t="inlineStr">
@@ -8543,6 +9428,11 @@
           <t>Blood</t>
         </is>
       </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>血</t>
+        </is>
+      </c>
     </row>
     <row r="402" ht="17" customHeight="1">
       <c r="A402" s="3" t="inlineStr">
@@ -8562,6 +9452,12 @@
 a thicker pulse line indicates greater blood stasis, while a thinner pulse line indicates greater blood deficiency.</t>
         </is>
       </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>波線の太さは血の状態を表します。
+太いほど瘀血が強く、細いほど血虚が強くなります。</t>
+        </is>
+      </c>
     </row>
     <row r="403" ht="17" customHeight="1">
       <c r="A403" s="3" t="inlineStr">
@@ -8579,6 +9475,11 @@
           <t>Dampness and Dryness</t>
         </is>
       </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>湿と燥</t>
+        </is>
+      </c>
     </row>
     <row r="404" ht="17" customHeight="1">
       <c r="A404" s="3" t="inlineStr">
@@ -8598,6 +9499,12 @@
 broader pulse width indicates greater Dampness, while narrower pulse width indicates greater Dryness.</t>
         </is>
       </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>波の幅は湿と燥の程度を表します。
+広いほど湿が強く、狭いほど燥が強くなります。</t>
+        </is>
+      </c>
     </row>
     <row r="405" ht="17" customHeight="1">
       <c r="A405" s="3" t="inlineStr">
@@ -8615,6 +9522,11 @@
           <t>Cold and Heat</t>
         </is>
       </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>寒と熱</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="17" customHeight="1">
       <c r="A406" s="3" t="inlineStr">
@@ -8634,6 +9546,12 @@
 higher pulse frequency indicates greater Heat, while lower pulse frequency indicates greater Cold.</t>
         </is>
       </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>一呼吸の間に指先を通る波の数が寒熱を表します。
+脈拍が多いほど熱、少ないほど寒が強くなります。</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="17" customHeight="1">
       <c r="A407" s="3" t="inlineStr">
@@ -8651,6 +9569,11 @@
           <t>Seeing Patients</t>
         </is>
       </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>診察</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="17" customHeight="1">
       <c r="A408" s="3" t="inlineStr">
@@ -8668,6 +9591,11 @@
           <t>During the day, see patients at the clinic. Check their pulse (F1) to identify the condition, consult the medical records (F3) for a formula, then diagnose and prescribe (F2).</t>
         </is>
       </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>昼は診療所で患者を迎え、脈診(F1)で病を調べ、診療記録(F3)を参考に処方を決め、診断と処方(F2)を行います。</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="17" customHeight="1">
       <c r="A409" s="3" t="inlineStr">
@@ -8685,6 +9613,11 @@
           <t>Pulse Diagnosis</t>
         </is>
       </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>脈診</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="17" customHeight="1">
       <c r="A410" s="3" t="inlineStr">
@@ -8702,6 +9635,11 @@
           <t>In the pulse window, hold Q, A or Z to show the right-hand pulse; hold W, S or X for the left-hand pulse.</t>
         </is>
       </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>脈診画面では Q・A・Z を押し続けると右手、W・S・X で左手の脈が表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="17" customHeight="1">
       <c r="A411" s="3" t="inlineStr">
@@ -8719,6 +9657,11 @@
           <t>Medical Records</t>
         </is>
       </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>診療記録</t>
+        </is>
+      </c>
     </row>
     <row r="412" ht="17" customHeight="1">
       <c r="A412" s="3" t="inlineStr">
@@ -8736,6 +9679,11 @@
           <t>Search the medical records by disease, formula or herb name, Chinese pinyin, or pinyin initials. Shortcuts: Conditions (1), Formulas (2), Herbs (3).</t>
         </is>
       </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>診療記録の検索欄では、病名・処方・薬材の漢字、ひらがな・カタカナ、ローマ字で検索できます。ショートカット：疾病(1)、処方(2)、薬材(3)。</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="17" customHeight="1">
       <c r="A413" s="3" t="inlineStr">
@@ -8753,6 +9701,11 @@
           <t>Diagnosis and Prescription</t>
         </is>
       </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>診断と処方</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="17" customHeight="1">
       <c r="A414" s="3" t="inlineStr">
@@ -8770,6 +9723,11 @@
           <t>In the diagnosis and prescription window, search by disease, formula or herb name, Chinese pinyin, or pinyin initials to filter entries.</t>
         </is>
       </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>診断と処方の検索欄では、病名・処方・薬材の漢字、ひらがな・カタカナ、ローマ字で項目を絞り込めます。</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="17" customHeight="1">
       <c r="A415" s="3" t="inlineStr">
@@ -8787,6 +9745,11 @@
           <t>Prescribing</t>
         </is>
       </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>処方</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="17" customHeight="1">
       <c r="A416" s="3" t="inlineStr">
@@ -8804,6 +9767,11 @@
           <t>Select a Chief, Deputy, Assistant or Envoy area, then left-click an herb to add it or right-click to reduce it. Right-click an herb already in the formula to remove it. Choose the dose per click. Shortcuts: Chief (1), Deputy (2), Assistant (3), Envoy (4); switch dose (~ or Tab).</t>
         </is>
       </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>君薬・臣薬・佐薬・使薬の欄を選び、薬材を左クリックして追加、右クリックして減量します。追加済みの薬材を欄内で右クリックすると削除できます。単位と用量を選ぶと一度に加える量が変わります。ショートカット：君(1)、臣(2)、佐(3)、使(4)、単位切り替え(~ / Tab)。</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="17" customHeight="1">
       <c r="A417" s="3" t="inlineStr">
@@ -8821,6 +9789,11 @@
           <t>Formulas</t>
         </is>
       </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>方剤</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="17" customHeight="1">
       <c r="A418" s="3" t="inlineStr">
@@ -8838,6 +9811,11 @@
           <t>Search for a formula to filter its herbs. After earning enough Miraculous Recovery ratings, a preset formula appears. Click it to fill in all of its herbs and doses automatically.</t>
         </is>
       </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>検索欄に処方名を入力すると、その処方に含まれる薬材を絞り込めます。同じ処方で「妙手回春」を一定回数達成すると定型処方が現れ、クリックすると薬材と用量が自動入力されます。</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="17" customHeight="1">
       <c r="A419" s="3" t="inlineStr">
@@ -8855,6 +9833,11 @@
           <t>Doctor</t>
         </is>
       </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>医 者</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="17" customHeight="1">
       <c r="A420" s="3" t="inlineStr">
@@ -8872,6 +9855,11 @@
           <t>Game Design</t>
         </is>
       </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>ゲームデザイン</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="17" customHeight="1">
       <c r="A421" s="3" t="inlineStr">
@@ -8889,6 +9877,11 @@
           <t>Li Qiaochen</t>
         </is>
       </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>李翹辰</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="17" customHeight="1">
       <c r="A422" s="3" t="inlineStr">
@@ -8906,6 +9899,11 @@
           <t>Programming</t>
         </is>
       </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>プログラミング</t>
+        </is>
+      </c>
     </row>
     <row r="423" ht="17" customHeight="1">
       <c r="A423" s="3" t="inlineStr">
@@ -8923,6 +9921,11 @@
           <t>Art</t>
         </is>
       </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>アート</t>
+        </is>
+      </c>
     </row>
     <row r="424" ht="17" customHeight="1">
       <c r="A424" s="3" t="inlineStr">
@@ -8940,6 +9943,11 @@
           <t>Music &amp; Sound</t>
         </is>
       </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>音 楽 ・ 効 果 音</t>
+        </is>
+      </c>
     </row>
     <row r="425" ht="17" customHeight="1">
       <c r="A425" s="3" t="inlineStr">
@@ -8957,6 +9965,11 @@
           <t>Music</t>
         </is>
       </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="17" customHeight="1">
       <c r="A426" s="3" t="inlineStr">
@@ -8974,6 +9987,11 @@
           <t>Sound Assets</t>
         </is>
       </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>効果音素材</t>
+        </is>
+      </c>
     </row>
     <row r="427" ht="17" customHeight="1">
       <c r="A427" s="3" t="inlineStr">
@@ -8991,6 +10009,11 @@
           <t>Special Thanks</t>
         </is>
       </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>特 別 な 感 謝</t>
+        </is>
+      </c>
     </row>
     <row r="428" ht="17" customHeight="1">
       <c r="A428" s="3" t="inlineStr">
@@ -9008,6 +10031,11 @@
           <t>Inspired by the work and ideas of</t>
         </is>
       </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>そして本作に着想と参考を与えてくださった</t>
+        </is>
+      </c>
     </row>
     <row r="429" ht="17" customHeight="1">
       <c r="A429" s="3" t="inlineStr">
@@ -9025,6 +10053,11 @@
           <t>Independent Game Developers</t>
         </is>
       </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>インディーゲーム制作者の皆様</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="17" customHeight="1">
       <c r="A430" s="3" t="inlineStr">
@@ -9042,6 +10075,11 @@
           <t>The End</t>
         </is>
       </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>終</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="17" customHeight="1">
       <c r="A431" s="3" t="inlineStr">
@@ -9059,6 +10097,11 @@
           <t>Thank You for Playing</t>
         </is>
       </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>ご遊戯ありがとうございました</t>
+        </is>
+      </c>
     </row>
     <row r="432" ht="17" customHeight="1">
       <c r="A432" s="3" t="inlineStr">
@@ -9076,6 +10119,11 @@
           <t>Compendium of Materia Medica</t>
         </is>
       </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>本草綱目</t>
+        </is>
+      </c>
     </row>
     <row r="433" ht="17" customHeight="1">
       <c r="A433" s="3" t="inlineStr">
@@ -9093,6 +10141,11 @@
           <t>Today's Finances</t>
         </is>
       </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>本日の収支</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="17" customHeight="1">
       <c r="A434" s="3" t="inlineStr">
@@ -9110,6 +10163,11 @@
           <t>Income</t>
         </is>
       </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>収入</t>
+        </is>
+      </c>
     </row>
     <row r="435" ht="17" customHeight="1">
       <c r="A435" s="3" t="inlineStr">
@@ -9127,6 +10185,11 @@
           <t>Consultation: %s</t>
         </is>
       </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>診察料：%s</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="17" customHeight="1">
       <c r="A436" s="3" t="inlineStr">
@@ -9144,6 +10207,11 @@
           <t>Net Herb Income: %s</t>
         </is>
       </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>薬材収入：%s</t>
+        </is>
+      </c>
     </row>
     <row r="437" ht="17" customHeight="1">
       <c r="A437" s="3" t="inlineStr">
@@ -9161,6 +10229,11 @@
           <t>Herb Sales: %s</t>
         </is>
       </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>薬材売上：%s</t>
+        </is>
+      </c>
     </row>
     <row r="438" ht="17" customHeight="1">
       <c r="A438" s="3" t="inlineStr">
@@ -9178,6 +10251,11 @@
           <t>Herb Profit (Legacy): %s</t>
         </is>
       </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>薬材の利益（旧帳簿）：%s</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="17" customHeight="1">
       <c r="A439" s="3" t="inlineStr">
@@ -9195,6 +10273,11 @@
           <t>Patient Gifts: %s</t>
         </is>
       </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>患者からの謝礼：%s</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="17" customHeight="1">
       <c r="A440" s="3" t="inlineStr">
@@ -9212,6 +10295,11 @@
           <t>Li Jianzhong's Salary: %s</t>
         </is>
       </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>李建中の俸禄：%s</t>
+        </is>
+      </c>
     </row>
     <row r="441" ht="17" customHeight="1">
       <c r="A441" s="3" t="inlineStr">
@@ -9229,6 +10317,11 @@
           <t>Li Yanwen's Income: %s</t>
         </is>
       </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>李言聞の収入：%s</t>
+        </is>
+      </c>
     </row>
     <row r="442" ht="17" customHeight="1">
       <c r="A442" s="3" t="inlineStr">
@@ -9246,6 +10339,11 @@
           <t>Land Rent: %s</t>
         </is>
       </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>地代：%s</t>
+        </is>
+      </c>
     </row>
     <row r="443" ht="17" customHeight="1">
       <c r="A443" s="3" t="inlineStr">
@@ -9263,6 +10361,11 @@
           <t>Total Income: %s</t>
         </is>
       </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>収入合計：%s</t>
+        </is>
+      </c>
     </row>
     <row r="444" ht="17" customHeight="1">
       <c r="A444" s="3" t="inlineStr">
@@ -9280,6 +10383,11 @@
           <t>Expenses</t>
         </is>
       </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
     </row>
     <row r="445" ht="17" customHeight="1">
       <c r="A445" s="3" t="inlineStr">
@@ -9297,6 +10405,11 @@
           <t>Herb Purchase Cost: %s</t>
         </is>
       </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>薬材の仕入れ：%s</t>
+        </is>
+      </c>
     </row>
     <row r="446" ht="17" customHeight="1">
       <c r="A446" s="3" t="inlineStr">
@@ -9314,6 +10427,11 @@
           <t>Failed Treatment Herbs (Legacy): %s</t>
         </is>
       </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>治療失敗時の薬材費（旧帳簿）：%s</t>
+        </is>
+      </c>
     </row>
     <row r="447" ht="17" customHeight="1">
       <c r="A447" s="3" t="inlineStr">
@@ -9331,6 +10449,11 @@
           <t>Chenpi &amp; Banxia Pay: %s</t>
         </is>
       </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>陳皮と半夏の給金：%s</t>
+        </is>
+      </c>
     </row>
     <row r="448" ht="17" customHeight="1">
       <c r="A448" s="3" t="inlineStr">
@@ -9348,6 +10471,11 @@
           <t>Food: %s</t>
         </is>
       </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>食費：%s</t>
+        </is>
+      </c>
     </row>
     <row r="449" ht="17" customHeight="1">
       <c r="A449" s="3" t="inlineStr">
@@ -9365,6 +10493,11 @@
           <t>Social Gifts: %s</t>
         </is>
       </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>贈答費：%s</t>
+        </is>
+      </c>
     </row>
     <row r="450" ht="17" customHeight="1">
       <c r="A450" s="3" t="inlineStr">
@@ -9382,6 +10515,11 @@
           <t>Medical Books: %s</t>
         </is>
       </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>医学書の購入：%s</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="17" customHeight="1">
       <c r="A451" s="3" t="inlineStr">
@@ -9399,6 +10537,11 @@
           <t>Coal: %s</t>
         </is>
       </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>石炭：%s</t>
+        </is>
+      </c>
     </row>
     <row r="452" ht="17" customHeight="1">
       <c r="A452" s="3" t="inlineStr">
@@ -9416,6 +10559,11 @@
           <t>Cloth &amp; Winter Clothes: %s</t>
         </is>
       </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>衣服と綿入れ：%s</t>
+        </is>
+      </c>
     </row>
     <row r="453" ht="17" customHeight="1">
       <c r="A453" s="3" t="inlineStr">
@@ -9433,6 +10581,11 @@
           <t>House Repairs: %s</t>
         </is>
       </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>家屋の修繕：%s</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="17" customHeight="1">
       <c r="A454" s="3" t="inlineStr">
@@ -9450,6 +10603,11 @@
           <t>Ancestral Rites: %s</t>
         </is>
       </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>墓参りと先祖供養：%s</t>
+        </is>
+      </c>
     </row>
     <row r="455" ht="17" customHeight="1">
       <c r="A455" s="3" t="inlineStr">
@@ -9467,6 +10625,11 @@
           <t>Spoiled Herbs: %s</t>
         </is>
       </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>薬材のカビ：%s</t>
+        </is>
+      </c>
     </row>
     <row r="456" ht="17" customHeight="1">
       <c r="A456" s="3" t="inlineStr">
@@ -9484,6 +10647,11 @@
           <t>Summer Tax: %s</t>
         </is>
       </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>夏の税：%s</t>
+        </is>
+      </c>
     </row>
     <row r="457" ht="17" customHeight="1">
       <c r="A457" s="3" t="inlineStr">
@@ -9501,6 +10669,11 @@
           <t>Autumn Tax: %s</t>
         </is>
       </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>秋の税：%s</t>
+        </is>
+      </c>
     </row>
     <row r="458" ht="17" customHeight="1">
       <c r="A458" s="3" t="inlineStr">
@@ -9518,6 +10691,11 @@
           <t>Total Expenses: %s</t>
         </is>
       </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>支出合計：%s</t>
+        </is>
+      </c>
     </row>
     <row r="459" ht="17" customHeight="1">
       <c r="A459" s="3" t="inlineStr">
@@ -9535,6 +10713,11 @@
           <t>Today's Change: %s</t>
         </is>
       </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>本日の増減：%s</t>
+        </is>
+      </c>
     </row>
     <row r="460" ht="17" customHeight="1">
       <c r="A460" s="3" t="inlineStr">
@@ -9552,6 +10735,11 @@
           <t>Essential Prescriptions Worth a Thousand Gold for Emergencies</t>
         </is>
       </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>備急千金要方</t>
+        </is>
+      </c>
     </row>
     <row r="461" ht="17" customHeight="1">
       <c r="A461" s="3" t="inlineStr">
@@ -9569,6 +10757,11 @@
           <t>Yellow Emperor's Inner Canon</t>
         </is>
       </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>黄帝内経</t>
+        </is>
+      </c>
     </row>
     <row r="462" ht="17" customHeight="1">
       <c r="A462" s="3" t="inlineStr">
@@ -9586,6 +10779,11 @@
           <t>Essentials from the Golden Cabinet</t>
         </is>
       </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>金匱要略</t>
+        </is>
+      </c>
     </row>
     <row r="463" ht="17" customHeight="1">
       <c r="A463" s="3" t="inlineStr">
@@ -9603,6 +10801,11 @@
           <t>Complete Works of Jingyue</t>
         </is>
       </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>景岳全書</t>
+        </is>
+      </c>
     </row>
     <row r="464" ht="17" customHeight="1">
       <c r="A464" s="3" t="inlineStr">
@@ -9620,6 +10823,11 @@
           <t>Formulas for Investigating Origins</t>
         </is>
       </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>究原方</t>
+        </is>
+      </c>
     </row>
     <row r="465" ht="17" customHeight="1">
       <c r="A465" s="3" t="inlineStr">
@@ -9637,6 +10845,11 @@
           <t>Secret Treasury of the Orchid Chamber</t>
         </is>
       </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>蘭室秘蔵</t>
+        </is>
+      </c>
     </row>
     <row r="466" ht="17" customHeight="1">
       <c r="A466" s="3" t="inlineStr">
@@ -9654,6 +10867,11 @@
           <t>Medical Talks from Liuzhou</t>
         </is>
       </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>柳州医話</t>
+        </is>
+      </c>
     </row>
     <row r="467" ht="17" customHeight="1">
       <c r="A467" s="3" t="inlineStr">
@@ -9671,6 +10889,11 @@
           <t>Proven Formulas for Universal Relief</t>
         </is>
       </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>普済本事方</t>
+        </is>
+      </c>
     </row>
     <row r="468" ht="17" customHeight="1">
       <c r="A468" s="3" t="inlineStr">
@@ -9688,6 +10911,11 @@
           <t>Renzhai's Direct Guide to Formulas and Medical Theory</t>
         </is>
       </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>仁斎直指方論</t>
+        </is>
+      </c>
     </row>
     <row r="469" ht="17" customHeight="1">
       <c r="A469" s="3" t="inlineStr">
@@ -9705,6 +10933,11 @@
           <t>Treatise on Cold Damage</t>
         </is>
       </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>傷寒論</t>
+        </is>
+      </c>
     </row>
     <row r="470" ht="17" customHeight="1">
       <c r="A470" s="3" t="inlineStr">
@@ -9722,6 +10955,11 @@
           <t>Divine Farmer's Classic of Materia Medica</t>
         </is>
       </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>神農本草経</t>
+        </is>
+      </c>
     </row>
     <row r="471" ht="17" customHeight="1">
       <c r="A471" s="3" t="inlineStr">
@@ -9739,6 +10977,11 @@
           <t>Formulary of the Taiping Imperial Pharmacy for the People's Welfare</t>
         </is>
       </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>太平恵民和剤局方</t>
+        </is>
+      </c>
     </row>
     <row r="472" ht="17" customHeight="1">
       <c r="A472" s="3" t="inlineStr">
@@ -9756,6 +10999,11 @@
           <t>Complete Collection of Proven and Miraculous Formulas from the Imperial Medical Academy</t>
         </is>
       </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>太医院経験奇効良方大全</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="17" customHeight="1">
       <c r="A473" s="3" t="inlineStr">
@@ -9773,6 +11021,11 @@
           <t>Wang's Formulas for Broad Relief</t>
         </is>
       </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>王氏博済方</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="17" customHeight="1">
       <c r="A474" s="3" t="inlineStr">
@@ -9790,6 +11043,11 @@
           <t>Systematic Differentiation of Warm Diseases</t>
         </is>
       </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>温病条弁</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="17" customHeight="1">
       <c r="A475" s="3" t="inlineStr">
@@ -9807,6 +11065,11 @@
           <t>Key to Therapeutics of Children's Diseases</t>
         </is>
       </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>小児薬証直訣</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="17" customHeight="1">
       <c r="A476" s="3" t="inlineStr">
@@ -9824,6 +11087,11 @@
           <t>Clinical Records</t>
         </is>
       </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>診療記録</t>
+        </is>
+      </c>
     </row>
     <row r="477" ht="17" customHeight="1">
       <c r="A477" s="3" t="inlineStr">
@@ -9841,6 +11109,11 @@
           <t>Yan's Formulas for Aiding Life</t>
         </is>
       </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>厳氏済生方</t>
+        </is>
+      </c>
     </row>
     <row r="478" ht="17" customHeight="1">
       <c r="A478" s="3" t="inlineStr">
@@ -9858,6 +11131,11 @@
           <t>Collected Explanations of Medical Formulas</t>
         </is>
       </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>医方集解</t>
+        </is>
+      </c>
     </row>
     <row r="479" ht="17" customHeight="1">
       <c r="A479" s="3" t="inlineStr">
@@ -9875,6 +11153,11 @@
           <t>Investigation of Medical Formulas</t>
         </is>
       </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>医方考</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="17" customHeight="1">
       <c r="A480" s="3" t="inlineStr">
@@ -9892,6 +11175,11 @@
           <t>Correction of Errors in Medical Classics</t>
         </is>
       </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>医林改錯</t>
+        </is>
+      </c>
     </row>
     <row r="481" ht="17" customHeight="1">
       <c r="A481" s="3" t="inlineStr">
@@ -9907,6 +11195,11 @@
       <c r="C481" s="2" t="inlineStr">
         <is>
           <t>Treatise on the Origins and Manifestations of Various Diseases</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>諸病源候論</t>
         </is>
       </c>
     </row>
@@ -37404,7 +38697,11 @@
           <t>Who could be knocking in the middle of the night?</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>こんな夜中に誰だ？　誰が戸を叩いている？</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -37444,7 +38741,11 @@
           <t>Ah! Good heavens!</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>うわあっ！　びっくりした！</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -37484,7 +38785,11 @@
           <t>What happened?</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>何があった？</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -37524,7 +38829,11 @@
           <t>Ah!</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>あっ！</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -37564,7 +38873,11 @@
           <t>By order of the Prince of Chu, you are requested at his residence.</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>楚王のご命令により、先生を王府へお連れします。</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -37604,7 +38917,11 @@
           <t>Is someone ill? Am I being called to treat a patient?</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>どなたか病気なのですか？　診療に行くのですか？</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -37644,7 +38961,11 @@
           <t>It is a matter of great importance. You will learn more when you arrive. The carriage is ready. Please leave at once.</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>重大な件です。行けば分かります。馬車は用意してありますので、すぐにお発ちください。</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -37662,7 +38983,11 @@
           <t>After a weary night on the road, Li Dongbi arrived at the Prince of Chu's residence.</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>一晩中の長旅を経て、李東璧は楚王府に到着した。</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -37702,7 +39027,11 @@
           <t>So you are the renowned Physician Li. You are much younger than I expected. I have asked you here because I need your help.</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>あなたが名医の李先生ですか。思ったよりずっとお若い。お呼びしたのは、私からお願いがあるからです。</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -37742,7 +39071,11 @@
           <t>My respects, Your Highness. How may I help you?</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>楚王殿下に拝謁いたします。私に何ができましょうか。</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -37782,7 +39115,11 @@
           <t>My son suddenly fell ill some days ago and has been confined to bed. He is listless and has no appetite. I have called several physicians and tried many prescriptions, but he has not improved. He grows thinner by the day. I fear what may happen if this continues…</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>息子が先日突然倒れ、床から起きられなくなった。気力も食欲もない。何人も医者を呼び、さまざまな処方を試したが良くならぬ。日に日に痩せて、このままでは取り返しがつかない……</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -37822,7 +39159,11 @@
           <t>I heard of your skill in Qizhou, Physician Li, and asked you here to treat my son.</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>蘄州の李先生は腕のよい医者だと聞き、息子の治療をお願いしたのです。</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -37862,7 +39203,11 @@
           <t>Cough, cough… Father…</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……父上……</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -37902,7 +39247,11 @@
           <t>He is my only son, Doctor. Please save him.</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>私にはこの子しかおりません。先生、どうか息子をお救いください。</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -37942,7 +39291,11 @@
           <t>Father, I feel much better.</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>父上、ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -37982,7 +39335,11 @@
           <t>Your son has spleen deficiency with an excess of dampness. If he takes the medicine as prescribed each day, he should recover well.</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>世子様は脾虚湿盛の証です。この処方の薬を毎日飲めば、大事には至りません。</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -38022,7 +39379,11 @@
           <t>You are Hua Tuo reborn! I cannot thank you enough. Please accept this thousand taels of silver as a token of gratitude for saving his life.</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>先生はまさに華佗の再来だ。感謝してもしきれぬ。この銀千両は気持ちばかりの謝礼です。命を救っていただき、ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -38062,7 +39423,11 @@
           <t>A thousand taels is far too much. I cannot accept it.</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>千両は多すぎます。いただけません。</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -38102,7 +39467,11 @@
           <t>Young master, that is a thousand taels of silver!</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>若旦那、銀千両ですよ！</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -38142,7 +39511,11 @@
           <t>Your son is of noble birth, but to me he is simply a patient in need of care. One tael of silver for the consultation will suffice, Your Highness.</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>世子様は尊いお方ですが、私にとっては治療を必要とする一人の患者です。診察料として銀一両だけいただきます。</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -38182,7 +39555,11 @@
           <t>…You are a man of rare integrity. Many scholars speak of virtue, yet few keep their heads when they see silver. The people are fortunate to have a doctor like you.</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>……先生の気骨には恐れ入った。日頃会う儒者は仁義を語るが、大金を前にして心を乱さぬ者は少ない。あなたのような医者がいるのは民の幸せだ。</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -38222,7 +39599,11 @@
           <t>I will remember what you have done. If there is ever anything I can do for you, you need only ask.</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>このご恩は忘れません。いつか力になれることがあれば、遠慮なくおっしゃってください。</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -38240,7 +39621,11 @@
           <t>Reputation +1000; received one tael of silver.</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>名声＋1000、収入：銀一両</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -38280,7 +39665,11 @@
           <t>Cough, cough… Ah…</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……うっ……</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -38320,7 +39709,11 @@
           <t>My son! What is happening to you?</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>息子よ、どうした！</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -38360,7 +39753,11 @@
           <t>Ah, well… Your Highness, please let me explain…</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>あの、その……王様、どうか話を聞いて……</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -38400,7 +39797,11 @@
           <t>Guards! Drag this damned charlatan out and execute him!</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>誰か！　この詐欺師を連れ出して斬れ！</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -38440,7 +39841,11 @@
           <t>Oh no! Aaaah!</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>まずい！　うわあああ！</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -38480,7 +39885,11 @@
           <t>May business prosper, Master Li. Heh, heh, heh.</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ご繁盛ですね、旦那。へへへ。</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -38520,7 +39929,11 @@
           <t>And you are…? (When did he come in…?)</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>失礼ですが、どなたですか？（いつの間に入ってきたんだ……）</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -38560,7 +39973,11 @@
           <t>I am Jia Quan, a medicinal herb merchant of some repute in Huguang Province. Heh, heh, heh.</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>薬材商の賈荃と申します。湖広では少し名の知れた商人ですよ。へへへ。</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -38600,7 +40017,11 @@
           <t>Of course I have heard of you. What brings you to my humble clinic today?</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>お名前はかねがね。今日は当院に何のご用ですか？</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -38640,7 +40061,11 @@
           <t>Well, I have come to discuss a profitable arrangement with the famous Physician Li.</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ええ、李先生にうまい商談を持ってきたのです。</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -38680,7 +40105,11 @@
           <t>Oh? I am listening.</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ほう？　詳しく聞かせてください。</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -38720,7 +40149,11 @@
           <t>I acquired a shipment of ginseng last month. I was hoping you could help me sell it through your clinic.</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>先月、人参を大量に仕入れましてね。先生の診療所で売っていただけませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -38760,7 +40193,11 @@
           <t>Most of my patients are ordinary people. We have little need for an expensive herb like ginseng.</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>うちに来る患者は普通の民が大半です。人参のような高価な薬材を使うことはあまりありません。</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -38800,7 +40237,11 @@
           <t>You are looking at it all wrong, Brother Li. Ginseng is a tonic. Every illness needs a tonic! Add a little even for a headache or a fever, and you will move plenty of it.</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>それは違いますよ。人参は補薬、病気には滋養が必要です。頭痛や熱程度の患者にも少し足せば、すぐに使い切れます。</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -38840,7 +40281,11 @@
           <t>How could I add herbs at random instead of prescribing for the patient's condition?</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>病に合わせて処方するのに、むやみに薬を加えられますか。</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -38880,7 +40325,11 @@
           <t>You would not be doing it for nothing. I will pay you one tael of silver for every jin of ginseng you sell. A fine arrangement, is it not?</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ただとは言いません。人参一斤につき銀一両の歩合を差し上げます。いい話でしょう？</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -38920,7 +40369,11 @@
           <t>I think you should leave. Chen Pi, show our guest out.</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>お帰りください。陳皮、お見送りを。</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -38960,7 +40413,11 @@
           <t>This way, Master Jia.</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>賈旦那、こちらへどうぞ。</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -39000,7 +40457,11 @@
           <t>Hmph. You do not know a good offer when you see one.</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ふん、融通の利かないやつだ。</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -39040,7 +40501,11 @@
           <t>My friend, it has been a while. I hope you are well.</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>友よ、元気にしていたか。</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -39080,7 +40545,11 @@
           <t>Captain Lei! It is good to see you again.</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>雷隊長、お久しぶりです。</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -39120,7 +40589,11 @@
           <t>My old trouble has flared up. I am afraid I must impose on you again.</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>また持病が出てしまってな。世話になるよ。</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -39160,7 +40633,11 @@
           <t>It is no trouble. Please, sit down.</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>お気になさらず。お掛けください。</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -39200,7 +40677,11 @@
           <t>Brother Lei, your liver yang is rising again. Along with taking the medicine, you must keep your temper in check and avoid stirring up liver fire.</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>雷兄、肝陽上亢の持病は、薬を飲むだけでなく、気持ちを落ち着けることも大切です。怒りで肝火を強めないようにしてください。</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -39240,7 +40721,11 @@
           <t>Ha! You saw right through me.</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>はは、見抜かれてしまったか。</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -39280,7 +40765,11 @@
           <t>Yesterday my men and I accompanied the prefecture's grain tax collectors. Those lackeys were heaping and kicking the measures so hard that I cursed them on the spot.</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>昨日、部下と徴税官を連れて年貢米を集めに行ったんだが、あの役人どもが升を蹴って米を巻き上げるやり方がひどくてな。思わずその場で怒鳴ったよ。</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -39320,7 +40809,11 @@
           <t>What do you mean by “heaping and kicking the measures”?</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>升を蹴るとは、どういうことですか？</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -39360,7 +40853,11 @@
           <t>When common folk pay their grain tax, they pour grain into a measuring vessel until it forms a mound above the rim. That is the “heaping.”</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>民が年貢を納めるとき、升の縁より高く山になるまで米を盛らせる。それを「尖り盛り」と呼ぶんだ。</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -39400,7 +40897,11 @@
           <t>Then an official kicks the vessel. The grain that spills out does not count toward the tax. Those lackeys pocket it instead.</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>役人が升を蹴ってこぼした米は納税分に数えられず、そのまま役人の懐に入る。</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -39440,7 +40941,11 @@
           <t>That is outrageous…</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>そんな……ひどすぎます……</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -39480,7 +40985,11 @@
           <t>It has become an unwritten rule everywhere, but yesterday those scoundrels kicked so hard it was open robbery.</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>今ではどこでも暗黙の慣習だが、昨日の連中は蹴りすぎだ。あれではただの強奪だよ。</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -39520,7 +41029,11 @@
           <t>Life is getting harder for the people. I will prepare your medicine, Brother Lei. Please wait here.</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>民の暮らしは苦しくなる一方ですね。薬を取ってきますので、雷兄は少々お待ちください。</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -39560,7 +41073,11 @@
           <t>Thank you, my friend.</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>すまないな。</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -39600,7 +41117,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -39640,7 +41161,11 @@
           <t>Doctor! Doctor, help! My master is dying!</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>先生！　先生！　助けてください！　うちの旦那様が危ないんです！</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -39680,7 +41205,11 @@
           <t>What happened?</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>何があったんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -39720,7 +41249,11 @@
           <t>He was drinking at the Drunken Immortal Tavern when he suddenly began speaking nonsense. He no longer knows what is going on.</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>旦那様が酔仙楼で飲んでいたところ、突然訳の分からないことを言い始め、意識もはっきりしなくなりました。</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -39760,7 +41293,11 @@
           <t>I am the richest man in Huguang! Ha, ha, ha! Let us see who dares look down on me now!</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>私は湖広一の大金持ちだ！　ははは！　もう誰にも見下されないぞ！</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -39800,7 +41337,11 @@
           <t>Is that Master Jia? Bring him over here, quickly.</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>賈旦那じゃないか。早くここへ運んで。</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -39840,7 +41381,11 @@
           <t>I have a grand deal, the greatest deal of all! Urgh…</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>大きな商売がある、ものすごい商売だ！　うっ……</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -39880,7 +41425,11 @@
           <t>Oh, my head is spinning.</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>ああ、頭がくらくらする……</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -39920,7 +41469,11 @@
           <t>Master Jia's confusion was caused by phlegm fire disturbing the heart. Strong swings in mood and too much wine made it worse. He must avoid alcohol, rest and take his medicine regularly.</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>賈旦那の意識の乱れは、痰火が心を乱したためです。激しい感情の起伏と飲みすぎで悪化しました。酒を断って静養し、薬を時間どおりに飲んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -39960,7 +41513,11 @@
           <t>Thank you so much, Doctor. Come, Master, let us go home.</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>先生、本当にありがとうございます。旦那様、帰りましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -40000,7 +41557,11 @@
           <t>Why did Master Jia suddenly fall ill? I bet that crooked merchant is getting what he deserves.</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>賈旦那はどうして急に倒れたんでしょう？　悪事を働いた報いじゃありませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -40040,7 +41601,11 @@
           <t>Do not say that. Clean up where he was sick. We still have patients to see.</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>余計なことを言わず、吐いた場所を片づけて。まだ患者を診なくては。</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -40080,7 +41645,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -40120,7 +41689,11 @@
           <t>Doctor Li, the prefect requests your presence at the government office.</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>李先生、知州様が州役所で相談したいことがあるそうです。</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -40160,7 +41733,11 @@
           <t>Understood. I will go at once.</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>分かりました。すぐ参ります。</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -40200,7 +41777,11 @@
           <t>I have summoned you all today to convey an order from the court.</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>今日皆を集めたのは、朝廷から命が下ったためだ。</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -40240,7 +41821,11 @@
           <t>Flooding has struck Chun'an and Jiande counties in Zhejiang. Disease has already appeared in nearby districts. To prevent an epidemic from spreading, the court has ordered surrounding prefectures to distribute medicinal supplies for disaster relief.</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>浙江省の淳安県と建徳県で突然洪水が起き、周辺では疫病も発生している。感染の拡大を防ぐため、朝廷は近隣の州府に救済用の薬材を配るよう命じた。</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -40280,7 +41865,11 @@
           <t>The supplies were procured yesterday. This time, private clinics and apothecaries must help the public dispensary treat patients and distribute medicine.</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>薬材の調達は昨日終わった。今回は恵民薬局だけでなく、各診療所と薬舗にも患者の診療と薬材の配布に協力してもらう。</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -40320,7 +41909,11 @@
           <t>You will sign the register at the storehouse shortly. Starting tomorrow, the authorities will post notices telling residents where to collect medicine nearby.</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>皆にはこのあと倉庫で署名と登録をしてもらう。明日から役所が告示を出し、民に近くで薬を受け取るよう知らせる。</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -40360,7 +41953,11 @@
           <t>Line up here to sign, one at a time. Write down your delivery address and we will send someone with the supplies.</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>皆さん、こちらで署名してください。一列に並んで順番に。届け先の住所を書けば、担当者が運びます。</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -40400,7 +41997,11 @@
           <t>Doctor Li, please sign here. Our superiors are pressing us to dispatch everything quickly.</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>李先生、こちらに署名を。上から急かされており、すぐに発送しなければなりません。</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -40440,7 +42041,11 @@
           <t>Yes, of course.</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>はい、分かりました。</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -40480,7 +42085,11 @@
           <t>Dongbi, you are back. Why did they call you away so early?</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>東璧、おかえり。朝早くから呼ばれて、何の用だったの？</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -40520,7 +42129,11 @@
           <t>The court has sent medicine for disaster relief. This time, our clinics and apothecaries must help distribute it alongside the public dispensary.</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>朝廷が救済用の薬材を配るそうだ。今回は恵民薬局だけでなく、うちのような診療所も配布を手伝う。</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -40560,7 +42173,11 @@
           <t>I have seen many displaced people in the east of town on my way to the market. A great disaster is often followed by an epidemic. The relief could not have come sooner.</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>最近、市場へ買い物に行くと城の東で避難民をよく見かけます。大災害のあとには疫病が起こりやすいですし、朝廷の救済はちょうどよかったですね。</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -40600,7 +42217,11 @@
           <t>Chen Pi, come help me clear the storeroom out back. The medicine will arrive soon, and we need to make room.</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>陳皮、裏の倉庫を片づけに行こう。もうすぐ薬材が届くから、急いで場所を空けないと。</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -40640,7 +42261,11 @@
           <t>Right away.</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>はい！</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">

--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -23480,6 +23480,16 @@
 [Standard formula] Ephedra Decoction</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>風寒表実証
+【病機】寒邪が体表を塞ぎ、皮膚のきめが閉じ、衛陽の働きが妨げられる。
+【症状】悪寒と発熱、頭や体の痛み、汗が出ず喘ぐ。
+【脈象】
+浮脈（表）：波の峰が高く、脈拍が少ない。
+【標準処方】麻黄湯</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -23529,6 +23539,16 @@
 [Standard formula] Cinnamon Twig Decoction</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>風寒表虚証
+【病機】風寒が体表を侵し、衛気が外を守れず、営陰が外へ漏れる。
+【症状】風を嫌う発熱、頭痛と透明な鼻水、発汗。
+【脈象】
+浮脈（表）：波の峰が低く、脈拍が少ない。
+【標準処方】桂枝湯</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -23578,6 +23598,16 @@
 [Standard formula] Honeysuckle and Forsythia Powder</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>風熱表証
+【病機】風熱の邪が肺と衛を侵し、衛気の調和が乱れて、肺の清粛の働きが失われる。
+【症状】高い熱、喉の発赤と腫れ、黄色く粘る痰と鼻水。
+【脈象】
+浮脈（表）：脈拍が多い。
+【標準処方】銀翹散</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -23627,6 +23657,16 @@
 [Standard formula] Mulberry Leaf and Apricot Kernel Decoction</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>温燥証
+【病機】初秋の乾燥と熱が肺と衛を侵し、肺の潤いが失われる。
+【症状】発熱して風を嫌い、口や鼻が乾く。喉の乾きと渇き、痰の少ない空咳、黄色く粘る痰や鼻水。
+【脈象】
+浮脈（表）：脈拍が多く、波の幅が狭い。
+【標準処方】桑杏湯</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -23676,6 +23716,16 @@
 [Standard formula] Apricot Kernel and Perilla Leaf Powder</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>涼燥証
+【病機】晩秋の寒さが強まるころ、乾燥の邪が風寒とともに肺と衛を侵す。
+【症状】悪寒と発熱、鼻づまりと透明な鼻水、痰の少ない空咳、喉と唇や皮膚の乾燥。
+【脈象】
+浮脈（表）：脈拍が少なく、波の幅が狭い。
+【標準処方】杏蘇散</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -23725,6 +23775,16 @@
 [Standard formula] Jade Windscreen Powder</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>衛気虚
+【病機】もともとの虚弱や長患いで肺気を消耗し、衛気が体表を守れない。皮膚のきめが緩み、防御と保持の働きが弱まる。
+【症状】自汗：動かなくても汗をかき、動くと増す。風邪をひきやすい：風や寒さを嫌い、少し冷えるだけで風邪をひく。顔色が白く、息切れと倦怠感があり、話すのもおっくう。肌のきめが緩く、よく風を嫌う。
+【脈象】
+浮脈（表）：波の峰が低い。
+【標準処方】玉屏風散</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -23774,6 +23834,16 @@
 [Standard formula] Aconite Decoction</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>痛痺（寒痺）
+【病機】風・寒・湿の邪が経絡を塞ぎ、とくに寒邪が強い。寒は収縮と停滞をもたらし、気血が通らなくなると強い痛みが生じる。
+【症状】手足の関節が強く痛み、痛む場所は変わらない。冷えると悪化し、温めると和らぐ。関節を曲げ伸ばししにくく、患部が冷える。
+【脈象】
+浮脈（表）：波の峰がやや高く、脈拍は著しく少なく、波の幅はやや広い。
+【標準処方】烏頭湯</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -23821,6 +23891,16 @@
 [Pulse]
 Floating pulse (Exterior): slightly increased amplitude, higher pulse frequency, slightly broader pulse width
 [Standard formula] White Tiger Decoction with Cinnamon Twig</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>熱痺
+【病機】風湿熱が経絡と関節を侵す。または風寒湿が体内で熱に変わり、気血が停滞して経絡を塞ぐ。
+【症状】関節が赤く腫れて熱を持ち、強く痛む。触ると熱く、押すと痛むが、冷やすと少し楽になる。発熱、口の渇き、いらだち、関節を曲げ伸ばししにくい。
+【脈象】
+浮脈（表）：波の峰がやや高く、脈拍が多く、波の幅がやや広い。
+【標準処方】白虎桂枝湯</t>
         </is>
       </c>
     </row>
@@ -23874,6 +23954,16 @@
 [Standard formula] Coix Seed Decoction</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>着痺（湿痺）
+【病機】風寒湿が侵入し、とくに湿邪が強い。湿の重さと粘りによって経絡が塞がれ、気の流れが妨げられる。
+【症状】関節が重く鈍く痛み、包まれたようにだるい。痛む場所は一定で、皮膚のしびれと手足の重だるさがある。関節が腫れて動かしにくく、雨や湿気で悪化する。
+【脈象】
+浮脈（表）：波の峰がやや高く、脈拍はやや少なく、波の幅が著しく広い。
+【標準処方】薏苡仁湯</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -23923,6 +24013,16 @@
 [Standard formula] Saposhnikovia Decoction</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>行痺（風痺）
+【病機】風寒湿が経絡を侵し、とくに風邪が強い。風の性質により、症状があちこちへ移り変わる。
+【症状】手足の関節が鈍く痛み、痛む場所が定まらず全身を移動する。
+【脈象】
+浮脈（表）：波の峰が著しく高く、脈拍はやや少なく、波の幅がやや広い。
+【標準処方】防風湯</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -23972,6 +24072,16 @@
 [Standard formula] Ephedra, Apricot Kernel, Gypsum and Licorice Decoction</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>肺熱壅盛
+【病機】熱邪が肺にこもり、肺の宣発と粛降が働かず、気の流れが塞がれて逆上する。
+【症状】激しい咳と呼吸、息苦しさと胸の圧迫感。黄色く粘り、出しにくい痰。発熱、口の渇き、喉の痛み。鼻翼が大きく動き、便は乾きがちで尿は黄色い。
+【脈象】
+右寸（肺）：脈拍が多い。
+【標準処方】麻杏石甘湯</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -24021,6 +24131,16 @@
 [Standard formula] Lung-Tonifying Decoction</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>肺気虚
+【病機】肺気が不足し、宣発と粛降の力が弱く、体表を守る衛気も不足する。
+【症状】力のない咳と喘ぎ、息切れ、話すのがおっくうで、動くと悪化する。声は小さく疲れやすい。自汗、風を嫌う、風邪をひきやすい。痰は透明で少量。
+【脈象】
+右寸（肺）：波の峰が低い。
+【標準処方】補肺湯</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
@@ -24070,6 +24190,16 @@
 [Standard formula] Two-Cured Decoction</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>痰湿阻肺
+【病機】脾の運化が低下して痰湿が生じ、肺に上って滞り、肺の宣発と粛降が失われる。
+【症状】咳が出て痰が多く、白く粘る痰を大量に吐きやすい。胸の圧迫感、喘ぎ、喉の痰音。手足が重だるく、口は淡く渇かない。
+【脈象】
+右寸（肺）：波の幅が広い。
+【標準処方】二陳湯</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -24119,6 +24249,16 @@
 [Standard formula] Adenophora and Ophiopogon Decoction</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>肺陰虚
+【病機】肺陰が不足して虚熱が生じ、肺の潤いと清粛の働きが失われる。
+【症状】痰のない空咳、または少量で粘り出しにくい痰。喉や口の乾燥、声がれ。午後からの熱感、寝汗、手足のほてり。頬が赤く、体が痩せる。
+【脈象】
+右寸（肺）：波線が細く、脈拍が多く、波の幅が狭い。
+【標準処方】沙参麦冬湯</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
@@ -24166,6 +24306,16 @@
 [Pulse]
 Right cun (Lung): higher pulse frequency, broader pulse width
 [Standard formula] Clear Qi and Transform Phlegm Pill</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>痰熱壅肺
+【病機】熱邪が内に入り、津液を焼いて痰を生む。痰と熱が結びついて肺気を塞ぎ、肺の宣発と粛降が失われる。
+【症状】咳と喘ぎがあり、黄色く粘る痰が多くて出しにくい。胸の圧迫感と痛み、重い場合は鼻翼が大きく動く。発熱、口の渇き、いらだち、便秘、黄色い尿。
+【脈象】
+右寸（肺）：脈拍が多く、波の幅が広い。
+【標準処方】清気化痰丸</t>
         </is>
       </c>
     </row>
@@ -24219,6 +24369,17 @@
 [Standard formula] Great Azure Dragon Decoction</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>表寒裏熱
+【病機】寒邪が体表を塞ぐ一方、体内にはこもった熱があり、寒と熱が混在する。
+【症状】寒気がして汗が出ず、口や喉が乾いて痛む。全身が痛んで寒がる一方、熱っぽくいらだつ。
+【脈象】
+浮脈（表）：脈拍が少ない。
+右寸（肺）：脈拍が多い。
+【標準処方】大青竜湯</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
@@ -24270,6 +24431,17 @@
 [Standard formula] Minor Azure Dragon Decoction</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>表寒裏飲
+【病機】外から風寒を受け、寒邪が体表を塞ぐ。体内には水飲が肺に潜み、内外の寒が重なって肺気を妨げる。
+【症状】悪寒と発熱、咳と喘ぎ。透明で薄い痰が多く、胸が重苦しく、顔がむくむ。
+【脈象】
+浮脈（表）：脈拍が少ない。
+右寸（肺）：波の幅が広い。
+【標準処方】小青竜湯</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -24319,6 +24491,16 @@
 [Standard formula] Four Gentlemen Decoction</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>脾気虚
+【病機】食生活や疲労、長患いによって脾が弱り、中気が不足して、運化がうまく働かない。
+【症状】食欲が乏しく、みぞおちや腹が張り、食後に悪化する。疲れやすく、息切れして話すのがおっくう。顔色が黄色く、痩せるかむくむ。便は柔らかい。
+【脈象】
+右関（脾）：波の峰が低い。
+【標準処方】四君子湯</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -24368,6 +24550,16 @@
 [Standard formula] Calm the Stomach Powder</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>湿盛困脾
+【病機】外から湿邪を受けるか、冷たい物や脂っこい甘味を好み、湿が停滞する。脾陽が妨げられ運化が低下した実証。
+【症状】みぞおちや腹がつかえ、食欲がない。吐き気、口の粘つき、口が淡く渇かない。頭と体が重く、手足がだるく眠い。便が柔らかく、すっきり出ない。
+【脈象】
+右関（脾）：波の幅が広い。
+【標準処方】平胃散</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -24417,6 +24609,16 @@
 [Standard formula] Regulate the Middle Pill</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>脾陽虚
+【病機】脾気の不足が長く続き、脾陽が衰えて内側に虚寒が生じ、消化と運化が弱まる。
+【症状】食欲が乏しく、腹が冷えて痛み、温めたり押したりすると楽になる。水っぽい便、未消化の便。寒がりで手足が冷え、疲れやすい。口は渇かず、顔色が白いか黄色い。むくみや薄い帯下が見られることもある。
+【脈象】
+右関（脾）：波の峰が低く、脈拍が少なく、波の幅が広い。
+【標準処方】理中丸</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -24464,6 +24666,16 @@
 [Pulse]
 Right guan (Spleen): decreased amplitude, broader pulse width
 [Standard formula] Ginseng, Poria and Atractylodes Powder</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>脾虚湿盛
+【病機】もともと脾気が弱く、運化が低下して体内に水湿が生じ、濁った湿が滞る。
+【症状】食欲がなく、みぞおちと腹が張り、食後に悪化する。疲労と息切れ、手足の重だるさ。柔らかい便や下痢、粘ついてすっきり出ない。顔色が黄色く、むくみや水っぽい帯下を伴うこともある。
+【脈象】
+右関（脾）：波の峰が低く、波の幅が広い。
+【標準処方】参苓白朮散</t>
         </is>
       </c>
     </row>
@@ -24517,6 +24729,17 @@
 [Standard formula] Patchouli Qi-Rectifying Powder</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>外感風寒・内傷湿滞
+【病機】外から受けた風寒が体表を塞ぎ、飲食などによる湿が中焦に滞る。表には風寒、裏には湿滞がある。
+【症状】風寒の症状：悪寒、発熱、頭痛、体の重さ、無汗、透明な鼻水。湿滞の症状：胸とみぞおちの張り、腹痛、吐き気、嘔吐、下痢。寒気と熱に加えて嘔吐や下痢、体の重さが見られる。
+【脈象】
+浮脈（表）：脈拍が少ない。
+右関（脾）：波の幅が広い。
+【標準処方】藿香正気散</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -24566,6 +24789,16 @@
 [Standard formula] Chinese Angelica Decoction for Frigid Extremities</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>寒凝心脈
+【病機】もともと陽が不足し、陰寒が凝り滞る。寒邪が心脈を塞ぎ、胸の陽気が弱まって心脈が収縮し、強く痛む。
+【症状】突然の激しい胸痛。寒さで悪化し、温めると和らぐ。胸の圧迫感、息切れ、動悸。寒がりで手足が冷え、顔色が白く、唇や爪が紫がかる。
+【脈象】
+左寸（心）：脈拍が少ない。
+【標準処方】当帰四逆湯</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -24615,6 +24848,16 @@
 [Standard formula] Guide Out the Red Powder</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>心火亢盛
+【病機】心火が内で燃え、熱が心神を乱し、脈絡を傷め、小腸にも及ぶ。
+【症状】胸のほてり、動悸と不眠、いらだち。口内炎、舌先の赤みと痛み。口の渇きと苦味、顔や目の赤み。尿は少なく赤く、排尿時に熱感や痛みがある。
+【脈象】
+左寸（心）：脈拍が多い。
+【標準処方】導赤散</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
@@ -24664,6 +24907,16 @@
 [Standard formula] Scour Phlegm Decoction</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>痰迷心竅
+【病機】痰湿が心竅を覆って意識を乱す。情緒の停滞や脾の運化低下で痰濁が生じ、心神を妨げる。
+【症状】反応が鈍く、気分が沈み、表情が乏しい。独り言や異常な振る舞い、意識の混濁。喉の痰音、胸の圧迫感と多量の痰。重い場合は突然倒れて意識を失う。
+【脈象】
+左寸（心）：波の幅が広い。
+【標準処方】滌痰湯</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
@@ -24713,6 +24966,16 @@
 [Standard formula] Nourish the Heart Decoction</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>心気虚
+【病機】心気が不足し、血を動かす力が弱く、心神への滋養が足りない。
+【症状】動悸があり、動くと悪化する。息切れ、胸苦しさ、疲労。自然に汗が出て、顔色が白い。
+【脈象】
+左寸（心）：波の峰が低い。
+【標準処方】養心湯</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
@@ -24762,6 +25025,16 @@
 [Standard formula] Drive Out Stasis in the Mansion of Blood Decoction</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>心脈瘀阻
+【病機】瘀血が心脈を塞ぎ、気血が通らず、心が十分に養われないため痛みが生じる。
+【症状】胸や心臓の辺りが痛み、動悸、胸苦しさ、息切れがある。横になれないほど喘ぐこともある。顔色は暗く、唇や爪が紫がかる。
+【脈象】
+左寸（心）：波線が太い。
+【標準処方】血府逐瘀湯</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -24811,6 +25084,16 @@
 [Standard formula] Heavenly Emperor's Heart-Tonifying Elixir</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>心陰虚
+【病機】心陰が不足し、心神が養われず、虚熱が内で乱す。
+【症状】動悸と不安、いらだち、不眠、夢が多く目覚めやすい。手足のほてり、午後からの熱感、寝汗。口や喉の乾燥、頬の赤み。
+【脈象】
+左寸（心）：波線が細く、脈拍が多く、波の幅が狭い。
+【標準処方】天王補心丹</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -24860,6 +25143,16 @@
 [Standard formula] Cinnamon Twig and Licorice Decoction</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>心陽虚
+【病機】心陽が不足し、温めて血を動かす力が弱く、内側に虚寒が生じる。
+【症状】動悸と不安、胸の圧迫感、息切れ。寒さで悪化し、手足が冷える。顔色が白く、疲れやすく、自然に汗が出る。
+【脈象】
+左寸（心）：波の峰が低く、脈拍が少ない。
+【標準処方】桂枝甘草湯</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -24907,6 +25200,16 @@
 [Pulse]
 Left cun (Heart): higher pulse frequency, broader pulse width
 [Standard formula] Coptis Warm-Gallbladder Decoction</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>痰火擾心
+【病機】痰濁が停滞して熱となり、痰と火が結びついて心神を乱す。
+【症状】いらだって眠れず、落ち着きがなく怒りやすい。悪夢や驚き、重いときは支離滅裂な言葉や不安定な感情。胸のつかえ、口の苦味、黄色く粘る痰が多い。
+【脈象】
+左寸（心）：脈拍が多く、波の幅が広い。
+【標準処方】黄連温胆湯</t>
         </is>
       </c>
     </row>
@@ -24960,6 +25263,17 @@
 [Standard formula] Restore the Spleen Decoction</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>心脾両虚
+【病機】考えすぎや疲労、長患い、失血などで脾気が弱り、気血が十分に作られず、心血が不足して心神を養えない。気血両虚の虚証。
+【症状】動悸、不眠、多夢、物忘れ、めまい。食欲不振、腹の張り、柔らかい便、疲労。顔色が黄色いか白く、手足がだるい。女性では月経量が少なく色が薄い、または出血が長引く。
+【脈象】
+左寸（心）：波線が細い。
+右関（脾）：波の峰が低い。
+【標準処方】帰脾湯</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
@@ -25009,6 +25323,16 @@
 [Standard formula] Gentian Decoction to Drain the Liver</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>肝火上炎
+【病機】肝気の鬱滞が火に変わるか、激怒で肝を傷め、肝火が強まって気と熱が上昇する実熱証。
+【症状】頭の張る痛みとめまい、顔や目の赤み、怒りっぽさ。口の苦味と乾燥、耳鳴りや聞こえづらさ、脇腹の熱い痛み。不眠や多夢、重い場合は激しい興奮。吐血や鼻血。
+【脈象】
+左関（肝）：脈拍が多い。
+【標準処方】竜胆瀉肝湯</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
@@ -25058,6 +25382,16 @@
 [Standard formula] Warm the Liver Decoction</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>寒滞肝脈
+【病機】外から寒邪を受け、肝経に凝り滞る。肝脈が収縮し、気血が滞って陽気が妨げられる実寒証。
+【症状】下腹部や精巣の冷える痛み、鼠径部の痛み。頭頂部の頭痛、寒がりで温かさを好み、温めると楽になり冷えると悪化する。手足がひどく冷え、顔色が青白い。
+【脈象】
+左関（肝）：脈拍が少ない。
+【標準処方】暖肝煎</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
@@ -25107,6 +25441,16 @@
 [Standard formula] Bupleurum Liver-Soothing Powder</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>肝気鬱結
+【病機】思いどおりにならないことが続き、肝の疏泄が乱れ、気と経脈の流れが滞る。
+【症状】胸や脇、乳房、下腹部に移動する張った痛み。気分が沈み、怒りやすく、ため息が多い。喉の異物感、胸苦しさ、げっぷ。女性では月経不順や月経痛。
+【脈象】
+左関（肝）：波の峰が高い。
+【標準処方】柴胡疏肝散</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
@@ -25156,6 +25500,16 @@
 [Standard formula] Four-Substance Decoction</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>肝血虚
+【病機】肝血が不足し、筋や経脈、目、爪、心神が十分に養われない。
+【症状】めまい、視力の低下とかすみ目。爪が乾いてもろく、手足のしびれや筋のひきつれ。顔色や唇、舌の色が薄い。女性では月経量が少なく色が薄い、重い場合は無月経。不眠、多夢、驚きやすさ。
+【脈象】
+左関（肝）：波線が細い。
+【標準処方】四物湯</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
@@ -25205,6 +25559,16 @@
 [Standard formula] Drive Out Blood Stasis Below the Diaphragm Decoction</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>肝血瘀滞
+【病機】肝の疏泄が乱れ、血が滞って瘀血が肝の脈絡を塞ぐ。
+【症状】皮膚が乾いてざらつき、全身にあざや細い赤い筋が見える。脇腹が刺すように痛んで張り、気分が沈み、怒ると痛みが増す。
+【脈象】
+左関（肝）：波線が太い。
+【標準処方】膈下逐瘀湯</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -25254,6 +25618,16 @@
 [Standard formula] Linking Decoction</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>肝陰虚
+【病機】情緒の乱れが熱に変わるか、長患いで消耗し、肝陰が不足する。虚熱が生じ、頭や目、筋脈が十分に養われない。
+【症状】めまい、耳鳴り、目の乾きとかすみ。脇腹のかすかな熱い痛み、手足のほてり。午後からの熱感、寝汗、口と喉の乾燥、顔のほてり。手足がぴくつき、筋がひきつる。
+【脈象】
+左関（肝）：波線が細く、脈拍が多く、波の幅が狭い。
+【標準処方】一貫煎</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
@@ -25301,6 +25675,16 @@
 [Pulse]
 Left guan (Liver): increased amplitude, higher pulse frequency
 [Standard formula] Uncaria Powder</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>肝陽上亢
+【病機】肝と腎の陰が不足し、陽を抑えられず、肝陽が過度に上昇して頭と目を乱す。根本は虚、現れは実。
+【症状】めまいと耳鳴り、頭や目の張る痛み、顔と目の赤み。いらだち、不眠、多夢、腰や膝のだるさ。頭が重く足元がふらつく。
+【脈象】
+左関（肝）：波の峰が高く、脈拍が多い。
+【標準処方】釣藤散</t>
         </is>
       </c>
     </row>
@@ -25354,6 +25738,17 @@
 [Standard formula] Free and Easy Wanderer Powder</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>肝脾不和（肝鬱脾虚）
+【病機】情緒の滞りで肝気が鬱結し、脾の働きを妨げる。脾も弱まり、肝気の影響を受けやすくなる。
+【症状】胸と脇が張って痛み、ため息が多く、気分が沈んで怒りやすい。みぞおちと腹の張り、げっぷ、食欲不振。腹痛と下痢があり、排便後に痛みが和らぐ。腹が鳴り、ガスが多い。
+【脈象】
+左関（肝）：波の峰が高い。
+右関（脾）：波の峰が低い。
+【標準処方】逍遥散</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -25405,6 +25800,17 @@
 [Standard formula] Ginseng and Gecko Powder</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>腎不納気
+【病機】長く続く咳と喘ぎ、高齢や過労で腎気が不足し、肺から下りる気を腎が受け止められない。虚証の喘ぎで、肺と腎がともに弱い。
+【症状】喘ぎが長引き、吐く息に比べ吸う息が浅く、動くと悪化する。息切れ、腰や膝のだるさ、疲労。自然に汗が出て、声が小さいこともある。
+【脈象】
+右寸（肺）：波の峰が低い。
+右尺（腎陽）：波の峰が低い。
+【標準処方】人参蛤蚧散</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
@@ -25456,6 +25862,17 @@
 [Standard formula] Six-Ingredient Rehmannia Pill</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>腎陰虚
+【病機】長患いや房事の過度、温燥の薬の使いすぎなどで腎陰が不足し、虚熱が生じ、滋養が足りなくなる。
+【症状】腰や膝のだるい痛み、めまい、耳鳴り、物忘れ。午後からの熱感、寝汗、手足のほてり、口と喉の乾燥。男性では遺精や早漏、女性では月経量の減少や無月経、不正出血。痩せ、不眠、多夢。
+【脈象】
+右尺（腎陽）：脈拍が多い。
+左尺（腎陰）：波線が細く、波の幅が狭い。
+【標準処方】六味地黄丸</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
@@ -25505,6 +25922,17 @@
 Right chi (Kidney Yang): decreased amplitude, lower pulse frequency
 Left chi (Kidney Yin): broader pulse width
 [Standard formula] Kidney Qi Pill from the Golden Cabinet</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>腎陽虚
+【病機】高齢や長患い、房事による消耗で腎陽が衰え、体を温めて水を巡らせる働きが低下する。
+【症状】腰や膝が冷えて痛み、力が入らない。特に下半身が冷える。元気がなく、顔色が白いか暗い。薄い尿が多く、夜間頻尿や尿漏れ。男性では勃起不全や早漏、女性では冷えによる不妊や水っぽい帯下。長引く下痢や未消化の便、夜明け前の下痢。
+【脈象】
+右尺（腎陽）：波の峰が低く、脈拍が少ない。
+左尺（腎陰）：波の幅が広い。
+【標準処方】金匱腎気丸</t>
         </is>
       </c>
     </row>
@@ -25560,6 +25988,18 @@
 [Standard formula] True Warrior Decoction</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>腎虚水泛
+【病機】腎陽が衰えて水の代謝ができず、水湿が体内に停滞して皮膚にあふれる。
+【症状】全身がむくみ、腰から下が特に腫れて、押すとへこんだまま戻りにくい。腰や膝が冷えて痛み、手足も冷える。尿量が少なく、排尿しにくい。動悸、息切れ、水のように薄い痰を伴う咳。顔色が白いか灰色がかる。
+【脈象】
+右関（脾）：波の幅が広い。
+右尺（腎陽）：波の峰が低く、脈拍が少ない。
+左尺（腎陰）：波の幅が広い。
+【標準処方】真武湯</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -25613,6 +26053,17 @@
 [Standard formula] Restore the Left Pill</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>腎精不足
+【病機】先天的な不足や過度の消耗、長患い、房事のしすぎで腎精が減り、骨、脳、生殖の基礎を養えない。
+【症状】小児では立つ、歩く、話す、髪や歯の発育が遅く、頭の泉門が閉じるのも遅い。発達の遅れや低身長。成人ではめまい、耳鳴り、物忘れ、不眠、反応の鈍さ。抜け毛や歯のぐらつき、若白髪、腰や膝のだるさ、脚の弱り。男性では精子の不足と不妊、女性では無月経や不妊。
+【脈象】
+右尺（腎陽）：波の峰が低い。
+左尺（腎陰）：波線が細い。
+【標準処方】左帰丸</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
@@ -25662,6 +26113,17 @@
 Right chi (Kidney Yang): decreased amplitude
 Left chi (Kidney Yin): broader pulse width
 [Standard formula] Metal Lock Pill to Secure the Essence</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>腎気不固
+【病機】長患いや疲労、高齢、房事の不摂生で腎気が不足し、蓄える力が弱まる。目立った寒熱のない虚証。
+【症状】腰や膝のだるさ、疲労、耳鳴り。尿の回数が増え、薄い尿や夜間頻尿、尿漏れがある。男性では遺精や早漏、女性では水っぽい帯下が多く、妊娠を維持しにくい。
+【脈象】
+右尺（腎陽）：波の峰が低い。
+左尺（腎陰）：波の幅が広い。
+【標準処方】金鎖固精丸</t>
         </is>
       </c>
     </row>
@@ -25717,6 +26179,18 @@
 [Standard formula] Mount Tai Rock-Solid Powder</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>妊娠
+【病機】気血が衝脈と任脈に集まって胎児を養う。母の気血が胎児の基礎となり、胎児は腎により生じ、脾によって養われる。
+【症状】吐き気と嘔吐、食べると吐く、脂っこいものを嫌う。めまいと倦怠感。
+【脈象】
+右関（脾）：波の幅が広い。
+右尺（腎陽）：波の峰が高い。
+左尺（腎陰）：波線が太い。
+【標準処方】泰山磐石散</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
@@ -25768,6 +26242,18 @@
 Left chi (Kidney Yin): thinner pulse line, narrower pulse width
 Right chi (Kidney Yang): higher pulse frequency
 [Standard formula] Coptis and Donkey-Hide Gelatin Decoction</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>心腎不交
+【病機】腎陰が不足して心火を抑えられず、心火が強まって心と腎の調和が崩れる。過労や長患い、情緒の鬱滞による熱が原因となりやすい陰虚火旺。
+【症状】上ではいらだち、不眠、多夢、動悸、口内炎。下では腰や膝のだるさ、めまい、耳鳴り、午後からの熱感、寝汗、手足のほてり。眠りが浅い。
+【脈象】
+左寸（心）：脈拍が多い。
+左尺（腎陰）：波線が細く、波の幅が狭い。
+右尺（腎陽）：脈拍が多い。
+【標準処方】黄連阿膠湯</t>
         </is>
       </c>
     </row>
@@ -25825,6 +26311,19 @@
 [Standard formula] White Tiger Decoction</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>気分熱盛
+【病機】温熱の邪が体内深く入り、気分に強い熱がこもって正気と激しく争う実熱証。
+【症状】高熱：全身が強く熱し、寒気より熱さを嫌う。大量の汗：熱で津液が流れ出る。強い渇き：冷たい飲み物を欲する。脈は大きく力強い。
+【脈象】
+浮脈（表）：波の峰がやや高く、脈拍がやや多く、波の幅がやや狭い。
+左寸（心）：波の峰がやや高く、脈拍がやや多く、波の幅がやや狭い。
+右寸（肺）：波の峰が著しく高く、脈拍が著しく多く、波の幅が著しく狭い。
+右関（脾）：波の峰が著しく高く、脈拍が著しく多く、波の幅が著しく狭い。
+【標準処方】白虎湯</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
@@ -25842,7 +26341,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
@@ -25860,7 +26363,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr"/>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
@@ -25878,7 +26385,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D100" s="8" t="inlineStr"/>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="17" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
@@ -25896,7 +26407,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr"/>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
@@ -25914,7 +26429,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr"/>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="17" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
@@ -25932,7 +26451,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr"/>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="17" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
@@ -25950,7 +26473,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr"/>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="17" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
@@ -25968,7 +26495,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr"/>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="8" t="inlineStr">
@@ -25986,7 +26517,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr"/>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="17" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
@@ -26004,7 +26539,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr"/>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="17" customHeight="1">
       <c r="A108" s="8" t="inlineStr">
@@ -26022,7 +26561,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr"/>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="17" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
@@ -26040,7 +26583,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr"/>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="17" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
@@ -26058,7 +26605,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D110" s="8" t="inlineStr"/>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="17" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
@@ -26076,7 +26627,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D111" s="8" t="inlineStr"/>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="17" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
@@ -26094,7 +26649,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D112" s="8" t="inlineStr"/>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="17" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
@@ -26112,7 +26671,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr"/>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="17" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
@@ -26130,7 +26693,11 @@
           <t>catching colds often</t>
         </is>
       </c>
-      <c r="D114" s="8" t="inlineStr"/>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>風邪をひきやすい</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="17" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
@@ -26148,7 +26715,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D115" s="8" t="inlineStr"/>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="17" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
@@ -26166,7 +26737,11 @@
           <t>having joint pain</t>
         </is>
       </c>
-      <c r="D116" s="8" t="inlineStr"/>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>関節が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="17" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
@@ -26184,7 +26759,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D117" s="8" t="inlineStr"/>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="17" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
@@ -26202,7 +26781,11 @@
           <t>having joint pain</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr"/>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>関節が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="17" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
@@ -26220,7 +26803,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D119" s="8" t="inlineStr"/>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="17" customHeight="1">
       <c r="A120" s="8" t="inlineStr">
@@ -26238,7 +26825,11 @@
           <t>having joint pain</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr"/>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>関節が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="17" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
@@ -26256,7 +26847,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D121" s="8" t="inlineStr"/>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="17" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
@@ -26274,7 +26869,11 @@
           <t>having joint pain</t>
         </is>
       </c>
-      <c r="D122" s="8" t="inlineStr"/>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>関節が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="17" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
@@ -26292,7 +26891,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D123" s="8" t="inlineStr"/>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="17" customHeight="1">
       <c r="A124" s="8" t="inlineStr">
@@ -26310,7 +26913,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D124" s="8" t="inlineStr"/>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="17" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
@@ -26328,7 +26935,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D125" s="8" t="inlineStr"/>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="17" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
@@ -26346,7 +26957,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D126" s="8" t="inlineStr"/>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="17" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
@@ -26364,7 +26979,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D127" s="8" t="inlineStr"/>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="17" customHeight="1">
       <c r="A128" s="8" t="inlineStr">
@@ -26382,7 +27001,11 @@
           <t>feeling tightness in my chest and short of breath</t>
         </is>
       </c>
-      <c r="D128" s="8" t="inlineStr"/>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>胸が苦しく、息切れする</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="17" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
@@ -26400,7 +27023,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D129" s="8" t="inlineStr"/>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="17" customHeight="1">
       <c r="A130" s="8" t="inlineStr">
@@ -26418,7 +27045,11 @@
           <t>bringing up a lot of phlegm</t>
         </is>
       </c>
-      <c r="D130" s="8" t="inlineStr"/>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>痰が多い</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="17" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
@@ -26436,7 +27067,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D131" s="8" t="inlineStr"/>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="A132" s="8" t="inlineStr">
@@ -26454,7 +27089,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D132" s="8" t="inlineStr"/>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="17" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
@@ -26472,7 +27111,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D133" s="8" t="inlineStr"/>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="A134" s="8" t="inlineStr">
@@ -26490,7 +27133,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D134" s="8" t="inlineStr"/>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="17" customHeight="1">
       <c r="A135" s="8" t="inlineStr">
@@ -26508,7 +27155,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D135" s="8" t="inlineStr"/>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="17" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
@@ -26526,7 +27177,11 @@
           <t>bringing up a lot of phlegm</t>
         </is>
       </c>
-      <c r="D136" s="8" t="inlineStr"/>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>痰が多い</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="17" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
@@ -26544,7 +27199,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D137" s="8" t="inlineStr"/>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="17" customHeight="1">
       <c r="A138" s="8" t="inlineStr">
@@ -26562,7 +27221,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D138" s="8" t="inlineStr"/>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="17" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
@@ -26580,7 +27243,11 @@
           <t>alternating between chills and fever</t>
         </is>
       </c>
-      <c r="D139" s="8" t="inlineStr"/>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>寒気と熱感を繰り返す</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="17" customHeight="1">
       <c r="A140" s="8" t="inlineStr">
@@ -26598,7 +27265,11 @@
           <t>bringing up a lot of phlegm</t>
         </is>
       </c>
-      <c r="D140" s="8" t="inlineStr"/>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>痰が多い</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="17" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
@@ -26616,7 +27287,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D141" s="8" t="inlineStr"/>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="17" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
@@ -26634,7 +27309,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D142" s="8" t="inlineStr"/>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="17" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
@@ -26652,7 +27331,11 @@
           <t>bringing up a lot of phlegm</t>
         </is>
       </c>
-      <c r="D143" s="8" t="inlineStr"/>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>痰が多い</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="17" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
@@ -26670,7 +27353,11 @@
           <t>coughing</t>
         </is>
       </c>
-      <c r="D144" s="8" t="inlineStr"/>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>咳が出る</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="17" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
@@ -26688,7 +27375,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D145" s="8" t="inlineStr"/>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="17" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
@@ -26706,7 +27397,11 @@
           <t>having diarrhea</t>
         </is>
       </c>
-      <c r="D146" s="8" t="inlineStr"/>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>下痢をする</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="17" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
@@ -26724,7 +27419,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D147" s="8" t="inlineStr"/>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="17" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
@@ -26742,7 +27441,11 @@
           <t>having diarrhea</t>
         </is>
       </c>
-      <c r="D148" s="8" t="inlineStr"/>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>下痢をする</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="17" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
@@ -26760,7 +27463,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D149" s="8" t="inlineStr"/>
+      <c r="D149" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="17" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
@@ -26778,7 +27485,11 @@
           <t>having diarrhea</t>
         </is>
       </c>
-      <c r="D150" s="8" t="inlineStr"/>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>下痢をする</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="17" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
@@ -26796,7 +27507,11 @@
           <t>having abdominal pain</t>
         </is>
       </c>
-      <c r="D151" s="8" t="inlineStr"/>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>腹が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="17" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
@@ -26814,7 +27529,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D152" s="8" t="inlineStr"/>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="17" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
@@ -26832,7 +27551,11 @@
           <t>having diarrhea</t>
         </is>
       </c>
-      <c r="D153" s="8" t="inlineStr"/>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>下痢をする</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="17" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
@@ -26850,7 +27573,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D154" s="8" t="inlineStr"/>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="17" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
@@ -26868,7 +27595,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D155" s="8" t="inlineStr"/>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
@@ -26886,7 +27617,11 @@
           <t>having diarrhea</t>
         </is>
       </c>
-      <c r="D156" s="8" t="inlineStr"/>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>下痢をする</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="17" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
@@ -26904,7 +27639,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D157" s="8" t="inlineStr"/>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="17" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
@@ -26922,7 +27661,11 @@
           <t>feeling restless and uneasy</t>
         </is>
       </c>
-      <c r="D158" s="8" t="inlineStr"/>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="17" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
@@ -26940,7 +27683,11 @@
           <t>feeling tightness in my chest and short of breath</t>
         </is>
       </c>
-      <c r="D159" s="8" t="inlineStr"/>
+      <c r="D159" s="8" t="inlineStr">
+        <is>
+          <t>胸が苦しく、息切れする</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="17" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
@@ -26958,7 +27705,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D160" s="8" t="inlineStr"/>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="17" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
@@ -26976,7 +27727,11 @@
           <t>feeling restless and uneasy</t>
         </is>
       </c>
-      <c r="D161" s="8" t="inlineStr"/>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="17" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
@@ -26994,7 +27749,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D162" s="8" t="inlineStr"/>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="17" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
@@ -27012,7 +27771,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D163" s="8" t="inlineStr"/>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="17" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
@@ -27030,7 +27793,11 @@
           <t>bringing up a lot of phlegm</t>
         </is>
       </c>
-      <c r="D164" s="8" t="inlineStr"/>
+      <c r="D164" s="8" t="inlineStr">
+        <is>
+          <t>痰が多い</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="17" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
@@ -27048,7 +27815,11 @@
           <t>feeling tightness in my chest and short of breath</t>
         </is>
       </c>
-      <c r="D165" s="8" t="inlineStr"/>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>胸が苦しく、息切れする</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="17" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
@@ -27066,7 +27837,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D166" s="8" t="inlineStr"/>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="17" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
@@ -27084,7 +27859,11 @@
           <t>feeling restless and uneasy</t>
         </is>
       </c>
-      <c r="D167" s="8" t="inlineStr"/>
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t>落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="17" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
@@ -27102,7 +27881,11 @@
           <t>feeling tightness in my chest and short of breath</t>
         </is>
       </c>
-      <c r="D168" s="8" t="inlineStr"/>
+      <c r="D168" s="8" t="inlineStr">
+        <is>
+          <t>胸が苦しく、息切れする</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="17" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
@@ -27120,7 +27903,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D169" s="8" t="inlineStr"/>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="17" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
@@ -27138,7 +27925,11 @@
           <t>feeling restless and uneasy</t>
         </is>
       </c>
-      <c r="D170" s="8" t="inlineStr"/>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="17" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
@@ -27156,7 +27947,11 @@
           <t>feeling tightness in my chest and short of breath</t>
         </is>
       </c>
-      <c r="D171" s="8" t="inlineStr"/>
+      <c r="D171" s="8" t="inlineStr">
+        <is>
+          <t>胸が苦しく、息切れする</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="17" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
@@ -27174,7 +27969,11 @@
           <t>having chest pain</t>
         </is>
       </c>
-      <c r="D172" s="8" t="inlineStr"/>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>胸が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="17" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
@@ -27192,7 +27991,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D173" s="8" t="inlineStr"/>
+      <c r="D173" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="17" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
@@ -27210,7 +28013,11 @@
           <t>feeling restless and uneasy</t>
         </is>
       </c>
-      <c r="D174" s="8" t="inlineStr"/>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="17" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
@@ -27228,7 +28035,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D175" s="8" t="inlineStr"/>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="17" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
@@ -27246,7 +28057,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D176" s="8" t="inlineStr"/>
+      <c r="D176" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="17" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
@@ -27264,7 +28079,11 @@
           <t>feeling restless and uneasy</t>
         </is>
       </c>
-      <c r="D177" s="8" t="inlineStr"/>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="17" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
@@ -27282,7 +28101,11 @@
           <t>feeling tightness in my chest and short of breath</t>
         </is>
       </c>
-      <c r="D178" s="8" t="inlineStr"/>
+      <c r="D178" s="8" t="inlineStr">
+        <is>
+          <t>胸が苦しく、息切れする</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="17" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
@@ -27300,7 +28123,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D179" s="8" t="inlineStr"/>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="17" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
@@ -27318,7 +28145,11 @@
           <t>feeling restless and uneasy</t>
         </is>
       </c>
-      <c r="D180" s="8" t="inlineStr"/>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t>落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="17" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
@@ -27336,7 +28167,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D181" s="8" t="inlineStr"/>
+      <c r="D181" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="17" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
@@ -27354,7 +28189,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D182" s="8" t="inlineStr"/>
+      <c r="D182" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="17" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
@@ -27372,7 +28211,11 @@
           <t>feeling restless and uneasy</t>
         </is>
       </c>
-      <c r="D183" s="8" t="inlineStr"/>
+      <c r="D183" s="8" t="inlineStr">
+        <is>
+          <t>落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="17" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
@@ -27390,7 +28233,11 @@
           <t>feeling dizzy</t>
         </is>
       </c>
-      <c r="D184" s="8" t="inlineStr"/>
+      <c r="D184" s="8" t="inlineStr">
+        <is>
+          <t>めまいがする</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="17" customHeight="1">
       <c r="A185" s="8" t="inlineStr">
@@ -27408,7 +28255,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D185" s="8" t="inlineStr"/>
+      <c r="D185" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="17" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
@@ -27426,7 +28277,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D186" s="8" t="inlineStr"/>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="17" customHeight="1">
       <c r="A187" s="8" t="inlineStr">
@@ -27444,7 +28299,11 @@
           <t>feeling dizzy</t>
         </is>
       </c>
-      <c r="D187" s="8" t="inlineStr"/>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t>めまいがする</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="17" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
@@ -27462,7 +28321,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D188" s="8" t="inlineStr"/>
+      <c r="D188" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="17" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
@@ -27480,7 +28343,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D189" s="8" t="inlineStr"/>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="17" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
@@ -27498,7 +28365,11 @@
           <t>having abdominal pain</t>
         </is>
       </c>
-      <c r="D190" s="8" t="inlineStr"/>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>腹が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="17" customHeight="1">
       <c r="A191" s="8" t="inlineStr">
@@ -27516,7 +28387,11 @@
           <t>feeling dizzy</t>
         </is>
       </c>
-      <c r="D191" s="8" t="inlineStr"/>
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t>めまいがする</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="17" customHeight="1">
       <c r="A192" s="8" t="inlineStr">
@@ -27534,7 +28409,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D192" s="8" t="inlineStr"/>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="17" customHeight="1">
       <c r="A193" s="8" t="inlineStr">
@@ -27552,7 +28431,11 @@
           <t>having abdominal pain</t>
         </is>
       </c>
-      <c r="D193" s="8" t="inlineStr"/>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t>腹が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="17" customHeight="1">
       <c r="A194" s="8" t="inlineStr">
@@ -27570,7 +28453,11 @@
           <t>feeling tightness in my chest and short of breath</t>
         </is>
       </c>
-      <c r="D194" s="8" t="inlineStr"/>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>胸が苦しく、息切れする</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="17" customHeight="1">
       <c r="A195" s="8" t="inlineStr">
@@ -27588,7 +28475,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D195" s="8" t="inlineStr"/>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="17" customHeight="1">
       <c r="A196" s="8" t="inlineStr">
@@ -27606,7 +28497,11 @@
           <t>feeling dizzy</t>
         </is>
       </c>
-      <c r="D196" s="8" t="inlineStr"/>
+      <c r="D196" s="8" t="inlineStr">
+        <is>
+          <t>めまいがする</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="17" customHeight="1">
       <c r="A197" s="8" t="inlineStr">
@@ -27624,7 +28519,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D197" s="8" t="inlineStr"/>
+      <c r="D197" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="17" customHeight="1">
       <c r="A198" s="8" t="inlineStr">
@@ -27642,7 +28541,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D198" s="8" t="inlineStr"/>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="17" customHeight="1">
       <c r="A199" s="8" t="inlineStr">
@@ -27660,7 +28563,11 @@
           <t>having pain below my ribs</t>
         </is>
       </c>
-      <c r="D199" s="8" t="inlineStr"/>
+      <c r="D199" s="8" t="inlineStr">
+        <is>
+          <t>脇腹が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="17" customHeight="1">
       <c r="A200" s="8" t="inlineStr">
@@ -27678,7 +28585,11 @@
           <t>feeling agitated and restless</t>
         </is>
       </c>
-      <c r="D200" s="8" t="inlineStr"/>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>いらいらして落ち着かない</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="17" customHeight="1">
       <c r="A201" s="8" t="inlineStr">
@@ -27696,7 +28607,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D201" s="8" t="inlineStr"/>
+      <c r="D201" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="17" customHeight="1">
       <c r="A202" s="8" t="inlineStr">
@@ -27714,7 +28629,11 @@
           <t>feeling dizzy</t>
         </is>
       </c>
-      <c r="D202" s="8" t="inlineStr"/>
+      <c r="D202" s="8" t="inlineStr">
+        <is>
+          <t>めまいがする</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="17" customHeight="1">
       <c r="A203" s="8" t="inlineStr">
@@ -27732,7 +28651,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D203" s="8" t="inlineStr"/>
+      <c r="D203" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="17" customHeight="1">
       <c r="A204" s="8" t="inlineStr">
@@ -27750,7 +28673,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D204" s="8" t="inlineStr"/>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="17" customHeight="1">
       <c r="A205" s="8" t="inlineStr">
@@ -27768,7 +28695,11 @@
           <t>feeling dizzy</t>
         </is>
       </c>
-      <c r="D205" s="8" t="inlineStr"/>
+      <c r="D205" s="8" t="inlineStr">
+        <is>
+          <t>めまいがする</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="17" customHeight="1">
       <c r="A206" s="8" t="inlineStr">
@@ -27786,7 +28717,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D206" s="8" t="inlineStr"/>
+      <c r="D206" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="17" customHeight="1">
       <c r="A207" s="8" t="inlineStr">
@@ -27804,7 +28739,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D207" s="8" t="inlineStr"/>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="17" customHeight="1">
       <c r="A208" s="8" t="inlineStr">
@@ -27822,7 +28761,11 @@
           <t>having abdominal pain</t>
         </is>
       </c>
-      <c r="D208" s="8" t="inlineStr"/>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>腹が痛い</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="17" customHeight="1">
       <c r="A209" s="8" t="inlineStr">
@@ -27840,7 +28783,11 @@
           <t>having diarrhea</t>
         </is>
       </c>
-      <c r="D209" s="8" t="inlineStr"/>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>下痢をする</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="17" customHeight="1">
       <c r="A210" s="8" t="inlineStr">
@@ -27858,7 +28805,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D210" s="8" t="inlineStr"/>
+      <c r="D210" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="17" customHeight="1">
       <c r="A211" s="8" t="inlineStr">
@@ -27876,7 +28827,11 @@
           <t>having soreness and weakness in my lower back and knees</t>
         </is>
       </c>
-      <c r="D211" s="8" t="inlineStr"/>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>腰や膝がだるい</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="17" customHeight="1">
       <c r="A212" s="8" t="inlineStr">
@@ -27894,7 +28849,11 @@
           <t>feeling tightness in my chest and short of breath</t>
         </is>
       </c>
-      <c r="D212" s="8" t="inlineStr"/>
+      <c r="D212" s="8" t="inlineStr">
+        <is>
+          <t>胸が苦しく、息切れする</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="17" customHeight="1">
       <c r="A213" s="8" t="inlineStr">
@@ -27912,7 +28871,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D213" s="8" t="inlineStr"/>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="17" customHeight="1">
       <c r="A214" s="8" t="inlineStr">
@@ -27930,7 +28893,11 @@
           <t>having soreness and weakness in my lower back and knees</t>
         </is>
       </c>
-      <c r="D214" s="8" t="inlineStr"/>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>腰や膝がだるい</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="17" customHeight="1">
       <c r="A215" s="8" t="inlineStr">
@@ -27948,7 +28915,11 @@
           <t>having ringing in my ears</t>
         </is>
       </c>
-      <c r="D215" s="8" t="inlineStr"/>
+      <c r="D215" s="8" t="inlineStr">
+        <is>
+          <t>耳鳴りがする</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="17" customHeight="1">
       <c r="A216" s="8" t="inlineStr">
@@ -27966,7 +28937,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D216" s="8" t="inlineStr"/>
+      <c r="D216" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="17" customHeight="1">
       <c r="A217" s="8" t="inlineStr">
@@ -27984,7 +28959,11 @@
           <t>having soreness and weakness in my lower back and knees</t>
         </is>
       </c>
-      <c r="D217" s="8" t="inlineStr"/>
+      <c r="D217" s="8" t="inlineStr">
+        <is>
+          <t>腰や膝がだるい</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="17" customHeight="1">
       <c r="A218" s="8" t="inlineStr">
@@ -28002,7 +28981,11 @@
           <t>urinating frequently at night</t>
         </is>
       </c>
-      <c r="D218" s="8" t="inlineStr"/>
+      <c r="D218" s="8" t="inlineStr">
+        <is>
+          <t>夜間の尿が多い</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="17" customHeight="1">
       <c r="A219" s="8" t="inlineStr">
@@ -28020,7 +29003,11 @@
           <t>having ringing in my ears</t>
         </is>
       </c>
-      <c r="D219" s="8" t="inlineStr"/>
+      <c r="D219" s="8" t="inlineStr">
+        <is>
+          <t>耳鳴りがする</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="17" customHeight="1">
       <c r="A220" s="8" t="inlineStr">
@@ -28038,7 +29025,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D220" s="8" t="inlineStr"/>
+      <c r="D220" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="17" customHeight="1">
       <c r="A221" s="8" t="inlineStr">
@@ -28056,7 +29047,11 @@
           <t>having soreness and weakness in my lower back and knees</t>
         </is>
       </c>
-      <c r="D221" s="8" t="inlineStr"/>
+      <c r="D221" s="8" t="inlineStr">
+        <is>
+          <t>腰や膝がだるい</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="17" customHeight="1">
       <c r="A222" s="8" t="inlineStr">
@@ -28074,7 +29069,11 @@
           <t>urinating frequently at night</t>
         </is>
       </c>
-      <c r="D222" s="8" t="inlineStr"/>
+      <c r="D222" s="8" t="inlineStr">
+        <is>
+          <t>夜間の尿が多い</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="17" customHeight="1">
       <c r="A223" s="8" t="inlineStr">
@@ -28092,7 +29091,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D223" s="8" t="inlineStr"/>
+      <c r="D223" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="17" customHeight="1">
       <c r="A224" s="8" t="inlineStr">
@@ -28110,7 +29113,11 @@
           <t>having soreness and weakness in my lower back and knees</t>
         </is>
       </c>
-      <c r="D224" s="8" t="inlineStr"/>
+      <c r="D224" s="8" t="inlineStr">
+        <is>
+          <t>腰や膝がだるい</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="17" customHeight="1">
       <c r="A225" s="8" t="inlineStr">
@@ -28128,7 +29135,11 @@
           <t>having ringing in my ears</t>
         </is>
       </c>
-      <c r="D225" s="8" t="inlineStr"/>
+      <c r="D225" s="8" t="inlineStr">
+        <is>
+          <t>耳鳴りがする</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="17" customHeight="1">
       <c r="A226" s="8" t="inlineStr">
@@ -28146,7 +29157,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D226" s="8" t="inlineStr"/>
+      <c r="D226" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="17" customHeight="1">
       <c r="A227" s="8" t="inlineStr">
@@ -28164,7 +29179,11 @@
           <t>having soreness and weakness in my lower back and knees</t>
         </is>
       </c>
-      <c r="D227" s="8" t="inlineStr"/>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>腰や膝がだるい</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="17" customHeight="1">
       <c r="A228" s="8" t="inlineStr">
@@ -28182,7 +29201,11 @@
           <t>urinating frequently at night</t>
         </is>
       </c>
-      <c r="D228" s="8" t="inlineStr"/>
+      <c r="D228" s="8" t="inlineStr">
+        <is>
+          <t>夜間の尿が多い</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="17" customHeight="1">
       <c r="A229" s="8" t="inlineStr">
@@ -28200,7 +29223,11 @@
           <t>having ringing in my ears</t>
         </is>
       </c>
-      <c r="D229" s="8" t="inlineStr"/>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>耳鳴りがする</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="17" customHeight="1">
       <c r="A230" s="8" t="inlineStr">
@@ -28218,7 +29245,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D230" s="8" t="inlineStr"/>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="17" customHeight="1">
       <c r="A231" s="8" t="inlineStr">
@@ -28236,7 +29267,11 @@
           <t>feeling nauseous</t>
         </is>
       </c>
-      <c r="D231" s="8" t="inlineStr"/>
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>吐き気がする</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="17" customHeight="1">
       <c r="A232" s="8" t="inlineStr">
@@ -28254,7 +29289,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D232" s="8" t="inlineStr"/>
+      <c r="D232" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="17" customHeight="1">
       <c r="A233" s="8" t="inlineStr">
@@ -28272,7 +29311,11 @@
           <t>sleeping poorly and having frequent dreams</t>
         </is>
       </c>
-      <c r="D233" s="8" t="inlineStr"/>
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>眠れず、夢をよく見る</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="17" customHeight="1">
       <c r="A234" s="8" t="inlineStr">
@@ -28290,7 +29333,11 @@
           <t>having soreness and weakness in my lower back and knees</t>
         </is>
       </c>
-      <c r="D234" s="8" t="inlineStr"/>
+      <c r="D234" s="8" t="inlineStr">
+        <is>
+          <t>腰や膝がだるい</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="17" customHeight="1">
       <c r="A235" s="8" t="inlineStr">
@@ -28308,7 +29355,11 @@
           <t>feeling unwell</t>
         </is>
       </c>
-      <c r="D235" s="8" t="inlineStr"/>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>具合が悪い</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="17" customHeight="1">
       <c r="A236" s="8" t="inlineStr">
@@ -28326,7 +29377,11 @@
           <t>running a fever</t>
         </is>
       </c>
-      <c r="D236" s="8" t="inlineStr"/>
+      <c r="D236" s="8" t="inlineStr">
+        <is>
+          <t>熱がある</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36263,7 +37318,11 @@
           <t>A secret record fit for emperors, a precious treasure for ministers and common people alike. This collection should not be hidden away in some mountain vault. Let it be carved and printed, so that future generations throughout the world may study its profound mysteries.</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>これは帝王の秘録にして、臣民の重宝である。この書を深山の石室にしまい込むのはふさわしくない。版木に刻み、後世の人々と広く分かち合うべきだ。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -36457,7 +37516,11 @@
           <t>I, Shizhen, am a humble man of Jingchu. Sickly as a child and slow of mind, I presumed to undertake this compilation. Over thirty years I consulted more than eight hundred works and revised the manuscript three times, cutting repetition, filling gaps and correcting errors. To the 1,528 medicinal substances in earlier works, I added 374, arranged them in sixteen divisions and completed fifty-two volumes. I have dared to call it the Compendium of Materia Medica.</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>時珍は荊楚の片田舎の者である。幼少より病弱で、才も鈍かった。僭越ながら書を編むこと三十年余り、八百余家の書を調べ、稿を三度改め、重複を削り、欠落を補い、誤りを正した。旧書の薬千五百二十八種に三百七十四種を加え、十六部、五十二巻にまとめ、恐れ多くも『本草綱目』と名づけた。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -42305,7 +43368,11 @@
           <t>The count is correct. Thank you, gentlemen. Would you come in for some water?</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>数は合っています。お疲れさまでした。中で水でも飲んでいきませんか。</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -42345,7 +43412,11 @@
           <t>We are still on duty, Doctor Li. No need to trouble yourself. Men, let us go!</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>まだ公務がありますので、お構いなく。皆、行くぞ！</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -42385,7 +43456,11 @@
           <t>Father, has everything arrived?</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>父上、荷は全部届きましたか？</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -42425,7 +43500,11 @@
           <t>Yes, I counted it all. It has already been packed into individual portions, so we will not need to weigh it ourselves. Excellent.</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>ああ、全部数えた。今回は一回分ずつ包んであるから、こちらで量り直さずに済む。よくできている。</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -42465,7 +43544,11 @@
           <t>Tomorrow I will distribute the medicine with Zhilan and the others. You look after the clinic.</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>明日はわしが芷蘭たちを連れて薬を配る。お前は診療所の仕事を頼む。</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -42505,7 +43588,11 @@
           <t>Of course, Father.</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>分かりました、父上。</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -42545,7 +43632,11 @@
           <t>Father, the medicine is ready.</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>父上、薬が煎じ上がりました。</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -42585,7 +43676,11 @@
           <t>After a full day's work, we have handed out nearly all the supplies. We should take our own medicine too. Let me see what formula they have given us.</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>一日働いて薬もほぼ配り終えた。わしらも飲んでおこう。今回はどんな処方か見せてくれ。</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -42625,7 +43720,11 @@
           <t>Hmm… Agastache and perilla leaf. This should be Agastache Powder to Rectify the Qi.</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>うむ……藿香と紫蘇が入っている。藿香正気散だろう。</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -42665,7 +43764,11 @@
           <t>Hm? It does not taste right. Why is flour mixed in with the medicine? They have bulked out the magnolia bark with ordinary tree bark, too.</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ん？　匂いがおかしい。薬に小麦粉が混じっているぞ。厚朴には別の木の皮まで混ぜてかさ増ししてある。</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -42705,7 +43808,11 @@
           <t>Let me taste it… They used agastache stems. The aroma is weak.</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>少し味を見よう……藿香は茎ばかりで、香りが弱い。</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -42745,7 +43852,11 @@
           <t>They even dared tamper with medicine meant for disaster relief…</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>そんな……救済用の薬材にまで手を加えるとは……</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -42785,7 +43896,11 @@
           <t>These supplies are too important. We must report this to the authorities.</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>救済用の薬材は大事なものだ。役所に報告しなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -42825,7 +43940,11 @@
           <t>Tomorrow I will discuss it with Doctor Sun at the dispensary.</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>明日、薬剤局へ行って孫先生に相談してみます。</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -42865,7 +43984,11 @@
           <t>Something terrible has happened! Doctor Sun has been arrested!</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>大変だ！　孫先生が捕まった！</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -42905,7 +44028,11 @@
           <t>What happened?</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>何があった？</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -42945,7 +44072,11 @@
           <t>Doctor Sun noticed the problems with the relief medicine too. He went to confront Wu Shiliang at the prefectural office. Instead, they accused him of secretly swapping the medicine, flogged him twenty times and threw him in prison.</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>孫先生も薬材の異常に気づいて、州役所の呉世良に会いに行った。ところが薬材を勝手にすり替えたと罪を着せられ、杖で二十回打たれて牢に入れられたんだ。</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -42985,7 +44116,11 @@
           <t>Wu Shiliang always looked respectable, but he is rotten to the core.</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>呉世良め、普段は立派そうに見えたのに、とんでもないやつだ。</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -43025,7 +44160,11 @@
           <t>We have to seek justice for Doctor Sun.</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>孫先生の無実を証明しなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -43065,7 +44204,11 @@
           <t>Son, I think we should stay out of this. Better to keep our heads down. Ordinary people like us cannot fight the authorities.</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>息子よ、この件には関わらないほうがいい。余計なことに首を突っ込まず、身を守りなさい。わしら庶民にどうにかできる話ではない。</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -43105,7 +44248,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>…………</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -43145,7 +44292,11 @@
           <t>My friend, it has been too long. I came to pick up some medicine and thought I would visit you.</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>久しぶりだな。薬を買いに来たついでに、お前の顔も見に来たよ。</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -43185,7 +44336,11 @@
           <t>What is troubling you, Brother Lei?</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>雷兄、どこか具合が悪いのですか？</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -43225,7 +44380,11 @@
           <t>All the disaster relief medicine for the province is being sent out from Qizhou. I was ordered to escort shipments from place to place, and I caught a chill on the road.</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>今回は省内各地へ送る救済用の薬材を、すべて蘄州から運ぶことになった。護送を命じられてあちこち走り回るうち、風邪をひいてしまった。</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -43265,7 +44424,11 @@
           <t>The whole province is receiving supplies from Qizhou?</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>全省分を蘄州から運ぶのですか？</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -43305,7 +44468,11 @@
           <t>Yes. All the medicine is bought and stored here, then sent wherever it is needed.</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>そうだ。蘄州で一括して買い入れ、保管している。薬が足りない所にはここから送る。</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -43345,7 +44512,11 @@
           <t>Have you heard? Someone has tampered with these relief supplies. They have replaced good medicine with poor quality stock. It cannot cure anyone.</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>ご存じですか？　今回の薬材には粗悪品が混ざっています。あれでは病を治せません。</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -43385,7 +44556,11 @@
           <t>What? Is that true?</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>何だって？　本当か？</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -43425,7 +44600,11 @@
           <t>Doctor Sun from the dispensary challenged Wu Shiliang about it and was imprisoned. The other doctors who know are afraid to speak up.</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>薬剤局の孫先生が呉世良に抗議したら、牢に入れられました。事情を知る医者は誰も声を上げられません。</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -43465,7 +44644,11 @@
           <t>Damn them! Has the law lost all meaning? We cannot go to the local officials. I will report this to the Huguang Provincial Surveillance Commission in Wuchang.</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>なんてことだ、法もないのか！　州役所には訴えられないな。武昌府の湖広按察司へ行って、この件を上に報告する。</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -43505,7 +44688,11 @@
           <t>Take care on the journey, Brother Lei.</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>雷兄、どうかお気をつけて。</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -43545,7 +44732,11 @@
           <t>Doctor Li, it is a pleasure to see you.</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>李先生、ご無沙汰しております。</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -43585,7 +44776,11 @@
           <t>Master Shen. Please, sit down.</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>沈殿でしたか。どうぞお掛けください。</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -43625,7 +44820,11 @@
           <t>I have been sleeping poorly and have little appetite. I hoped you would examine me.</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>最近よく眠れず、食欲もありません。診ていただきたいのです。</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -43665,7 +44864,11 @@
           <t>You have a deficiency of both heart and spleen. Too much worry has depleted your heart blood and weakened your spleen qi. I will prescribe Restore the Spleen Decoction. Please make sure you rest.</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>心脾両虚の証です。考えすぎて心血を消耗し、脾の気も弱っています。帰脾湯を処方しますから、しっかり休んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -43705,7 +44908,11 @@
           <t>Your reputation is well deserved. Official business has kept me very busy. A financial secretary never has a moment to spare.</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>さすが名医の李先生。最近は役所の仕事が忙しくて。金銭や穀物の帳簿を扱う書記は、休む暇もありません。</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -43745,7 +44952,11 @@
           <t>Have you been occupied with buying the relief medicine?</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>救済用の薬材の調達でお忙しいのですか？</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -43785,7 +44996,11 @@
           <t>That is government business. I cannot discuss it, and I advise you not to inquire into official affairs.</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>それは役所の公務ですから、お話しできません。先生も役所のことは詮索しないほうがいい。</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -43825,7 +45040,11 @@
           <t>Forgive my presumption.</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>出過ぎたことを申しました。</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -43865,7 +45084,11 @@
           <t>No matter. You and your father are skilled physicians. I imagine you know exactly what is in the relief medicine.</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>いえ。あなたと父上ほどの医者なら、救済用の薬材に何が使われているか、お分かりでしょう。</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -43905,7 +45128,11 @@
           <t>But let me warn you: these supplies concern more than one or two prefectures. Neither you nor I can set things right.</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>ただ、ひとつ忠告します。この件は一つ二つの州府だけの問題ではない。私たちにどうにかできることでもありません。</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -43945,7 +45172,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>…………</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -43985,7 +45216,11 @@
           <t>Your medical skill is renowned throughout the province, and I admire it greatly. Do not squander the gift Heaven has given you. I shall take my leave.</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>先生の医術は省中に知れ渡っています。その天から授かった才能を無駄になさらぬよう。では失礼します。</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -44003,7 +45238,11 @@
           <t>Received one tael of silver.</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>収入：銀一両</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -44043,7 +45282,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -44061,7 +45304,11 @@
           <t>Knock, knock, knock…</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>トントン……</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -44101,7 +45348,11 @@
           <t>Who is there?</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>誰だ？</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -44141,7 +45392,11 @@
           <t>It is me, my friend.</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>私だよ。</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -44181,7 +45436,11 @@
           <t>Brother Lei! Have you made any progress?</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>雷兄、どうでした？　何か分かりましたか？</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -44221,7 +45480,11 @@
           <t>No… Neither the provincial surveillance office nor the provincial administration would hear the case. I even went to see the commander at the military commission. He said the matter runs too deep and told me to stay out of it…</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>はあ……按察司も布政司も訴えを受け付けなかった。都指揮使司の長官にも会ったが、裏が深いから関わるなと言われたよ……</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -44261,7 +45524,11 @@
           <t>Then this is far more complicated than we thought…</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>どうやら想像以上に複雑な話ですね……</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -44301,7 +45568,11 @@
           <t>If we let it go, something terrible will happen…</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>放っておけば大変なことになる……</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -44341,7 +45612,11 @@
           <t>I know someone who might help.</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>助けてくれそうな人に心当たりがあります。</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -44381,7 +45656,11 @@
           <t>Oh? Who?</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>ほう？　誰だ？</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -44421,7 +45700,11 @@
           <t>The Prince of Chu.</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>楚王です。</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -44461,7 +45744,11 @@
           <t>You know someone so powerful?</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>お前、そんな大物と知り合いなのか？</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -44501,7 +45788,11 @@
           <t>I treated his son. He may be willing to hear me out.</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>以前、世子様を治療しました。話は聞いていただけるはずです。</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -44541,7 +45832,11 @@
           <t>Then what are we waiting for? I will go with you now!</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>それならすぐに行こう。私も同行する！</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -44559,7 +45854,11 @@
           <t>The two traveled to the Prince of Chu's residence in silence.</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>道中、二人は無言のまま楚王府へたどり着いた。</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -44599,7 +45898,11 @@
           <t>Doctor Li, it is good to see you again.</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>先日以来ですね。先生、お元気でしたか。</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -44639,7 +45942,11 @@
           <t>My respects, Your Highness. I have come to ask for your help.</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>殿下に拝謁いたします。本日はお願いがあって参りました。</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -44679,7 +45986,11 @@
           <t>You saved my son's life. If there is anything within my power, I will do my best.</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>先生は息子の命の恩人です。私にできることなら、力を尽くしましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -44697,7 +46008,11 @@
           <t>Li Dongbi told the Prince of Chu everything that had happened.</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>李東璧は事の経緯をありのまま楚王に伝えた。</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -44737,7 +46052,11 @@
           <t>Hmm… These local officials are brazen indeed. But since the reign of the Yongle Emperor, imperial princes have been forbidden to govern the people or interfere in local military and civil affairs. To do so would be treated as treason. I fear I cannot intervene.</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>うむ……地方官どもは大胆なことをする。だが成祖文皇帝以来、藩王は民を治めず政務にも携わらぬことになっている。地方の軍政への介入は謀反の罪となる。私にも手出しはできない。</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -44777,7 +46096,11 @@
           <t>If you do nothing, no one can… If an epidemic breaks out, the people of Huguang will suffer terribly.</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>殿下が動かなければ、もう誰も動けません……疫病が広がれば、湖広の民は苦しみます。</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -44817,7 +46140,11 @@
           <t>Many people are implicated. Are you not afraid of putting yourself in danger?</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>関係者は多い。先生は自分に災いが及ぶことが怖くないのですか？</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -44857,7 +46184,11 @@
           <t>Since childhood I have studied the classics and the teachings of the sages. I have written no great work and earned no official title. All I have learned, all I seek, is to help the people live. If my one life can save millions, I will give it gladly.</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>幼い頃から四書五経や諸子百家を学びました。文章も功名も得られませんでしたが、学んだのは民の命を支えるためです。私一人の命で大勢の民を救えるなら、喜んで進みます。</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -44897,7 +46228,11 @@
           <t>Your words put me to shame… I will send a secret memorial to His Majesty explaining the matter. But you must speak of this to no one else.</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>先生の言葉に恥じ入るばかりだ……私から陛下へ密奏を送り、この件をお伝えしよう。先生もほかの者には口外しないでください。</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -44937,7 +46272,11 @@
           <t>Master Shen, are you feeling any better?</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>沈殿、病は良くなりましたか？</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -44977,7 +46316,11 @@
           <t>I do not have much time left.</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>私にはもう時間がありません。</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -45017,7 +46360,11 @@
           <t>What? Your illness is not that serious. Take the medicine and get enough rest, and you will recover.</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>え？　それほど重い病ではありませんよ。薬を飲んで休めば、きっと良くなります。</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -45057,7 +46404,11 @@
           <t>Medicine can cure an illness, but it cannot change one's fate. I came to give you something.</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>病は治せても、運命は治せません。今日は先生にお渡ししたいものがあります。</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -45097,7 +46448,11 @@
           <t>What is this?</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>これは？</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -45137,7 +46492,11 @@
           <t>A copy of the accounts Wu Shiliang ordered me to keep. I think it will be useful in your hands.</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>呉世良に命じられて私が書いた帳簿の写しです。あなたのお役に立つでしょう。</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -45177,7 +46536,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>…………</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -45217,7 +46580,11 @@
           <t>To tell the truth, I envy you. Your abilities can be put to good use. Ah… Farewell, Doctor Li.</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>正直、先生が羨ましい。学んだことを人々のために生かせるのですから……では失礼します。</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -45257,7 +46624,11 @@
           <t>Master Shen…</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>沈殿……</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -45275,7 +46646,11 @@
           <t>Obtained a copy of the disaster relief medicine accounts.</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>救済用薬材の帳簿の写しを入手した。</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -45315,7 +46690,11 @@
           <t>Doctor Li, my lower back and legs have felt weak these past few days, and I keep waking to urinate. Could you prescribe something?</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>李先生、この二日ほど腰と脚がだるく、夜も何度も小便に起きます。薬を出してください。</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -45355,7 +46734,11 @@
           <t>Please, sit down, Officer Yang.</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>楊殿、どうぞお掛けください。</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -45395,7 +46778,11 @@
           <t>You have a failure of the kidneys to secure qi. You need rest. Has something frightened you recently?</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>楊殿は腎気不固の証です。静養してください。最近、何か怖い目に遭いましたか？</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -45435,7 +46822,11 @@
           <t>Have you heard what happened to Secretary Shen?</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>沈書記の件を聞きましたか？</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -45475,7 +46866,11 @@
           <t>What happened to him?</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>沈殿に何があったのです？</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -45515,7 +46910,11 @@
           <t>They found him dead in his room yesterday…</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>昨日、自室で亡くなっていたんです……</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -45555,7 +46954,11 @@
           <t>What?!</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>！！！</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -45595,7 +46998,11 @@
           <t>They have begun silencing witnesses… I will be next…</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>口封じが始まった……次は私の番だ……</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -45635,7 +47042,11 @@
           <t>I oversaw the receipt of that shipment and its dispatch to each district. How much medicine there was, its quality, where it went—my signature is on every entry. If they want to erase the trail, they cannot leave me alive.</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>この薬材の検収から各地への発送まで、すべて私が担当しました。量、品質、届け先、帳簿には私の署名が残っています。証拠を消すつもりなら、私を生かしてはおかないでしょう。</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -45675,7 +47086,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>…………</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -45693,7 +47108,11 @@
           <t>Received one tael of silver.</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>収入：銀一両</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -45733,7 +47152,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -45751,7 +47174,11 @@
           <t>“The storeroom is on fire! Somebody help!”</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>「倉庫が火事だ！　誰か、火を消してくれ！」</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -45791,7 +47218,11 @@
           <t>Young master, the public dispensary's medicine storehouse is burning!</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>若旦那、恵民薬局の薬材倉庫が燃えています！</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -45831,7 +47262,11 @@
           <t>Come on. Let us help.</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>行こう、手伝うぞ。</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -45871,7 +47306,11 @@
           <t>There is something suspicious about this fire.</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>この火事は妙だ。</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -45911,7 +47350,11 @@
           <t>They are carrying someone out over there.</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>向こうから誰かが運び出されてくる。</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -45951,7 +47394,11 @@
           <t>…It is Yang Shanquan.</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>……楊善泉だ。</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -45991,7 +47438,11 @@
           <t>Business looks good, Master Li. (Looks around…) That door leads to the rear courtyard, does it?</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>お店は繁盛しているようですね。（辺りを見回す……）あの扉は裏庭に通じるんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -46031,7 +47482,11 @@
           <t>May I ask what brings you to my clinic?</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>当院に何のご用ですか？</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -46071,7 +47526,11 @@
           <t>Oh, ha, ha, nothing in particular. I heard Qizhou had a famous Physician Li and came to see him for myself.</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>いや、はは、何でもありません。蘄州に名医の李先生がいると聞いて、お顔を拝みに来ただけです。</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -46111,7 +47570,11 @@
           <t>We have patients to see. If you have no business here, please leave.</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>患者を診ています。ご用がなければお引き取りください。</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -46151,7 +47614,11 @@
           <t>Hmph. We will meet again.</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>ちぇっ、また会おうぜ。</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -46169,7 +47636,11 @@
           <t>Click.</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>カタン。</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -46209,7 +47680,11 @@
           <t>Who is there?!</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>誰だ！</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -46249,7 +47724,11 @@
           <t>Doctor Li, I have come to send you to the next world.</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>李先生、あの世へ送ってやるよ。</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -46289,7 +47768,11 @@
           <t>What?!</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>！！！</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -46307,7 +47790,11 @@
           <t>Bang!</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>バン！</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -46347,7 +47834,11 @@
           <t>Ow!</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>痛っ！</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -46387,7 +47878,11 @@
           <t>What?!</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>！！！</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -46427,7 +47922,11 @@
           <t>My friend, are you all right? When His Highness heard that Shen Xiuwen and Yang Shanquan had both been silenced, he feared you would be next. He sent us to protect you in secret.</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>無事か？　沈修文と楊善泉が口封じに遭ったと知った王様は、次はお前の番だと考え、我々を護衛に遣わしたのだ。</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -46467,7 +47966,11 @@
           <t>Tie him up.</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>そいつを縛れ。</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -46507,7 +48010,11 @@
           <t>It is a misunderstanding, sir! A misunderstanding!</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>誤解です、お役人様、誤解です！</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -46525,7 +48032,11 @@
           <t>The group arrived at the prince's residence.</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>一行は王府へ向かった。</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -46565,7 +48076,11 @@
           <t>Your Highness, we have brought them all here.</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>王様、全員連れてまいりました。</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -46605,7 +48120,11 @@
           <t>These gentlemen are imperial investigators sent to examine the disaster relief medicine case.</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>こちらは救済用薬材の事件を調べるため、朝廷から派遣された使者たちです。</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -46645,7 +48164,11 @@
           <t>Lu Ding of the Northern Pacification Office. Are you Li Dongbi?</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>北鎮撫司の陸丁だ。お前が李東璧か？</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -46685,7 +48208,11 @@
           <t>I am, sir.</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>はい、私でございます。</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -46703,7 +48230,11 @@
           <t>Li Dongbi gave the imperial investigators a full account of everything that had happened.</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>李東璧は事件の一部始終を、朝廷の使者に包み隠さず伝えた。</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -46721,7 +48252,11 @@
           <t>The corruption of Qizhou's disaster relief medicine drew the court's attention. The Imperial Guards were ordered to investigate. Dozens of local officials were implicated, and nearly ten thousand taels of silver had been embezzled.</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>蘄州の救済用薬材をめぐる汚職事件は朝廷を揺るがした。錦衣衛が勅命を受けて捜査し、数十人の地方官が関与、横領額は銀一万両近くに上った。</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -46739,7 +48274,11 @@
           <t>The principal offenders, including Wu Shiliang and Zhao Shun, were executed at once. Chen Shixian, governor of Huguang, and others were demoted two ranks for failing to uncover the crime.</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>主犯の呉世良、趙順らは直ちに斬首された。湖広巡撫の陳仕賢らも監督不行き届きで連座し、官位を二階級下げられた。</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -46757,7 +48296,11 @@
           <t>The Imperial Medical Academy supplied a new shipment of relief medicine for Qizhou to distribute.</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>蘄州に必要な薬材は太医院から改めて送られ、配り直された。</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -46797,7 +48340,11 @@
           <t>In the end, Wu Shiliang was little more than a scapegoat.</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>結局、呉世良は身代わりにされたにすぎない。</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -46837,7 +48384,11 @@
           <t>The Yan faction controls the court. Every official has ties to another. If anyone truly followed the trail, it would lead into a hopeless tangle.</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>朝政は厳党に握られている。役人同士は皆つながっている。突き詰めれば、またうやむやになるだろう。</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -46877,7 +48428,11 @@
           <t>Doctor Li.</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>李先生。</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -46917,7 +48472,11 @@
           <t>Your Highness.</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>楚王殿下。</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -46957,7 +48516,11 @@
           <t>When I reported the medicine case to His Majesty, I also recommended you for service at court. A deputy director's post at the Imperial Medical Academy happened to be vacant, and His Majesty has approved your appointment.</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>このたび陛下に上奏した際、薬材の事件とともに先生を朝廷へ推薦しました。太医院の院判がちょうど欠員となり、先生の任官が特に認められました。</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -46997,7 +48560,11 @@
           <t>Thank you for your kindness, Your Highness. But I am only a humble man of Jingchu, sickly since childhood and slow of mind. I fear I am not equal to the task.</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>殿下のお引き立てに感謝します。しかし私は荊楚の田舎者で、幼少から病弱、才にも乏しい身です。大任を果たす自信がありません。</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -47037,7 +48604,11 @@
           <t>…Very well. I will not press you.</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>……そうですか。無理強いはしません。</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -47077,7 +48648,11 @@
           <t>Cough, cough… Doctor, I do not know what has happened to my throat. It hurts and itches, and I have coughed until my voice is hoarse.</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>ゴホゴホ……先生、喉がどうしたのか痛くてかゆくて、咳で声まで枯れました。</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -47117,7 +48692,11 @@
           <t>Master Liu, please sit down.</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>柳先生でしたか。どうぞお掛けください。</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -47157,7 +48736,11 @@
           <t>Ah, that feels much better.</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>ああ、ずいぶん楽になりました。</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -47197,7 +48780,11 @@
           <t>You have a warm dryness pattern. Sitting and telling stories all day without much movement has depleted your fluids and qi, making you prone to internal heat.</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>温燥の証です。毎日の語りで座りっぱなしですから、津液と気を損ない、体内に熱が生じやすくなっています。</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -47237,7 +48824,11 @@
           <t>I will prescribe Mulberry Leaf and Apricot Kernel Decoction, three doses a day. Remember to drink plenty of water too.</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>桑杏湯を処方します。一日三回服用し、水もよく飲んでください。</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -47277,7 +48868,11 @@
           <t>Master Liu, I love hearing your stories! You know everything, and you bring every tale to life.</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>柳先生の語りは大好きです！　何でもご存じで、どんな話も本物みたいに語りますね。</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -47317,7 +48912,11 @@
           <t>Heh, heh. You flatter me, young man. I only tell tales of kings and generals, scholars and beauties. I tell the audience whatever they want to hear.</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>いやあ、褒めすぎだよ。王侯将相や才子佳人の話を、お客が好むように語っているだけさ。</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -47357,7 +48956,11 @@
           <t>Please tell us a story now, Master Liu.</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>先生、今ここで一席お願いします！</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -47397,7 +49000,11 @@
           <t>Yes, please! Just one story!</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>そうだ、聞かせてください！</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -47437,7 +49044,11 @@
           <t>Master Liu is still ill. Stop pestering him.</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>柳先生は病気なのよ。困らせないで。</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -47477,7 +49088,11 @@
           <t>It is all right. Let me tell you the tale of Daoist Wang and his remedy for jealousy.</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>構わないさ。では「王道士がでっち上げた嫉妬の薬」をひとつ。</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -47517,7 +49132,11 @@
           <t>Once, a wealthy merchant in the capital married a very jealous woman. Their home knew no peace. A friend decided her jealousy was an illness that needed a cure.</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>都にある裕福な商人が、ひどく嫉妬深い妻をめとった。家は毎日大騒ぎ。友人は、これは病気だから治してもらおうと考えた。</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -47557,7 +49176,11 @@
           <t>At Tianqi Temple, a Daoist called Wang sold medicinal plasters. His plasters were so effective that everyone called him Wang the One-Plaster Wonder. The friend went to ask him for a remedy.</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>ちょうど天斉廟に、効く膏薬で「王一貼」と呼ばれる王道士がいた。友人は彼に薬を求めに行った。</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -47597,7 +49220,11 @@
           <t>Wang said, “I have never made a plaster for jealousy. There is a decoction that might help, but it works slowly. Do not expect an immediate cure.”</t>
         </is>
       </c>
-      <c r="D598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>王一貼は言った。「嫉妬に効く膏薬は知らないが、煎じ薬ならあるかもしれん。ただし効き目は遅く、すぐには治らない」</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -47637,7 +49264,11 @@
           <t>The friend asked, “What decoction? How does she take it?”</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>友人は尋ねた。「どんな薬で、どう飲むんだ？」</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -47677,7 +49308,11 @@
           <t>Wang replied, “It is called Jealousy-Curing Decoction. Take one fine autumn pear, two qian of rock sugar and one qian of aged tangerine peel. Boil them in three bowls of water until the pear is tender. Have her eat one pear each morning. Keep at it, and she will get better.”</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>王一貼は答えた。「『療妬湯』という。上等な秋梨一個、氷砂糖二銭、陳皮一銭を水三杯で煮込み、梨が柔らかくなればよい。毎朝梨を一個食べれば、そのうち治る」</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -47717,7 +49352,11 @@
           <t>“That costs next to nothing,” the friend said. “But will it really work?”</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>友人は言った。「大した手間ではないが、効くとは思えない」</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -47757,7 +49396,11 @@
           <t>Wang replied, “If one dose fails, give her ten. If it fails today, try tomorrow. If it fails this year, try again next year.”</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>王一貼は答えた。「一回で効かなければ十回飲め。今日効かなければ明日、今年効かなければ来年だ」</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -47797,7 +49440,11 @@
           <t>“After all, these ingredients soothe the lungs and aid the appetite. They are sweet, tasty and ease a cough. They will do her no harm. Once she is past a hundred, she must die someday. And once she is dead, she cannot be jealous. Then you will see it has worked!”</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>「どれも肺を潤して食欲を促す、害のない甘い薬だ。咳にもよく、おいしい。百歳まで飲めば、いずれ人は死ぬ。死んでしまえば嫉妬もしない。そのときには確かに効くだろう」</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -47837,7 +49484,11 @@
           <t>Ha, ha, ha! What sort of prescription is that?</t>
         </is>
       </c>
-      <c r="D610" t="inlineStr"/>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>ははは、そんな処方があるのか。</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -47877,7 +49528,11 @@
           <t>Ha, ha, ha! The Daoist does have a point.</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>ははは、道士の言うことも一理あるな。</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -47895,7 +49550,11 @@
           <t>Received one tael of silver.</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>収入：銀一両</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -47935,7 +49594,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -47975,7 +49638,11 @@
           <t>Doctor Li, please examine my daughter. She hardly eats or drinks, looks miserable all day and cannot stop coughing.</t>
         </is>
       </c>
-      <c r="D617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>李先生、娘を診てください。食事も取らず、沈んだ顔で咳ばかりしているんです。</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -48015,7 +49682,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -48055,7 +49726,11 @@
           <t>She is your daughter?</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>こちらは娘さんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -48095,7 +49770,11 @@
           <t>Why, of course! She has studied with me for two and a half years. She is a fine singer and dancer, the star of our Willow Moon House.</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>そうですよ。二年半も私について芸を学び、特に歌と踊りが得意な柳月坊の花魁です。</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -48135,7 +49814,11 @@
           <t>But look at her now. How is she supposed to entertain guests like this?</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>でも今のこの様子では、お客をもてなせません。</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -48175,7 +49858,11 @@
           <t>Please sit down, miss. I will take your pulse. Banxia, what are you doing here?</t>
         </is>
       </c>
-      <c r="D627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>お嬢さん、座ってください。脈を診ます。……半夏、ここで何をしている？</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -48215,7 +49902,11 @@
           <t>The young mistress sent me to keep an eye on you.</t>
         </is>
       </c>
-      <c r="D629" t="inlineStr"/>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>若奥様の代わりに、旦那様を見張っています。</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -48255,7 +49946,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -48295,7 +49990,11 @@
           <t>You have a deficiency of lung qi. Keep warm and avoid the wind. I will prescribe a Lung-Tonifying Decoction. In the mornings, practice the “si” sound of the Six Healing Sounds to ease the flow of qi in your chest.</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>肺気虚です。普段は風と寒さを避け、補肺湯で養生してください。朝は六字訣の「呬」の呼吸を練習し、胸の気を巡らせるとよいでしょう。</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -48335,7 +50034,11 @@
           <t>…Thank you, Doctor.</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>……ありがとうございます。</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -48375,7 +50078,11 @@
           <t>Is something troubling you?</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>何か悩みがあるのですか？</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -48415,7 +50122,11 @@
           <t>She eats and drinks well every day. What could she possibly be worried about?</t>
         </is>
       </c>
-      <c r="D639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>毎日おいしいものを食べさせているのに、何を悩むことがあるんです？</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -48455,7 +50166,11 @@
           <t>Thank you, Doctor. Come along, daughter.</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>先生、ありがとうございました。さあ、帰るよ。</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -48495,7 +50210,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -48513,7 +50232,11 @@
           <t>Received one tael of silver.</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>収入：銀一両</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -48553,7 +50276,11 @@
           <t>Doctor, what was wrong with the young woman who just left?</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>先生、さっきの娘さんは何の病気だったんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -48593,7 +50320,11 @@
           <t>And you are?</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>失礼ですが、あなたは？</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -48633,7 +50364,11 @@
           <t>I am an acquaintance of hers. I am worried about her health and came to ask.</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr"/>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>彼女の知人です。体が心配で、お尋ねに来ました。</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -48673,7 +50408,11 @@
           <t>She has a deficiency of lung qi. It is not serious, but she seems deeply troubled. Do you know why?</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>肺気虚ですが、大事には至りません。ただ何か悩みがあるようでした。事情をご存じですか？</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -48713,7 +50452,11 @@
           <t>Oh? There is a story here? Tell us!</t>
         </is>
       </c>
-      <c r="D654" t="inlineStr"/>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>おや、何か訳がありそうだ。聞かせてくれ。</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -48753,7 +50496,11 @@
           <t>To be honest, I met Feiyan at Willow Moon House. We fell in love at first sight and privately pledged to marry.</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>実は柳月坊で飛燕と出会い、一目で心を奪われました。二人で将来を誓い合っています。</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -48793,7 +50540,11 @@
           <t>I hoped to save five hundred taels to buy her freedom. But the madam doubled the price to a thousand. How could we ever raise that much silver?</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>銀五百両を貯めて身請けするつもりでした。ところが楼主が突然値を上げ、千両を要求してきたのです。そんな大金、どこから用意すれば……</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -48833,7 +50584,11 @@
           <t>No wonder her health has suffered from worry.</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>そのせいで、彼女は心労から体を壊したのでしょう。</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -48873,7 +50628,11 @@
           <t>Ah, another pair of ill-fated lovers.</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr"/>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>はあ、また不遇な恋人たちか。</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -48913,7 +50672,11 @@
           <t>Dear, we should find a way to help them.</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>あなた、二人を助けてあげましょうよ。</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -48953,7 +50716,11 @@
           <t>I would like to, but how?</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>助けたいが、どうすればいい？</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -48993,7 +50760,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr"/>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -49033,7 +50804,11 @@
           <t>You have come back, miss. Are you feeling any better?</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>お嬢さん、また来たのですね。具合は良くなりましたか？</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -49073,7 +50848,11 @@
           <t>Not really. I even coughed up a little blood the day before yesterday…</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>いいえ、ずっと良くならず、一昨日は咳に血まで混じりました……</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -49113,7 +50892,11 @@
           <t>Please sit. I will examine you again.</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>お掛けください。もう一度診ましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -49153,7 +50936,11 @@
           <t>Your longstanding qi deficiency has kept fluids from forming, and your condition has progressed to a deficiency of lung yin. I will prescribe Glehnia and Ophiopogon Decoction to nourish your fluids and lungs.</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>長く気虚が続き、津液を作れず、肺陰虚に悪化しています。沙参麦冬湯を処方して、肺を養いましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -49193,7 +50980,11 @@
           <t>Thank you, Doctor…</t>
         </is>
       </c>
-      <c r="D678" t="inlineStr"/>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>ありがとうございます……</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -49233,7 +51024,11 @@
           <t>But medicine can only treat your lungs. It cannot cure what weighs on your heart. That needs a different remedy.</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>ただ、この薬で治せるのは肺の病だけ。心の悩みには、別の手立てが必要ですよ。</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -49273,7 +51068,11 @@
           <t>What do you mean, madam?</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>奥様、それはどういう意味ですか？</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -49313,7 +51112,11 @@
           <t>When you left after your last visit, Young Master Wang came to ask about your health. He was terribly worried.</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>先日、あなたが帰った直後に王さんが病状を尋ねに来ました。とても心配していましたよ。</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -49353,7 +51156,11 @@
           <t>Women in my profession cannot work forever. We hope to find a kind husband and marry into a good family while we are still young.</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>この仕事は長く続けられません。若いうちに良い人と結ばれたい、それだけを願っています。</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -49393,7 +51200,11 @@
           <t>Wang truly loves me. We dreamed of buying my freedom and marrying, but I never imagined my foster mother would treat me this way…</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>王様は私を心から大切にしてくれます。身請けが済んだら結婚できると二人で喜んでいたのに、おかみさんがあんな仕打ちをするなんて……</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -49433,7 +51244,11 @@
           <t>I have an idea that may help the two of you marry.</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>二人が結ばれるための策があります。</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -49473,7 +51288,11 @@
           <t>Young mistress, what is it? Tell us!</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>若奥様、どんな策ですか？　早く教えてください！</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -49513,7 +51332,11 @@
           <t>Ask Madam Guo to come here tomorrow. Here is what we shall do…</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>明日、郭おばさんをここへ呼んでください。それから……</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -49531,7 +51354,11 @@
           <t>Wu Zhilan explained her plan to everyone.</t>
         </is>
       </c>
-      <c r="D695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>呉芷蘭は皆に考えた策を話した。</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -49571,7 +51398,11 @@
           <t>If you can see us through this, we will owe you as much as we owe our own parents.</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>先生にこの苦境を救っていただけるなら、一生の恩人です。</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -49589,7 +51420,11 @@
           <t>Received one tael of silver.</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>収入：銀一両</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -49607,7 +51442,11 @@
           <t>The next day.</t>
         </is>
       </c>
-      <c r="D699" t="inlineStr"/>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>翌日。</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -49647,7 +51486,11 @@
           <t>Doctor Li, why did you ask me to come?</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr"/>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>李先生、何の用で呼んだんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -49687,7 +51530,11 @@
           <t>After a careful examination yesterday, I found that Miss Xie has consumption of the lungs. We can ease it, but not cure it, and people close to her may catch it.</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>昨日詳しく診たところ、謝さんは肺癆でした。この病は和らげられても根治は難しく、近くの人にうつるおそれもあります。</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -49727,7 +51574,11 @@
           <t>What? What am I to do?</t>
         </is>
       </c>
-      <c r="D705" t="inlineStr"/>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>えっ？　どうしたらいいの？</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -49767,7 +51618,11 @@
           <t>You had best make arrangements soon and find your daughter a good home.</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>早めに娘さんの行く末を考え、良い嫁ぎ先を探してあげてください。</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -49807,7 +51662,11 @@
           <t>(In that case, I should let that young man have her cheaply before he finds out…)</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>（そういうことなら、あの若造が知らぬうちに安く引き取らせたほうがいい……）</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -49847,7 +51706,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D711" t="inlineStr"/>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -49887,7 +51750,11 @@
           <t>My benefactor! I have come to pay my respects.</t>
         </is>
       </c>
-      <c r="D713" t="inlineStr"/>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>恩人様！　お目にかかれて光栄です。</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -49927,7 +51794,11 @@
           <t>It is you. Please, get up. How are you and Miss Xie?</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>あなたでしたか。さあ、お立ちください。謝さんとはどうなりました？</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -49967,7 +51838,11 @@
           <t>Thanks to your help, we are married and have settled outside the city. We came today to thank you.</t>
         </is>
       </c>
-      <c r="D717" t="inlineStr"/>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>お力添えのおかげで夫婦になり、城の外に住まいを構えました。今日はお礼を申し上げに参りました。</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -50007,7 +51882,11 @@
           <t>I hear you are devoted to medical books. My late father practiced medicine all his life and left many notes. I would like you to have them.</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>先生は医学書がお好きと聞きました。父も生涯医者を務め、多くの手控えを残しました。今日、それをお贈りします。</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -50047,7 +51926,11 @@
           <t>That is wonderful! I could ask for nothing better.</t>
         </is>
       </c>
-      <c r="D721" t="inlineStr"/>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>それはありがたい！　願ってもない贈り物です。</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -50087,7 +51970,11 @@
           <t>Amitabha Buddha. My Dharma name is Xingkong. The Treatise on the Middle Way says: “Whatever arises through causes and conditions, I call emptiness. It is also a provisional name and the meaning of the Middle Way.” Such is the emptiness of dependent arising.</t>
         </is>
       </c>
-      <c r="D723" t="inlineStr"/>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>阿弥陀仏。拙僧は性空と申す。『中論』に「因縁より生じるものは空であり、仮の名であり、中道でもある」とある。これぞ縁起性空ですな。</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -50127,7 +52014,11 @@
           <t>Please, sit down, Master. What brings you to my clinic today? (He smells strongly of wine…)</t>
         </is>
       </c>
-      <c r="D725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>どうぞお掛けください。今日は何のご用で？（この僧、酒の匂いが強いな……）</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -50167,7 +52058,11 @@
           <t>I have not felt well lately. My ears ring and I often feel dizzy. Would you examine me, Doctor?</t>
         </is>
       </c>
-      <c r="D727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>近ごろ具合が悪く、耳鳴りやめまいがします。診ていただきたい。</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -50207,7 +52102,11 @@
           <t>You have a deficiency of kidney essence. Hmm… caused by excessive sexual activity…</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>腎精不足の証ですね。ええと……房事のしすぎが原因かと……</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -50247,7 +52146,11 @@
           <t>My good man, you must not say such things! I am a monk. How could I do that?</t>
         </is>
       </c>
-      <c r="D731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>おいおい、そんなことを言ってはいかん。拙僧は出家の身、そんなことをするはずがなかろう。</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -50287,7 +52190,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D733" t="inlineStr"/>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -50327,7 +52234,11 @@
           <t>It must be that I caught a chill while reciting sutras late at night.</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>夜に読経を頑張りすぎて、冷えたのに違いない。</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -50367,7 +52278,11 @@
           <t>Of course, Master. That is possible too.</t>
         </is>
       </c>
-      <c r="D737" t="inlineStr"/>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>ええ、おっしゃるとおりです。そういう可能性もありますね。</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -50407,7 +52322,11 @@
           <t>Yes. Do not spread any rumors. Here, take this money. What a young doctor you are…</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>うむ、人には言うでないぞ。ほら、これを受け取れ。まったく、この若い医者は……</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -50425,7 +52344,11 @@
           <t>Received two taels of silver.</t>
         </is>
       </c>
-      <c r="D740" t="inlineStr"/>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>収入：銀二両</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -50465,7 +52388,11 @@
           <t>Wow. Is that what they call a worldly monk?</t>
         </is>
       </c>
-      <c r="D742" t="inlineStr"/>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>わあ、あれが噂の生臭坊主ってやつ？</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -50505,7 +52432,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D744" t="inlineStr"/>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -50545,7 +52476,11 @@
           <t>He is a monk with a wandering eye, and you are lovestruck. You would make a fine pair.</t>
         </is>
       </c>
-      <c r="D746" t="inlineStr"/>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>あの人は生臭坊主、お前は色恋に夢中。お似合いだな。</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -50585,7 +52520,11 @@
           <t>You are asking for it!</t>
         </is>
       </c>
-      <c r="D748" t="inlineStr"/>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>もう、怒るよ！</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -50625,7 +52564,11 @@
           <t>Ow!</t>
         </is>
       </c>
-      <c r="D750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>痛っ！</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -50665,7 +52608,11 @@
           <t>He may not be a model monk, but I still need to diagnose his illness properly.</t>
         </is>
       </c>
-      <c r="D752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>まともな僧とは言えないが、病はきちんと考えなければ。</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -50705,7 +52652,11 @@
           <t>Young master! The young mistress has fainted in her room! Please come quickly!</t>
         </is>
       </c>
-      <c r="D754" t="inlineStr"/>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>若旦那、若奥様がお部屋で倒れました！　早く来てください！</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -50745,7 +52696,11 @@
           <t>Zhilan!</t>
         </is>
       </c>
-      <c r="D756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>芷蘭！！！</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -50785,7 +52740,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D758" t="inlineStr"/>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>…………</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -50825,7 +52784,11 @@
           <t>Husband, I have been dizzy lately, and sometimes I feel sick to my stomach. I do not know what is wrong…</t>
         </is>
       </c>
-      <c r="D760" t="inlineStr"/>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>あなた、最近めまいがして、ときどき吐き気もするの。どうしたのかしら……</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -50865,7 +52828,11 @@
           <t>You must be exhausted from running the household. Let me take your pulse.</t>
         </is>
       </c>
-      <c r="D762" t="inlineStr"/>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>家事で疲れすぎたんだろう。脈を診るよ。</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -50905,7 +52872,11 @@
           <t>Oh no… What illness does the young mistress have?</t>
         </is>
       </c>
-      <c r="D764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>うう……若奥様は何の病気なんですか？</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -50945,7 +52916,11 @@
           <t>Zhilan… We are going to have a child…</t>
         </is>
       </c>
-      <c r="D766" t="inlineStr"/>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>芷蘭……私たちに子どもができたんだ……</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -50985,7 +52960,11 @@
           <t>Really? Oh, that is wonderful! A boy or a girl?</t>
         </is>
       </c>
-      <c r="D768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>本当？　うれしい！　男の子？　女の子？</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -51025,7 +53004,11 @@
           <t>It is too early to tell. Boy or girl, it does not matter. We are going to be parents.</t>
         </is>
       </c>
-      <c r="D770" t="inlineStr"/>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>今はまだ分からないよ。どちらでもいい。私たち、親になるんだ。</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -51065,7 +53048,11 @@
           <t>Congratulations! The Bodhisattva has blessed us! I am going to tell the master the good news!</t>
         </is>
       </c>
-      <c r="D772" t="inlineStr"/>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>わあ、おめでとうございます！　ありがたいことです。旦那様にも知らせてきます！</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -51105,7 +53092,11 @@
           <t>No, no. What am I doing? Calm down and think again.</t>
         </is>
       </c>
-      <c r="D774" t="inlineStr"/>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>違う、私は何を考えているんだ。落ち着いて、もう一度よく考えよう。</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -51145,7 +53136,11 @@
           <t>It is the Lantern Festival today. Let us all go into town. I hear this year's celebrations are especially lively.</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>今日は元宵節だ。家族みんなで町へ出よう。今年の灯籠祭りはとりわけ賑やからしい。</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -51185,7 +53180,11 @@
           <t>Wonderful! Let us go.</t>
         </is>
       </c>
-      <c r="D778" t="inlineStr"/>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>やった！　早く行きましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -51225,7 +53224,11 @@
           <t>Come along.</t>
         </is>
       </c>
-      <c r="D780" t="inlineStr"/>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>行こう。</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -51265,7 +53268,11 @@
           <t>Wow, so many people! It is so lively!</t>
         </is>
       </c>
-      <c r="D782" t="inlineStr"/>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>わあ、人がいっぱい！　すごい賑わいだ！</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -51305,7 +53312,11 @@
           <t>You act as if you have never been out before.</t>
         </is>
       </c>
-      <c r="D784" t="inlineStr"/>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>まるで世間を知らない子どもね。</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -51345,7 +53356,11 @@
           <t>Just you wait! Stop running!</t>
         </is>
       </c>
-      <c r="D786" t="inlineStr"/>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>こら、待ちなさい！</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -51385,7 +53400,11 @@
           <t>There seems to be a play over there. Let us go and watch.</t>
         </is>
       </c>
-      <c r="D788" t="inlineStr"/>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>あちらで芝居をしているみたい。見に行きましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -51425,7 +53444,11 @@
           <t>Dear, there is a bridge over there. Let us cross it to ward off illness!</t>
         </is>
       </c>
-      <c r="D790" t="inlineStr"/>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>あなた、向こうに橋があるわ。渡って厄払いをしましょう！</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -51465,7 +53488,11 @@
           <t>Yes! Cross three bridges tonight, and we will be free of sickness all year.</t>
         </is>
       </c>
-      <c r="D792" t="inlineStr"/>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>行こう。今夜三つの橋を渡れば、一年病気知らずだ。</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -51505,7 +53532,11 @@
           <t>Son, when are you and Zhilan going to have a child?</t>
         </is>
       </c>
-      <c r="D794" t="inlineStr"/>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>ところで、東璧と芷蘭はいつ子どもを作るつもりだ？</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -51545,7 +53576,11 @@
           <t>Oh, Father, please do not worry about that.</t>
         </is>
       </c>
-      <c r="D796" t="inlineStr"/>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>父上、もう心配なさらないでください。</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -51585,7 +53620,11 @@
           <t>You two should go to the south gate and touch the lucky charm. I hear it really works.</t>
         </is>
       </c>
-      <c r="D798" t="inlineStr"/>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>あとで南門へ行って幸運を願うといい。よく効くらしいぞ。</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -51625,7 +53664,11 @@
           <t>Please, Father. Let us watch the play.</t>
         </is>
       </c>
-      <c r="D800" t="inlineStr"/>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>父上、その話はもう。芝居を見に行きましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -51665,7 +53708,11 @@
           <t>Master, they are performing The Purple Hairpin over there.</t>
         </is>
       </c>
-      <c r="D802" t="inlineStr"/>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>旦那様、あちらでは『紫釵記』を演じていますよ。</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -51683,7 +53730,11 @@
           <t>We thank the emperor for lantern light and moonlight; we thank Heaven for springtime and the turning year. Peace fills the realm. Hear the revelers sing! What splendid lanterns! The finest shine at the southern gate. Carriages crowd beneath red silk lanterns. The escort calls for a halt, and through the dusty shadows we wonder who has come.</t>
         </is>
       </c>
-      <c r="D803" t="inlineStr"/>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>皇恩に感謝せん、灯も月も華やかに。天恩に感謝せん、春も歳も栄えゆく。国泰民安の世に歌声は満ち、灯火の美しさは南天門が随一。絹の灯籠を掲げた車が行き交い、馬を止め、塵の中に誰の家かを眺める。</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -51723,7 +53774,11 @@
           <t>Husband, let us go solve the lantern riddles!</t>
         </is>
       </c>
-      <c r="D805" t="inlineStr"/>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>あなた、灯籠のなぞなぞを解きましょう！</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -51763,7 +53818,11 @@
           <t>Let us!</t>
         </is>
       </c>
-      <c r="D807" t="inlineStr"/>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>いいね！</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -51803,7 +53862,11 @@
           <t>There are so many! “A dot above a long stroke, a slant toward the south; a person in Nanyang, with an inch below.” Guess the Chinese character…</t>
         </is>
       </c>
-      <c r="D809" t="inlineStr"/>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>こんなにたくさん。これは「広い屋根の下に『付』がいる。さて何の字？」</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -51843,7 +53906,11 @@
           <t>I know! It is “府.”</t>
         </is>
       </c>
-      <c r="D811" t="inlineStr"/>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>分かった。「府」だね。</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -51883,7 +53950,11 @@
           <t>You are clever as ever, my dear. Ha, ha!</t>
         </is>
       </c>
-      <c r="D813" t="inlineStr"/>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>さすが芷蘭、頭がいいな。ははは。</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -51923,7 +53994,11 @@
           <t>Look at this one: “Heavy snow presses on a green pine.” Name a medicinal herb.</t>
         </is>
       </c>
-      <c r="D815" t="inlineStr"/>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>こっちは「大雪が青松を押す」。薬材の名前を当てるんだ。</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -51963,7 +54038,11 @@
           <t>I know this one. It is honeysuckle.</t>
         </is>
       </c>
-      <c r="D817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>これは分かる。「忍冬」だよ。</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -52003,7 +54082,11 @@
           <t>Wow! Fireworks!</t>
         </is>
       </c>
-      <c r="D819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>わあ、花火だ！</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -52043,7 +54126,11 @@
           <t>How beautiful.</t>
         </is>
       </c>
-      <c r="D821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>きれいだね。</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -52083,7 +54170,11 @@
           <t>Dongbi, Zhilan, let us sit at a stall and have some sweet rice balls.</t>
         </is>
       </c>
-      <c r="D823" t="inlineStr"/>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>東璧、芷蘭、露店で休んで元宵を食べよう。</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -52123,7 +54214,11 @@
           <t>You have spent a year treating patients at the clinic. How does it feel? Is it what you expected?</t>
         </is>
       </c>
-      <c r="D825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>医者として一年働いて、どうだった？　想像していたとおりか？</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -52163,7 +54258,11 @@
           <t>I do enjoy the work. I only wish it earned more. You and Zhilan have had to make sacrifices because of me…</t>
         </is>
       </c>
-      <c r="D827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>私はこの仕事が好きです。ただ収入が少なく、父上と芷蘭に苦労をかけてしまって……</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -52203,7 +54302,11 @@
           <t>As long as our family can live safely together, I have all I need. What would we do with more money?</t>
         </is>
       </c>
-      <c r="D829" t="inlineStr"/>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>家族みんなが無事に暮らせれば、私はそれで十分。そんなにお金があっても仕方ないわ。</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -52243,7 +54346,11 @@
           <t>Yes. Being together and well is enough.</t>
         </is>
       </c>
-      <c r="D831" t="inlineStr"/>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>そうだな。皆が無事なのが一番だ。</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -52283,7 +54390,11 @@
           <t>It is getting late. We should go home.</t>
         </is>
       </c>
-      <c r="D833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>さあ、もう遅い。家に帰ろう。</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -52323,7 +54434,11 @@
           <t>Doctor, please look at my son. He stares into space all day and does not answer when spoken to. He mutters to himself. It is downright uncanny…</t>
         </is>
       </c>
-      <c r="D835" t="inlineStr"/>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>先生、この子を診てください。一日中ぼんやりして、呼んでも返事をせず、何やら独り言をつぶやいているんです。気味が悪くて……</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -52363,7 +54478,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D837" t="inlineStr"/>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -52403,7 +54522,11 @@
           <t>Do not worry. Sit down and let me examine him.</t>
         </is>
       </c>
-      <c r="D839" t="inlineStr"/>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>落ち着いて。座って診せてください。</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -52443,7 +54566,11 @@
           <t>Your son has phlegm clouding the mind. I will prescribe Phlegm-Expelling Decoction to help him recover.</t>
         </is>
       </c>
-      <c r="D841" t="inlineStr"/>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>息子さんは痰迷心竅の証です。滌痰湯を処方して、調子を整えましょう。</t>
+        </is>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -52483,7 +54610,11 @@
           <t>How did he suddenly develop such a strange illness?</t>
         </is>
       </c>
-      <c r="D843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>元気だったのに、どうしてこんな病に？</t>
+        </is>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -52523,7 +54654,11 @@
           <t>Could the pressure of studying be too much for him?</t>
         </is>
       </c>
-      <c r="D845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>勉強の重圧が大きすぎたのでは？</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -52563,7 +54698,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -52603,7 +54742,11 @@
           <t>All he does is study. We take care of everything else. What pressure could he have?</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>この子は勉強だけして、ほかは何もしなくていいのよ。どんな重圧があるというの？</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -52643,7 +54786,11 @@
           <t>Besides, there are countless scholars in the world. Why would only he fall ill like this?</t>
         </is>
       </c>
-      <c r="D851" t="inlineStr"/>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>ほかにも勉強している子は大勢いるのに、どうしてこの子だけ？</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -52683,7 +54830,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -52723,7 +54874,11 @@
           <t>Many people seem perfectly well on the outside when they are suffering deeply within.</t>
         </is>
       </c>
-      <c r="D855" t="inlineStr"/>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>外からは普通に見えても、心に重い病を抱えている人は少なくありません。</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -52763,7 +54918,11 @@
           <t>Nonsense! You call him sick when he is not, just to sell him medicine.</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>でたらめを言うな。病気でもないのに薬を売りつけたいだけだろう。</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -52803,7 +54962,11 @@
           <t>We spent so much on your education that we even sold our land! All we ask is that you succeed and bring honor to the family. Why can you not live up to that?</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>うちはお前を学ばせるために大金を使い、畑まで売ったんだ。出世して家の名を上げてほしいだけなのに、どうして期待に応えてくれない？</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -52843,7 +55006,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -52883,7 +55050,11 @@
           <t>Sir, I too studied and sat the imperial examinations. Scholars face many hardships of their own.</t>
         </is>
       </c>
-      <c r="D863" t="inlineStr"/>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>私も科挙を受けたことがあります。学問をする者にも、さまざまな苦しみがあるのです。</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -52923,7 +55094,11 @@
           <t>Hardships? Are they harder than earning enough to feed a family? Who has it harder than us parents?</t>
         </is>
       </c>
-      <c r="D865" t="inlineStr"/>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>苦しみ？　家族を食べさせる私より苦しいと？　親ほど苦労している者がいるか？</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -52963,7 +55138,11 @@
           <t>The examinations are only six months away. You must do well this time, whatever it takes.</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr"/>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>試験まであと半年だ。今度こそ必ずしっかり勉強しなさい。</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -53003,7 +55182,11 @@
           <t>…</t>
         </is>
       </c>
-      <c r="D869" t="inlineStr"/>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -53043,7 +55226,11 @@
           <t>No, that is not right. I need to think carefully about the illness and the proper prescription.</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>違う。これは何の病か、どんな処方を出すべきか、よく考えなければ。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -20194,6 +20194,23 @@
 Licorice Root harmonizes the ingredients.</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>麻黄湯
+【出典】『傷寒論』
+【効能】発汗して表の邪を解き、肺気を巡らせて喘ぎを鎮める
+【主治】風寒表実証
+【構成】
+君：麻黄 三銭
+臣：桂枝 二銭
+佐：杏仁 二銭
+使：甘草 一銭
+【配伍】
+麻黄と桂枝を併用し、発汗と散寒の働きを強め、表実で汗が出ない状態を治す。
+麻黄と杏仁は肺気の宣発と下降を助け合い、寒邪が肺を塞いで起こる喘ぎに用いる。
+甘草は薬材全体を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -20253,6 +20270,22 @@
 [How the ingredients work together]
 Cinnamon Twig is acrid and disperses pathogenic influences from the defensive layer; White Peony Root is sour and astringent, protecting nutritive Yin. One disperses and the other gathers, harmonizing nutritive and defensive Qi without weakening healthy Qi or trapping the pathogenic influence.
 Fresh Ginger and Jujube work together to harmonize the Spleen and Stomach and support the formation of Qi and blood, the source of nutritive and defensive Qi.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>桂枝湯
+【出典】『傷寒論』
+【効能】肌表を解き、営と衛を調和させる
+【主治】風寒表虚証
+【構成】
+君：桂枝 三銭
+臣：白芍 三銭
+佐：生姜 三銭、大棗 二銭
+使：甘草 二銭
+【配伍】
+桂枝は衛の邪を散らし、白芍は営陰を収める。散らす働きと収める働きが営衛を整え、正気を傷めず邪も閉じ込めない。
+生姜と大棗は脾胃を整え、気血を生み、営衛を養う。</t>
         </is>
       </c>
     </row>
@@ -20322,6 +20355,26 @@
 Platycodon Root disperses Lung Qi, soothes the throat and relieves cough.
 Bamboo Leaf and Reed Rhizome clear Heat, generate body fluids and ease restlessness and thirst.
 Licorice Root harmonizes the ingredients while helping to clear Heat and ease throat pain.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>銀翹散
+【出典】『温病条弁』
+【効能】辛涼の薬で表の邪を透かし、熱を清め毒を解く
+【主治】風熱表証
+【構成】
+君：金銀花 一両、連翹 一両
+臣：牛蒡子 六銭、荊芥 四銭、薄荷 六銭、淡豆豉 五銭
+佐：桔梗 六銭、芦根 四銭、竹葉 四銭
+使：甘草 五銭
+【配伍】
+金銀花・連翹：風熱を散らし、熱を清め毒を解き、上焦の邪を外へ透かす。
+薄荷・牛蒡子：風熱を散らし、喉を清め、肺気を巡らせて咳を鎮める。
+荊芥穂・淡豆豉：温かい性質で発汗を促し、寒涼の薬で気の流れが滞るのを防ぐ。
+桔梗：肺気を巡らせ、喉を整え、咳を鎮める。
+淡竹葉・芦根：熱を清めて津液を生み、いらだちと渇きを和らげる。
+生甘草：諸薬を調和し、熱を清め、喉の痛みを和らげる。</t>
         </is>
       </c>
     </row>
@@ -20395,6 +20448,27 @@
 Pear Peel clears Heat, moistens Dryness, generates fluids and eases thirst.</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>桑杏湯
+【出典】『温病条弁』
+【効能】温燥を清めて肺気を巡らせ、肺を潤して咳を鎮める
+【主治】温燥証
+【構成】
+君：桑葉 一銭五分、杏仁 二銭
+臣：沙参 一銭
+佐：貝母 一銭、淡豆豉 一銭、山梔子 一銭、梨皮 一銭
+使：
+【配伍】
+桑葉：軽やかに上焦の温燥を外へ透かす。
+杏仁：肺気を下ろし、乾燥を潤して咳を鎮める。
+淡豆豉：表の邪を散らす。
+貝母：熱を清めて痰を除き、肺を潤す。
+沙参：陰と津液を養い、肺を潤す。
+山梔子：上焦の燥熱を清める。
+梨皮：熱と乾燥を和らげ、津液を生んで渇きを鎮める。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -20464,6 +20538,26 @@
 Licorice Root harmonizes the ingredients.</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>杏蘇散
+【出典】『温病条弁』
+【効能】涼燥を軽く散らし、肺気を整えて痰を除く
+【主治】涼燥証
+【構成】
+君：杏仁 三銭、蘇葉 三銭
+臣：半夏 三銭、前胡 三銭、陳皮 三銭
+佐：茯苓 二銭、桔梗 二銭、枳殻 二銭
+使：甘草 一銭
+【配伍】
+蘇葉：温かい性質で風寒と涼燥を軽く散らす。
+杏仁：乾燥を潤し、肺気を下ろして咳を鎮める。
+前胡：風を散らし、気を下ろして痰を除く。
+桔梗と枳殻：一方は気を上げ、他方は下ろして肺気を整える。
+半夏・陳皮・茯苓：湿を乾かして痰を除き、気と脾を整えて痰の生じる元を抑える。
+生甘草：諸薬を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -20525,6 +20619,23 @@
 Astragalus Root supports Lung and Spleen Qi, strengthens the Exterior and defensive Qi, and reduces sweating.
 White Atractylodes Rhizome strengthens Spleen Qi, helping Astragalus Root support original Qi and protect the body's surface.
 Saposhnikovia Root reaches the surface and disperses Wind. It allows the formula to strengthen the Exterior without retaining a pathogenic influence, and to dispel Wind without weakening healthy Qi.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>玉屏風散
+【出典】『究原方』
+【効能】気を補って表を固め、汗を止めて風を防ぐ
+【主治】衛気虚
+【構成】
+君：黄耆 一両
+臣：白朮 一両
+佐：防風 五銭
+使：
+【配伍】
+黄耆：肺と脾の気を大いに補い、体表を固めて汗を抑える。
+白朮：脾と気を補い、黄耆を助けて体表を守る。
+防風：肌表の風邪を散らす。表を固めながら邪を閉じ込めず、風を除きながら正気を傷めない。</t>
         </is>
       </c>
     </row>
@@ -20594,6 +20705,25 @@
 Prepared Licorice Root and Honey temper the strong toxicity of Aconite Root, harmonize the ingredients and ease spasms and pain.</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>烏頭湯
+【出典】『金匱要略』
+【効能】経絡を温めて寒を散らし、湿を除いて痛みを鎮める
+【主治】痛痺（寒痺）
+【構成】
+君：烏頭 二銭
+臣：麻黄 三銭
+佐：白芍 三銭、黄耆 三銭
+使：甘草 三銭、蜂蜜 一斤
+【配伍】
+烏頭：強い温熱の性質で経絡を温め、寒湿を追い払い、強い痛みを鎮める。
+麻黄：発汗して寒を散らし、経絡を通じさせて邪を外へ出す。
+黄耆：気を補って表を固め、辛散による消耗を防ぐ。
+白芍：血と営を養い、筋のひきつれを緩めて痛みを鎮める。
+炙甘草・蜂蜜：烏頭の強い毒性を和らげ、諸薬を調和し、痛みを緩める。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -20657,6 +20787,24 @@
 Anemarrhena Rhizome clears Heat and nourishes Yin, reinforcing Gypsum in clearing internal Heat.
 Cinnamon Twig warms and opens the channels, dispels Wind and harmonizes the nutritive layer, guiding the formula toward the joints. Its warmth also balances the cooling ingredients.
 Prepared Licorice Root and Non-Glutinous Rice support Qi and the Stomach, temper the cooling nature of Gypsum and Anemarrhena Rhizome, and protect Stomach Qi.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>白虎桂枝湯
+【出典】『金匱要略』
+【効能】熱を清めて経絡を通し、営を整えて風を除く
+【主治】熱痺
+【構成】
+君：石膏 二両
+臣：知母 六銭
+佐：桂枝 三銭、粳米 五銭
+使：甘草 三銭
+【配伍】
+生石膏：気分の強い熱を清め、火といらだちを除き、赤く腫れて熱を持つ関節に用いる。
+知母：熱を清め、陰を養って乾燥を潤し、石膏を助ける。
+桂枝：経絡を温めて通し、風を除いて営を整える。薬を関節へ導き、寒涼の薬で気血が滞るのを防ぐ。
+炙甘草・粳米：気と胃を養い、石膏と知母の冷やす性質を和らげる。</t>
         </is>
       </c>
     </row>
@@ -20724,6 +20872,25 @@
 Ephedra Herb and Cinnamon Twig warm the channels, disperse Cold and support the removal of Dampness.
 Chinese Angelica Root and Sichuan Lovage Rhizome nourish and move blood, open the channels and ease pain. Moving blood also helps address Wind.
 Licorice Root harmonizes the ingredients and supports the warm dispersal of Dampness.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>薏苡仁湯
+【出典】『太医院経験奇効良方大全』
+【効能】湿を除いて経絡を通し、風と寒を散らす
+【主治】着痺（湿痺）
+【構成】
+君：薏苡仁 一両
+臣：羌活 三銭、独活 三銭、麻黄 三銭、桂枝 三銭
+佐：当帰 二銭、川芎 二銭
+使：甘草 三銭
+【配伍】
+薏苡仁：水と湿を排し、脾を整えて痺れを除き、筋を緩める。重だるい湿痺に用いる。
+羌活・独活：風湿を除いて経絡を通し、全身の上下に働く。
+麻黄・桂枝：経絡を温めて寒を散らし、陽を通して湿を除く。
+当帰・川芎：血を養って巡らせ、経絡の痛みを和らげる。
+甘草：諸薬を調和し、湿を除く働きを助ける。</t>
         </is>
       </c>
     </row>
@@ -20797,6 +20964,27 @@
 Licorice Root harmonizes the ingredients and the nutritive and defensive layers.</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>防風湯
+【出典】『太平恵民和剤局方』
+【効能】風を除いて経絡を通し、寒と湿を散らす
+【主治】行痺（風痺）
+【構成】
+君：防風 五銭
+臣：桂枝 三銭、秦艽 三銭
+佐：当帰 二銭、川芎 二銭、葛根 三銭
+使：甘草 一銭
+【配伍】
+防風：風湿を除き経絡を巡って、場所の移る痺痛に用いる。
+桂枝：風寒を温めて散らし、経絡を通す。
+秦艽：風湿を除き、経絡の痛みを和らげる。
+当帰：血と営を養い、風を除いて経絡を通す。
+川芎：血を巡らせて経絡を通す。
+葛根：肌を解き、筋を緩める。
+甘草：諸薬と営衛を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -20862,6 +21050,24 @@
 Prepared Licorice Root harmonizes the ingredients, supports Qi and the middle, and moistens the Lung.</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>麻杏石甘湯
+【出典】『傷寒論』
+【効能】辛涼の薬で表を解き、肺熱を清めて喘ぎを鎮める
+【主治】肺熱壅盛
+【構成】
+君：麻黄 三銭
+臣：石膏 八銭
+佐：杏仁 三銭
+使：甘草 二銭
+【配伍】
+麻黄：温かい性質で肺気を開き、喘ぎを鎮め、表の邪を散らす。
+石膏：強い寒性で肺の熱を清め、津液を生んで渇きを鎮め、麻黄の温性を抑える。
+杏仁：肺気を下ろして喘ぎを鎮め、麻黄とともに肺気の上下を整える。
+炙甘草：諸薬を調和し、気と胃を守り、肺を潤す。</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -20927,6 +21133,24 @@
 Aster Root and Mulberry Root Bark direct Lung Qi downward, transform phlegm and ease cough without being overly drying.</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>補肺湯
+【出典】『備急千金要方』
+【効能】肺を補って気を益し、咳と喘ぎを鎮める
+【主治】肺気虚
+【構成】
+君：人参 三銭、黄耆 五銭
+臣：熟地黄 五銭
+佐：五味子 二銭、紫苑 三銭、桑白皮 三銭
+使：
+【配伍】
+人参・黄耆：肺気を大いに補い、表を固めて肺気虚の根本に働く。
+熟地黄：腎を潤して精を補い、肺気の源を養う。
+五味子：肺気と汗を収め、喘ぎや自汗を抑える。
+紫苑・桑白皮：肺気を下ろし、痰と咳を鎮める。潤いを保ちつつ、補っても滞らせない。</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -20990,6 +21214,24 @@
 Aged Tangerine Peel regulates Qi and dries Dampness so phlegm can be resolved as Qi moves freely.
 Poria supports the Spleen and drains Dampness, reducing the source of phlegm.
 Licorice Root harmonizes the ingredients, supports Qi and harmonizes the middle.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>二陳湯
+【出典】『太平恵民和剤局方』
+【効能】湿を乾かして痰を除き、気と胃を整える
+【主治】痰湿阻肺
+【構成】
+君：半夏 五銭
+臣：陳皮 五銭
+佐：茯苓 三銭
+使：甘草 一銭五分
+【配伍】
+半夏：温かく乾かす性質で湿と痰を除き、逆上する気と吐き気を抑える。
+陳皮：気を巡らせて湿と痰を除く。気が順調に巡れば痰も減る。
+茯苓：脾を整え湿を排し、痰の生じる元を抑える。
+甘草：諸薬を調和し、気を補って胃を整える。</t>
         </is>
       </c>
     </row>
@@ -21057,6 +21299,25 @@
 Mulberry Leaf gently disperses Lung Qi and clears Deficiency Heat.
 Hyacinth Bean strengthens the Spleen and nourishes the Stomach, supporting the source of body fluids.
 Licorice Root harmonizes the ingredients, supports Qi and harmonizes the middle.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>沙参麦冬湯
+【出典】『温病条弁』
+【効能】肺と胃を養い、津液を生んで乾燥を潤す
+【主治】肺陰虚
+【構成】
+君：沙参 三銭、麦門冬 三銭
+臣：玉竹 二銭、天花粉 一銭五分
+佐：扁豆 一銭五分、桑葉 一銭五分
+使：甘草 一銭
+【配伍】
+沙参・麦門冬：陰と肺を養い、津液を生んで渇きを鎮める。
+玉竹・天花粉：陰と津液を補い、乾燥と咳を和らげ、虚熱を清める。
+桑葉：肺気を軽く巡らせ、虚熱を散らす。
+扁豆：脾と胃を整えて津液の源を養う。
+甘草：諸薬を調和し、気と胃を整える。</t>
         </is>
       </c>
     </row>
@@ -21130,6 +21391,27 @@
 Fresh Ginger tempers the toxicity of Bile-Processed Arisaema and Pinellia Rhizome.</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>清気化痰丸
+【出典】『医方考』
+【効能】熱を清めて痰を除き、気を巡らせて咳を鎮める
+【主治】痰熱壅肺
+【構成】
+君：胆南星 一両五銭
+臣：半夏 一両五銭、瓜蔞仁 一両、黄芩 一両
+佐：杏仁 一両、陳皮 一両、枳実 一両、茯苓 一両
+使：生姜 三両
+【配伍】
+胆南星：熱と痰を清め、痰熱が肺にこもる状態に用いる。
+瓜蔞仁：熱と痰を除き、肺を潤して気を下ろし、胸のつかえを和らげる。
+黄芩：肺の熱を清め、胆南星を助ける。
+杏仁・半夏：肺気を下ろし、痰と咳を鎮める。
+陳皮・枳実：気を巡らせ、つかえを解く。
+茯苓：脾を整え湿を排し、痰の生じる元を抑える。
+生姜：胆南星と半夏の毒性を和らげる。</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -21201,6 +21483,27 @@
 Prepared Licorice Root harmonizes the formula, tempers Ephedra Herb and protects the middle. Alongside Fresh Ginger and Jujube, it helps protect nutritive Yin and fluids.</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>大青竜湯
+【出典】『傷寒論』
+【効能】発汗して表を解き、内側の熱も清める
+【主治】表寒裏熱
+【構成】
+君：麻黄 六銭
+臣：桂枝 二銭、石膏 一両
+佐：杏仁 三銭、生姜 三銭、大棗 三銭
+使：甘草 二銭
+【配伍】
+麻黄：強い発汗で表の寒を散らし、肺気を巡らせて喘ぎを鎮める。
+桂枝：麻黄を助け、体表の寒と全身の痛みを和らげる。
+石膏：肌と肺胃にこもる熱を清め、いらだちを鎮め、麻黄の温熱を抑える。
+杏仁：肺気を下ろし、麻黄とともに咳と喘ぎを鎮める。
+生姜：表を解き、胃を整える。
+大棗：中焦と津液を補い、強い発汗による消耗を防ぐ。
+炙甘草：諸薬を調和し、胃を守り、麻黄の強い働きを緩める。</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -21270,6 +21573,26 @@
 Prepared Licorice Root harmonizes the formula, supports the middle and tempers the stronger warming ingredients.</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>小青竜湯
+【出典】『傷寒論』
+【効能】表を解いて寒を散らし、肺を温めて水飲を除く
+【主治】表寒裏飲
+【構成】
+君：麻黄 三銭、桂枝 三銭
+臣：乾姜 二銭、細辛 二銭
+佐：白芍 三銭、五味子 二銭、半夏 三銭
+使：甘草 二銭
+【配伍】
+麻黄・桂枝：発汗して体表の風寒を散らし、肺気を巡らせて喘ぎを鎮める。
+乾姜・細辛：脾と肺を温め、内に潜む寒と水飲を除く。
+半夏：湿と痰を除き、逆上する気と咳を抑える。
+五味子：肺気を収めて咳を鎮め、温散する薬による肺気の消耗を防ぐ。
+白芍：陰と営を守り、温性の薬による陰血の消耗を防ぐ。
+炙甘草：諸薬を調和し、脾胃を守って強い温散を緩める。</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -21335,6 +21658,24 @@
 Prepared Licorice Root supports Qi, harmonizes the middle and brings the ingredients together.</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>四君子湯
+【出典】『太平恵民和剤局方』
+【効能】気を補い、脾を健やかにする
+【主治】脾気虚
+【構成】
+君：人参 四銭
+臣：白朮 三銭
+佐：茯苓 三銭
+使：甘草 二銭
+【配伍】
+人参：元気を大いに補い、脾を整える。
+白朮：脾を健やかにし、湿を乾かして人参を助ける。
+茯苓：脾を整えて湿を排し、心を落ち着かせる。
+炙甘草：気と胃を養い、諸薬を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -21400,6 +21741,24 @@
 Prepared Licorice Root supports Qi and harmonizes the formula; Fresh Ginger and Jujube are also described as harmonizing the Spleen and Stomach.</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>平胃散
+【出典】『太平恵民和剤局方』
+【効能】湿を乾かして脾を働かせ、気と胃を整える
+【主治】湿盛困脾
+【構成】
+君：蒼朮 三銭
+臣：厚朴 二銭
+佐：陳皮 二銭
+使：甘草 一銭
+【配伍】
+蒼朮：湿を乾かし、脾を整えて運化を助ける。
+厚朴：気を巡らせ、湿と濁りを除き、みぞおちと腹の張りを和らげる。
+陳皮：気と胃を整え、湿を乾かす。
+炙甘草：気と胃を養い、諸薬を調和させる。生姜と大棗も脾胃を整える。</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -21463,6 +21822,24 @@
 Ginseng Root supports Qi and the Spleen, addressing the underlying Spleen and Stomach Deficiency.
 White Atractylodes Rhizome strengthens the Spleen and dries Dampness, supporting the transport of food and fluids.
 Prepared Licorice Root supports Qi, harmonizes the middle and the ingredients, and eases spasmodic pain.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>理中丸
+【出典】『傷寒論』
+【効能】中焦を温めて寒を除き、気と脾を補う
+【主治】脾陽虚
+【構成】
+君：乾姜 五銭
+臣：人参 五銭
+佐：白朮 五銭
+使：甘草 五銭
+【配伍】
+乾姜：強い温熱の性質で中焦を温め、寒を除き、脾陽を助ける。
+人参：気と脾を補い、脾胃の虚弱を支える。
+白朮：脾を整え、湿を乾かして運化を助ける。
+炙甘草：気と胃を養い、諸薬を調和し、痛みを緩める。</t>
         </is>
       </c>
     </row>

--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -11271,6 +11271,26 @@
 Right Chi: Kidney Yang</t>
         </is>
       </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>【四診】
+四診とは、東洋医学で患者の状態を調べる四つの基本的な診察法で、望診・聞診・問診・切診からなる。医者は観察、聴覚や嗅覚、質問、触診から得られる情報をもとに、病因、病位、性質、正気と邪気の勢いを把握し、弁証と治療に役立てる。
+望診：顔色や姿勢、体形、舌の状態などを観察する。
+聞診：話し声、呼吸、咳などの音や異常な匂いを調べる。
+問診：病気の経過、主な症状、生活習慣や既往歴を尋ねる。
+切診：脈を診たり体に触れたりして、脈の特徴や局所の変化を調べる。
+【寸関尺】
+寸・関・尺は、手首の橈骨動脈に沿った三つの脈診部位である。それぞれを指で押さえ、脈の強弱、速さ、浮き沈み、滑らかさなどを確かめ、体の各部位や臓腑の状態を推し量る。
+【対応する臓腑】
+浮脈：表
+左寸：心
+左関：肝
+左尺：腎陰
+右寸：肺
+右関：脾
+右尺：腎陽</t>
+        </is>
+      </c>
     </row>
     <row r="484" ht="17" customHeight="1">
       <c r="A484" s="3" t="inlineStr">
@@ -11322,6 +11342,17 @@
 The eight principles are not mutually exclusive. A pattern may combine several qualities, such as Exterior Cold, Interior Heat or Deficiency Cold. As a condition develops, it may shift between Exterior and Interior, change from Cold to Heat, or vary between Deficiency and Excess. A physician therefore considers all four examinations together to understand the condition as a whole.</t>
         </is>
       </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>【八綱弁証】
+八綱弁証は、病状を分析する基本的な方法である。望・聞・問・切の四診で集めた情報を陰・陽・表・裏・寒・熱・虚・実の八つに整理し、病の位置や性質、正気と邪気の勢いを判断する。
+表裏：病位の浅深を見分ける。皮膚や経絡にあれば表、臓腑や気血に及べば裏と考える。
+寒熱：病の性質を見分ける。寒証では寒がって温かさを好み、渇きが少ない。熱証では熱感や渇き、いらだちが多い。
+虚実：正気の不足と邪気の強さを見分ける。虚証は正気や機能の低下、実証は邪気や病理的な停滞が強い状態をいう。
+陰陽：ほかの六綱を統括する。一般に表・熱・実は陽に、裏・寒・虚は陰に属する。
+八綱は別々に存在するわけではない。一つの病に表寒や裏熱、虚寒など複数の性質が同時に現れ、経過とともに表裏、寒熱、虚実も変わりうる。医者は四診を総合して病状の全体を捉える。</t>
+        </is>
+      </c>
     </row>
     <row r="486" ht="17" customHeight="1">
       <c r="A486" s="3" t="inlineStr">
@@ -11363,6 +11394,13 @@
           <t>YIN AND YANG
 Yin and Yang are a basic framework in traditional Chinese medicine for understanding the human body and changes in nature. Yin represents qualities that are relatively still, cool and inward directed, while Yang represents qualities that are relatively active, warm and outward directed. They are opposing yet interdependent, and their balance changes over time and with the environment.
 Cold and Heat, Exterior and Interior, Deficiency and Excess, and activity and stillness in the body can all be understood through Yin and Yang. When Yin and Yang remain in balance, the body can function normally; when either becomes excessive or deficient, illness may arise. In diagnosis, a physician identifies changes in Yin and Yang, locates the imbalance, then chooses an appropriate approach to restore harmony.</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>【陰陽】
+陰陽は、東洋医学で人体と自然の変化を理解するための基本的な考え方である。陰は比較的静かで冷たく内に向かう側面、陽は活動的で温かく外へ向かう側面を表す。二つは対立しながらも互いに依存し、時間や環境に応じて増減する。
+寒熱、表裏、虚実、動静も陰陽によって捉えられる。両者が調和していれば体は正常に働くが、どちらかが過剰または不足すると病が生じうる。診察ではその偏りを見極め、再び調和に向かう方法を考える。</t>
         </is>
       </c>
     </row>
@@ -11412,6 +11450,15 @@
 Exterior and Interior patterns can occur together. A shift from Exterior to Interior generally indicates that the pathogenic influence is moving deeper; a shift from Interior to Exterior may indicate that it is moving outward. A physician considers Cold and Heat, Deficiency and Excess, and information from all four examinations rather than judging by a single sign. After identifying the location, the general approach is to release an Exterior pattern or to address an Interior pattern according to its specific qualities.</t>
         </is>
       </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>【表裏】
+表裏は、八綱弁証で病の深さと進み方を判断する二つの綱領である。表証は邪が皮膚、筋肉の浅い部分や経絡にあり、外から邪を受けた初期に多い。裏証は邪が臓腑や気血など深部に及ぶ場合のほか、飲食、情緒、疲労による内傷から直接生じる場合もある。単なる体の外側と内側ではなく、病位と病勢を総合して表す。
+表証：悪寒と発熱、頭や体の痛み、鼻づまり、鼻水、咳、薄く白い舌苔、浮いた脈などが見られる。比較的急に始まり、経過は短いことが多い。
+裏証：熱感と渇き、いらだち、腹痛、嘔吐、下痢、便秘、排尿の異常、厚い舌苔や沈んだ脈など、現れ方は多様である。寒熱や虚実、影響を受けた臓腑によって症状が変わる。
+表証と裏証が併存することもある。表から裏への移行は邪の深入りを、裏から表への移行は邪が外へ出ることを示す場合がある。寒熱、虚実と四診の情報を合わせ、一つの症状だけで決めつけてはならない。表証には表を解く治法を、裏証には具体的な寒熱や虚実に応じた治法を用いる。</t>
+        </is>
+      </c>
     </row>
     <row r="490" ht="17" customHeight="1">
       <c r="A490" s="3" t="inlineStr">
@@ -11459,6 +11506,15 @@
 Cold patterns can be further classified as Excess Cold or Deficiency Cold; Heat patterns as Excess Heat or Deficiency Heat. A physician considers Exterior and Interior, Deficiency and Excess, and all four examinations rather than relying on one sign. Once the nature of the pattern is clear, the general approach is to warm Cold patterns and clear Heat patterns.</t>
         </is>
       </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>【寒熱】
+寒熱は、八綱弁証で病の性質を判断する二つの綱領である。寒証は寒邪の侵入や陽気の不足、熱証は熱邪、陽気の過剰、または陰液の不足などによって生じる。体温だけを指すのではなく、患者の状態全体から判断する。
+寒証：寒がって温かさを好み、手足の冷え、顔色の白さ、渇きの少なさ、薄く多い尿、柔らかい便、淡い舌と白い舌苔、遅い脈などが見られる。
+熱証：熱感があり涼しさを好み、顔の赤み、いらだち、冷たい飲み物を欲する渇き、少なく黄色い尿、便秘、赤い舌と黄色い舌苔、速い脈などが見られる。
+寒証には実寒と虚寒、熱証には実熱と虚熱がある。表裏や虚実、四診の情報を合わせ、一つの症状だけで判断しない。基本的には寒証を温め、熱証を清める方向で治法を選ぶ。</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="17" customHeight="1">
       <c r="A492" s="3" t="inlineStr">
@@ -11504,6 +11560,15 @@
 Deficiency pattern: Common signs include fatigue, weakness, a dull complexion, a weak voice, shortness of breath, spontaneous or night sweating, pain relieved by pressure, a pale tender tongue or little tongue coating, and a thin weak pulse. Specific signs vary according to whether Qi, blood, Yin or Yang is deficient.
 Excess pattern: Common signs include a sudden onset, restlessness, a loud voice, heavy breathing, abdominal distension that resists pressure, pronounced pain, abundant phlegm, constipation or difficulty urinating, a thick greasy tongue coating and a forceful pulse. Specific signs vary with the nature of the pathogenic influence and whether the pattern is Cold or Heat.
 Deficiency may involve Qi, blood, Yin or Yang; Excess may involve Qi stagnation, blood stasis, phlegm and dampness, or food accumulation. The two can coexist, and a condition can shift from Excess to Deficiency or develop Excess because of underlying Deficiency. A physician considers Exterior and Interior, Cold and Heat, and all four examinations rather than relying on one sign. The general approach is to support healthy Qi in Deficiency patterns and dispel pathogenic influences in Excess patterns.</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>【虚実】
+虚実は、八綱弁証で正気の強弱と邪気の勢いを判断する二つの綱領である。虚証は正気の不足や臓腑機能の低下、気血や陰陽の欠乏から生じる。実証は外邪、痰飲、瘀血、食積などが強く滞る状態である。単に体格の強弱ではなく、正邪の関係と病の状態を総合して表す。
+虚証：疲労、力のなさ、顔色の悪さ、弱い声、息切れ、自汗や寝汗、押すと和らぐ痛み、淡い舌や薄い舌苔、細く力のない脈などが見られる。気・血・陰・陽のどれが不足するかで症状も変わる。
+実証：急な発症、いらだち、大きな声、荒い呼吸、押すと痛む腹の張り、強い痛み、多量の痰、便秘や排尿困難、厚く粘る舌苔、力のある脈などが見られる。寒熱や邪の種類で症状は異なる。
+虚証には気虚、血虚、陰虚、陽虚があり、実証には気滞、血瘀、痰湿、食積などがある。虚実が混在したり、経過とともに実から虚へ、虚から実へ変わったりもする。表裏、寒熱と四診を合わせて見極め、虚には正気を補い、実には邪を除くことを基本とする。</t>
         </is>
       </c>
     </row>
@@ -11579,6 +11644,28 @@
 These correspondences do not mean that an organ is affected by only one season, climate or flavor. They describe possible relationships among the environment, diet, emotions and bodily functions. A physician may use them to observe how a condition arises and changes, while still considering all of the patient's signs when making a diagnosis.</t>
         </is>
       </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>【五行】
+五行は木・火・土・金・水という五つの性質を使い、自然と人体が関わりながら変化する様子を説明する考え方である。五種類の物質そのものではなく、成長、温熱、保持、収斂、潤いなどの特徴を表す。
+五行には相生と相克がある。木は火を生み、火は土、土は金、金は水、水は木を生む。木は土を抑え、土は水、水は火、火は金、金は木を抑える。肝は木、心は火、脾は土、肺は金、腎は水に対応する。臓腑は互いに養い制御して均衡を保ち、その関係が乱れると病が伝わることもある。
+【五行と五つの対応】
+五行は自然現象と人体機能を分類する方法でもある。木・火・土・金・水を成長、温熱、保持、収斂、蓄積に見立て、季節、気候、味、色、臓腑などを結びつけ、環境と体の変化を観察する。
+五行：木、火、土、金、水
+五季：春、夏、長夏、秋、冬
+五気：温、熱、平、涼、寒
+五味：酸、苦、甘、辛、鹹
+五色：青、赤、黄、白、黒
+五臓：肝、心、脾、肺、腎
+五腑：胆、小腸、胃、大腸、膀胱
+五官：目、舌、口、鼻、耳
+五志：怒、喜、思、悲、恐
+五体：筋、脈、肉、皮膚、骨
+五液：涙、汗、涎、鼻水、唾液
+春は万物が芽吹く木で、風、酸味、肝に対応する。夏は暑い火で、暑、苦味、心に対応する。長夏は湿気の多い土で、湿、甘味、脾に対応する。秋は収斂する金で、燥、辛味、肺に対応する。冬は蓄える水で、寒、鹹味、腎に対応する。
+こうした対応は、一つの臓腑が特定の季節や味だけに左右されるという意味ではない。環境、飲食、情緒と体の働きの関連を考える手がかりであり、診断には患者の症状全体を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="496" ht="17" customHeight="1">
       <c r="A496" s="3" t="inlineStr">
@@ -11624,6 +11711,14 @@
 Visceral Manifestations treats the body as an interconnected whole. Each system has its own functions and coordinates with others through Qi, blood, body fluids, the channels and the generating and restraining relationships of the Five Phases. The systems are also connected with the body's tissues, sense organs, emotions and natural environment. The zang and fu of traditional Chinese medicine are functional systems and cannot be equated directly with anatomical organs in modern medicine.</t>
         </is>
       </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>【蔵象】
+蔵象は、臓腑の生理的な働きと病理的な変化、相互の関係を扱う理論である。「蔵」は体内の臓腑、「象」はその働きが外に現れた徴候を指す。顔色、体形、感情、声、舌、脈などを観察して、臓腑の働きを推し量る。
+臓腑は五臓、六腑、奇恒の腑に分けられる。五臓は肝・心・脾・肺・腎で、精気を作り蓄える。六腑は胆・小腸・胃・大腸・膀胱・三焦で、飲食物を受け入れ運ぶ。奇恒の腑には脳・髄・骨・脈・胆・女子胞が含まれる。
+蔵象は人体を互いに結びついた全体として捉える。臓腑はそれぞれの働きを持つと同時に、気血津液、経絡、五行の関係を通じて協調し、体、感覚器官、情緒、自然環境とも関わる。ここでいう臓腑は機能的な体系であり、現代医学の解剖学的な器官と完全には一致しない。</t>
+        </is>
+      </c>
     </row>
     <row r="498" ht="17" customHeight="1">
       <c r="A498" s="3" t="inlineStr">
@@ -11669,6 +11764,14 @@
 Disruption of the Liver's free flow may be associated with low mood, irritability, distension in the chest and flanks, or poor appetite. Excessive Liver Yang or rising Liver fire may be associated with dizziness, headache, a flushed face and red eyes. A physician assesses Liver function in relation to Qi, blood, Yin and Yang and the other organs.</t>
         </is>
       </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>【肝】
+肝は五臓の一つで、五行では木に属し、胆と表裏の関係にある。東洋医学では、肝には疏泄をつかさどり、血を蔵する働きがあると考える。疏泄とは全身の気の巡りを整え、脾胃の運化、胆汁の排泄、感情の働きを促すことをいう。蔵血とは血液を蓄え、活動や休息に応じて血量を調節することをいう。
+肝は筋と関わり、その状態は爪に現れ、目に開竅する。感情では怒、体液では涙に対応する。肝血が十分なら筋は養われて手足は滑らかに動き、視力は明瞭で、爪は丈夫でつやがある。肝血が不足すると、目のかすみ、手足のしびれ、筋のひきつり、爪のつやの低下などが現れることがある。
+肝の疏泄が乱れると、気分の落ち込み、いらだちや怒りっぽさ、胸や脇の張り、食欲不振などが見られる。肝陽が過剰になったり肝火が上ったりすると、めまい、頭痛、顔のほてり、目の充血などが現れることがある。肝の状態は気血・陰陽とほかの臓腑の状態を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="17" customHeight="1">
       <c r="A500" s="3" t="inlineStr">
@@ -11714,6 +11817,14 @@
 Insufficient Heart Qi or weakened Heart Yang may be associated with palpitations, shortness of breath, fatigue, aversion to cold and cold limbs. Excessive Heart fire may be associated with restlessness and insomnia, sores in the mouth or on the tongue, and a red tongue tip. A physician assesses Heart function in relation to the vessels, mental activity, the tongue and the pulse.</t>
         </is>
       </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>【心】
+心は五臓の一つで、五行では火に属し、小腸と表裏の関係にある。東洋医学では、心には血脈をつかさどり、神を蔵する働きがあると考える。血脈をつかさどるとは、心気が血を脈の中に巡らせて全身を養うことをいう。神を蔵するとは、心が精神、意識、思考、感情、睡眠などと深く関わることをいう。
+心は脈と関わり、その状態は顔に現れ、舌に開竅する。感情では喜、体液では汗に対応する。心気と心血が十分なら血の巡りは滞りなく、顔色は血色よく、気力が充実し、意識は明瞭で言葉も正常に出る。心血が不足したり心神が養われなかったりすると、動悸、不眠、多夢、物忘れ、顔色の悪さなどが現れることがある。
+心気が不足したり心陽が衰えたりすると、動悸や息切れ、疲労感、寒がり、手足の冷えなどが見られる。心火が盛んになると、いらだちや不眠、口や舌のただれ、舌先の赤みなどが現れることがある。心の状態は血脈、精神状態、舌と脈の様子を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="502" ht="17" customHeight="1">
       <c r="A502" s="3" t="inlineStr">
@@ -11759,6 +11870,14 @@
 Insufficient Spleen Qi may reduce the production of nourishing substances from food and drink. It may also allow fluids to accumulate and form phlegm and dampness. If the Spleen fails to keep blood within the vessels, signs may include blood in the stool, bleeding beneath the skin or heavy menstrual bleeding. A physician assesses Spleen function together with the Stomach's ability to receive food, the production of Qi and blood, and fluid metabolism.</t>
         </is>
       </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>【脾】
+脾は五臓の一つで、五行では土に属し、胃と表裏の関係にある。東洋医学では、脾には運化、昇清、統血の働きがあると考える。運化とは飲食物を水穀の精微に変え、全身へ運ぶことをいう。昇清とはその精微な物質を上方へ送ること、統血とは脾気が血をつなぎとめて脈の中を正常に巡らせることをいう。
+脾は筋肉と関わり、四肢をつかさどり、その状態は唇に現れ、口に開竅する。感情では思、体液では涎に対応する。脾気が健やかに働けば消化は順調で、筋肉は充実し、手足には力があり、唇は血色がよい。脾の運化が衰えると、食欲不振、腹部の張り、軟便、体の重だるさ、手足の脱力などが現れることがある。
+脾気の不足は水穀の精微の生成を妨げ、水湿を停滞させて痰湿を生じることもある。統血ができなくなると、血便、皮下出血、月経過多などが現れることがある。脾の状態は胃の受納、気血の生成、水分代謝を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="504" ht="17" customHeight="1">
       <c r="A504" s="3" t="inlineStr">
@@ -11804,6 +11923,14 @@
 When the Lung fails to disperse and descend, signs may include coughing, wheezing, a blocked nose or increased phlegm. Disruption of its regulation of the water pathways may also lead to fluid accumulation, difficulty urinating or swelling. A physician assesses Lung function in relation to breathing, the voice, skin and hair, the nose and fluid metabolism.</t>
         </is>
       </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>【肺】
+肺は五臓の一つで、五行では金に属し、大腸と表裏の関係にある。東洋医学では、肺には気と呼吸をつかさどり、宣発・粛降を行い、水道を調節する働きがあると考える。肺は自然界の清気を吸い込み、宗気の生成に関わる。宣発によって気や津液を上方と体表へ送り、粛降によって下方へ巡らせ、呼吸を円滑に保つ。
+肺は皮膚と関わり、その状態は体毛に現れ、鼻に開竅する。感情では悲・憂、体液では鼻汁に対応する。肺気が十分なら呼吸は穏やかで声に力があり、皮膚や毛が養われ、外邪への抵抗力も保たれる。肺気が不足すると、息切れ、咳、弱い声、自汗、外邪を受けやすいなどの状態が現れることがある。
+肺の宣発・粛降が乱れると、咳、喘ぎ、鼻づまり、痰の増加などが見られる。水道を調節する働きが失われると、水分の停滞、尿の出にくさ、むくみなどが現れることもある。肺の状態は呼吸、声、皮膚と体毛、鼻、水分代謝を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="506" ht="17" customHeight="1">
       <c r="A506" s="3" t="inlineStr">
@@ -11849,6 +11976,14 @@
 Insufficient Kidney Yang may be associated with aversion to cold, cold limbs, swelling or increased urination at night. Insufficient Kidney Yin may be associated with tidal fever, night sweats, dryness of the mouth and throat, dizziness or ringing in the ears. If the Kidney fails to grasp Qi, breathing may be short and wheezing may occur with exertion. A physician assesses Kidney function in relation to essence, Qi, Yin and Yang, and fluid metabolism.</t>
         </is>
       </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>【腎】
+腎は五臓の一つで、五行では水に属し、膀胱と表裏の関係にある。東洋医学では、腎には精を蔵し、成長・発育と生殖、水分代謝、納気をつかさどる働きがあると考える。腎精は成長、発育、生殖を支える重要な物質的基盤である。腎が水をつかさどるとは全身の水分代謝の調節に関わること、納気とは肺を助けて呼吸の深さと安定を保つことをいう。
+腎は骨と関わり、髄を生じて脳を養い、その状態は髪に現れ、耳と二陰に開竅する。感情では恐、体液では唾液に対応する。腎精が十分なら骨と歯は丈夫で、聴力と髪のつやが保たれ、成長や生殖の働きも正常となる。腎精が不足すると、腰や膝のだるさ、耳鳴り、物忘れ、歯のぐらつき、発育の遅れなどが現れることがある。
+腎陽が不足すると寒がり、手足の冷え、むくみ、夜間尿の増加などが見られる。腎陰が不足すると、潮熱、寝汗、口や喉の乾き、めまい、耳鳴りなどが現れることがある。腎が気を納められないと、呼吸が浅くなり、動くと息切れする。腎の状態は精・気・陰・陽と水分代謝を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="17" customHeight="1">
       <c r="A508" s="3" t="inlineStr">
@@ -11894,6 +12029,14 @@
 When Qi is produced in insufficient amounts or its functions weaken, a Deficiency of Qi may arise, with signs such as fatigue, shortness of breath, a weak voice and spontaneous sweating. When its movement is obstructed, Qi stagnation may cause distension or pain. Abnormal upward movement, sinking or blockage of Qi may give rise to other patterns. A physician assesses Qi in relation to organ function, blood, body fluids and the overall pattern of signs.</t>
         </is>
       </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>【気】
+気は東洋医学の生命観における基本概念で、人体を構成し生命活動を支える精微な物質を指すとともに、臓腑や経絡の働きも表す。人体の気は主に先天の精、水穀の精微、自然界の清気から生じ、肺・脾・腎などの臓腑が協力して保っている。
+気には推動、温煦、防御、固摂、気化などの作用がある。血や津液を巡らせ、臓腑と体を温め、外邪を防ぎ、血液・汗・尿・便を適切に保ち、飲食物や水分の変化を促す。由来、分布、働きの違いによって、元気、宗気、営気、衛気などに分けられる。
+気の生成が足りなかったり働きが弱まったりすると気虚となり、疲れやすさ、息切れ、弱い声、自汗などが見られる。気の巡りが滞ると気滞となり、張りや痛みが現れる。気が逆に上る、下に落ちる、閉ざされる場合には、それぞれ気逆、気陥、気閉となる。気の状態は臓腑の働き、気血津液、全身の症状を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="510" ht="17" customHeight="1">
       <c r="A510" s="3" t="inlineStr">
@@ -11939,6 +12082,14 @@
 Insufficient blood may form a Blood Deficiency pattern, with signs such as a pale complexion, dizziness, palpitations and numb limbs. Impaired circulation may lead to Blood Stasis, with fixed stabbing pain, lumps or a darkened complexion. Heat or Cold affecting blood, or blood leaving the vessels, may produce other patterns. A physician assesses blood together with Qi, body fluids and the related organ functions.</t>
         </is>
       </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>【血】
+血とは東洋医学でいう、脈の中を巡って体を養い潤す赤い液体であり、生命活動を支える重要な基盤でもある。主に脾胃の運化で得られた水穀の精微から生じ、その生成には営気、津液、腎精も深く関わる。
+血は心気に動かされて脈を巡り、肝に蓄えられ調節される。また、脾気の固摂によって脈の外へ漏れ出ずに保たれる。血は臓腑、経絡、筋肉、皮膚、感覚器官を養い、精神や意識の働きを支える物質的基盤にもなる。血が十分で巡りがよければ顔色にはつやがあり、感覚と運動は正常で、精神も安定する。
+血が不足すると血虚となり、顔色の白さ、めまい、動悸、手足のしびれなどが見られる。血の巡りが悪いと血瘀となり、一定の場所の刺すような痛み、しこり、顔色のくすみなどが見られる。血熱、血寒、血が脈外に漏れることも、それぞれ異なる証を生む。血の状態は気、津液、関係する臓腑の働きと合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="512" ht="17" customHeight="1">
       <c r="A512" s="3" t="inlineStr">
@@ -11984,6 +12135,14 @@
 When body fluids are insufficient, signs may include thirst, a dry mouth or nose, dry skin, reduced urination or hard stools. If Jin is not distributed or eliminated properly, fluids may accumulate as dampness, phlegm and retained fluids, or swelling. Jin and Ye have different qualities but can transform into one another, so they are usually assessed together.</t>
         </is>
       </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>【津】
+津は人体の正常な水分の一部で、液と合わせて「津液」と呼ぶ。東洋医学では、津は比較的さらさらとして流動性が高く、主に皮膚、筋肉、体の開口部に分布し、血脈にしみ込んで血の構成と循環にも関わると考える。
+津は皮膚、筋肉、口や鼻などの器官を潤し、汗や尿の生成と排泄にも関わる。その分布は脾の運化、肺の宣発・粛降、腎の気化、三焦の水道が滞りなく通じているかどうかと深く関係する。
+津液が不足すると、喉の渇き、口や鼻の乾燥、肌の乾き、尿量の減少、便秘などが見られる。津の分布や排泄が乱れると、水湿や痰飲として停滞し、むくみを生じることもある。津と液には性質の違いがあるが、互いに変化し得るため、臨床では通常合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="514" ht="17" customHeight="1">
       <c r="A514" s="3" t="inlineStr">
@@ -12029,6 +12188,14 @@
 Insufficient Ye may be associated with stiff joints, dry skin, a dry mouth or throat, dizziness or loss of body mass. If its movement is disrupted, it may collect as phlegm, retained fluids or dampness. In general, Jin is thinner and moistens the body's surface, while Ye is thicker and nourishes deeper tissues, though the boundary between them is not absolute.</t>
         </is>
       </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>【液】
+液は人体の正常な水分の一部で、津と合わせて「津液」と呼ぶ。東洋医学では、液は比較的濃く、流動性が低く、主に臓腑、関節、骨髄、脳髄など体の深い部分に分布すると考える。
+液は臓腑を養い、関節の動きを滑らかにし、骨髄や脳髄を満たして深部の組織を潤す。液の生成、分布、排泄にも脾、肺、腎、三焦などの臓腑が協調して働く必要がある。
+液が不足すると、関節の動かしにくさ、肌の潤いの低下、口や喉の乾燥、めまい、やせなどが現れることがある。液の巡りが乱れると、痰飲や水湿などの病的なものとして停滞する場合もある。一般に津は薄くて体表を潤し、液は濃くて体内を養うが、両者の間に厳密な境界はない。</t>
+        </is>
+      </c>
     </row>
     <row r="516" ht="17" customHeight="1">
       <c r="A516" s="3" t="inlineStr">
@@ -12074,6 +12241,14 @@
 Each influence has its own characteristic effects, but the signs of illness also depend on a person's constitution, environment, course of illness and organ functions. A physician considers Exterior and Interior, Cold and Heat, Deficiency and Excess, and information from all four examinations. A season or single symptom alone cannot establish which influence is involved.</t>
         </is>
       </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>【外感六邪】
+外感六邪とは、風・寒・暑・湿・燥・熱という六種類の外から来る病因の総称で、「六淫」とも呼ばれる。これらは本来、自然界の正常な気候変化である「六気」を指す。しかし気候の変化が激しすぎる、通常と異なる、あるいは人体の正気や適応力が低下した場合、病因となり得る。
+外感六邪は通常、皮膚や毛、口や鼻から体に入り、季節や地域によって現れやすさが異なる。たとえば春は風、冬は寒、長夏は湿、秋は燥が多い。六邪は単独でも病を起こすが、互いに結びついて風寒、風熱、寒湿、湿熱などの証を生じ、条件によっては互いに変化することもある。
+邪気ごとに病の起こし方には特徴があるが、実際の症状は体質、環境、経過、臓腑の状態によっても変わる。医者は表裏・寒熱・虚実と望診・聞診・問診・切診で得た情報を総合し、季節や一つの症状だけで邪気の種類を決めない。</t>
+        </is>
+      </c>
     </row>
     <row r="518" ht="17" customHeight="1">
       <c r="A518" s="3" t="inlineStr">
@@ -12119,6 +12294,14 @@
 Common signs associated with Wind include aversion to drafts, fever, headache, a blocked nose, cough, sweating and itching. Because Wind readily combines with other influences, it is sometimes called the forerunner of many illnesses. Combined patterns include Wind-Cold, Wind-Heat, Wind-Dampness and Wind-Dryness.</t>
         </is>
       </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>【風邪】
+風邪は外感六邪の一つで、春と対応するが、ほかの季節にも現れる。東洋医学では風を陽の邪気と捉え、軽く上へ昇り、体表を開きやすい性質があると考える。頭や顔、体表、肺衛を侵しやすいため、そこでの症状が多い。
+風邪には「善行数変」という特徴がある。「善行」は関節の痛みが移動するように症状の場所が定まらないこと、「数変」は発病が急で症状も速く変わることをいう。また動きを生じさせる性質があり、めまい、震え、けいれん、手足の動きの異常などが現れる場合もある。
+風邪による症状には、風に当たるのを嫌がる、発熱、頭痛、鼻づまり、咳、発汗、皮膚のかゆみなどがある。ほかの邪気と結びつきやすいため「百病の長」とも呼ばれ、風寒、風熱、風湿、風燥などの証が見られる。</t>
+        </is>
+      </c>
     </row>
     <row r="520" ht="17" customHeight="1">
       <c r="A520" s="3" t="inlineStr">
@@ -12164,6 +12347,14 @@
 When Cold affects the surface, common signs include marked aversion to cold, mild fever, no sweating, headache and body aches, a clear runny nose, a thin white tongue coating and a floating tight pulse. If Cold penetrates deeper, signs may include cold pain in the stomach or abdomen, vomiting, diarrhea or cold limbs. A physician also distinguishes external Cold from internal Cold and considers where the pattern is located.</t>
         </is>
       </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>【寒邪】
+寒邪は外感六邪の一つで、冬に対応し、急な気温低下、薄着、寒い場所に長くいることなどで体に入りやすい。東洋医学では寒を陰の邪気と捉え、人体の陽気を傷つけ、体を温めたり気血を動かしたりする働きを妨げると考える。
+寒邪には凝滞と収引という特徴がある。凝滞は気血の巡りを滞らせて強い痛みを生じやすいこと、収引は皮膚のきめや筋・経絡を縮ませて、汗が出ない、手足がこわばる、関節が曲げ伸ばししにくいといった状態を生むことをいう。
+寒邪が体表を侵すと、強い悪寒、軽い発熱、無汗、頭痛や体の痛み、透明な鼻水、薄く白い舌苔、浮緊の脈などが見られる。臓腑の奥へ入ると、みぞおちや腹の冷える痛み、嘔吐、下痢、手足の冷えなどが現れることもある。弁証と治療では外寒と内寒、寒邪のある場所を見分ける必要がある。</t>
+        </is>
+      </c>
     </row>
     <row r="522" ht="17" customHeight="1">
       <c r="A522" s="3" t="inlineStr">
@@ -12209,6 +12400,14 @@
 Because summers are often hot and humid, Summer Heat may occur together with Dampness in a Summer Heat-Dampness pattern. Along with fever and thirst, signs may include chest tightness, nausea, poor appetite, heaviness, diarrhea and a greasy tongue coating. The relative contribution of Heat and Dampness is assessed in each case.</t>
         </is>
       </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>【暑邪】
+暑邪は外感六邪の一つで、夏に特有の邪気である。炎天下や高温の場所に長くいたり、暑い中で働きすぎたりすると生じやすい。東洋医学では暑を陽の邪気と捉え、熱く上昇・発散する性質によって体表が開き、大量の汗をかくと考える。
+暑邪は気と津液を消耗させやすく、高熱、顔の赤み、いらだち、喉の渇き、大量の発汗、脱力、息切れ、少量で黄色い尿などが見られる。ひどい場合は、めまい、吐き気、突然倒れる、意識の異常なども起こり得る。
+夏は暑さと湿気が重なることが多く、暑邪が湿邪とともに体に入ると「暑湿」となる。発熱や喉の渇きのほか、胸のつかえ、吐き気、食欲不振、体の重だるさ、下痢、ねっとりした舌苔などが見られる。弁証と治療では暑熱と湿邪のどちらが強いかを判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="524" ht="17" customHeight="1">
       <c r="A524" s="3" t="inlineStr">
@@ -12254,6 +12453,14 @@
 Common signs associated with Dampness include chest tightness, fullness in the upper abdomen, poor appetite, nausea, bloating, loose stools, heavy limbs, aching joints and a thick greasy tongue coating. Dampness may combine with Wind, Cold or Heat to form Wind-Dampness, Cold-Dampness or Damp-Heat patterns.</t>
         </is>
       </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>【湿邪】
+湿邪は外感六邪の一つで、長夏に対応し、湿った気候、雨にぬれること、水の中を歩くこと、湿気の多い環境で長く過ごすことなどと関係する。東洋医学では湿を陰の邪気と捉え、気の巡りを妨げ、陽気を傷つけ、脾の運化にも影響すると考える。
+湿邪には重濁、粘滞、下降しやすいという特徴がある。重濁は体が重く、頭を包まれるように重く感じ、手足がだるくなることをいう。粘滞は症状が長引き、分泌物がねばつくこと、下降しやすいとは体の下部に症状が出やすいことをいう。
+湿邪では胸やみぞおちのつかえ、食欲不振、吐き気、腹の張り、軟便、手足の重さ、関節の鈍痛、厚くねっとりした舌苔などが見られる。風・寒・熱とも結びつき、風湿、寒湿、湿熱などの異なる証を生じる。</t>
+        </is>
+      </c>
     </row>
     <row r="526" ht="17" customHeight="1">
       <c r="A526" s="3" t="inlineStr">
@@ -12299,6 +12506,14 @@
 Dryness may be Warm or Cool. Warm Dryness tends to include Heat signs, such as fever, slight aversion to drafts and thirst. Cool Dryness tends to include Cold signs, such as aversion to cold, headache and no sweating. A physician considers the season, Cold and Heat signs, and the extent of fluid depletion together.</t>
         </is>
       </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>【燥邪】
+燥邪は外感六邪の一つで、秋に対応する。乾いた気候や、環境の変化に適応するだけの津液が足りないときに見られる。東洋医学では燥邪は乾く性質を持ち、津液を傷つけやすく、肺も侵しやすいと考える。
+津液が損なわれると、口や鼻、喉の乾き、肌や髪の潤いの低下、硬い便、尿量の減少などが見られる。肺は潤いを好み乾燥を嫌う繊細な臓であるため、燥邪が肺を侵すと、痰の少ない乾いた咳や、粘って出にくい痰などが現れることもある。
+燥邪は温燥と涼燥に分けられる。温燥には発熱、軽い悪風、喉の渇きなど熱の徴候が多く、涼燥には悪寒、頭痛、無汗など寒の徴候が多い。季節、寒熱、津液が傷ついた程度を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="528" ht="17" customHeight="1">
       <c r="A528" s="3" t="inlineStr">
@@ -12342,6 +12557,14 @@
 Heat is one of the six external pathogenic influences and is also associated with Fire. Traditional Chinese medicine regards it as a Yang influence that burns and rises, producing signs of excessive Yang heat. Heat may enter from outside or develop when another influence transforms inside the body. A more severe form is often described as Fire.
 Heat may deplete Qi and body fluids. Common signs include high fever, thirst for cold drinks, heavy sweating, weakness, scant dark yellow urine and hard stools. Because Heat rises, it may also cause upper-body signs such as a flushed face, red eyes, a swollen sore throat, or sores in the mouth and on the tongue.
 Heat may also stir Wind, disturb the blood or contribute to pus formation. Extreme Heat that stirs Wind may cause convulsions or a stiff neck. Heat that drives blood out of its normal course may cause bleeding or rashes. Concentrated Heat may produce sores with redness, swelling, warmth and pain. A physician considers the location, course and extent of fluid depletion when assessing Heat.</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>【熱邪】
+熱邪は外感六邪の一つで、火邪とも呼ばれる。東洋医学では熱を陽の邪気と捉え、熱く上へ昇る性質を持ち、体内の陽熱が盛んな状態を生みやすいと考える。外から侵入するほか、ほかの邪気が体内で変化して生じることもあり、重くなったものを火邪と呼ぶことが多い。
+熱邪は気と津液を消耗させやすい。高熱、冷たい飲み物を欲する喉の渇き、多汗、脱力、少量で黄色い尿、硬い便などが見られる。また上へ燃え上がる性質により、顔の赤み、目の充血、喉の腫れと痛み、口や舌のただれなど、体の上部に症状が出やすい。
+熱邪はさらに風を生じさせ、血を動かし、組織を傷つけて膿を生じさせることがある。熱が極まって風を生じるとけいれんや首のこわばり、熱が血を押し動かすと出血や発疹、局所に熱邪が集まると赤み・腫れ・熱感・痛みを伴うできものが見られる。病の場所、経過、津液の損傷を合わせて判断する。</t>
         </is>
       </c>
     </row>
@@ -12391,6 +12614,15 @@
 The seven emotions may directly affect the internal organs and contribute to Qi stagnation, blood stasis, phlegm and dampness, or an imbalance of Yin and Yang. The pattern varies with the person, the intensity of the emotion and its duration. A physician considers emotional changes, organ-related signs and information from all four examinations together.</t>
         </is>
       </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>【七情内傷】
+七情内傷とは、喜・怒・憂・思・悲・恐・驚という七つの感情によって病が生じることをいう。七情は本来、外界に対する正常な感情反応であり、通常は病因にならない。しかし感情が強すぎる、急に生じる、長く続くなどして自分で調節できなくなると、臓腑や気血に影響して内傷の原因となり得る。
+東洋医学では七情と五臓を結びつけ、喜は心、怒は肝、思は脾、憂と悲は肺、恐は腎に対応すると考える。感情が過度になれば対応する臓腑が影響を受けやすく、反対に臓腑の働きが乱れることで感情が変化する場合もある。
+七情は主に気の巡りを乱して病を生じ、「怒れば気は上り、喜べば気は緩み、悲しめば気は消え、恐れれば気は下り、驚けば気は乱れ、思えば気は結ぶ」とまとめられる。たとえば怒りすぎると頭痛、顔の赤み、胸や脇の張り、思い悩みすぎると食欲不振、腹の張り、不眠、強く驚き恐れると動悸、心の落ち着かなさ、大小便の異常などが現れることがある。
+七情内傷は内側の臓腑に直接影響し、気滞、血瘀、痰湿、陰陽の乱れにもつながり得る。感情は互いに影響し合い、症状も体質、感情の強さと持続時間によって変わる。感情の変化、臓腑に関わる症状、四診で得た情報を総合して判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="532" ht="17" customHeight="1">
       <c r="A532" s="3" t="inlineStr">
@@ -12436,6 +12668,14 @@
 When excessive joy affects the Heart, signs may include palpitations, insomnia, scattered thoughts, poor concentration or unusually heightened excitement. Severe cases may include confusion. A physician considers changes in emotion, signs relating to the Heart and spirit, and the person's constitution.</t>
         </is>
       </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>【喜】
+喜は七情の一つで、願いがかなったり楽しいことに出会ったりしたときに生じる正常な感情である。適度な喜びは気分を晴らし、気血の巡りを穏やかにして心身に良い働きをする。東洋医学では喜は心と対応し、正常な喜びは心気を整えると考える。
+喜びすぎたり突然大きな喜びを感じたりすると、心気が散り、心神が安定を失うことがあり、これを「喜べば気は緩む」という。「緩む」には気の巡りが穏やかになる意味もあるが、過度になると気が緩みすぎて集中できなくなる意味も含まれる。
+過度な喜びが心を傷つけると、動悸、不眠、気が散る、集中力の低下、異常な興奮などが現れ、重い場合には意識がぼんやりすることもある。喜びが原因かどうかは、感情の変化、心神の状態、体質を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="534" ht="17" customHeight="1">
       <c r="A534" s="3" t="inlineStr">
@@ -12481,6 +12721,14 @@
 When anger affects the Liver, signs may include a distending headache, a flushed face and red eyes, irritability, fullness in the chest and flanks, a bitter taste or dizziness. Prolonged stagnation of Liver Qi may also affect the Spleen and Stomach, causing poor appetite or bloating. A physician distinguishes Liver Qi stagnation, rising Liver fire and excessive Liver Yang.</t>
         </is>
       </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>【怒】
+怒は七情の一つで、挫折、抑圧、不公平な扱いなどに対して生じる正常な感情である。適度に怒りを表すことは感情の発散につながるが、長く抑え込む、頻繁に怒る、突然激怒することは気の巡りに影響し得る。
+東洋医学では怒は肝と対応する。肝は疏泄によって気の巡りを整えるが、怒りすぎるとその働きが乱れ、気が逆に上へ昇る。これを「怒れば気は上る」という。
+怒りが肝を傷つけると、頭の張りや痛み、顔の赤み、目の充血、いらだち、胸や脇の張り、口の苦さ、めまいなどが見られる。肝気の停滞が続けば脾胃にも影響し、食欲不振や腹の張りが現れることがある。肝気鬱結、肝火上炎、肝陽上亢などの違いを見分ける必要がある。</t>
+        </is>
+      </c>
     </row>
     <row r="536" ht="17" customHeight="1">
       <c r="A536" s="3" t="inlineStr">
@@ -12526,6 +12774,14 @@
 When worry affects the Lung, signs may include chest tightness, shortness of breath, uneven breathing, a weak voice, fatigue or frequent sighing. If the Spleen and Stomach are also affected, poor appetite, bloating and weakness may occur. A physician considers how long the worry has lasted and signs associated with the Lung and Spleen.</t>
         </is>
       </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>【憂】
+憂は七情の一つで、心配、懸念、不安な境遇から生じる憂鬱な感情を主に指す。一時的な心配は正常な心の働きだが、長く心配し続けると気の巡りが抑えられることがある。
+東洋医学では憂は肺と深く関わる。過度な心配は肺気を傷つけ、肺の宣発・粛降を乱しやすい。心配が長引けば脾の運化にも影響し、気血の生成が不足することがある。
+憂いが肺を傷つけると、胸のつかえ、息切れ、呼吸のしづらさ、弱い声、疲労感、ため息が多いなどの状態が現れることがある。脾胃に影響すると食欲の低下、腹の張り、脱力なども見られる。心配が続いた期間と肺や脾に関わる症状を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="538" ht="17" customHeight="1">
       <c r="A538" s="3" t="inlineStr">
@@ -12571,6 +12827,14 @@
 When pensiveness affects the Spleen, signs may include poor appetite, bloating, loose stools, weakness and mental fatigue. If the Heart and Spleen are both affected, palpitations, forgetfulness, insomnia and frequent dreams may also occur. A physician considers diet, sleep and mental state together.</t>
         </is>
       </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>【思】
+思は七情の一つで、思考、計画、集中などの精神活動を主に指す。通常の思考は学習や問題への対処に役立つが、考えすぎ、長く頭を使い続ける、同じことを繰り返し思い悩む場合、気の巡りに影響し得る。
+東洋医学では思は脾と対応する。考えすぎは気を停滞させやすく、「思えば気は結ぶ」といい、脾の運化も妨げて飲食物を気血津液へ正常に変えられなくなることがある。
+思い悩むことが脾を傷つけると、食欲不振、腹の張り、軟便、脱力、精神的な疲れなどが見られる。心と脾の双方に影響すると、動悸、物忘れ、不眠、多夢なども現れることがある。食事、睡眠、精神状態を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="540" ht="17" customHeight="1">
       <c r="A540" s="3" t="inlineStr">
@@ -12616,6 +12880,14 @@
 Signs associated with prolonged grief may include low spirits, shortness of breath, fatigue, a weak voice, chest tightness, crying and loss of appetite. Prolonged grief may also affect the Heart or Spleen. Worry and Grief are both linked with the Lung, but Worry centers on concern and apprehension, while Grief centers on sorrow and loss.</t>
         </is>
       </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>【悲】
+悲は七情の一つで、喪失、別れ、大きな打撃を受けたときに生じる悲しみである。適度な悲しみは正常な感情反応だが、強すぎたり長く癒えなかったりすると、人体の気を消耗させ、心身を徐々に弱らせることがある。
+東洋医学では悲は肺と対応し、悲しみすぎると肺気を消耗させる。これを「悲しめば気は消える」という。肺気が損なわれると、気と呼吸をつかさどる働きや宣発・粛降にも影響し得る。
+過度の悲しみでは、気分の落ち込み、息切れ、脱力、弱い声、胸のつかえ、涙、食欲の低下などが見られる。長引けば心や脾にも影響することがある。憂も悲も肺に関係するが、憂は心配や懸念、悲は喪失による痛みに重点がある。</t>
+        </is>
+      </c>
     </row>
     <row r="542" ht="17" customHeight="1">
       <c r="A542" s="3" t="inlineStr">
@@ -12661,6 +12933,14 @@
 When fear affects the Kidney, signs may include soreness or weakness in the lower back and knees, unease, bed-wetting, urinary incontinence or changes in urination and bowel movements. Prolonged fear may also deplete Kidney essence and be associated with forgetfulness, ringing in the ears or loss of resolve. A physician considers the cause and duration of fear together with Kidney-related signs.</t>
         </is>
       </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>【恐】
+恐は七情の一つで、危険や脅威、未知のものに直面したときの恐怖である。適度な恐怖は警戒して危険を避ける助けとなるが、長く恐れ続けたり突然強く脅かされたりすると、臓腑の気の巡りを乱すことがある。
+東洋医学では恐は腎と対応する。恐れすぎると腎気が安定を失い、気が下へ落ち込む。これを「恐れれば気は下る」といい、腎の封蔵や大小便を保持する働きにも影響する。
+恐れが腎を傷つけると、腰や膝のだるさ、心の落ち着かなさ、夜尿、尿失禁、大小便の異常などが現れることがある。長期の恐怖は腎精も消耗させ、物忘れ、耳鳴り、意欲の低下を生む場合がある。恐れの原因、続いた期間、腎に関わる症状を合わせて判断する。</t>
+        </is>
+      </c>
     </row>
     <row r="544" ht="17" customHeight="1">
       <c r="A544" s="3" t="inlineStr">
@@ -12704,6 +12984,14 @@
 Fright is one of the seven emotions. It is an abrupt emotional response to an unexpected event, sound or danger. It differs from Fear: Fright follows a sudden stimulus that a person was not prepared for, while Fear is more often a response to a known or anticipated threat.
 In traditional Chinese medicine, Fright primarily affects the Heart and spirit. It may disorder the movement of Qi, described as 'fright disorders Qi.' After a sudden scare, the spirit may become unsettled and the movement of Qi and blood may be temporarily disrupted. The Kidney's storing function may also be affected.
 When fright affects the Heart and spirit, signs may include palpitations, insomnia, restlessness, confusion, being easily startled or difficulty concentrating. Severe cases may include fainting or altered awareness. A physician considers the intensity of the stimulus, how long its effects last and the person's prior physical and emotional state.</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>【驚】
+驚は七情の一つで、突然の出来事、音、危険などに遭ったときに生じる強い感情反応である。恐との違いは、驚は予期しない急な刺激で起こることが多く、恐は知っている、あるいは予想される危険への怖さである点にある。
+東洋医学では驚は主に心神に影響し、気の巡りを乱すため「驚けば気は乱れる」という。突然驚くと心神は安定を失い、気血の巡りも一時的に乱れ、腎の封蔵にも影響することがある。
+驚きが心神を傷つけると、動悸、不眠、心が落ち着かない、意識がぼんやりする、驚きやすくなる、集中しにくいなどの状態が見られる。重い場合には失神や意識の異常も起こり得る。刺激の強さ、その後の影響の長さ、元の心身の状態を合わせて判断する。</t>
         </is>
       </c>
     </row>
@@ -12825,6 +13113,28 @@
 Shizhen: White peony benefits the Spleen and checks Wood within Earth; red peony disperses pathogens and moves stagnation in the blood. Daming's claim that red peony supplements Qi and white peony treats blood is not sufficiently precise. Liver blood is already deficient after childbirth, so it should not be drained further. But there are many sour, cold medicines: why single out peony? Gao explains that although sourness is generally thought to gather, the Benjing's statement that peony promotes urination means it nourishes Yin and retains moisture, allowing urination to regulate itself; it is not simply a diuretic. 'Relaxing the middle' means moderating the Liver and regulating blood, hence peony in Four-Substance Decoction. Sour, astringent medicines generally restrain and retain fluids; peony acts in the Hand and Foot Taiyin channels and also reaches the sea of blood and the deep Jueyin level. In five-phase color theory, white belongs to the west and supplements, while red belongs to the south and drains.</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>白芍（芍薬）
+【性味】苦・酸、微寒。
+【毒性】無毒。
+【帰経】肝経・脾経に帰する。
+【主治】養血調経、斂陰止汗、柔肝止痛、平抑肝陽。
+【名称の由来】将離（『本草綱目』）、犁食（『名医別録』）、白術（『名医別録』）、余容（『名医別録』）、鋌（『名医別録』）。白いものを金芍薬、赤いものを木芍薬という（『図経本草』）。
+李時珍はいう。芍薬の「芍」は「約」に通じ、美しい姿を意味する。この草の花がたおやかで美しいため、そう名づけられた。また『雅翼』には、食物の毒を抑えるには芍薬に勝るものはないので薬の名を得たとあり、この解釈も通る。
+『詩経』鄭風には、互いに戯れながら芍薬を贈ると詠まれている。
+『韓詩外伝』には芍薬は離草であるとある。董子は芍薬を将離とも呼ぶため、別れ際に贈るのだという。花弁が重なるものを俗に小牡丹、赤いものを木芍薬と呼び、牡丹と名を共有する。
+【考証】
+志はいう。赤いものは尿を出し、気を下げる。白いものは痛みを止め、血の滞りを散らす。
+大明はいう。赤いものは気を補い、白いものは血を補う。
+陶弘景はいう。赤いものには軽い利尿作用があり、民間の処方では痛みを止める働きが当帰に劣らない。白いものは道家も服用し、石を煮る際にも使う。
+成無己はいう。**白いものは補い、赤いものは瀉す。白は収め、赤は散らす。酸味で収斂し、甘味で緩めるため、酸甘を合わせて陰血を補う。逆上する気を収めて肺の燥を除く。**また、芍薬の酸味は津液を収斂して営血を養い、陰気を収めて邪熱を除くという。
+張元素はいう。**白は補い、赤は散らし、肝を瀉して脾胃を補う。**酒に浸せば経を巡らせ、中部の腹痛を止める。生姜とともに用いれば経を温め、湿を散じて閉塞を通じさせ、腹痛や胃気の滞りに働く。**白芍は脾経に入り、中焦を補うため、下痢の治療に欠かせない。**下痢は太陰の病なので省けない。炙甘草を佐薬とすれば腹痛を治し、夏は黄芩を少量加え、悪寒には桂を加える。これは張仲景の優れた処方である。用途は六つある。脾経を安定させること、腹痛を治すこと、胃気を収めること、下痢や赤痢を止めること、血脈を調えること、皮膚のきめを固めることである。
+寇宗奭はいう。芍薬は花弁が一重で赤いものがよい。ただし血虚で冷えのある人には禁ずる。古人が「中寒を避けるには芍薬を減らす」といったことを忘れてはならない。
+朱震亨はいう。芍薬は脾の火を瀉し、酸味・寒性なので冬には必ず酒で炒る。腹痛の多くは血脈の凝りと滞りによるため、これも酒で炒って用いる。ただし血虚による腹痛にしか効かず、ほかの腹痛には用いない。酸寒で収斂し、温めて散らす働きがないためである。下痢と腹痛には炒って用い、しぶり腹には炒らない。産後に用いないのは酸寒が生発の気を損なうためで、やむを得ない場合も酒炒して用いる。
+李時珍はいう。白芍薬は脾を養い、土の中の木を瀉す。赤芍薬は邪気を散らし、血中の滞りを巡らせる。『日華子本草』が赤は気を補い、白は血を治すとするのは十分に吟味されていない。産後には肝血がすでに虚しているため、さらに瀉してはならないので禁じる。酸寒の薬は多いのに芍薬だけを避けるのはなぜか。李杲は次のように答える。酸渋の薬は収めるといわれるのに、『神農本草経』に利尿とあるのはなぜか。芍薬は陰を養って潤いを増し、津液を保つため、尿が自然に出るのであり、通利させるためではない。また「中を緩める」とは何か。肝を抑えて中を緩める、すなわち血を調えることであり、四物湯に芍薬を用いるのもそのためである。おおむね酸渋のものは収斂して湿を留め、手足の太陰経の収斂に働き、血海を治して深部へ至り、最後に厥陰経に入る。白は西方の色なので補い、赤は南方の色なので瀉す。</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -12894,6 +13204,25 @@
 Zongshi: Treatise on Medicinal Properties says Angelica Dahurica Root can help eliminate pus. He describes its traditional use for persistent foul discharge and lower abdominal pain attributed to retained pus and blood. One old formula combined Angelica Dahurica Root with hollyhock root, White Peony Root and alum, made into pills and taken with rice water until the discharge cleared, after which strengthening medicines were used.</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>白芷
+【性味】辛、温。
+【毒性】無毒。
+【帰経】肺経・胃経・大腸経に帰する。
+【主治】解表散寒、祛風止痛、宣通鼻竅、燥湿止帯、消腫排膿。
+【名称の由来】白茝（音は止、また昌海切。『名医別録』）、芳香（『神農本草経』）、沢芬（『名医別録』）、苻蘺（『名医別録』）、䖀（許驕切。『呉普本草』）、莞（音は官。『名医別録』）。葉は蒚麻（音は力。『名医別録』）、薬（音は約。『図経本草』）とも呼ぶ。
+李時珍はいう。徐鍇によれば、初生の根が乾いたものを芷と呼ぶため、白芷の名はこれに由来する。
+王安石の『字説』には、香りが鼻を養い、体も養うので、字は「臣」に従うとある。臣の音は怡で、養うという意味である。
+許慎の『説文解字』には、晋・斉・楚での異名が記され、楚では蘺、また薬と呼ぶ。低湿地に生え、蘭のように香るため、詩人は蘭とともに詠み、本草には芳香・沢芬の名がある。古人は香白芷とも呼んだ。なお原文には一部、異名の字が欠けている。
+【考証】
+李杲はいう。白芷は風の病に広く用い、芳香の気が九竅を通じさせるため、発汗による解表に欠かせない。
+劉完素はいう。陽明経の頭痛や熱厥による頭痛には、白芷を加えて用いる。
+王好古はいう。辛夷・細辛とともに鼻の病に用いる。内托散に加えて肉芽を生じさせることからも、陽明経に入ることが分かる。
+李時珍はいう。白芷は白く辛いため手の陽明経の庚金を巡り、温かく気が濃いため足の陽明経の戊土を巡る。香りは上へ達して手の太陰肺経に入る。肺は庚の弟、戊の子であるため、主治する病はこの三経に関わる。頭・目・眉・歯の病は三経の風熱、漏下・帯下・癰疽は三経の湿熱による。風熱は辛味で散らし、湿熱は温性で除く。陽明の主薬なので血の病や妊娠に関わる病にも用い、排膿、肉芽の形成、止痛にも働く。王某の『百一選方』によれば、王定国が風による頭痛を患い、都梁で名医の楊介に三丸を続けて服用させられると、たちまち治まった。処方を尋ねると、香白芷だけを洗って日に干し、粉末にし、煉蜜で弾丸ほどの丸薬にしたものだった。一回に一丸を噛み、薄い茶または荊芥湯で服用する。そこで都梁丸と名づけた。頭風によるめまい、妊娠中や産後の女性の風邪による頭痛、血風頭痛にも効くという。戴原礼の『要訣』にも、熱を伴う頭痛で首にしこりのある場合に適するという。また『仙神隠書』には白芷を植えると蛇を避けるとあり、『夷堅志』の蛇傷の処方も蛇が嫌うものを用いたのだろうが、本草には記されていない。
+寇宗奭はいう。『薬性論』には白芷は膿を腐食させるとある。今では帯下、腸内の腐敗した膿、止まらない悪臭のある分泌物、それに伴う臍腹の冷えた痛みに用い、膿を出す必要がある。白芷一両、一重咲きの赤い蜀葵の根二両、白芍薬と白枯礬をそれぞれ半両、粉末にして蝋で梧桐の実ほどの丸薬を作る。空腹時と食前に米のとぎ汁で十～十五丸を服用し、膿がなくなった後はほかの薬で補う。</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -12952,6 +13281,21 @@
 Haogu: Early materia medica did not clearly separate White Atractylodes Rhizome and Atractylodes Rhizome. In later practice White Atractylodes Rhizome became widely used to treat Wind affecting the skin, stop sweating, reduce focal fullness, strengthen the Stomach and harmonize the exterior. Its ability to stop spontaneous sweating was compared with Astragalus Root.
 Yuansu: White Atractylodes Rhizome removes Dampness, promotes dryness where Dampness is excessive, harmonizes the middle and supports Qi. He lists nine uses: warming the middle; removing Dampness from the Spleen and Stomach; clearing pathological Heat in the Stomach; strengthening digestion and appetite; harmonizing the Stomach and supporting fluids; reducing muscle Heat; treating heavy, tired limbs, sleepiness and poor appetite; relieving thirst; and helping steady pregnancy. When Dampness obstructs the middle burner and prevents proper fluid movement, White Atractylodes Rhizome is used to drain retained water while strengthening the Spleen. This is why it serves as the chief herb in Immature Bitter Orange and White Atractylodes Pill, with Immature Bitter Orange addressing focal fullness.
 Ji: The Spleen dislikes Dampness. When Dampness prevails, Qi transformation is impaired and body fluids cannot be properly generated or distributed. By removing Dampness, White Atractylodes Rhizome allows Qi to circulate and normal fluid production and movement to resume.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>白朮（朮）
+【性味】苦・甘、温。
+【毒性】無毒。
+【帰経】脾経・胃経に帰する。
+【主治】健脾益気、燥湿利水、止汗、安胎。
+【名称の由来】山薊（『神農本草経』）、楊桴（音は孚）、桴薊（『爾雅』）、馬薊（『本草綱目』）、山姜・山連（『名医別録』）、吃力伽（『日華子本草』）。
+李時珍はいう。『六書本義』によれば、「朮」の篆書はその根・茎・枝・葉の形を表す。『呉普本草』では山芥、天薊とも呼ぶ。葉が薊に似て、味が姜や芥に似るからである。西域では吃力伽と呼ばれ、『外台秘要』には吃力伽散がある。揚州には白朮が多く、形が桴（太鼓のばち）に似るため楊桴・桴薊とも呼ばれ、今の呉朮がこれに当たる。古い処方では蒼朮と白朮を区別せずに使い、後世になって分けられた。詳しくは後述する。
+【考証】
+王好古はいう。古い本草に蒼朮・白朮の名はなく、近ごろは白朮を多く用いる。皮膚の風を治し、汗を止め、つかえを除き、胃を補って調える。汗を止める点では黄耆と同じ働きがある。
+張元素はいう。白朮は湿を除いて乾かし、中焦を調え、気を補う。用途は九つある。中を温めること、脾胃の湿を除くこと、胃の熱を除くこと、脾胃を強め食欲を増すこと、胃を調えて津液を生じること、筋肉の熱を止めること、手足のだるさ、眠気、目が開けられない、食欲がない状態を治すこと、喉の渇きを止めること、胎を安定させることである。中焦に湿が滞って下へ排出できない場合、白朮で水を追い出して脾を養う必要がある。湿を除くには白朮、つかえを消すには枳実が必要なので、枳朮丸では白朮を君薬とする。
+王機はいう。脾は湿を嫌い、湿が盛んになると気が変化を行えず、津液も生じない。膀胱は津液の府であり、気化が働いて初めて排出できる。白朮で湿を除けば気が全身を巡り、津液が生じる。</t>
         </is>
       </c>
     </row>
@@ -13014,6 +13358,22 @@
 Wang Haogu: Arborvitae Seed acts on the Qi aspect of the Liver channel and also moistens the Kidney. It appears in the old formula Ten Essences Pill.
 Shizhen: Arborvitae Seed is neutral rather than cold or drying. Its sweetness is nourishing, while its slight acridity and aromatic quality help it moisten and penetrate toward the Heart and Kidney. It was therefore valued in nourishing formulas and in older longevity traditions.
 Lie Xian Zhuan tells the legendary story of Chi Songzi, who ate cypress seeds, regrew lost teeth and could travel as fast as a running horse. The passage reflects the herb's old reputation as a longevity medicine rather than a literal clinical claim.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>柏子仁（柏）
+【性味】甘、平。
+【毒性】無毒。
+【帰経】心経・腎経・大腸経に帰する。
+【主治】養心安神、潤腸通便、止汗。
+【名称の由来】椈（音は菊。『爾雅』）、側柏（『爾雅翼』）。
+李時珍はいう。魏子才の『六書精蘊』によれば、木はみな日に向かうが、柏だけは西を指す。陰の木で節操があるので字に「白」が含まれ、白は西方を表す。陸佃の『埤雅』では、柏が西を指すのは針が南を指すのと同じだという。柏にはいくつか種類があるが、薬には葉が平たく横向きに生えるものだけを採るので側柏という。
+寇宗奭はいう。陝西で役人を務めたとき、高所から柏を見渡すと、何千何万の木がすべて西を指していた。この木はきわめて堅く、霜雪を恐れず、木の正気を備えてほかの木に勝る。金の正気に制せられるため、一様に西を指すのだ。
+【考証】
+王好古はいう。柏子仁は肝経の気分に用いる薬で、腎も潤す。古い処方の十精丸にも使われる。
+李時珍はいう。柏子仁は性が平らかで寒すぎず燥しすぎず、甘味で補い、辛味で潤す。清らかな香りが心と腎に通じ、脾を養う。仙家の上品薬であり、滋養の処方に使うのは理にかなう。
+『列仙伝』には、赤松子が柏の実を食べ、抜けた歯が再び生え、走る馬と並んで進んだとある。決して虚言ではないだろう。</t>
         </is>
       </c>
     </row>
@@ -13086,6 +13446,25 @@
 He also notes that some ancient formulas used Pinellia Rhizome for throat obstruction, bleeding and traumatic injury, while cautioning that it can further damage fluids in Yin-deficiency and consumptive conditions. An old insomnia formula, Pinellia Decoction, is cited as evidence that its traditional uses were broader than phlegm alone; the formula was intended to restore communication between Yin and Yang so that sleep could occur.</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>半夏
+【性味】辛、温。
+【毒性】有毒。
+【帰経】脾経・胃経・肺経に帰する。
+【主治】燥湿化痰、降逆止嘔、消痞散結。
+【名称の由来】守田（『名医別録』）、水玉・地文（『神農本草経』）、和姑（『呉普本草』）。
+李時珍はいう。『礼記・月令』には五月に半夏が生じるとあり、夏の半ばに当たるため名づけられた。守田は意味から、水玉は形から名づけられた。
+【考証】
+甄権はいう。半夏は使薬であり、虚して痰気がある場合には加えるのがよい。
+蘇頌はいう。胃が冷えて吐き気やしゃっくりがある場合、処方の中でも特に重要な薬である。
+成無己はいう。辛味には散らし、潤す働きがある。半夏の辛味は逆上する気や結んだ気を散らしていらだちや嘔吐を除き、声を出しやすくし、水気を巡らせて腎の乾燥を潤す。
+王好古はいう。古典には「腎は五液をつかさどり、五湿に変わる」とある。腎自身では唾となり、肝では涙、心では汗、脾では痰、肺では鼻汁となる。痰があるものを嗽、痰がないものを咳という。痰とは咳によって脾の湿が動いたものである。半夏は痰の表面的な症状を除くが、根本までは除かない。根本を除くには腎を瀉す。咳は形がなく、痰には形がある。形のないものは潤し、形あるものは乾かすため、湿を巡らせて燥を潤すという。半夏を肺の薬とする俗説は誤りである。嘔吐を止めるのは足陽明、痰を除くのは足太陰への作用である。柴胡と組み合わせて柴胡湯に使うと、嘔吐を止めるだけでなく、柴胡・黄芩を助けて寒熱往来にも働くので、足少陽・陽明にも関係する。
+寇宗奭はいう。今の人は半夏が痰を除くことだけを知り、脾を養うことを語らないが、水分を分けて巡らせることができるからである。脾は湿を嫌い、湿で困れば水を処理できなくなる。古典には「湿が勝てば下痢する」とある。ある男性が夜間に何度も便所へ通った。生姜一両、半夏と大棗を各三十個、水一升を磁器の瓶に入れ、弱火で煮て時々飲ませると治まったという。趙継宗はいう。朱丹溪のいう二陳湯は全身の痰を治すということで、世の医者は痰があれば何にでも使う。しかし半夏は乾燥させる力が強く、風痰・寒痰・湿痰・食痰には適しても、労痰や喀血を伴う痰には血や津液を乾かして病を悪化させる。注意すべきである。
+王機はいう。半夏は乾燥性があり有毒なので、俗に貝母で代用する。しかし貝母は太陰肺経の薬、半夏は太陰脾経と陽明胃経の薬であり、代えられない。咳と喀痰、虚労による喀血、血の混じる痰、気の鬱結、喉の痛みや閉塞、肺癰や肺痿、癰疽、乳汁の出が悪い場合などは貝母を導き手とし、半夏は禁じる。一方、涎は脾の液で、濃厚で脂っこい食事は脾胃の湿熱を生み、涎が痰へ変わる。長引けば痰火が上を攻め、意識が混濁し、口が開かず、半身が麻痺して倒れ、言葉が出ず、生死を争う。この場合、半夏や南星なしにどう治せようか。貝母で代えれば死を待つだけだ。
+李時珍はいう。脾に湿が残らなければ痰は生じない。ゆえに脾は痰を生む源、肺は痰を蓄える器である。半夏が痰飲と腹の張りを治すのは、滑らかな性質と辛味・温性による。涎の滑らかさは潤し、辛温は散らしながら潤すので、湿を巡らせて便通を助け、竅を通じて排尿を促す。「辛は気へ走り、液を変化させ、辛で潤す」とはこのことだ。張潔古は半夏と南星で痰を治せば咳も自然に治るといい、朱丹溪は二陳湯が便を潤し、尿を増やすという。成無己も半夏の辛味が水気を巡らせ腎の乾燥を潤すという。『和剤局方』の半硫丸が老人の虚性便秘に用いられるのも、滑らかに潤す働きによる。世間では南星と半夏をともに乾燥性とみなすが誤りである。湿が去れば脾土が乾いて痰涎を生じなくなるのであって、薬そのものが乾燥性ということではない。古い処方では喉の痛みや閉塞、吐血、下血にも両薬を多く用い、必ずしも禁薬ではない。血の滞りも散らすため、外傷や打撲にも用いる。ただし陰虚や消耗性の病は湿熱によらないため、水湿を流す薬を使えば津液をさらに失わせる。これは医者の過ちであり、薬のせいではない。『鍼灸甲乙経』には不眠の治療に使うとある。本当に乾燥性だけの薬といえるだろうか。岐伯は、衛気が陽に巡って陽気が満ち、陰に入れず陰気が虚するため眠れないという。半夏湯一剤で陰陽が通じればすぐ眠れる。処方は、遠くから流れてきた水八升を何度もすくって空気を含ませ、澄んだ水五升を取って葦を燃料に沸かす。強く煮立ったら秫米一升と半夏五合を入れ、一升半まで煮詰め、汁を一杯ずつ一日三回、効き目が現れるまで飲む。発症したばかりなら飲み終えると眠り、汗が出れば治まり、長引いたものは三回飲めば治るという。</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -13154,6 +13533,25 @@
 A Tang-dynasty anecdote tells of a merchant with a strange sore on his arm said to resemble a human face. Many substances reportedly produced no reaction, but when Fritillaria Bulb was applied the sore 'closed its mouth'; the herb was then administered through a small tube and the lesion eventually scabbed over. The story is legendary, but reflects the old reputation of Fritillaria Bulb for sores and wounds. The Benjing also lists it for traumatic wounds.</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>貝母
+【性味】甘・苦、微寒。
+【毒性】無毒。
+【帰経】肺経・心経に帰する。
+【主治】清熱潤肺、化痰止咳、散結消癰。
+【名称の由来】『爾雅』に記された異名（音は萌。原文では字が欠ける）、勤母・苦菜・苦花・薬実（『名医別録』）、空草（『神農本草経』）。
+陶弘景はいう。形が貝を寄せ集めたようなので貝母という。
+李時珍はいう。『詩経』に「その〔原文欠字〕を採る」とあるのがこれである。虻とも書き、根が虻に似るという。苦菜や薬実は野苦〔原文欠字〕や黄薬子とも同じ名である。
+【考証】
+寇宗奭はいう。貝母は胸の中で鬱結した気を散らす。『詩経』でこれを採ると詠んだのもそのためで、詩人は志を得られない思いを述べていた。胸の気が晴れず憂鬱な人に用いると特に効果があるという。
+王好古はいう。貝母は肺経の気分に用いる薬である。張仲景は寒実結胸で表に熱の徴候がない場合、三物小陥胸湯を主として用い、白散もよいとした。貝母が配合されているためである。
+成無己はいう。辛味は散らし苦味は下へ流す。桔梗や貝母の苦辛の味を用いて気を下げる。
+王機はいう。半夏は有毒なので貝母で代用することがあるが、貝母は太陰肺経、半夏は太陰脾経と陽明胃経の薬であり、同じものにはできない。虚労の咳、吐血・喀血、肺痿や肺癰、乳腺の腫れ、癰疽、さまざまな鬱結には半夏を禁じ、貝母を導き手として用いる。しかし脾胃の湿熱で涎が痰に変わり、長引いて痰火が上り、意識混濁、硬直して倒れること、発語困難などが起き、生死を争う場合に貝母が半夏の代わりになるだろうか。蘇頌は貝母が悪性の瘡を治すという。
+唐代の記録によれば、江南のある商人の左腕に人の顔のようなできものが生じた。ほかに苦痛はなかったが、戯れに酒を口の部分へ垂らすと顔が赤くなり、食べ物を与えると食べ、たくさん与えれば腕の肉が膨らんだ。食べさせないと腕がしびれた。名医に勧められて金石・草木などの薬を順に試したところ、貝母を与えたときだけ、できものが眉を寄せて口を閉じた。商人は喜び、小さな葦の筒で口をこじ開けて貝母を流し込み、数日後にかさぶたができて治ったという。ただし何の病だったかは不明である。
+『神農本草経』には刀傷を主治するとある。これもその類だったのだろうか。</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -13209,6 +13607,19 @@
 [Historical commentary]
 Shizhen: The preferred medicinal form is the firm-shelled white bean, whose seed is full, whitish with a slight yellow tint, and mildly aromatic. Its balanced, slightly warm nature led him to call it a grain of the Spleen. It enters the Taiyin Qi level, supports movement through the three burners, helps the clear ascend and the turbid descend, and is therefore used for disorders of the middle burner, especially summer-Heat and Dampness.
 He distinguishes softer-shelled or dark mottled varieties as somewhat cooler and more suitable as food, though they too were considered helpful for harmonizing the Spleen and Stomach.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>扁豆（藊豆）
+【性味】甘、微温。
+【毒性】無毒。
+【帰経】脾経・胃経に帰する。
+【主治】健脾化湿、和中消暑。
+【名称の由来】沿籬豆（俗称）、蛾眉豆（『本草綱目』）。
+李時珍はいう。「藊」はもと「扁」と書き、さやが平たいことに由来する。「沿籬」はつるが垣根に沿って伸びること、「蛾眉」は豆の背にある白い筋の形を表す。
+【考証】
+李時珍はいう。硬いさやを持つ白扁豆は実が充実し、白くわずかに黄色がかり、生臭さを含んだ香りがある。温和で偏りのない性質を得ており、脾に適した穀物である。太陰の気分に入り、三焦を通じ、清を変化させて上げ、濁を下げる。ゆえに中焦の病に用い、暑を和らげ、湿を除き、毒を解く。柔らかいさやのものや黒い鵲のような色のものはやや涼性で、食用に適し、脾胃も整える。</t>
         </is>
       </c>
     </row>
@@ -13275,6 +13686,25 @@
 Zongshi: It was traditionally used to guide formulas for children with high fever and agitation. Its juice also appears in old preparations for chronic deficiency Heat.
 Haogu: Mint enters the Qi level of the Jueyin systems and can course constrained Liver Qi. It was also used for shoulder and upper-back pain associated with excess in the Lung and for exterior Wind-Cold with sweating.
 Shizhen: Because acridity disperses and coolness clears, mint was valued for headache, Wind disorders of the head, eye and throat problems, tooth and mouth disorders, childhood febrile agitation, scrofula and skin sores. Old writings also preserve folk observations about cats reacting strongly to mint.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>薄荷
+【性味】辛、涼。
+【毒性】無毒。
+【帰経】肺経・肝経に帰する。
+【主治】疏散風熱、清利頭目、利咽透疹、疏肝行気。
+【名称の由来】菝（『食性本草』）、蕃荷菜（『千金方』）、呉菝（『食性本草』）、南薄荷（『本草衍義』）、金銭薄荷（『会編』）。
+李時珍はいう。薄荷は俗称である。陳士良の『食性本草』では菝、揚雄の『甘泉賦』や呂忱の『字林』では茇と書くので、薄荷は訛った呼び名と分かる。
+孫思邈の『千金方』では蕃荷と書き、これも地方の発音の訛りである。今は蘇州産を薬用として上質とするので、陳士良は胡菝と区別して呉菝と呼んだ。
+寇宗奭はいう。竜脳薄荷という別種と区別するため、南薄荷と呼ばれる。王機はいう。小児の処方には金銭薄荷を多く用いる。葉が小さく丸く、銭に似るためで、「金銀」と書くのは誤りである。
+【考証】
+張元素はいう。薄荷は辛く涼しく、気味ともに薄く、浮いて上昇する陽の性質がある。頭頂部や皮膚の風熱を除く。
+陳士良はいう。薄荷は諸薬を営衛へ導くため、風寒を発散できる。
+寇宗奭はいう。小児の驚きによる興奮と高熱には、薄荷で薬を導く。また骨蒸の熱と虚労には、汁をほかの薬と煮詰めて膏を作る。猫が薄荷を食べると酔うのは、物同士の作用による。
+王好古はいう。薄荷は手足の厥陰経の気分に用いる薬で、肝気を巡らせる。また肺気が過盛で起こる肩や背の痛み、風寒による発汗にも用いる。
+李時珍はいう。薄荷は手太陰と足厥陰に入り、辛味は発散し、涼性は熱を清める。風を除き熱を散らすのに優れ、頭痛、頭部の風、目・喉・口・歯の病、小児の驚熱、瘰癧や皮膚のできものにも重要である。戴原礼は猫に噛まれた傷に汁を塗って効果を得た。猫と薄荷が作用し合う性質によるのだろう。陸佃は、薄荷は猫にとっての酒、犬は虎の酒、桑の実は鳩の酒、草は魚の酒といった。原文は「昝殷」で途切れている。</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13775,26 @@
 Xu Shuwei recorded a long-standing disorder marked by retained fluids, rib pain, poor appetite and periodic vomiting. After many treatments failed, he attributed the problem to Dampness obstructing the Spleen and used Atractylodes Rhizome with sesame and jujube. He reported gradual recovery after prolonged use, while also noting that excessive dryness could occur early in treatment.</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>蒼朮
+【性味】辛・苦、温。
+【毒性】無毒。
+【帰経】脾経・胃経・肝経に帰する。
+【主治】燥湿健脾、祛風散寒、明目。
+【名称の由来】赤朮（『名医別録』）、山精（『抱朴子』）、仙朮（『本草綱目』）、山薊（『神農本草経』）。
+李時珍はいう。『異術』には、朮は山の精で、服用すれば長生きし、穀物を断っても仙人になれるとある。山精・仙朮という名はこのためである。朮には赤と白の二種があり、主治は近いが性味や発汗・止汗の働きが異なる。古い本草が蒼朮と白朮を分けないからといって、そのまま同一視することはできない。そこで『神農本草経』『名医別録』、甄権、大明の四者の記述を照合して分け、それぞれに処方を付した。
+【考証】
+寇宗奭はいう。蒼朮は辛味が強く、白朮はやや辛苦だが激しくない。古い処方や『神農本草経』には単に朮とあり、蒼白を区別しない。陶弘景が二種あると述べて以来、人々は白を重んじて蒼朮を使わないことが多くなった。しかし古方の平胃散などでは蒼朮が最も重要で、効き目も速い。もともと古い本草に白朮という名はない。嵇康が伝えた、朮と黄精を食べれば長寿になるという道士の言葉にも「白」はない。用いる際にはよく吟味すべきだ。
+李杲はいう。古い本草は朮を蒼白に分けない。蒼朮には強く上へ向かう気があり、湿を除き、下では太陰を安定させ、邪気が脾へ入るのを防ぐ。米のとぎ汁に浸して炒ると汗を出す働きがあり、白朮の止汗作用とは異なる。互いに代用してはならない。発汗と止汗以外の主治は共通する。
+張元素はいう。蒼朮と白朮の主治は同じだが、蒼朮のほうが気が強く重い。上部の湿を除いて発汗させる力は大きい。一方、中焦を補い、脾胃の湿を除く力は白朮に及ばない。腹中が狭くつかえる場合には蒼朮を用いる。
+朱震亨はいう。蒼朮は上・中・下のどの部位の湿にも使え、諸々の鬱結も解く。痰・火・湿・食・気・血の六鬱は、変化と運搬が乱れて昇降できないために生じる。病が中焦にあるので薬には昇降の双方が必要であり、上げるにはまず下げ、下げるにはまず上げる。蒼朮は足陽明経の薬で、辛味が強く脾胃を強め、水穀の気を発し、諸経に入り、陽明の湿を除いて滞りを通す。香附は陰の中で気を快く巡らせ、気を下げるのが速い。一方が昇り、一方が降りて鬱が散る。楊士瀛は、脾の精を保てず尿が濁って漏れ、淋が続き、腰背が痛む場合、穀物から生じる脾精を収めるため蒼朮を使うという。陶弘景は白朮は膏分が少ないので丸薬や散剤に、赤朮は膏分が多いので煎じ薬に向くという。かつて劉涓子が朮の精を採って丸薬にし、守中金丸と名づけ長寿の薬とした。蘇頌は、単独で服用するか白茯苓・石菖蒲と合わせて粉末にし、朝に水で服し夕方に再び飲むとよいという。生の朮の土を落として水に浸し、飴のようになるまで何度も煎じて酒で飲む方法はさらによい。茅山で作る朮煎はこの製法である。
+陶隠居は精を採って丸薬にすると述べたが、現在のものは膏を煎じたもので、本来のものとは違うかもしれない。唐慎微は梁の庾肩吾が陶隠居へ送った朮煎に関する文を引用する。緑の葉が伸び、紫の花が色を添え、外では諸邪を防ぎ、内では六腑を満たす。山精の名は書にあり、華神の名も記録にある。木が栄え火が衰える時まで採集と抽出を重ねたという。朮を蒸した品への謝辞には、味は金の液より濃く香りは玉液に勝り、長生きを得るに足ると記される。
+葛洪の『抱朴子・内篇』には、後漢末、南陽の文氏が戦乱を避け壺山で飢え死にしそうになったが、朮を食べるよう教えられて飢えを免れた話がある。数十年後に帰郷すると顔は若返り、力も増していた。ゆえに朮を山精と呼び、『神農薬経』も長生きしたければ山精を常に服すべきだと説く。
+李時珍はさらにいう。『吐納経』に伝わる紫微夫人の朮序では、草木の中で体に速く大きく役立つものは朮に及ばず、長生きして視力を保ち、遠くまで見通せるとされる。山林の隠者には服用者が五岳に並ぶほどいるという。『神仙伝』では陳子皇が朮の処方を得て、病んだ妻の姜氏が服して治り、顔色も体力も二十歳のころに戻ったという。これらの話は白朮だけでなく蒼朮にも当てはまり、今も服食家は蒼朮を仙朮と呼ぶのでここに記した。張仲景は赤朮と豚の蹄の爪を燃やして煙を出し、悪い気を避けた。陶隠居も朮が悪気を除いて災いを鎮めるといい、疫病の時や元旦に蒼朮を焚く家が多い。『類編』には、越の高氏の妻がぼんやりしてうわごとを言い、亡夫の霊に取りつかれたとき、家で蒼朮を焚くと霊が逃げようとしたという話がある。『夷堅志』では女の妖に取りつかれた江西の男性に対し、霊が別れ際に「陰気に侵されて激しい下痢になるので、蒼朮を含み邪を除く平胃散を多く服すとよい」と告げる。
+許叔微の『本事方』には自らの体験が記される。若いころ夜に左へ身を傾けて文章を書き、食べ物が左に落ち、夜中に酒を飲んでは左向きに寝たため、三十年にわたり飲癖を患った。数年後には飲んだ酒が左側へ落ちる音がし、脇の痛み、食欲減退、胸の不快感が生じ、酒も半杯しか飲めなくなった。十日余りごとに何升もの酸っぱい水を吐き、夏には右側だけ汗をかいた。名医や民間の処方を試し、一月余りは効いても再発した。天雄・附子・礬石などの補薬も、牽牛・甘遂・大戟などの利水薬も試した。自分の体内に水のたまる窪みのような袋があり、澄んだものは流れても濁ったものは滞り、五～七日で吐き出すのだろうと考えた。湿を嫌う脾を乾かし、土を盛って窪みを埋めるため、他の薬をすべてやめ、皮を除いて刻み粉にした蒼朮一斤、生の胡麻半両を水二碗で挽いて濾した汁、煮て皮と種を除いた大棗五十個を合わせ、梧桐の実ほどの丸薬にした。毎日空腹時に温かい湯で五十丸から始め、百～二百丸に増やした。桃、李、雀の肉を避け、三か月で病は治った。その後も服用を続け、嘔吐も痛みもなく、胸がすっきりして食事も元に戻り、夏には全身で汗をかき、灯火の下で細字も書けるようになった。最初に軽い乾燥感があれば山梔子の粉末を熱湯で飲んで解き、長く服せば乾燥感もなくなるという。</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -13413,6 +13863,26 @@
 He also records a case of long-standing malaria-like fever and severe wasting that reportedly improved rapidly with Minor Bupleurum Decoction after warming tonics had worsened the Heat. The story illustrates the traditional principle that treatment depends on identifying the location and nature of Heat rather than treating weakness alone.</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>柴胡（茈胡）
+【性味】苦・辛、微寒。
+【毒性】無毒。
+【帰経】肝経・胆経・肺経に帰する。
+【主治】疏散退熱、疏肝解鬱、昇挙陽気。
+【名称の由来】地熏（『神農本草経』）、芸蒿（『名医別録』）、山菜・茹草（『呉普本草』）。
+蘇恭はいう。「茈」は古い「柴」の字で、『上林賦』の茈姜や『爾雅』の茈草にも同じ字を用いる。この草の根は紫色で、太常で用いる茈胡がこれである。後に字の一部を木に改めて柴胡と呼ぶようになった。他の本草に柴胡の名は見当たらない。
+李時珍はいう。「茈」には柴と紫の二つの読みがある。茈姜・茈草では紫、茈胡では柴と読む。山に生え、若いうちは食べられ、老いると薪になるので、苗を芸蒿・山菜・茹草、根を柴胡と呼ぶ。蘇恭の説明は十分に明瞭でない。古い『傷寒論』でも茈の字を用いる。
+【考証】
+徐之才はいう。茈胡に茯苓、桔梗、大黄、石膏、麻子仁、甘草、桂を合わせ、水一斗で四升に煎じ、硝石三方寸匕を加えると、傷寒による寒熱、頭痛、心窩部の煩悶と張りを治す。
+蘇頌はいう。張仲景には大柴胡湯、小柴胡湯、柴胡加竜骨湯、柴胡加芒硝湯などがあり、後世の寒熱治療で柴胡は特に重要な薬となった。
+李杲はいう。清気を導いて陽の道を巡らせる。傷寒以外でも熱があれば加え、熱がなければ加えない。胃気を上に引き上げ、春の気のように昇らせたい場合にもよい。瘧には柴胡を君薬とし、発症の時刻と経絡に応じて引経薬を添える。十二経の瘡や癰では、経の血の結びと気の滞りを散らすため柴胡を使い、連翹と同じように働く。
+王好古はいう。柴胡は臓腑の内外の不足を除き、清気を上げて陽の道を整え、足少陽にも入る。経絡では気、臓では血に働く。症状が進むと熱を嫌い、退くと寒を嫌う。気が微寒で味が薄いため経を巡る。三棱・莪朮・巴豆を佐薬とすれば硬い積を消すので、血にも働く。婦人の月経が来たばかり、あるいは止まったばかりの時の傷寒や雑病には、小柴胡湯に四物湯の薬、秦艽や牡丹皮などを加えて月経を整える処方にする。産後の血熱にも必要な薬という。
+寇宗奭はいう。『神農本草経』には柴胡で虚労を治すとは一字もないのに、今の虚労の処方にはほぼ必ず用いられる。これは害が大きい。虚労の中には臓が虚損したうえで邪熱を受け、虚をきっかけに病むものがあるため、使用には吟味が要る。『経験方』の青蒿煎に柴胡を入れて虚労の熱を治すのは適切で、熱が去ればすぐ止めるべきだ。熱がないのに用いると悪化する例を多く見た。『日華子本草』は五労七傷を補うといい、『薬性論』は疲労や痩せを治すというが、実熱のない人へむやみに用いれば危うい。本草の注釈は一字たりとも軽んじられず、後世への影響を考え慎むべきだ。張仲景が瘧のような寒熱往来に柴胡湯を用いるのは適切である。
+李時珍はいう。五労は五臓に関わる。肝・胆・心・心包に熱がある場合、または少陽経に寒熱がある場合、柴胡は手足の厥陰・少陽に必要となる。脾胃に熱がある場合や陽気が下に落ちる場合にも、清気を上げて熱を退けるため必要である。肺や腎に虚労があるだけなら使わなくてよい。しかし李杲は熱があれば加え、なければ加えず、各経の瘧では柴胡を君薬とし、十二経の瘡や癰でも結びを散らすという。つまり肺・腎に関わる瘧や瘡でも熱があれば使える。病の原因を深く考え、配合と量を調整すればよい。寇宗奭が臓腑や経絡、熱の有無を分けず、柴胡は虚労を治さないと一律に退けるのは妥当でない。『和剤局方』の竜脳鶏蘇丸は上下の出血を治すため銀柴胡の浸出液を煮詰めて膏とするが、この意味を知る人は少ない。
+李時珍はさらに龐元英の『談藪』を引く。張知という人は一年余り瘧を患い、熱が出ると火のようで骨と皮だけに痩せた。医者が鹿茸や附子などを使うと熱は増し、孫琳が小柴胡湯を一服与えると熱は九割減り、三服で治った。孫琳は、これは骨髄から熱の出る労瘧で、強い温熱薬を加えるほど気血を損ない痩せるという。熱には皮膚、臓腑、骨髄にあるものがあり、柴胡が欠かせない。銀柴胡なら一服でよいが、南方産は力が弱いため三服を要した。これは用薬の妙を示し、寇氏の説だけに頼れないという。</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -13474,6 +13944,22 @@
 Haogu: Plantain Seed promotes urination without excessively dispersing Qi, an action he compared with Poria.
 Shizhen: Historical sources differed on the best harvest season, probably because plant development varies by region. Poetry from the Tang period also links the herb with treatment of eye disorders.
 He cautions that, when used in long-term tonic regimens, it should be balanced with other herbs because using it alone may drain fluids too strongly. He records a case attributed to Ouyang Xiu in which sudden severe diarrhea reportedly responded to powdered Plantain Seed taken with rice water. The traditional explanation was that by opening the waterways, clear and turbid fluids separate and the diarrhea stops.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>車前子（車前）
+【性味】甘、寒。
+【毒性】無毒。
+【帰経】肝経・腎経・肺経・小腸経に帰する。
+【主治】清熱利尿、滲湿止瀉、明目、清肺化痰。
+【名称の由来】当道（『神農本草経』）、芣苡（音は浮以）、馬舄（音は昔）・牛遺（『名医別録』）、牛舌（『詩疏』）、車輪菜（『救荒本草』）、地衣（『本草綱目』）、蛤蟆衣（『名医別録』）。
+李時珍はいう。『爾雅』では芣苡を馬舄、馬舄を車前とする。陸璣の『詩疏』によれば、牛馬の足跡のある道に生えるため、車前・当道・馬舄・牛遺の名がある。舄は履物の意味である。幽州では牛舌草、蛙が下に隠れるため江東では蛤蟆衣と呼ぶ。『韓詩外伝』の直立するものを車前、曲がったものを芣苡とする説明はこじつけかもしれない。原文末尾には「両側に生えるもの」と続くが、文脈が欠けている。
+【考証】
+陶弘景はいう。車前子は冷やして水を出す性質がある。仙人の書にも服用すれば体が軽くなり、谷を跳び越え、老いず長生きするとある。
+蘇頌はいう。車前子は薬によく使われる。駐景丸は車前と菟糸子の二つを蜜丸にし、食後に服用するもので、古今の優れた処方とされる。
+王好古はいう。車前子は気を消耗させずに排尿を促し、茯苓と似た働きをする。
+李時珍はいう。『神仙服食経』には車前を地衣とも呼び、雷の精で、服用すると姿が変わり、八月に採るとある。実際は五月に種が熟すので、七～八月とするのは土地の気候の違いだろう。張籍の詩には、開州の五月に採った車前を、目の病を哀れんで遠くから送ると詠まれている。これも五月採りの開州産がよいことと、目への働きを示す。服食には六味地黄丸の沢瀉のように他薬と組み合わせるべきで、単独では排泄が強すぎ、長期服用には向かないだろう。欧陽公が突然の下痢を患い、宮中の医者でも治せなかったとき、夫人が市販の薬を買って与えると治った。尋ねると車前子だけを粉末にし、米のとぎ汁で二銭匕飲む処方だった。水の通りをよくしても気は動かさず、清濁が分かれれば下痢も自然に止まるという。</t>
         </is>
       </c>
     </row>
@@ -13541,6 +14027,23 @@
 He cites Two Worthies Powder, made from tangerine peel, Licorice Root and salt, as an old remedy for phlegm and Qi constraint. A historical case describes severe post-meal chest fullness that reportedly resolved after prolonged use. Shizhen adds that such strongly Qi-moving formulas suit excess-type patients better than those with marked Qi deficiency.</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>陳皮（橘）
+【性味】苦・辛、温。
+【毒性】無毒。
+【帰経】脾経・肺経に帰する。
+【主治】理気健脾、燥湿化痰。
+【名称の由来】紅皮（『湯液本草』）、陳皮（『食療本草』）。
+陶弘景はいう。橘皮は気の病によく効き、東方産がよく、西江産はそれに劣る。長く保存したものを良品とする。
+王好古はいう。赤みがあり、長く保存した橘皮がよいので紅皮・陳皮という。白い内側を除いたものを橘紅と呼ぶ。
+【考証】
+李杲はいう。橘皮は気が薄く味が濃く、陽の中の陰である。上げることも下げることもでき、脾・肺二経の気分に用いる。白い内側を残せば脾胃を補い、取り去れば肺気を整える。白朮と合わせれば脾胃を、甘草と合わせれば肺を補う。単独なら肺を瀉して脾を損なう。軽く浮く性質があり、胸中の寒邪を導いて除き、気滞を破り、脾胃を養う。青皮を半量加えれば滞った気を除いて新陳代謝を促すが、多量に長く服すと元気を傷つける。
+原という人は、橘皮には散らす、瀉す、温める、補う、調和させる働きがあり、痰を除いて咳を治し、気を整えて中焦を調え、脾を整え胸のつかえを解き、五淋を通じ、酒による病を治すので、多くの薬に勝るという。
+李時珍はいう。橘皮は苦味で瀉して乾かし、辛味で散らし、温性で調和させる。多くの病への働きは、結局、気を整え湿を乾かす点にある。
+補薬と合わせれば補い、瀉薬と合わせれば瀉し、上げる薬と合わせれば上げ、下げる薬と合わせれば下げる。脾は元気の母で、肺は気を収める〔原文に欠字〕。このため橘皮は両経の気分に働き、配合に応じて補瀉と昇降が変わる。張潔古は陳皮と枳殻で気を巡らせれば痰も自然に下がると述べた。杏仁と合わせれば大腸の気滞による便秘、桃仁と合わせれば血滞による便秘に用いる。いずれも滞りを通す働きを利用し、詳細は杏仁の項にある。方勺の『泊宅編』によれば、橘皮は胸を広げ気を下げ、痰飲を除く力に優れる。他の薬は新しいものが重んじられるが、橘皮だけは古いものがよい。義父の莫強中が豊城の県令だったころ、食後にいつも胸が張って食物が下りず、どの処方も効かなかった。家人が橘紅湯を作ったので試すと具合がよく、数日飲み続けた。ある日突然、胸の中のものが落ちる感覚があり、驚いて目を見開き、雨のように汗をかいた。まもなく腹が痛んで鉄の弾ほどの塊を数個排出し、ひどい臭いがした。それ以来胸はすっきりし病も治った。脾の冷えた積滞だったのだろう。処方は白い内側を除いた橘皮一斤、甘草と塩の結晶を各四両、水五碗を弱火で煮詰め、乾かして粉末にし、白湯で飲む。二賢散といい、痰気に特に効く。世の医者が半夏・南星ばかり知るのは惜しい。李時珍はいう。朱丹溪は二賢散を潤下丸に変えて痰気に用い、効果を得た。ただし気が充実した人には向くが、気不足の人には適さない。</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -13596,6 +14099,20 @@
 The Nan Yue Zhi records the name Mi Xiang in Jiaozhou because its fragrance was compared with honey. Buddhist texts also preserve the transliterated name A Jia Xiang.
 [Historical commentary]
 The surviving entry here contains only the heading for this section and no additional commentary.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>沈香
+【性味】辛・苦、微温。
+【毒性】無毒。
+【帰経】脾経・胃経・腎経に帰する。
+【主治】行気止痛、温中止嘔、納気平喘。
+【名称の由来】沈水香（『本草綱目』）、蜜香（『南越志』）。
+李時珍はいう。木の芯や節を水に入れると沈むため沈水香、または水沈という。半分沈むものは桟香、沈まないものは黄熟香と呼ぶ。
+『南越志』によれば、交州の人は蜜香と呼ぶ。蜜の巣のような香りがするためである。梵語の書には阿迦香とある。
+【考証】
+原文には見出しのみで本文がない。</t>
         </is>
       </c>
     </row>
@@ -13667,6 +14184,28 @@
 Shizhen ultimately distinguishes the two by saying White Peony Root supports the Spleen and restrains excessive Liver activity, whereas Red Peony Root disperses pathogenic constraint and moves stagnation in the blood. He rejects oversimplified statements that reverse these roles and stresses pattern-based use.</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>赤芍（芍薬）
+【性味】苦、微寒。
+【毒性】無毒。
+【帰経】肝経に帰する。
+【主治】清熱涼血、散瘀止痛、清肝瀉火。
+【名称の由来】将離（『本草綱目』）、犁食（『名医別録』）、白術（『名医別録』）、余容（『名医別録』）、鋌（『名医別録』）。白いものを金芍薬、赤いものを木芍薬という（『図経本草』）。
+李時珍はいう。芍薬の「芍」は「約」に通じ、美しい姿を意味する。この草の花がたおやかで美しいため、そう名づけられた。また『雅翼』には、食物の毒を抑えるには芍薬に勝るものはないので薬の名を得たとあり、この解釈も通る。
+『詩経』鄭風には、互いに戯れながら芍薬を贈ると詠まれている。
+『韓詩外伝』には芍薬は離草であるとある。董子は芍薬を将離とも呼ぶため、別れ際に贈るのだという。花弁が重なるものを俗に小牡丹、赤いものを木芍薬と呼び、牡丹と名を共有する。
+【考証】
+志はいう。赤いものは尿を出し、気を下げる。白いものは痛みを止め、血の滞りを散らす。
+大明はいう。赤いものは気を補い、白いものは血を補う。
+陶弘景はいう。赤いものには軽い利尿作用があり、民間の処方では痛みを止める働きが当帰に劣らない。白いものは道家も服用し、石を煮る際にも使う。
+成無己はいう。**白いものは補い、赤いものは瀉す。白は収め、赤は散らす。酸味で収斂し、甘味で緩めるため、酸甘を合わせて陰血を補う。逆上する気を収めて肺の燥を除く。**また、芍薬の酸味は津液を収斂して営血を養い、陰気を収めて邪熱を除くという。
+張元素はいう。**白は補い、赤は散らし、肝を瀉して脾胃を補う。**酒に浸せば経を巡らせ、中部の腹痛を止める。生姜とともに用いれば経を温め、湿を散じて閉塞を通じさせ、腹痛や胃気の滞りに働く。**白芍は脾経に入り、中焦を補うため、下痢の治療に欠かせない。**下痢は太陰の病なので省けない。炙甘草を佐薬とすれば腹痛を治し、夏は黄芩を少量加え、悪寒には桂を加える。これは張仲景の優れた処方である。用途は六つある。脾経を安定させること、腹痛を治すこと、胃気を収めること、下痢や赤痢を止めること、血脈を調えること、皮膚のきめを固めることである。
+寇宗奭はいう。芍薬は花弁が一重で赤いものがよい。ただし血虚で冷えのある人には禁ずる。古人が「中寒を避けるには芍薬を減らす」といったことを忘れてはならない。
+朱震亨はいう。芍薬は脾の火を瀉し、酸味・寒性なので冬には必ず酒で炒る。腹痛の多くは血脈の凝りと滞りによるため、これも酒で炒って用いる。ただし血虚による腹痛にしか効かず、ほかの腹痛には用いない。酸寒で収斂し、温めて散らす働きがないためである。下痢と腹痛には炒って用い、しぶり腹には炒らない。産後に用いないのは酸寒が生発の気を損なうためで、やむを得ない場合も酒炒して用いる。
+李時珍はいう。白芍薬は脾を養い、土の中の木を瀉す。赤芍薬は邪気を散らし、血中の滞りを巡らせる。『日華子本草』が赤は気を補い、白は血を治すとするのは十分に吟味されていない。産後には肝血がすでに虚しているため、さらに瀉してはならないので禁じる。酸寒の薬は多いのに芍薬だけを避けるのはなぜか。李杲は次のように答える。酸渋の薬は収めるといわれるのに、『神農本草経』に利尿とあるのはなぜか。芍薬は陰を養って潤いを増し、津液を保つため、尿が自然に出るのであり、通利させるためではない。また「中を緩める」とは何か。肝を抑えて中を緩める、すなわち血を調えることであり、四物湯に芍薬を用いるのもそのためである。おおむね酸渋のものは収斂して湿を留め、手足の太陰経の収斂に働き、血海を治して深部へ至り、最後に厥陰経に入る。白は西方の色なので補い、赤は南方の色なので瀉す。</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -13724,6 +14263,20 @@
 Yuansu: It is especially important for sudden severe pain associated with Heat.
 Shizhen: The fruit was traditionally used to drain Heat from the Small Intestine and Bladder and to guide ministerial Fire downward. For that reason it became an important herb for abdominal pain and hernia-type pain associated with Heat and constrained Qi.
 He disputes claims that it should never be used in decoction, pointing to older descriptions of its use for Heat agitation and difficult urination. Later hernia formulas used it in several different combinations, illustrating that its effect depends greatly on accompanying herbs.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>川楝子（楝）
+【性味】苦、寒。
+【毒性】小毒。
+【帰経】肝経・小腸経・膀胱経に帰する。
+【主治】疏肝泄熱、行気止痛、殺虫。
+【名称の由来】苦楝（『図経本草』）、果実は金鈴子（『侯氏薬譜』）。
+李時珍はいう。羅願の『爾雅翼』によれば、楝の葉で物を洗えるため楝という。実は小さな鈴に似て熟すと黄色くなるので、形にちなみ金鈴と呼ぶ。
+【考証】
+張元素はいう。熱厥による突然の痛みは川楝子なしには除けない。
+李時珍はいう。楝の実は小腸と膀胱の熱を導き、心包の相火を下へ引くので、胸腹の痛みや疝気に重要な薬である。甄権は煎じ薬に用いないというが、それなら『神農本草経』が熱による狂乱を治し排尿を促すと記すのはなぜか。近ごろの疝気の処方には四治・五治・七治などの方法があり、薬の組み合わせの巧みさによるものだ。</t>
         </is>
       </c>
     </row>
@@ -13793,6 +14346,25 @@
 Zongshi and later authors caution against long-term use of Sichuan Lovage Rhizome by itself, especially in weak patients or those with deficiency Heat and heavy sweating, because its strongly dispersing nature may further exhaust Qi and Yin. Shizhen likewise stresses balanced formulas and appropriate duration rather than prolonged single-herb use.</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>川芎（芎䓖）
+【性味】辛、温。
+【毒性】無毒。
+【帰経】肝経・胆経・心包経に帰する。
+【主治】活血行気、祛風止痛。
+【名称の由来】胡䓖（『名医別録』）、川芎（『本草綱目』）、香果（『名医別録』）、山鞠窮（『本草綱目』）。
+李時珍はいう。「芎」の古字と名の由来は詳らかでない。頭が天の穹窿のように高く、この薬が上へ向かって頭の病を治すため芎䓖と名づけたともいう。胡の地のものがよいので胡芎、根の節が馬のくつわに似るので馬銜芎、雀の脳に似るので雀脳芎とも呼ぶ。関中産は京芎または西芎、蜀産は川芎、天台産は台芎、江南産は撫芎と、産地で名が変わる。『春秋左氏伝』では楚人が河魚を食べて腹を病んだ人に麦曲と山鞠窮を勧めた。二つとも湿を防ぐためである。朱丹溪の六鬱を治す越鞠丸は越桃と鞠窮を用いることから名づけられた。『金光明経』には莫迦とある。
+【考証】
+寇宗奭はいう。今ではよく用いられ、頭や顔の風の病には欠かせないが、ほかの薬を添える必要がある。
+張元素はいう。川芎は上へ昇って頭と目に、下へ降りて血海に働く。清神の処方や四物湯に用いるのはそのためである。肝経の風を散らし、少陽・厥陰経の頭痛や血虚による頭痛に優れる。用途は四つあり、少陽経へ薬を導くこと、諸経の頭痛、清陽の気を助けること、頭の湿を除くことである。
+李杲はいう。頭痛には川芎を必ず用い、治らなければ経絡に応じて薬を加える。太陽には羌活、陽明には白芷、少陽には柴胡、太陰には蒼朮、厥陰には呉茱萸、少陰には細辛である。
+朱震亨はいう。鬱が中焦にあるときは撫芎で気を開いて上げれば、鬱は自然に下がる。撫芎は諸鬱を解いて三焦へ達し、陰陽・気血を通じさせる使薬となる。
+李時珍はいう。芎䓖は血の中の気に働く薬である。肝は急な状態を嫌い、辛味で補うので血虚に適する。辛味は散らすので気鬱にもよい。『春秋左氏伝』は麦曲と鞠窮で湿を防ぎ、河魚による腹の病を治すと記す。私も湿による下痢には二味を加え、すぐに効いた。血痢が通じても痛みが残るのは陰の不足と気の鬱結によるため、芎を添えて気血を巡らせれば治まる。これらは医学の妙であり、柔軟に判断できる人にこそ語れる。
+寇宗奭はいう。沈括の『夢渓筆談』には、一族の子が川芎を長く飲み、医者の鄭叔熊に長期服用は突然死を招くといわれた後、病気もないのに亡くなった話がある。また張子通の妻も頭部の風の病で長く服し、突然亡くなったという。いずれも見聞した例である。単独で長く服すと真気を散らしてしまう。他薬を添え、長く飲まず、効いた時点で止めればこうはならない。虞搏も骨蒸による多汗や気の弱い人には長く服させないという。辛味で散らす性質により真気を漏らし、陰虚を深めるためである。
+李時珍はいう。五味は胃に入ってそれぞれの臓へ帰し、長く服せば一方の気が強くなって偏り、突然死の危険が生じる。五味と四気を備え、君臣佐使を適切に組み合わせれば、そのような害はない。川芎は肝経の薬だが、単独で長く飲むと辛味が肺へ集まり、肺の金が過剰となって肝の木を傷つけ、ついには命に関わる。医者は物事の理を見極めるべきである。</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -13847,6 +14419,19 @@
 He rejects as less convincing another old theory that pointed fruits were called bin and round fruits lang. Historical annotations also identify Ren Pin as another name for areca, while some regions used local names comparing the fruit with olives.
 [Historical commentary]
 The surviving entry here contains only the heading for this section and no additional commentary.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>大腹皮（檳榔）
+【性味】辛、微温。
+【毒性】無毒。
+【帰経】脾経・胃経・大腸経・小腸経に帰する。
+【主治】行気寛中、行水消腫。
+【名称の由来】賓門（李当之『薬対』）、仁頻（『上林賦』）、洗瘴丹（『侯氏薬譜』）。
+李時珍はいう。「賓」も「郎」も大切な客の呼び名である。嵇含の『南方草木状』によれば、交州や広州では身分の高い客にまずこの果実を差し出し、偶然会っても出さなければ恨まれることがあった。檳榔の名はこれに由来する。雷斅の『炮炙論』は尖ったものを檳、丸いものを榔とするが、こじつけにも見える。顔師古は『上林賦』の仁頻を檳榔と注し、孟詵は福建では橄欖子と呼ぶという。
+【考証】
+原文には見出しのみで本文がない。</t>
         </is>
       </c>
     </row>
@@ -13916,6 +14501,23 @@
 He also records traditional use of Jujube Decoction for 'zang zao,' a condition described as recurrent sadness and crying, including pregnancy-associated cases in older gynecological texts.</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>大棗（棗）
+【性味】甘、温。
+【毒性】無毒。
+【帰経】脾経・胃経・心経に帰する。
+【主治】補中益気、養血安神、薬性の緩和。
+【名称の由来】乾棗・美棗・良棗（『名医別録』）。
+『名医別録』には八月に採って日に干すとある。瑞という人は、これが乾燥させた大棗で、味がよいため薬に適し、今は肥えた膠棗を使う人もいるという。
+【考証】
+陶弘景はいう。道家の薬では棗は服食に適し、皮には排出作用、果肉には虚を補う働きがある。そのため煎じ薬では割って用いる。
+李杲はいう。大棗は気味がともに濃い陽の薬で、温性で不足を補い、甘味で陰血を緩める。
+成無己はいう。邪が営衛にあるときは辛甘で解き、生姜と棗で営衛を調え、脾胃の上昇する気を生じさせる。張仲景が奔豚に大棗を用いたのは脾土を養って腎気を鎮めるためであり、水飲による脇の痛みに十棗湯を用いたのは土を益して水に勝つためである。
+朱震亨はいう。棗は土に属して火を含み、甘く穏やかである。甘味は先に脾へ入るが、脾を補うために必ずしも甘味を使うわけではない。甘いものを多く食べると脾を病む。
+李時珍はいう。『素問』は棗を脾の果実とし、脾の病に適すると説く。病の治療で薬を調和させる場合、棗は脾経の血分に用いる薬だが、理由なく頻繁に食べると虫が生じ歯を傷める。王好古は、腹が張る人は甘いものを避けるべきだという。甘味が腹の張りを生むため、張仲景も建中湯で心窩部につかえがあれば飴と棗を減らし、甘草も同様に扱う。これが正しい使い方である。許叔微の『本事方』には、臓燥で泣き続けた女性を古方の大棗湯で治した例がある。陳自明の『婦人良方』には、程虎卿の妻が妊娠四、五か月のころ、昼になると悲しみ涙を流し、医者や巫者でも治らなかったが、管伯周が勧めた大棗湯一服で治った例がある。処方は後の条に記す。『摘玄方』は赤い棗を焼いて炭化させ、三銭を酒で飲ませる。これも大棗湯の変法である。</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -13973,6 +14575,20 @@
 Song: Medical texts frequently used fermented soybeans. In Jiangnan, Scallion and Prepared Soybean Decoction, made with scallion and prepared soybean, was commonly taken at the early stage of externally contracted illness to induce mild sweating.
 Shizhen: Processing changes the action of black soybeans. After steaming and fermentation, the preparation becomes more dispersing and upward-moving. Combined with scallion it promotes sweating; with salt it may induce vomiting; with wine it was traditionally used for Wind disorders; with garlic or chive it was paired for other conditions.
 He stresses that Fermented Soybean is not simply food but a processed medicine whose effects depend strongly on preparation and combination.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>淡豆豉（大豆豉）
+【性味】苦・辛、涼。
+【毒性】無毒。
+【帰経】肺経・胃経に帰する。
+【主治】解表除煩、鬱熱の発散。
+【名称の由来】李時珍はいう。劉熙の『釈名』は「豉」を「嗜」と解し、五味を調えて好んで食べられるからだという。許慎の『説文解字』が塩と合わせて発酵させた豆というのは塩辛い豉である。
+【考証】
+陶弘景はいう。豉は日常の食べ物で、春夏に気の巡りが乱れたとき、蒸して炒り、酒に浸して飲むとよい。康伯の方法では酢と酒で湿らせて蒸し、干し、胡麻油を混ぜて再び蒸して干す。三度繰り返して胡椒と生姜の粉末を加えて食べれば、今の油豉より優れる。脚の病を患う人は酒に浸したものを飲み、残りを足に塗ると治るという。
+蘇頌はいう。古今の処方で豉は多く用いられ、江南の人は製造に巧みである。流行性の病にかかるとまず葱豉湯で汗を出し、治ることが多い。
+李時珍はいう。陶弘景の述べた康伯の製法は『博物志』にあり、外国から伝わったので中国では考案者の名で康伯と呼ぶ。豉は中焦を調え気を下げる。黒豆は平性だが豉にすれば温性となり、蒸して発酵させるため上昇・発散する。葱と合わせれば発汗し、塩となら嘔吐を促し、酒となら風を治し、薤となら下痢を治し、蒜となら止血する。炒れば逆に汗を止める。麻黄の根と節が茎と異なるのと同じ道理である。</t>
         </is>
       </c>
     </row>
@@ -14038,6 +14654,21 @@
 Yang Shiying records the use of Nan Xing for Wind disorders with clenched jaw, assisted by Ginseng Root and Acorus Rhizome in appropriate formulas.</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>胆南星（虎掌）
+【性味】苦・やや辛、涼。
+【毒性】有毒。
+【帰経】肺経・肝経・脾経に帰する。
+【主治】清熱化痰、息風定驚。
+【名称の由来】虎膏（『本草綱目』）、鬼蒟蒻（『日華子本草』）。
+蘇恭はいう。根の周囲に丸い芽があり、虎の足に似るので虎掌と呼ぶ。蘇頌はいう。天南星は古い本草の虎掌で、小さいものは由跋と呼ぶ。古い処方には虎掌とあり、天南星の名は後世、唐代の中風や痰毒の処方に使われるようになってから付いた。
+李時珍はいう。虎掌は根でなく葉が虎の足に似るための名である。根が丸く白く老人星のようなので南星といい、虎掌と同じものである。蘇頌の説明は明らかなのに、宋代の『開宝本草』は南星を重ねて別項目にしたので、ここで一つにまとめる。
+【考証】
+李時珍はいう。虎掌・天南星は手足の太陰、つまり脾と肺に働く薬である。辛く舌がしびれる味は風を治して血を散らし、温かく乾かす性質は湿や涎を除き、強く有毒な性質は積滞を攻め腫れを引かせ、口や舌のただれに働く。
+楊士瀛の『直指方』には、風の病で口が開かないときに南星を用い、人参と石菖蒲を佐薬にするとある。</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -14100,6 +14731,21 @@
 He also preserves an old distinction claiming red-flowered forms were more draining while white-flowered forms were more nourishing, though such distinctions belong to historical materia medica theory.</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>牡丹皮（牡丹）
+【性味】苦・辛、微寒。
+【毒性】無毒。
+【帰経】心経・肝経・腎経に帰する。
+【主治】清熱涼血、活血化瘀、虚熱を退ける。
+【名称の由来】鼠姑・鹿韭（『神農本草経』）、百両金（『唐本草』）、木芍薬（『本草綱目』）、花王（『洛陽名園記』）。
+李時珍はいう。牡丹は赤いものを最上とする。種を結んでも根から新しい芽が生じるため牡丹という。唐の人は花が芍薬に似て幹が木質になるため木芍薬と呼んだ。花の品種の中では牡丹を第一、芍薬を第二とし、花王・花相と呼ぶ。欧陽脩の『花譜』には三十余種があり、産地、人、色、特徴から名づけられたものがある。
+【考証】
+張元素はいう。牡丹は天地の精で花の首位にある。葉は陽で発生、花は陰で結実を表し、丹の赤は火なので、陰胞の火を瀉す。四物湯に加えて女性の骨蒸を治す。牡丹皮は手厥陰と足少陰に入り、汗のない骨蒸に、地骨皮は足少陰と手少陽に入り、汗を伴う骨蒸に用いる。心神の不足は手少陰、志の不足は足少陰に関わるため、張仲景の腎気丸は牡丹皮を用いて神志の不足を治す。また腸胃の古い血の滞り、吐血、鼻血にも欠かせず、犀角地黄湯に含まれる。
+李杲はいう。心が虚し、腸胃に熱が積もり、心火が盛んで心気が足りない場合、牡丹皮を君薬とする。
+李時珍はいう。牡丹皮は手足の少陰・厥陰の四経に潜む血分の火を治す。潜伏した火は陰火、陰火は相火である。古方では相火にこれを用い、張仲景の腎気丸にも入る。後世は黄柏ばかり使うが、牡丹皮の働きはさらに優れる。赤い花は排泄させ、白い花は補う。これを理解して分けるべきである。</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -14157,6 +14803,19 @@
 Shizhen: Red Sage Root is red in color and bitter in taste, with a descending action. It enters the blood level of the Heart and Pericardium.
 He cites an old gynecological text stating that a single-herb Red Sage Root powder could, in some contexts, perform functions similar to Four-Substance Decoction. Historically it was credited with removing old blood stasis, supporting generation of new blood, regulating menstruation, treating abnormal uterine bleeding and vaginal discharge, and managing certain pregnancy-related blood disorders.
 Because of these actions, Shizhen compares its overall blood-regulating role with that of Chinese Angelica Root, Di Huang, Sichuan Lovage Rhizome and Shao Yao.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>丹参
+【性味】苦、微寒。
+【毒性】無毒。
+【帰経】心経・肝経に帰する。
+【主治】活血祛瘀、通経止痛、清心除煩、涼血消癰。
+【名称の由来】赤参・蝉草（『名医別録』『神農本草経』）、山参（『日華子本草』）、木羊乳（『呉普本草』）、逐馬（陶弘景）、奔馬草（『四声本草』）。
+李時珍はいう。五つの参には五色と五臓が対応し、人参は脾に入る黄参、沙参は肺に入る白参、玄参は腎に入る黒参、牡蒙は肝に入る紫参、丹参は心に入る赤参である。苦参は右腎の命門の薬だ。古人が紫参を外し苦参を数えたのは、この意味を知らなかったためである。炳という人は丹参が風による足の弱りを治し、走る馬に追いつけるため奔馬草と名づけたといい、実際に使って効いたという。
+【考証】
+李時珍はいう。丹参は赤く苦く、気は平らかで下へ向かい、陰中の陽である。手少陰・厥陰に入り、心と心包の血分に働く。『婦人明理論』によれば、四物湯は妊娠前・産後や月経量の多少を問わず女性の病に広く用いるが、丹参一味の散剤も同じような主治を持つ。古い血を除き新しい血を補い、生きた胎児を安定させ、死胎を排出し、子宮出血や帯下を止め、月経を調えるからであり、当帰・地黄・川芎・芍薬に似た働きがある。</t>
         </is>
       </c>
     </row>
@@ -14231,6 +14890,27 @@
 Its central importance is reflected in Four-Substance Decoction, where Chinese Angelica Root is one of the core herbs for nourishing and regulating blood.</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>当帰
+【性味】甘・辛、温。
+【毒性】無毒。
+【帰経】肝経・心経・脾経に帰する。
+【主治】補血活血、調経止痛、潤腸通便。
+【名称の由来】乾帰（『神農本草経』）、山蕲・白蕲（『爾雅』）、文無（『本草綱目』）。
+蘇頌はいう。許慎の『説文解字』では山に生えるものを薜、または山蕲と呼ぶ。したがって当帰は芹の仲間で、平地のものは芹、山の大きなものは当帰だという。原文冒頭には「太く大きい」とだけあり前文が欠ける。
+寇宗奭はいう。今は四川などで畑に栽培し、肥えて油分が多い。平地か山かで優劣は決められない。
+李時珍はいう。当帰は本来芹の仲間ではないが、花や葉が似るため芹の名を得た。古人は子を残すため妻を娶る。当帰は血を調える女性の要薬で、夫の帰りを思う意味からこの名がある。古い詩の「帰る時なのに帰らない」という意味とも通じる。崔豹の『古今注』によれば、古人は芍薬を贈って別れ、文無を贈って招いた。文無は当帰、芍薬は将離とも呼ぶ。寇宗奭はいう。妊婦や産後に悪い血が上へ突き上げ気血が乱れたとき、当帰は速やかに効く。気血をあるべき場所に帰すことから名づけられたのかもしれない。
+【考証】
+甄権はいう。虚して冷える患者には加えて用いる。
+寇宗奭はいう。世間では血だけを治すというが、『金匱要略』『外台秘要』『千金方』では不足を大いに補い速効を得る薬とされる。産後の悪血の逆上や気血の乱れには特に速く働き、虚を補う産後の要薬である。
+寇宗奭はさらにいう。『薬性論』の「女性の諸々の不足を補う」という一言に、当帰の用途は尽きる。成無己は、脈は血の府で、すべての血は心に属するため、脈を通すにはまず心と血を補うという。張仲景が手足の強い冷え、細く途切れそうな脈に当帰を使うのも心血を助けるためである。
+張元素はいう。当帰には心経の本薬、血の調和、夜に悪化する病の治療という三つの用途がある。血の病には欠かせない。血が滞れば痛むが、甘温は血を調え、辛温は内寒を散らし、苦温は心を助けて寒を散らすため、気血がそれぞれ本来の場所へ帰る。
+王好古はいう。心が血を生むため手少陰へ、脾が血を包むため足太陰へ、肝が血を蔵するため足厥陰へ入る。根の頭は血の滞りを破り、中央部は血を養い、尾は血を巡らせる。全体を人参・黄耆と合わせれば気を補って血を生じ、牽牛などと合わせれば〔原文の語句が欠ける〕。頭痛には、さまざまな痛みが木に属するため血の薬を用いる。
+王機はいう。頭痛には酒で煮た澄んだ汁を飲み、浮いて上へ向かう働きを取る。心痛には粉末を酒で飲み、濁りがあって半ば沈み半ば浮く働きを取る。血尿には酒で煎じ、下へ沈む働きを取る。王海蔵が血の薬でなぜ胸の咳逆を治せるかと問うが、当帰の辛味は散らすため血中の気に働く。陰虚で陽の拠り所がなく気が逆上する場合、血を補えば気も下がる。
+韓𢘅はいう。当帰は血分の病を治す。四川産は力が強く攻める用に、秦の産は穏やかで補う用に向く。病に応じて酒で炮製し、痰があれば生姜で炮製する。血虚には人参・石脂、血熱には生地黄・条芩を佐薬にして血を生む源を保ち、血の積滞には大黄を配する。血の薬に当帰は欠かせず、古方の四物湯では当帰を君、芍薬を臣、地黄を佐、川芎を使とする。</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -14295,6 +14975,21 @@
 Older anecdotes also preserve legendary dream accounts of Notopterygium Root curing Wind disease, reflecting the high reputation these herbs held in traditional medicine.</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>独活（独活・羌活）
+【性味】辛・苦、温。
+【毒性】無毒。
+【帰経】膀胱経・腎経に帰する。
+【主治】解表散寒、祛風除湿、止痛。
+【名称の由来】羌活・羌青・護羌使者（『神農本草経』）、独揺草（『名医別録』）、胡王使者（『呉普本草』）、長生草（『本草綱目』）。
+陶弘景はいう。一本の茎がまっすぐ伸び、風に揺らされないので独活という。『名医別録』は、風があっても揺れず無風でも動くため独揺草と呼ぶ。大明は、独活は羌活の母であるという。
+李時珍はいう。独活と羌活は同じ類の二種で、独活も羌の地から来たものがよい。そのため羌活・胡王使者などの名があり、川芎と撫芎、白朮と蒼朮の関係に似る。原文の説明は「使用には」で途切れている。
+【考証】
+蘇恭はいう。風を治すには独活、水湿を伴う場合には羌活を用いる。
+劉完素はいう。独活は風にも揺れず風を治し、浮萍は水に沈まず水を出す。自ら勝つ性質を利用するのだ。張元素は、風は湿に勝つため羌活は水湿を治すという。独活と細辛を合わせれば少陰の頭痛、めまいに、羌活と川芎を合わせれば太陽・少陰の頭痛、関節の滞り、督脈の病による背骨のこわばりと冷えに働く。王好古は、羌活は足太陽・厥陰・少陰の薬で、独活と別種としないが、後人は羌活の気は強く独活の気は穏やかと分けるという。強い方は足太陽の風湿による頭痛、関節痛、全身痛に欠かせない君薬である。穏やかな方は足少陰に潜む風による頭痛、両足の湿痺で動けない状態を治し、太陽の証には用いない。李時珍は両者とも風を追い湿を除き、関節を通すが、気の強弱が異なるという。『素問』には下から上るものは引いて除くとあり、二薬は苦辛で温かく、薄い味を持つ陰中の陽なので、気を上へ導いて全身へ通し、風湿を散らす。伝承では、唐の劉師貞の兄が風の病にかかり、夢で胡王使者を酒に浸して飲むよう神人に告げられたが、何か分からなかった。再び夢に母が現れ、羌活のことだと教え、服用して治った。嘉謨は、羌活は手足太陽の表裏に薬を導き、足少陰・厥陰にも入り、体表のさまざまな風邪を散らして全身の関節痛を和らげるという。</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -14360,6 +15055,22 @@
 Older texts also describe its use after childhood convulsions and in some dysenteric disorders, but the core principle remains nourishment of blood and fluids rather than strong draining or dispersing action.</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>阿膠
+【性味】甘、平。
+【毒性】無毒。
+【帰経】肺経・肝経・腎経に帰する。
+【主治】補血滋陰、潤燥、止血。
+【名称の由来】傅致膠（『神農本草経』）。
+陶弘景はいう。東阿の産物なので阿膠と呼ぶ。李時珍は、阿井は今の山東省兗州府陽谷県の東北六十里、古代の東阿県にあり、官の建物が管理しているという。
+酈道元の『水経注』によれば、東阿には車輪ほどの大きさで深さ六、七丈の井戸があり、毎年そこで膠を煮て朝廷へ納めていた。済水の水が注ぐ井戸で、その水は濁った水に混ぜても澄ませる。その水で煮た膠を服すと横隔膜の下へ気を通し、痰を除き、嘔吐を止めるという。済水は澄んで重く、下へ向かう性質があるため、濁った滞りや逆上する痰を治すとされた。
+【考証】
+陳蔵器はいう。さまざまな膠は風を治し、下痢を止め、虚を補うが、驢馬の皮は風を治す力が最も強い。
+寇宗奭はいう。驢馬の皮を煎じて膠にするのは皮膚の外へ発散する働きを取るためである。黒いものを用いるのは黒が水に属し、熱を抑えて風の発生を防ぐためで、黒蛇、烏、黒鶏などと同じ考え方だ。李時珍は、阿膠の中心となる働きは血と津液を補うことで、肺を清め陰を養うという。陳自明は、虚を補うには牛皮の膠、風を除くには驢馬の皮の膠を使うという。
+成無己は、陰の不足は味で補い、阿膠の甘味で陰血を補うという。肺の虚実にかかわらず、下したり温めたりする処方には阿膠を用いて肺を安定させ潤す。平和な性質の肺経の要薬である。小児が驚風の後で瞳が定まらない場合、人参の倍量の阿膠を煎じるとよいという。阿膠は心神を育て、人参は気を養う。また痢疾は暑気や潜む熱から生じることが多く、阿膠は大腸にも重要な薬で、熱毒が滞ればそれを導き、なければ落ち着かせる。これらの説から阿膠の働きが分かる。</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -14417,6 +15128,19 @@
 It was used for generalized body pain, stiff neck and spine, severe lumbar stiffness and other Taiyang-type exterior patterns.
 Gao also notes its use in sores above the chest and diaphragm because it disperses constraint and Wind in the upper body. In formulas that tonify the Spleen and Stomach, Saposhnikovia Root may serve as a guiding herb that helps the formula reach the exterior.
 Its inclusion in Drain the Yellow Powder at a relatively high dose was explained through the traditional principle of restraining Liver-Wood within Spleen-Earth.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>防風
+【性味】辛・甘、微温。
+【毒性】無毒。
+【帰経】膀胱経・肝経・脾経に帰する。
+【主治】祛風解表、勝湿止痛、止痙。
+【名称の由来】銅芸（『神農本草経』）、茴芸・百蜚（『呉普本草』）、茴草・屏風・根の異名〔原文欠字〕・百枝（『名医別録』）。
+李時珍はいう。「防」は防ぐことを意味し、風を治す要薬なので防風と名づけられた。屏風は防風を暗示する名であり、芸・茴・蕳の名は花が茴香に似て香りが芸蒿や蕳蘭に似るためである。
+【考証】
+張元素はいう。防風は風の病に広く使う。上半身の風には根の中央、下半身には先端を用い、風を治し湿を除く妙薬である。風が湿に勝つからだ。肺の実を瀉すが、誤って服すと上焦の元気を損なう。李杲は、防風は全身の痛みに用い、導く薬に従って患部へ達する、風の薬の中では潤いを持つものだという。脾胃を補う薬も防風で導かなければ巡らない。背骨が痛み、首がこわばって振り向けず、腰が折れるようで首が引き抜かれるような症状は手足太陽の証で、用いるべきである。胸から上の瘡にも、太陽の証の有無にかかわらず、結びを散らし上部の風を除くために使う。体がこわばりだるい人は風によるので、瘡にこの症状があれば用いる。銭仲陽が瀉黄散に防風を倍量入れるのは、土の中の木を瀉すためである。</t>
         </is>
       </c>
     </row>
@@ -14479,6 +15203,21 @@
 Because sweetness relaxes urgency, honey was traditionally used for cramping or painful conditions of the abdomen, muscles and sores.
 Zhang Zhongjing's famous honey suppository method for severe Yangming dryness and constipation is cited as a classic example of honey's moistening action.
 Older authors also recommended honey drinks for internal Heat and topical use for eye or skin disorders, although such applications belong to historical practice.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>蜂蜜
+【性味】甘、平。
+【毒性】無毒。
+【帰経】肺経・脾経・大腸経に帰する。
+【主治】補中潤燥、止痛解毒。外用して肉芽形成を助け瘡を収める。
+【名称の由来】蜂糖（俗称）、岩に生じるものを石蜜・石飴（『神農本草経』）、岩蜜（『本草拾遺』）と呼ぶ。
+李時珍はいう。蜜は密に作られるので蜜という。『神農本草経』は石蜜と記すが、岩に生じるものをよいとしただけで、後世の議論を招いた。蜂蜜という名称のほうが適切である。
+【考証】
+陶弘景はいう。道家が丸薬を作るとき石蜜は欠かせず、仙方には単独で煮詰めて飲めば長生きできるともある。
+李時珍はいう。蜂は毒のない花から蜜を集めて作る。薬としては熱を清め、中焦を補い、毒を解き、乾燥を潤し、痛みを止める五つの働きがある。生なら涼性で熱を清め、加熱すれば温性となり中を補う。甘く穏やかなので解毒し、柔らかく潤すので燥を除く。穏やかな作用で急な痛みを和らげ、胸腹、筋肉、瘡の痛みを止め、さまざまな薬を調和させる点では甘草に似る。張仲景の蜜煎導法は陽明の乾燥による便秘に用いる優れた方法である。
+孟詵はいう。熱があり手足の調子が悪ければ蜜を水に溶いたもの一碗を飲むとよい。目の熱を伴う膜に点じるには家で飼う蜂の白蜜が最上で、木蜜、崖蜜の順に劣る。生姜の汁と煮詰めれば癩を治すという。</t>
         </is>
       </c>
     </row>
@@ -14550,6 +15289,26 @@
 Shizhen reconciles the apparently contradictory claims that Poria can both increase and reduce urination. He explains that its bland nature supports normal fluid transformation: fluids first ascend to the Lung, then descend through the waterways to the Bladder. Thus its effect depends on the underlying cause rather than simply 'draining downward.' He emphasizes that deficiency with cold limbs and weak pulses requires warming and tonifying treatment instead of indiscriminate use of bland diuretics.</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>茯苓
+【性味】甘・淡、平。
+【毒性】無毒。
+【帰経】心経・肺経・脾経・腎経に帰する。
+【主治】利水滲湿、健脾寧心。
+【名称の由来】伏霊（『本草綱目』）、伏菟（『神農本草経』）、松腴・不死面（『記事珠』）。松の根を抱き込むものを茯神（『名医別録』）という。
+寇宗奭はいう。長年切られた松の根に残る精気が盛んな場合、外へ出て茯苓となり、根から離れて生じる。精気が足りなければ根に付いたまま結実し、離れないので茯神という。
+李時珍はいう。『史記・亀策伝』では伏霊と書く。松の神霊の気が潜んで結実するため伏霊・茯神と呼ぶ。仙人の書には拳ほどの伏霊を身につけると百鬼が消えるとあり、神霊の気の証拠とされた。「苓」の字は写し誤りという。下に伏霊があり上に菟糸が生えるため伏菟とも呼ぶ。形が兎に似るからだという説もある。
+【考証】
+陶弘景はいう。白い茯苓は補い、赤いものは排出させる。仙方でも重要で、精神を調え、魂魄を養い、竅を通し、筋肉や腸を養い心を晴らし、営衛を整える上品の薬とされ、穀物を断っても飢えないという。
+寇宗奭はいう。茯苓は水を巡らせる力が強く、心と脾を養うのにも欠かせない。
+張元素はいう。赤が瀉し白が補うという区別は古代にはなかった。気味は薄く、浮いて上昇する。排尿を促す、皮膚のきめを開く、津液を生じる、虚熱を除く、下痢を止めるという五つの働きがある。尿が出やすい人や頻尿の人が多く飲むと目を傷め、多汗の人なら元気を損なう。淡味で水分をしみ出させるためだ。淡味は天の陽で上へ向かうのに、なぜ水を下へ出すのか。気が薄いものは陽中の陰であり、陽の性質を持ちながら排尿を促すため、手太陽に入る。
+李杲はいう。白は壬癸、赤は丙丁に入る。甘く淡く、陽中の陰で下へ向かう。竅を通して湿を除く、気を養い中を調える、驚悸を治す、津液を生む、尿が多ければ抑え、滞れば通すという六つの働きがある。湿が盛んで排尿しにくいとき、淡味は竅を開き甘味は陽を助け、脾を養って水を追い出す湿除けの要薬となる。
+王好古はいう。白いものは手太陰・足太陽・少陽の気分に、赤いものは足太陰・手少陰・太陽の気分に入り、腎の邪を除く。尿が多ければ抑え、出にくければ促す。車前子と似て、尿を出しても気を消耗させない。酒に浸し光明朱砂と合わせれば真元を守るという。甘く平らかなのにどうして排尿を促すのかとも問う。
+朱震亨はいう。松の残った気から生じ金に属する。張仲景は急性の病の利尿に多用したが、陰虚には適さないかもしれない。長く服すと体を損なう。八味丸に入れるのも、ほかの薬を腎経へ導き、膀胱内の古い汚れを運び出すためである。
+李時珍はいう。本草は茯苓に利尿と腎邪を除く働きがあると記す。一方、李杲や王好古は尿が多ければ抑え、出にくければ通し、朱砂と合わせれば真元を守るという。朱震亨は陰虚には使わないというが、矛盾して見える。茯苓は淡味で水をしみ出させ、上に向かって津液を生み、皮膚のきめを開き、水の源を養った後に下降して尿を出す。張元素のいう上昇する陽は性質を、李杲のいう陽中の陰で下降するものは働きを指す。『素問』では飲食の精気は胃から肺へ上り、水道を通って膀胱へ下る。淡味で水を通す薬もまず上へ向かい、それから下りるのである。頻尿の原因はさまざまだ。『素問』には肺気が盛ん、肺や心の虚、下焦の虚、膀胱へ移った熱、膀胱の固摂の不足、厥陰の病などが挙げられる。肺気が盛んな実熱では体力があり脈も強く、茯苓の甘淡で熱を排出すれば頻尿を止められる。一方、肺・心の虚や膀胱の熱、厥陰の病では虚熱があり、上が熱く下が冷え、脈は弱い。陽を上げ水火を調える薬を用いるべきだ。膀胱が尿を保持できない下焦の虚では手足が冷え脈が遅く、温熱の薬で下を強く補う。後の二種の証は茯苓のような淡味で水をしみ出させる薬では治せず、陰虚に不適というのはこのためである。仙人の服食法も人に合わせて用いるべきだ。</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -14612,6 +15371,22 @@
 Zhang Jiegu was quoted as saying that dizziness from Wind combined with Heart deficiency especially calls for Poria with Pine Root, although ordinary Poria can also treat Heart-related conditions.
 Shizhen also discusses the historical distinction between red and white poria and cautions against rigidly assigning them to blood or Qi without considering actual effects.
 General Records of Holy Universal Relief records Pine Joint Powder, combining the central pine-root portion of Poria with Pine Root with Ru Xiang and taking it with papaya wine for Wind-Cold-Damp pain, contracted sinews and difficulty walking.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>茯神（茯苓）
+【性味】甘・淡、平。
+【毒性】無毒。
+【帰経】心経・脾経に帰する。
+【主治】寧心安神、利水滲湿。
+【名称の由来】伏霊（『本草綱目』）、伏菟（『神農本草経』）、松腴・不死面（『記事珠』）。松の根を抱き込むものを茯神（『名医別録』）という。
+寇宗奭はいう。長年切られた松の根に残る精気が盛んな場合、外へ出て茯苓となり、根から離れて生じる。精気が足りなければ根に付いたまま結実し、離れないので茯神という。
+李時珍はいう。『史記・亀策伝』では伏霊と書く。松の神霊の気が潜んで結実するため伏霊・茯神と呼ぶ。仙人の書には拳ほどの伏霊を身につけると百鬼が消えるとあり、神霊の気の証拠とされた。「苓」の字は写し誤りという。下に伏霊があり上に菟糸が生えるため伏菟とも呼ぶ。形が兎に似るからだという説もある。
+【考証】
+陶弘景はいう。仙方には茯苓としか書かれず茯神の名はない。治療の働きは同じなので用いるのに差し支えない。
+李時珍はいう。『神農本草経』には茯苓だけがあり、『名医別録』で初めて茯神が加えられたが、主治は同じである。後人は心の病には茯神を必ず用い、張潔古も風によるめまいや心虚は茯神なしには治せないという。しかし茯苓も心の病に効く。陶弘景は赤い茯苓は瀉し白いものは補うと述べ、李杲は赤は丙丁、白は壬癸に入ると分けた。李時珍は、赤は血分にのみ入ると決めつければ白い茯神が心病を治せず、赤い茯苓も膀胱へ入れないことになり、張元素が赤白を分けない説も理が十分でないという。
+『聖済録』の松節散は、茯神の中心の木一両と乳香一銭を石器で炒って粉にし、一回二銭を木瓜酒で飲む。風寒と冷湿が筋骨を侵し、足の筋がつって痛み歩きにくい場合をはじめ、筋のひきつりと痛みに用いる。</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15456,23 @@
 Shizhen concludes that Prepared Aconite Root and Aconite Root are toxic medicines generally reserved for serious conditions or used in very small amounts to guide other herbs. Historical anecdotes of people tolerating unusually large quantities are presented as exceptional constitutions, not normal dosing examples.</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>附子
+【性味】辛・甘、大熱。
+【毒性】有毒。
+【帰経】心経・腎経・脾経に帰する。
+【主治】回陽救逆、補火助陽、散寒止痛。
+【名称の由来】母となる根は烏頭（『神農本草経』）という。
+李時珍はいう。初めに植えたものを、烏の頭に似るので烏頭という。そこに子が母に付くように生えるものが附子であり、芋の親芋と子芋に似る。同じ植物だが、別に草烏頭や白附子があるため、区別して黒附子・川烏頭とも呼ぶ。古い注釈は川烏と草烏を混同していたので、ここで正す。
+【考証】
+寇宗奭はいう。虚寒を補うには附子、風の病には天雄を多く使い、烏頭・烏喙・附子はそれぞれに応じて用いる。李時珍は王氏の『究原方』を引く。附子は重く留まり、脾を温め寒を追う。川烏頭は軽く散り、脾を温め風を除く。寒の病には附子、風の病には川烏頭を使う。中風には最初から風薬や烏附を用いず、まず気の薬を使い、後に烏附を用いるという説もある。烏附の薬は冷まして服すのがよいという。下に陰寒があり虚陽が上へ浮く場合、冷薬では陰寒が強まり、熱薬を熱いまま飲むと体が拒む。熱薬を冷まして飲めば、飲み込んだ後で冷たさは消え、熱性が働く。これは反治の妙とされる。張仲景は寒疝に蜜で煎じた烏頭、『近効方』は喉の閉塞に蜜炙した附子を口に含む方法、朱丹溪は疝気に烏頭と梔子を用いた。李杲は陰が盛んで陽が拒まれる傷寒の患者が顔と目が赤く渇き、脈が非常に速いのに押すと散る場合、姜附湯に人参を加え、半斤を服させて発汗後に治したという。
+呉綬はいう。附子は陰証の要薬で、傷寒が三陰へ移った場合や内寒を伴い、体が熱くても脈が沈む場合に用いる。手足の冷え、腹痛、細く沈む脈、重ければ唇が青く陰嚢が縮む場合は急いで用い、陰を退け陽を戻す。近ごろは陰証を疑って使うのが遅れがちだという。内外ともに陰で陽気が急に衰えたとき、人参で元を養い、附子で経を温め寒を散らすべきだと説く。
+劉完素はいう。しびれに烏頭や附子を用いるのは強い気が道を開くためで、最初はかえってしびれが増しても、薬の気が尽き正気が巡ると治る。張元素は白朮を佐薬とした附子が寒湿を除く要薬で、湿の薬に少量加えて経へ導くといい、火の源を養い陰寒を除けば排泄も整うという。虞摶は、附子は力強く、補気薬を十二経へ導いて失われた元陽を戻し、補血薬を血分へ、発散薬を体表へ、温める薬を下焦へ導くという。
+朱震亨はいう。気虚で熱が強い場合や湿の多い肥満の人には、附子や烏頭を少量添えて薬を巡らせることがある。張仲景の八味丸で附子は少陰へ導く役であり、補う主体は地黄である。附子そのものを補薬とみなすのは誤りで、滞らず下へ走る性質で地黄の滞りを動かす。烏頭・天雄を風の治療や補薬として安易に用い、人を害した例も多い。王履はこれに対し、八味丸は陽の火の不足、銭仲陽の六味地黄丸は陰虚に用いるので、附子は陽を補う薬で、単に滞りを動かすためではないという。
+王好古は、体が冷え手足が厥冷する人以外には烏附をむやみに用いるべきでなく、附子で火を補えば水を枯らす恐れがあるという。李時珍は、烏附は有毒で重い病でなければ用いないが、補薬に少量加えて導けば速効があるという。少し飲んだだけでひどく乾燥する人もいる一方、附子湯や硫黄を数年続けた痩せて冷える王族、鹿茸・附子を服して八十余歳まで健康だった武官、毎日乾姜・附子と硫黄の丸薬を用いて九十歳まで生きた役人の話もある。ほかの人なら一粒でも害になることがあり、体質の偏りを一律には扱えない。『瑣砕録』には寒さの厳しい滑台で、住民が芋や栗のように附子を食べるとある。土地の気候によるのだろう。</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -14749,6 +15541,22 @@
 Song cites old antidotal traditions in which Licorice Root was used after toxic exposures. These accounts reflect its historical reputation for moderating toxicity, though they should not be treated as modern emergency treatment instructions.</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>甘草
+【性味】甘、平。
+【毒性】無毒。
+【帰経】心経・肺経・脾経・胃経に帰する。
+【主治】益気補中、清熱解毒、祛痰止咳、緩急止痛、諸薬の調和。
+【名称の由来】密甘・密草・美草・蕗草・国老（『名医別録』）、霊通（『記事珠』）。
+陶弘景はいう。甘草は多くの薬をまとめる重要な草で、古方に使わないものは少ない。香木の中の沈香に似る。「国老」は皇帝の師の称号で、君主ではないが君主に尊ばれる。草木や鉱物の薬を調和させ、毒を解くための名である。甄権は甘草を諸薬の君とし、多くの石薬や草木の毒を解き、諸薬を調えるので国老と呼ぶという。
+【考証】
+朱震亨はいう。甘味でさまざまな火の勢いを大きく緩める、徳の厚い君子のような薬である。下焦へ作用させるには根の先端を使う。
+李杲はいう。甘草は気が薄く味が濃く、上昇も下降もする陰中の陽である。陽の不足を甘味で補い、甘温によって強い熱を鎮める。生で用いれば平性で脾胃の不足を補い心火を瀉す。炙れば温性となり三焦の元気を補い、表の寒や邪熱、喉の痛みを除き、正気を緩め陰血を養う。心火が脾を攻めて腹が急に痛む場合には倍量用いる。急な状態を和らげ、ほかの薬を協調させるため、熱薬の熱も寒薬の寒も緩め、寒熱の混在も調和する。
+王好古はいう。苦味は下し、辛味は散らし、酸味は収め、鹹味は引き締め、甘味は上へ向かうのに、本草が甘草は気を下げるというのはなぜか。甘味は中をつかさどり、昇降・浮沈・内外のすべてに働き、調和・緩和・補瀉を行う。附子理中湯では附子が上りすぎないよう、調胃承気湯では急に下しすぎないよう甘草で緩める。小柴胡湯では柴胡・黄芩の寒と人参・半夏の温を調える。建中湯では中を補って脾の急を、鳳髄丹では腎の急を緩め元気を生む。一方、甘味は腹を張らせるため、すでに腹が張る人には適さない。張りがなければ炙甘草で補い、張りがあれば生甘草で瀉して薬を患部へ導く。『経』の「甘で補い、甘で瀉し、甘で緩める」とはこのことである。
+李時珍はいう。甘草は外が赤く中が黄色で、地と火の色を兼ねる。諸薬を調和させ、多くの邪を治す薬中の良相である。ただし腹の張り、嘔吐、飲酒に関わる病には甘味が合わず、大戟・芫花・甘遂・海藻とは相反する。蘇頌は孫思邈の『千金方』を引き、甘草が多くの薬毒を雪に熱湯を注ぐように解くという。烏頭・巴豆の毒には甘草が効くとされ、大豆汁だけでは効かなかったが甘草を加えた甘豆湯には効き目があったという。葛洪の『肘後備急方』によれば、嶺南の人は蠱毒を避ける薬の秘密を「三百頭の牛」「三百両の銀」と称した。食前に炙甘草一寸を噛み汁を飲み、毒があればすぐ吐くという。さらに炙甘草三両・生姜四両を水六升で二升まで煎じ、一日三回飲むか、都淋藤・黄藤を酒で煎じて飲む方法も記す。甘草を携帯し、噛んでから食べても吐かなければ毒ではないとした。「三百頭の牛」は土常山、「三百両の銀」は馬兜鈴藤を指し、各項に詳しい。</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -14811,6 +15619,22 @@
 Haogu: Dried Ginger acts strongly on the Qi level of the Heart and Spleen. Its drying action removes Cold-Dampness from the Spleen rather than draining normal Qi.
 Zhenheng describes different processing methods for blood disorders, including charring it when traditional theory called for warming the channels and controlling bleeding.
 Shizhen emphasizes Dried Ginger's role as a guiding herb, carrying blood medicines into the blood level and Qi medicines into the Qi level. He explains its occasional use in bleeding accompanied by profound Cold as an example of treating a complex presentation according to the underlying pattern rather than the visible symptom alone.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>乾姜
+【性味】辛、熱。
+【毒性】無毒。
+【帰経】脾経・胃経・腎経・心経・肺経に帰する。
+【主治】温中散寒、回陽通脈、温肺化飲。
+【名称の由来】李時珍はいう。生姜を乾かしたため乾姜と呼び、親の生姜から作る。白くしっかりしたものがよいので白姜、均姜ともいう。薬に用いるときは炮製するのがよい。
+【考証】
+張元素はいう。乾姜は気が薄く味が濃く、半ば沈み半ば浮いて昇降できる陽中の陰であり、一方で非常に辛く熱い陽中の陽でもある。心を通し陽を助ける、臓腑に深く残る寒を除く、諸経の寒気を発散させる、寒を受けた腹痛を治す、という四つの用途がある。腎の陽がなく脈が絶えそうなら黒附子を導き手にして水で煎じ、姜附湯とする。中焦の寒にも用い、辛味で寒を散らす。下焦も補うため四逆湯に含まれる。生の乾姜は辛いが炮製すればやや苦くなって中に留まり、附子のように走らないので内側の寒を治す。理中湯に入れるのも陽を戻すためである。
+李杲はいう。生の乾姜は辛く、炮製品は苦く、ともに陽の薬である。生なら寒邪を追って表に発し、炮製すれば胃の冷えを除き中に留まる。多量では元気を消耗するため生甘草で緩める。五味子と合わせて肺を温め、人参と合わせて胃を温める。
+王好古はいう。乾姜は心・脾二経の気分に用い、心気の不足を補う。辛熱なのに脾を補うといわれ、理中湯では「瀉す」ともいうのは、脾の寒湿の邪を乾かして除くのであって正気を瀉すのではない。中焦を治すために使っても、気が上へ越えることがあるので注意すべきだという。
+朱震亨はいう。肺に入れば肺気を巡らせ、腎では下の湿を乾かす。肝経で血の薬を導いて血を生じ、陰を補う薬と合わせても血薬を気分へ導くので、血虚の発熱や産後の高熱に用いる。唾液や便に混じる血を止めるには黒く炒る。血を失って顔色が白くつやがなく、脈が柔らかいのは強い寒であり、乾姜で経を温め血を養う。
+李時珍はいう。乾姜は血薬を血分へ、気薬を気分へ導き、古いものを除き新しいものを養う。陽が生じれば陰も育つため血虚に用いる。吐血、鼻血、下血でも陰ばかりで陽がない場合には用いる。熱性の薬を熱の徴候に用いる従治の方法である。</t>
         </is>
       </c>
     </row>
@@ -14881,6 +15705,24 @@
 Shizhen contrasts Kudzu Root with Ephedra Herb: both are light and dispersing, but Ephedra Herb primarily acts on the Taiyang and Lung exterior, whereas Kudzu Root primarily acts on the Yangming and Spleen muscle layer.</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>葛根（葛）
+【性味】甘・辛、涼。
+【毒性】無毒。
+【帰経】脾経・胃経・肺経に帰する。
+【主治】解肌退熱、麻疹の発疹を促す、生津止渇、昇陽止瀉、経絡を通す、酒毒を解く。
+【名称の由来】鶏斉（『神農本草経』）、鹿藿・黄斤（『名医別録』）。
+李時珍はいう。「葛」は「曷」を音に借りた字である。鹿が食べる九草の一つなので鹿藿という。黄斤の名の由来は分からない。
+【考証】
+陶弘景はいう。生の葛を搗いて汁を飲めば温病の熱を解く。旧暦五月五日の正午に根を採って刻み、黄黒くなるまで煎り、粉末を水で方寸匕飲めば瘧や瘡によいという。
+蘇頌はいう。張仲景が傷寒に葛根湯を用いるのは、高熱を治し、肌を解き、皮膚のきめを開くためである。
+張元素はいう。陽を上げ津液を生じ、脾虚による渇きを治すが、胃気を傷つけぬよう多用しない。張仲景は太陽と陽明が同時に病むとき桂枝湯に麻黄・葛根を加え、葛根黄芩黄連の解肌湯も使った。太陽の邪が陽明へ入るのを防ぐためで、葛根は太陽だけの薬ではない。割れるような頭痛を伴う陽明中風には葛根葱白湯が適するが、太陽病の初期で陽明に入る前の頭痛に升麻・葛根を使えば、かえって邪を陽明へ導く。
+朱震亨はいう。痘瘡に赤い点が出た後は、表を虚させ斑を悪化させる恐れがあるため、葛根升麻湯を用いない。
+李杲はいう。乾葛は軽く浮き、胃気を上へ促して津液を生じ、肌の熱を除く。脾胃の虚弱による下痢に重要である。徐用誠は、気味が薄く軽く上昇するがわずかに下降もする陽中の陰で、渇きを止め、酒を解き、表の邪を散らし、発疹の出にくさを改善するという四つの用途を挙げる。
+李時珍はいう。『本草』の十剤に、軽い薬は実を除くとして麻黄・葛根を挙げる。麻黄は太陽と肺経に入り皮膚や毛に、葛根は陽明と脾経に入り筋肉に働く。両者とも軽く発散するが、作用する経は異なる。</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -14940,6 +15782,20 @@
 He compares part of its tonic action with Ginseng Root and part with nourishing animal foods such as mutton.
 Later physicians used it for chronic deficiency, weakness, wasting and severe wheezing when both Lung and Kidney were considered depleted.
 Liu Chun says it is appropriate when Qi and fluids decline and Yin and blood are exhausted. He Daying praises it particularly for chronic wheezing and cough.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>蛤蚧
+【性味】鹹、平。
+【毒性】小毒。
+【帰経】肺経・腎経に帰する。
+【主治】補肺益腎、納気定喘、助陽益精。
+【名称の由来】蛤蟹（『日華子本草』）、仙蟾（『本草綱目』）。
+志という人は、雌雄が一対で、いつも自分の名を鳴くという。李時珍は、蛤蚧は鳴き声、仙蟾は姿から名づけられたという。嶺南では蛙を蛤と呼び、頭が蛙や蟾蜍に似るためでもある。雷斅が雄を蛤、雌を蚧とする説も成り立つ。
+【考証】
+寇宗奭はいう。肺虚による消耗性の咳を補う効果がある。
+李時珍はいう。古人は弱さを補うものとして人参や羊肉を挙げた。蛤蚧は肺気を補い、喘ぎや渇きを止める点で人参に似る。陰血を養い精を助け、衰弱を補う点では羊肉に似る。近世の虚労や萎弱の治療、許叔微の消渇治療にも滋補のために使われる。劉純は気と津液が衰え陰血が尽きた人に適するといい、何大英は喘ぎと咳にはこれに勝るものがないという。</t>
         </is>
       </c>
     </row>
@@ -15008,6 +15864,22 @@
 Numerous legends describe extremely old goji plants, dog-shaped roots and people gaining unusual longevity after consuming them. Shizhen preserves these stories while still distinguishing the practical medicinal actions of the plant's different parts.</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>枸杞子（枸杞・地骨皮）
+【性味】甘、平。
+【毒性】無毒。
+【帰経】肝経・腎経に帰する。
+【主治】滋補肝腎、益精明目。
+【名称の由来】枸〔原文欠字〕（『爾雅』、音は計）、枸棘（『本草衍義』）、苦杞（『詩疏』）、紅菜頭（『図経本草』）、天精（『抱朴子』）、地骨・地輔（『神農本草経』）、地仙（『日華子本草』）、却暑（『名医別録』）。
+李時珍はいう。棘が枸に、茎が杞に似るため両字を合わせた。道書には千年ものの枸杞は犬の形になるので「枸」と名づけたというが、確かではない。蘇頌は、仙人杖には枸杞、苦苣に似た葉を持つ菜、黒く枯れた竹の三種があるという。
+【考証】
+陶弘景はいう。枸杞の葉を汁物にすると少し苦い。「遠く旅するなら蘿摩と枸杞を食べるな」という俗言は、両者が精気や生殖の力を強めるという意味である。根と実は服食家に好まれ、仙人の杖の名もふさわしい。
+蘇頌はいう。茎・葉・実は体を軽くして気を益す。『淮南枕中記』には、正月の寅の日に根を採って二月の卯の日に調え服す、三月の辰の日に茎を採って四月の巳の日に服す、五月の午の日に葉を採って六月の未の日に服す、七月の申の日に花を採って八月の酉の日に服す、九月の戌の日に実を採って十月の亥の日に服す、十一月の子の日に根を採って十二月の丑の日に服すとある。花・実・根・茎・葉を煎じたり、実の汁を煮詰めたりしても働きは同じという。蓬莱県の南丘村には一、二丈の枸杞が多く、村人の長寿は水土の気にもよるだろう。潤州開元寺の古い井戸のそばに育つ枸杞にちなんだ「枸杞井」の水も体によいとされる。雷斅は根が物の形に似たものを上品とする。
+李時珍は劉禹錫の『枸杞井詩』を引く。僧房の薬木は冷たい井戸に寄り、清水と薬には霊があり、緑の葉と赤い実を結び、枝は仙人の杖、古い根は瑞犬の姿となり、一杯の水が寿命を延ばすと詠む。『続仙伝』には朱孺子が二匹の花犬を追って枸杞の茂みに入り、犬形の根を掘って食べると体が軽くなった話がある。周密の『浩然斎日抄』にも、宋の徽宗の時に順州の土中から犬形の古い枸杞を得て献上したとある。滋養に働くのは実だけではなく、根も単なる解熱にとどまらない。ただし部位ごとに性味と用途は異なる。苗は天精といい苦甘・涼で上焦の心肺の熱に、根は地骨といい甘淡・寒で下焦の肝腎の虚熱に向く。ともに三焦の気分に働き、甘寒で内熱を瀉す。実は甘平で潤し、熱を退けず、腎と肺を補い精と気を養う。部位別にも併用でも役立つ。黄芩・黄連で上焦の火、黄柏・知母で下焦の陰火を苦寒で下すことばかりを補陰降火とし、長期服用で元気を傷めるのは惜しい。枸杞や地骨の甘寒で穏やかに補えば、精気が満ちて邪火は自然に退く。私も青蒿を地骨に添えて熱を退けるのに用い、たびたび効果を得たという。
+兵部尚書の劉天和が集めた『保寿堂方』には地仙丹がある。赤脚張という異人が猗氏県の老人に伝え、服した老人は百余歳まで生き、速く歩き、白髪が黒くなり歯が生え直したという。平性で邪熱を除き、目を明らかにして体を軽くするとされる。春に葉を採って天精草、夏に花を採って長生草、秋に実を採って枸杞子、冬に根を採って地骨皮とする。それぞれ陰干しし、灰を含まない酒に一夜浸し、昼夜四十九日さらして乾かし粉末にする。煉蜜で弾丸大の丸薬を作り、朝夕一丸ずつ噛んで、一晩置いて沸かした湯で飲む。刺がなく甘いものを採り、刺のあるものは服しても益がないという。</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -15068,6 +15940,18 @@
 The surviving source text ends abruptly after this explanation.</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>釣藤鈎（鉤藤）
+【性味】甘、涼。
+【毒性】無毒。
+【帰経】肝経・心包経に帰する。
+【主治】息風定驚、清熱平肝。
+【名称の由来】陶弘景は、建平の産で吊藤とも書き、小児の治療に用い、ほかの処方には入れないという。李時珍は、とげが釣り針のように曲がるため釣藤と呼び、「吊」は簡略な表記だという。
+【考証】
+李時珍はいう。釣藤は手足厥陰の薬である。足厥陰は風、手厥陰は火をつかさどる。驚癇やめまいは肝風と相火に関わり、釣藤が心包と肝を通じさせ、風と火が鎮まれば症状も治まる。原文は「あるいは数寸を入れるという」で途切れている。</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -15130,6 +16014,20 @@
 Shizhen criticizes descriptions calling the herb bitter, noting that its actual taste is sweet rather than bitter and that its action should be understood from this quality.</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>瓜蔞仁（栝楼仁）
+【性味】甘、寒。
+【毒性】無毒。
+【帰経】肺経・胃経・大腸経に帰する。
+【主治】潤肺化痰、滑腸通便。
+【名称の由来】果裸（音は裸）、栝楼（『本草綱目』）、天瓜・黄瓜・沢姑（『名医別録』）、地楼（『神農本草経』）。根は白薬・天花粉（『図経本草』）、瑞雪（趙宜真）という。
+李時珍はいう。「裸」は「蓏」と同じで、許慎は木の上に実るものを果、地に生じるものを蓏という。この植物はつるが木に絡むため両方を名に含む。『詩経』に果裸の実が家の軒まで伸びるとある。栝楼は果裸の音が変わったもので、表記が重ねて変わり元の姿から離れた。昔は瓜と姑が同音だったので沢姑とも呼び、斉では形から天瓜と呼ぶ。雷斅が丸いものを栝、長いものを楼とするのはこじつけで、雌雄で分ければよい。根を粉にすると雪のように白いので天花粉といい、蘇頌の『図経』が別項目にしたのは誤りなので統合する。
+【考証】
+朱震亨はいう。栝楼の実を胸痺に用いるのは甘く潤すためである。甘味は肺を補い、潤いは気を下げる。胸に痰があるのは肺が火に迫られ下降の働きを失ったためで、甘く緩め潤して下せば痰も下がる。咳の重要な薬であり、胸や横隔膜の汚れた鬱熱も洗い流し、消渇にもよい。
+李時珍はいう。張仲景が胸の痛みが心や背に及び、咳や喘ぎのある胸痺、また胸の結びと張りの痛みに栝楼の実を用いたのは、甘寒で胃気を傷めず、上焦の火を下げ痰気を降ろすためである。成無己が苦寒で熱を瀉すと説いたのは、実際の甘い味を確かめず文に合わせた解釈である。</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -15188,6 +16086,19 @@
 Traditional theory regarded the tortoise as a deeply Yin creature associated with the northern direction and Water. For that reason its shell was used to nourish Yin, support blood and treat deficiency.
 Shizhen contrasts tortoise and deer. The tortoise was associated with the Ren vessel and with nourishing Heart, Kidney and blood; deer antler was associated with the Du vessel and with supporting Yang, essence and Qi.
 He concludes that the classical indications of tortoise shell largely involve Yin deficiency and weak blood, reflecting this traditional symbolic framework.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>亀板膠（水亀）
+【性味】甘・鹹、涼。
+【毒性】無毒。
+【帰経】肝経・腎経・心経に帰する。
+【主治】滋陰潜陽、益腎健骨、養血補心、涼血止血。
+【名称の由来】神屋（『神農本草経』）、敗亀版・敗将（『日華子本草』）、漏天機（『図経本草』）。李時珍はこれらはいずれも隠語だという。
+【考証】
+陰に属するもので、北方の気を受けて生じるため、陰を補い、血の病や虚労を治すという。
+李時珍はいう。亀も鹿も霊性があり長寿である。亀は頭を腹に向けて隠すことが多く任脈に通じるので、甲羅で心・腎・血を補い陰を養う。鹿は鼻を尾の方へ向けることが多く督脈に通じるので、角で命門・精・気を補い陽を養う。これは生き物の理の奥深いところで、亀甲の主治が陰虚・血弱に属することも理解できる。鼈甲の項も参照。</t>
         </is>
       </c>
     </row>
@@ -15255,6 +16166,21 @@
 He also distinguishes cinnamon bark as a more downward-moving medicine that supports the source of Fire, while Cinnamon Twig has a stronger role in the surface and channels.</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>桂枝（桂）
+【性味】辛・甘、温。
+【毒性】無毒。
+【帰経】心経・肺経・膀胱経に帰する。
+【主治】発汗解肌、温通経脈、助陽化気。
+【名称の由来】李時珍は范成大の『桂海志』を引く。木の葉の中心には通常一本の筋があるが、桂には圭の形をした二本の筋があり、「圭」の字を含むという。陸佃の『埤雅』は、桂は圭を持つ使者のように諸薬を導くという。『爾雅』の「梫」はほかの木を侵す性質に由来し、『呂氏春秋』には桂枝の下に雑木は生えず、『雷公炮炙論』には桂を木の根に打つと枯れるとある。桂と牡桂には厚さや辛味の違いがあるが、『名医別録』の別項目を統合して以下で分ける。
+【考証】
+寇宗奭はいう。桂は甘辛で大熱であり、『素問』は辛甘の発散を陽とする。張仲景の桂枝湯が傷寒の表虚に用いられるのもそのためである。ほかの桂は温性が弱く風寒を治せない。『神農本草経』には単に桂とあり、桂枝とは枝の皮を取ることを指す。
+王好古は問う。本草は桂が煩いを止めて汗を出すというのに、張仲景は無汗の人は桂枝湯を飲まず、汗をかいた人は再び汗を出してはならないとしながら、多汗には桂枝甘草湯を用いる。発汗と止汗をどう両立させるのか。桂枝の辛甘は血脈を通じさせ、営衛を調えることで自然に汗が出て邪が去るのであって、皮膚の毛穴を直接開いて汗を強制するわけではない。太陽中風では衛が強く営が弱く、熱と自汗があるため桂枝で営を調え、衛を整える。汗が多い場合も営衛を調えれば邪が去って汗が自然に止まるのであり、汗孔を閉じるわけではない。無汗の傷寒に桂枝を用いるのは誤りである。桂枝湯の「発汗」は自然に汗が出る意味で、麻黄による発汗とは異なる。虚による汗の治療もこの意味を見極めるべきだ。
+成無己はいう。桂枝はもともと肌を解く薬である。太陽中風でも皮膚のきめが密で、営衛とも邪が強く、脈が浮緊で発熱しても無汗なら用いない。皮膚が緩み、自汗があり、脈が浮緩で、風邪が衛気を侵す場合に適する。辛甘で発散させるため桂枝を君薬、芍薬を臣薬、甘草を佐薬とする。辛苦で風を抑え、甘で緩め、酸で収める。生姜・大棗を使薬とするのは脾胃の津液を巡らせ営衛を調えるためで、単なる発散ではない。麻黄湯には生姜・大棗を入れず、もっぱら汗を出す。
+李時珍はいう。麻黄は皮膚と毛に達し、肺へ入る辛味によって発汗して寒邪を散らす。桂枝は営衛へ通じ、脾へ入る甘味と肺へ入る辛味によって肌を解き風邪を除く。肉桂は下へ向かって火の源を養う。『聖恵方』には桂心は心へ入り、血を導いて汗や膿に変えるとある。手少陰の君火と厥陰の相火が命門と同じ気を持つためで、『名医別録』が桂は血脈を通すというのもその意味である。</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
@@ -15310,6 +16236,18 @@
 He preserves the old saying that larger amounts move blood more strongly, while smaller amounts may have a gentler, nourishing effect.
 An anecdote tells of a woman who collapsed after childbirth and was thought to have severe blood obstruction. Large quantities of safflower were boiled and the steam used around her bed; she reportedly regained consciousness.
 The story illustrates the herb's historical reputation for strongly moving blood, rather than a modern treatment recommendation.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>紅花（紅藍花）
+【性味】辛、温。
+【毒性】無毒。
+【帰経】心経・肝経に帰する。
+【主治】活血通経、散瘀止痛。
+【名称の由来】紅花（『開宝本草』）、黄藍。蘇頌は、花が赤く葉が藍に似るので藍の名があるという。
+【考証】
+李時珍はいう。血は心包で生じ肝に蔵され、衝脈と任脈に属する。紅花の汁は血と同類なので、男性の血脈を巡らせ、女性の月経を通じさせる。多量では血を動かし、少量では血を養う。ある記録には、新昌の徐氏の妻が産後のめまいで亡くなったように見えたが、胸だけがわずかに温かかったとある。名医の陸氏は血が塞いだためと診て、紅花数十斤を大鍋で煮て三桶の湯を窓の下に並べ、女性を寝台ごとその上へ運び、湯が冷めれば足して蒸した。まもなく指が動き、半日後に意識を回復した。これは唐の許胤宗が黄いろい湯の蒸気で柳太后の風の病を治した方法に似るという。</t>
         </is>
       </c>
     </row>
@@ -15375,6 +16313,22 @@
 Zhenheng stresses that Magnolia Bark is not simply a tonic. Its warm, acrid nature moves stagnant Qi and drains excess from the Stomach. In Calm the Stomach Powder it works with Atractylodes Rhizome to remove Dampness and restore balance rather than merely 'warming and supplementing.'
 Haogu explains its apparently opposite effects through combination. With Immature Bitter Orange or Da Huang it drains excess fullness; with Aged Tangerine Peel and Atractylodes Rhizome it resolves Damp fullness and warms the middle.
 Its bitterness directs Qi downward and relieves excess; its warmth helps disperse Cold-Dampness. Thus the formula context determines whether its effect appears more draining or more supportive.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>厚朴（濃朴）
+【性味】苦・辛、温。
+【毒性】無毒。
+【帰経】脾経・胃経・肺経・大腸経に帰する。
+【主治】燥湿消痰、下気除満。
+【名称の由来】烈朴（『日華子本草』）、赤朴・濃皮（『名医別録』）、重皮（『広雅』）。木は榛、実は逐折（『名医別録』）ともいう。
+李時珍はいう。木質は素朴で皮は厚く、味は辛く強く色は赤紫なので、濃朴・烈朴・赤朴と呼ぶ。蘇頌は『広雅』の重皮を引き、処方書では濃皮とも書くという。
+【考証】
+寇宗奭はいう。厚朴は平胃散に入り、中焦をよく調える。脾胃を温め冷えた気を巡らせるため、今も広く用いられる。
+張元素はいう。胃を整える、腹の張りを除く、妊婦には避けるという三点がある。腹の張りを除くとしても虚弱者には慎重に用い、誤用すれば元気を失わせる。寒による張りには強い温熱薬に添えると、結びを散らす重要な薬となる。
+朱震亨はいう。厚朴は土に属し火を含み、温かい気で胃の実を瀉す。平胃散で蒼朮と合わせるのは胃の湿を除き、行き過ぎた胃土を中庸に戻すためで、脾胃を温めて補うためではない。腹が張る場合、辛味で滞った気を動かしたら薬を去るべきだ。気が実した人が人参や黄耆を過剰に飲み、張りや喘ぎを生じたときにはこれで瀉す。
+王好古はいう。本草は厚朴が中風・傷寒の頭痛、中焦の温め、益気、痰を消して気を下げる、腸胃を養い腹の張りを除くとする。気を瀉すのか益すのか。枳実・大黄と合わせれば実した張りを瀉し、橘皮・蒼朮と合わせれば湿による張りを除いて中を温め気を養う。解表の薬と合わせれば傷寒の頭痛、下痢を治す薬と合わせれば腸胃を整える。苦味で瀉し温性で補うので、成無己も苦味が腹の張りを瀉すという。李杲は、苦味は気を下げて実した張りを瀉し、温性は気を養い湿による張りを散らすという。</t>
         </is>
       </c>
     </row>
@@ -15450,6 +16404,21 @@
 Gao describes its use in inflamed sores, acute red and painful eyes, and food stagnation with focal epigastric fullness when appropriately combined.
 Shizhen highlights how classical formulas pair Coptis Rhizome with warming or Qi-moving herbs: Costus Root for dysentery, Dried Ginger or Fresh Ginger for Cold-Heat balance, Wu Zhu Yu for Liver Fire, and Asarum Herb for mouth sores. Such pairings prevent an overly one-sided bitter-cold effect.
 He rejects Daoist claims that prolonged use promotes immortality. Because Coptis Rhizome is intensely bitter and cold, he argues that it should be stopped once the targeted Heat and Dampness are corrected; long-term excessive use can damage normal physiological balance.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>黄連
+【性味】苦味、非常に寒性。
+【毒性】無毒。
+【帰経】心・脾・胃・肝・胆・大腸経。
+【主治】熱を清め湿を乾かし、火を瀉して毒を解く。
+【名称の由来】王連（『本経』）、支連（『薬性』）。李時珍によれば、根が数珠状につながり黄色いため、この名がある。
+【考証】張元素は、寒性で苦味が強く、昇降の両方に働き、手少陰経に入るという。作用は心火を瀉す、中焦の湿熱を除く、瘡を治す、風湿を除く、急な目の充血を治す、中焦の出血を止める、の六つ。張仲景の心下痞を治す諸種の瀉心湯にも用いる。成無己は、苦味は心に入り寒性は熱に勝ち、心下の虚熱を導くと説く。蛔虫は甘味で動き苦味で鎮まるため、黄連・黄柏の苦味を用いる。王好古は、心火を瀉すのは脾を瀉すことにも通じるという。朱震亨は中焦の湿熱と心火を除くとし、脾胃の気が虚して運化できない場合は茯苓・黄芩に替える。猪胆汁で炒めて竜胆草を添えると肝胆の火を強く瀉す。熱のため食べられない下痢には人参と煎じ、少量ずつ飲ませるという。
+劉完素は、古方で痢疾の要薬とされる理由を、辛味が鬱結を開き、苦味が湿を乾かし、寒性が熱を制することに求める。寇宗奭は、初発の実熱で血便を伴う場合には効くが、虚寒の下痢や少量の血を見ただけで漫然と使うのは危険と戒める。李杲は瘡には当帰を合わせ、赤く腫れて痛む目には酒で浸した黄連・当帰を煎じ、食滞による心下痞満には枳実を合わせる。蘇頌は羊肝丸や、黄連・当帰・芍薬を等量煎じて温かいうちに目を洗う古法を挙げる。韓氏は人乳で蒸したものを目に用いるほか、桂枝・蜂蜜、五苓散・滑石、使君子・白芍薬・木香などとの配合例を記す。李時珍は目の病と痢疾の要薬とし、香連丸、姜連散、変通丸、姜黄散のほか、消渇には酒蒸し、伏暑には酒煮、下血には大蒜、肝火には茱萸、口瘡には細辛と組み合わせる例を示す。寒熱・陰陽の薬を助け合わせる配合の妙である。
+陶弘景は痢疾や口渇への使用と、道家の長期服用説を記す。『黄連賛』『黄連頌』や『神仙伝』にも長寿の伝承があるが、李時珍は『本経』『別録』にその説はなく、強い苦寒の薬は火と湿が治まれば止めるべきだと論じる。『素問』の五味の偏り、王冰の注、秦観が眼病に黄連を大量服用する友人に宛てた戒めを引き、久服でかえって熱が盛んになると述べる。明の荊端王が黄芩・黄連・梔子・黄柏からなる金花丸を数年服用し、内障で失明した話も挙げる。楊士瀛は心の悪血を除くと述べた。
+【古典での配合と議論】韓氏は黄連を人乳に浸して蒸し、目に点じたり服用したりすると記す。少量の官桂とともに煎じ、蜂蜜を加えて空腹時に服む方法、五苓散・滑石と合わせて夢精を治す方法も挙げる。黄土・生姜汁・酒・蜂蜜でそれぞれ炒めた黄連を主として使君子、酒煮の白芍薬、木香を配する小児の五疳の処方、呉茱萸で炒めた黄連に木香と倍量の生大黄を加えて丸薬にする五痢の処方にも触れる。
+李時珍は『素問』の「五味は長く取り過ぎると臓気に偏りを生じる」という論を引く。王冰の注では酸・苦・辛・鹹・甘がそれぞれの臓に偏るため、苦寒の黄連や苦参を久服しても逆に熱を生じうる。秦観の書簡は、肝熱による眼病で黄連を十数両も飲み続ければ心火を偏らせると戒める。荊端王の金花丸長服による失明の例は、この久服批判の根拠として示された歴史的記述である。</t>
         </is>
       </c>
     </row>
@@ -15528,6 +16497,21 @@
 Jiamo distinguishes Ginseng Root and Astragalus Root by emphasis: Ginseng Root is stronger for internal Spleen-Stomach deficiency, while Astragalus Root is stronger for exterior Qi deficiency, spontaneous sweating and chronic sores. Which is chief or deputy depends on the pattern.</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>黄耆（黄芪）
+【性味】甘味、微温性。
+【毒性】無毒。
+【帰経】脾・肺経。
+【主治】気を補って陽を上げ、表を固め汗を止める。水を巡らせ腫れを引き、津液と血を養い、滞りと痺れを除く。膿の排出を助け、瘡を収めて肉芽を生じさせる。
+【名称の由来】黄耆、戴糝、戴椹、芰草、百本、王孫。李時珍によれば「耆」は長を意味し、黄色で補薬の長とされるため黄耆という。黄芪とも書くが、蓍とは別物。王孫も牡蒙とは同名異物である。
+【考証】陶弘景は隴西産を温補、白水産を冷補とし、赤いものは膏にして癰腫を消すという。陳蔵器も虚して熱がある場合は白水産、冷えがある場合は隴西産を用いる。大明は補益の働きから「薬中の羊肉」と呼び、白水耆・赤水耆・木耆それぞれの排膿、血熱を除く作用を記す。張元素は甘温で純陽、諸虚を補い、元気を益し、脾胃を強め、肌熱を除き、膿を出して痛みを止め、血を巡らせて生じさせるという。陰疽を内から支える瘡の要薬とした。王好古は自汗・寝汗と皮膚痛には表、喀血と脾胃には中、傷寒で尺脈が絶えた時には裏を補い、三焦の内外に働くと説明する。
+李杲は『霊枢』の衛気論を引き、黄耆は肌肉を温め皮膚と腠理を充実させて汗を止め、元気と三焦を補うという。桂枝に似るが辛熱ではなく、桂枝が血脈を通すのに対し黄耆は気を益する。人参・甘草とともに躁熱や肌熱を除く。朱震亨は白くふくよかで汗の多い人に適する一方、色黒で痩せた実証では胸が張るおそれがあるという。寇宗奭は防風との併用を挙げ、許胤宗が言葉を失った柳太后に黄耆防風湯の蒸気を吸わせて回復させた故事を記す。李杲は防風が黄耆を制しつつ効力を高めるといい、朱震亨は口と鼻から薬気を受けたものと解説する。
+小児の慢驚が脾胃の虚に由来する場合について、李杲は温燥薬の誤用を戒め、黄耆湯を示す。炙黄耆二銭、人参一銭、炙甘草・白芍薬各五分を水一大杯で半量に煎じ、温服する。汪機は魏直の痘瘡の順・逆・険の分類を紹介し、険証には保元湯を加減するという。これは黄耆湯から白芍薬を除き生姜を加えたもので、炙黄耆三銭、人参二銭、炙甘草一銭、生姜一片を水煎する。初発の乾いた紅色、漿の光沢と陥没、灰色、痂皮後の口渇や腫瘍などの険証に用い、川芎・肉桂・糯米を加える例もある。嘉謨は、人参は中を補い黄耆は表を充実させるため、脾胃の内傷では人参を主、表虚で自汗や潰瘍があれば黄耆を主とし、証に応じて使い分けると説く。
+【古典での使い分け】大明は白水耆を涼性で排膿・治血・骨蒸熱に、赤水耆を涼性で治血・退熱に、木耆を排膿の力がやや弱い代用品に位置づける。李杲によると、脾胃の虚では肺気が先に衰えるため、黄耆で肌肉を温め腠理を固めて元気を支える。小児の脾胃寒湿には益黄散の適応もあるが、伏火や胃虚による慢驚に温燥の益黄・理中を誤用すると害があるとして、甘温で土を補い甘寒で火を瀉す黄耆湯を立てた。
+保元湯の適応として、痘疹の初発時に周囲が乾いて赤い、漿の形成時に頂部が陥没する、灰色で生気がない、痂皮が落ちてから食べられず口渇がある、痂皮後の癰腫が治りにくい、といった状態が列挙される。汪機は症状により川芎・官桂・糯米を加えるとしている。</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -15595,6 +16579,19 @@
 He records personal recovery from a severe febrile cough and profuse phlegm after taking a single-herb Scutellaria Root decoction, using the case to illustrate the importance of matching medicine to pattern rather than following formulas mechanically.</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>黄芩
+【性味】苦味、寒性。
+【毒性】無毒。
+【帰経】肺・胆・脾・大腸・小腸経。
+【主治】熱を清め湿を乾かし、火を瀉して毒を解き、出血を止め、胎を安定させる。
+【名称の由来】腐腸、空腸、内虚、妬婦、経芩、黄文、印頭、苦督郵。実の詰まった若い根は子芩・条芩・尾芩・鼠尾芩ともいう。陶弘景は丸いものを子芩、古く内部が空洞のものを宿芩とする。李時珍は古根の片芩と新根の条芩の違い、外黄内黒の色に由来する名称を説明する。
+【考証】李杲は空洞で軽い根は肺火、気滞、痰、風熱と肌表の熱を除き、細く堅い根は大腸火を瀉して陰を養い、膀胱の水の源を助けるという。張元素は肺熱、上焦の風熱・風湿、諸熱、胸の気滞、痰、脾の湿、産後の熱を除き、胎を安定させるなど九つの働きを挙げる。酒で炒めると上部の瘀血に働く。膿血を伴う下痢と腹痛には芍薬・甘草を合わせ、瘡の激痛には黄連とともに用いる。朱震亨は火を下げることで痰を降ろすといい、上焦の湿熱には酒で洗い、片芩には桑白皮を添える。肺虚では多用を避け天門冬で肺気を守る。黄芩と白朮は古来の安胎薬とする。羅天益は肺熱によるしびれや咽頭の生臭さを挙げ、蘇頌は瀉心湯、葛根黄芩黄連湯、妊娠の安胎散の例を記す。
+李時珍は、張潔古の肺火と脾湿、李東垣の片芩と条芩の区別、朱丹渓の上・中焦の火、張仲景の小柴胡湯・黄芩湯・瀉心湯の例を照合する。苦味が心に入り寒性が熱を制し、心火と脾の湿熱を除くことで肺も守るが、肺虚に苦寒を多用すると脾胃を損なう。少陽病の寒熱、胸脇の張り、食欲不振、煩躁と嘔気には上焦と中焦の病が併存するため黄芩を使う。柴胡は邪熱を発散させ、黄芩は寒性で熱の根を抑えるという違いを述べる。『傷寒論』で腹痛に黄芩を除いて芍薬を、小便不利と動悸には茯苓を加えるとあるが、文字に拘泥せず脈と証を見よという。寒冷による腹痛・飲水後の動悸で熱証がなければ黄芩は使わず、熱による腹痛や肺熱に伴う小便不利なら用いる。黄芩・木通・甘草で酒色による下腹部痛と排尿痛が治まった例、附子の過服後の尿閉が黄芩・黄連で治った例も挙げる。李時珍自身も若い頃、長引く咳、骨蒸熱、口渇、多量の痰を患い、柴胡・麦門冬などでは悪化したが、片芩一両を水二杯から一杯に煎じて一度に服し、翌日熱と咳痰が治まったと記す。
+【古典での弁証】少陽証の胸脇痞満、心煩、嘔気、口渇や尿の出にくさを、李時珍は上焦の心肺と中焦の脾胃の症状が重なるものとして説明する。成無己の「苦味は腸胃の気を堅くする」という解釈や、楊士瀛の「柴胡より黄芩のほうが解熱に優れる」という一律の比較には異議を唱え、病因と脈証から使い分けよという。『別録』の下腹部痛・利小腸の記述と仲景の加減法が食い違うように見えても、冷えによる腹痛か熱による腹痛かを見定める必要がある。自身の経験では、片芩一両を水二鐘から一鐘まで煎じて頓服したと記す。</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -15659,6 +16656,20 @@
 An old formula combined fennel with fresh ginger and salt for Spleen-Stomach weakness and hernia-type lower abdominal pain. Salt was said to guide fennel toward the Kidney channel, illustrating the traditional importance of processing and combination.</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>茴香
+【性味】辛、温。
+【毒性】無毒。
+【帰経】肝経・腎経・脾経・胃経に帰する。
+【主治】散寒止痛、理気和胃。
+【名称の由来】茴香（『図経本草』）、八月珠（『侯氏薬譜』）。
+蘇頌は、北方の人が茴香と呼ぶのは別名と音が近いからだという。孫思邈は、臭い肉を煮るとき少し入れれば臭いが消え、臭い醤に粉を加えても香りがよくなるので茴香という。李時珍は、民間では襟に入れて携え、噛むことが多く、別名の由来はそのためかもしれないという。原文ではその別名の字が欠ける。
+【考証】
+孟詵はいう。人々は茴香が生殖の力を助けると重んじるが、具体的な用法は分からない。王好古は、膀胱に働き、小腸の燥を潤し、手足の少陰も通じさせ、上と下の経絡をつなぐと説く。
+李時珍はいう。小茴香は平性で気を整え食欲を促し、夏には虫や悪臭を遠ざけ、料理に適する。大茴香は熱性で多食すると目を傷め瘡を生じるので、料理に使いすぎない。古方の去鈴丸では茴香二両と皮付き生姜四両を容器で一昼夜漬け、弱火で炒り、塩一両を加え粉末にして糊で梧桐の実ほどの丸薬にする。空腹時に三十～五十丸を塩を加えた酒で飲む。もとは脾胃の虚弱を治す処方で、塩が茴香を腎経へ導き邪気を出す。小腸の疝気にも効くという。</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="17" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -15717,6 +16728,20 @@
 Haogu classifies it as a Taiyin herb acting on both Lung and Spleen.
 When combined in Qi-regulating formulas it can support the Lung; in formulas with Astragalus Root or the Four Gentlemen Decoction group it supports the Spleen.
 Its aromatic, slightly warm nature made it especially important for Dampness obstructing the middle burner with nausea, poor appetite and a heavy sensation.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>藿香
+【性味】辛、微温。
+【毒性】無毒。
+【帰経】脾経・胃経・肺経に帰する。
+【主治】芳香化湿、和中止嘔、解表解暑。
+【名称の由来】兜婁婆香（『楞厳経』）。
+李時珍はいう。葉が豆の葉である藿に似るため藿香という。『楞厳経』には壇の前で兜婁婆香を煎じた水で沐浴するとあり、これを指す。『法華経』の多摩羅跋香、『金光明経』の鉢怛羅香も同じ梵語の異なる表記で、『涅槃経』には迦算香とある。
+【考証】
+李杲はいう。芳香が脾胃を助けるため、藿香は吐き気を止め食欲を増す。
+王好古はいう。手足太陰の薬で、順気烏薬散に入れれば肺を、黄耆や四君子湯と合わせれば脾を補う。</t>
         </is>
       </c>
     </row>
@@ -15779,6 +16804,19 @@
 Song records that eggs appear frequently in traditional medicine. One unusual external preparation combined egg yolk with burned human hair to produce an oily liquid for childhood Heat sores.
 Liu Yuxi relates a personal anecdote in which a newborn with extensive inflamed skin lesions reportedly improved after such an application.
 These accounts reflect historical topical practice; the central internal role of egg yolk remained nourishing Yin and blood and moistening dryness.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>鶏子黄
+【性味】甘、平。
+【毒性】無毒。
+【帰経】心経・腎経・脾経に帰する。
+【主治】滋陰養血、潤燥息風、清心安神、養胃止渇。
+【名称の由来】燭夜（『古今志』）。
+李時珍は徐鉉の説を引き、鶏は時刻を知るため「稽」と音が通じるという。『広志』は大きいものを蜀、小さいものを荊、ひなを𪇗と呼ぶ。梵語の書では鶏を鳩七咤と呼ぶという。原文の引用には欠字がある。
+【考証】
+李時珍はいう。卵黄は気味がともに濃く、陰中の陰であり、体を養う。阿膠と同じ働きとされたのもこのためである。嘔吐や瘡には熱を除き虫を誘い出す働きを利用する。蘇頌は、鶏卵の処方は多いが、毛髪と煎じるものが特に変わっているという。劉禹錫の『伝信方』には、小児の熱性の瘡に卵五個の黄身と卵ほどの量の乱れた毛髪を混ぜ、鉄鍋で炭火にかけ、毛が焦げて液が出たら少しずつ器に取り、液が出なくなるまで煎じて患部へ塗り、苦参の粉末を振りかける方法がある。蘇頌の子は生まれてすぐに熱性の瘡が半身に広がり、薬が効かず泣き続けて授乳も睡眠もできなかった。本草に毛髪と卵黄を煎じて小児の驚熱や下痢を治す記述、卵が熱傷を治す記述を見て試すとよく効いたという。</t>
         </is>
       </c>
     </row>
@@ -15845,6 +16883,21 @@
 Zhenheng emphasizes its ability to open constrained Lung Qi. For dry cough from phlegm-Fire constraint or abdominal pain in dysentery linked to Qi obstruction, Platycodon Root was used first to open and raise Qi before other medicines acted.</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>桔梗
+【性味】苦・辛、平。
+【毒性】小毒。
+【帰経】肺経に帰する。
+【主治】宣肺利咽、祛痰排膿。
+【名称の由来】白薬・梗草（『名医別録』）、荠〔原文欠字〕（『神農本草経』）。
+李時珍はいう。根が締まって硬く、茎がまっすぐなので桔梗という。『呉普本草』には利如・符扈・房図という異名もあるが、処方書には見えない。桔梗と荠〔原文欠字〕は似ているが、甘いものと苦いものの二種がある。『神農本草経』は同じ名とし、民間では甘いほうを甜桔梗と呼ぶ。『名医別録』は別種として分け、性味や用途も異なるのでその区別がよい。
+【考証】
+王好古はいう。桔梗はやや温で苦辛、味が濃く気が軽い、陽中の陰で上昇する。手太陰肺経の気分と足少陰に入る。
+張元素はいう。桔梗は肺気を清め、喉を通し、白い色から肺経へ薬を導く。甘草とともに諸薬を上へ運ぶ舟の役割を果たす。大黄のように激しく下す薬を胸の高い位置へ導くには、辛甘の薬で引き上げる必要がある。重い鉄や石が舟なしでは川を渡れないのと同じで、桔梗を含む処方は沈みにくい。
+李時珍はいう。朱肱の『活人書』は痛みのない胸のつかえに桔梗と枳殻を使い、肺と横隔膜を通して気を下げる。張仲景は寒実結胸に桔梗・貝母・巴豆で中を温め積滞を除き、肺癰で膿を吐く場合には桔梗・甘草で肺を清め排膿する。少陰証の二、三日目の喉の痛みにも桔梗・甘草を用い、寒熱を調える。後世は甘桔湯と名づけ喉や口の病に広く使い、宋仁宗が荊芥・防風・連翹を加えたものは如聖湯と呼ばれる。王好古の『医塁元戎』には加減が詳しい。声がかれるとき訶子、声が出ないとき半夏、気の逆上には陳皮、痰を伴う咳には知母・貝母、咳と渇きには五味子、酒毒には葛根、息切れには人参、嘔吐には半夏・生姜、膿血を吐くとき紫菀、肺痿には阿膠、胸や横隔膜の不調には枳殻、心胸のつかえには枳実、目の充血には梔子・大黄、顔のむくみには茯苓、皮膚の痛みには黄耆、発疹には防風・荊芥、疫毒には牛蒡子・大黄、不眠には梔子を加える。朱震亨は、乾いた咳には肺に鬱した痰火を開き、痢疾の腹痛には大腸に鬱した肺気を開いてから下痢の薬を用いるといい、気血を引き上げて通すので気の処方にも適すると説く。</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
@@ -15904,6 +16957,20 @@
 Shizhen says the stems, leaves and flowers were all regarded as medicinal. Earlier writers emphasized Wind disorders and swelling, while later physicians increasingly valued it for sores, abscesses and toxic swelling.
 He cites Ren Dong Jiu, a honeysuckle wine used in older surgical texts for early-stage abscesses and deep sores.
 Numerous historical case collections praised honeysuckle for reducing swelling and dispersing toxicity, helping establish its later reputation as a major herb for Heat-toxin patterns.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>金銀花（忍冬）
+【性味】甘、寒。
+【毒性】無毒。
+【帰経】肺経・心経・胃経に帰する。
+【主治】清熱解毒、疏散風熱。
+【名称の由来】金銀藤・鴛鴦藤・鷺鷥藤・老翁鬚・左纏藤・金釵股（『本草綱目』）、通霊草・蜜桶藤（『土宿真君本草』）。
+陶弘景はいう。各地に生えるつるで、冬を越しても枯れないため忍冬という。李時珍は、長い花びらと垂れる雄しべ、白と黄色の花、左巻きのつるから金銀・鴛鴦などの名が生じたという。金釵股は薬効を重んじた名で、汁が硫黄や水銀の処理に使われるとされ通霊草とも呼ぶ。
+【考証】
+陶弘景はいう。忍冬の煮汁で酒を醸して飲むと虚を補い風を治す。長寿にもよいとされるが、容易に採れる草なので仙方では軽んじられがちだ。
+李時珍はいう。茎・葉・花の働きは同じである。古人は風、張り、痢疾などを治す薬とし、後世は腫れや毒、瘡を治す薬と重んじた。古今で用途が変わるので一律には語れない。陳自明の『外科精要』は、癰疽が背にできた初期に忍冬酒を用いると効果が高いという。洪邁・沈括などの処方集にも詳しく、丹陽の僧、江西の鑑清、金陵の王琪らの記録にも背の癰疽への処方として現れる。張相公が、ありふれた安価な草に特別な効き目があるといったのはこのような例である。</t>
         </is>
       </c>
     </row>
@@ -15974,6 +17041,20 @@
 He therefore preserves them as traditional cautions rather than as a settled pharmacological rule.</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>荊芥（仮蘇）
+【性味】辛、微温。
+【毒性】無毒。
+【帰経】肺経・肝経に帰する。
+【主治】解表散風、透疹、利咽消腫、止血。
+【名称の由来】姜芥（『名医別録』）、荊芥（『呉普本草』）、鼠蓂（『神農本草経』）。
+陶弘景は仮蘇は処方に使われなくなったという。蘇恭は、これは食用の荊芥で、「姜芥」は音の訛りと考え、草部から菜部へ移した。陳士良は仮蘇は別の植物で、葉がとがり丸く野生し、香りが蘇に似るという。蘇頌は江南では仮蘇と荊芥を別物とするという。李時珍は『呉普本草』が仮蘇を荊芥の別名とし、葉が落藜に似て細く、蜀では生食すると記すことを引く。呉普は『名医別録』に近い時代なので信頼でき、後世の別種説は推測にすぎない。「蘇」「姜」「芥」は蘇・姜・芥に似た辛い香りに由来する。
+【考証】
+張元素は荊芥が辛苦で気味が薄く、浮いて上昇する陽の薬という。王好古は肝経の気分に働いて肝気を巡らせるという。李時珍は、足厥陰へ入り、風邪を除き、瘀血を散らし、気の結びや瘡毒を解くのに優れると説く。厥陰は風木で血をつかさどり相火が宿るため、風・血・瘡の病に使う。賈丞相の再生丹、許学士の称賛、戴院使の産後の要薬、蕭存敬の一捻金、陳無択の挙卿古拝散などの名声がある。「挙卿古拝」は「荊芥」二字の反切を隠語としたものだ。
+李時珍はさらにいう。荊芥と魚介、特に河豚の食べ合わせが悪いという説は古い本草や医方にはないが、雑記には多くある。『延寿書』は鱗のない魚と併用を避け、黄魚の後なら吐血し地漿で解くといい、蟹と合わせると風が動くという。『鉄囲山叢話』には黄顙魚の後に姜芥を食べて急死した例、『夷堅志』には黄顙魚の羹の後に荊芥茶を飲み、足のかゆみから全身の異常を生じ二日で治った例、『輟耕録』には河豚と荊芥の併用で死んだ例がある。『葦航紀談』も荊芥の風薬を服す際には魚を避けるという。李時珍は警戒のため詳しく記す一方、『物類相感志』には河豚を荊芥と何度も水を替えて煮れば無毒とあり、説が矛盾すると述べる。健康を守るなら慎重な説に従うべきだという。</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -16036,6 +17117,22 @@
 Ying praises rice as one of the basic grains that sustain life and emphasizes its overall harmony rather than a strong, specialized medicinal action.
 Haogu points out that although Non-Glutinous Rice primarily supports the Spleen and Stomach, Zhang Zhongjing also used it in White Tiger Decoction and other formulas to protect Qi and fluids during treatment of Heat.
 Shizhen further distinguishes regional and seasonal differences. In cooler northern climates, somewhat earlier rice could be medicinally suitable, while in warmer southern climates the latest harvest was considered cooler and therefore better for Heat-clearing formulas.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>粳米（粳）
+【性味】甘、平。
+【毒性】無毒。
+【帰経】脾経・胃経・肺経に帰する。
+【主治】補中益気、健脾和胃、煩渇を除く、下痢を止める。
+【名称の由来】秔（『説文解字』。粳と同字）。
+李時珍はいう。粳はうるち米全体の名で、早・中・晩の三時期に収穫する。晩稲だけを粳とする本草は誤りで、粘るものが糯、粘らないものが粳である。熱を除く薬には晩粳がよい。
+【考証】
+孟詵はいう。赤い粳米は大粒で香り、水に浸しても味がよい。収穫したばかりの米や二年を越えたものは気を乱して病を起こし得る。江南では稲を倉に保存し、春に精米して食べるとよい。中を温め気を益し、下の元気を補う。
+寇宗奭は白い晩米が最良で、早稲は及ばないという。五臓を調え胃気を補うが、火の通りが浅いと脾に益せず、よく炊くのがよい。穎という人も早・中・晩のうち晩白米を最良とし、産地や品種で性味には多少の違いがあるが、五穀は人を養う基礎であり、粳は天地の調和した気を得るのでほかのものとは比べがたいという。
+王好古はいう。本草では脾胃を養うのに、張仲景の白虎湯では肺へ導く。甘味は陽明、白色は西方の金を表し、冷やす気が手太陰へ入るからだ。少陰証の桃花湯では正気を補い、竹葉石膏湯では不足を養う。
+李時珍はいう。六月・七月収穫が早粳で食用、八月・九月が遅粳、十月が晩粳である。北方は寒く、八・九月の米も涼性で薬に使える。南方は暖かく、十月の晩稲だけが涼性で薬に向く。遅粳・晩粳は金の気が多いので白いものが肺に入って熱を解く。早粳は土の気が多く、赤いものは脾、白いものは胃を益す。雲南や嶺南の粳は熱性で、その土地に適する。</t>
         </is>
       </c>
     </row>
@@ -16103,6 +17200,20 @@
 Historical accounts of chrysanthemum wine and 'immortal' use belong to longevity folklore rather than ordinary clinical practice.</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>菊花（菊）
+【性味】甘・苦、微寒。
+【毒性】無毒。
+【帰経】肺経・肝経に帰する。
+【主治】疏散風熱、平抑肝陽、清肝明目、清熱解毒。
+【名称の由来】節華（『神農本草経』）、女節・女華・女茎・日精・更生・傅延年・陰成・周盈（『名医別録』）、治蔷（『爾雅』）、金蕊（『本草綱目』）。
+李時珍は陸佃の『埤雅』を引き、菊はもと「蘜」で、「鞠」は終わりを意味するという。九月に黄色い花を咲かせ、花の季節が尽きるため名づけられ、節華も季節に応じる名である。崔寔は女節・女華を花、治蔷・日精を根の名とし、『抱朴子』は日精・更生・周盈を同じ菊の根・茎・花・実の異名とする。
+【考証】
+朱震亨はいう。黄色い菊は土と金に属して水と火も含み、陰血を養うので目によい。
+李時珍はいう。菊は春に生まれ夏に茂り、秋に花を咲かせ冬に実る。四季の気を受け霜露に耐え、葉は枯れても落ちず花もすぐ散らない。甘苦を兼ね穏やかな性質で、風熱を除き肝と陰を養い、金と水の二臓にも益する。水を補えば火を抑え、金を益せば木を平らかにし、風と熱が治まる。黄色は金水の陰分、白色は陽分、赤色は女性の血分に働くという。芽は野菜、葉は飲み物、花は食用、根と実は薬、袋に入れれば枕、醸せば酒となり、どの部分も役立つ。神農は上品とし、隠者は酒に入れ詩人は花びらを食べた。費長房は九月九日の菊酒が災いを避けるといい、『神仙伝』には菊を飲んで仙人になった話、『荊州記』には菊潭の水で長寿になった話がある。鍾会の『菊有五美賛』は、高い丸花は天、純粋な黄色は大地、早く植えて遅く咲くのは君子の徳、霜の中の開花は貞節、杯に浮く軽さは仙人の食を表すという。『西京雑記』には菊の花・茎・葉を秫米とともに醸し、翌年九月に酒ができるとある。原文はここで途切れる。</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -16167,6 +17278,21 @@
 He also records stories of chronic Heat disorders improving with daily pear consumption, while stressing that only suitable pear varieties were considered medicinal and that excessive intake could still be harmful to the Spleen.</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>梨皮（梨）
+【性味】甘・やや渋、涼。
+【毒性】無毒。
+【帰経】肺経・心経・腎経に帰する。
+【主治】清心潤肺、降火生津、止咳化痰。
+【名称の由来】快果（陶弘景）、果宗・玉乳（『本草綱目』）、蜜父（『清異録』）。
+朱震亨は「梨」は「利」で、下へ向かって通す性質に由来するという。陶弘景は種類が多く、いずれも冷やして排出を促すため食べすぎると体を損ない、快果と呼ばれるが薬には使わないという。
+【考証】
+寇宗奭はいう。梨を食べすぎると脾を乱すが、少なすぎても病に効かず、量を考える必要がある。酒の後の渇きにはよいが、病をすべて治すわけではない。
+唐慎微は孫光憲の『北夢瑣言』を引く。朝廷の官吏が風の病を重く患い、梁新という医者には帰郷を勧められた。別の医者の趙鄂も同じ診断だったが、消梨を多く食べ、噛みきれなければ汁を搾って飲むよう勧めた。帰宅後十日ほど梨だけをとり、体がすっきりしたという。
+李時珍はいう。『名医別録』は梨の害だけを記し、陶弘景も薬に使わないとした。古人は風寒の病を重んじ桂や附子を用いたため、梨が風熱を治し肺と心を潤して痰や火を除く働きを知らなかったのだろう。ただし食べすぎはよくない。『類編』には、楊吉老から熱証が極まり三年内に癰疽で亡くなると告げられた人が、茅山の道士の弟子となり、毎日よい梨を一つ、季節外には干した梨を湯に浸して実と汁を食べるよう言われた話がある。一年後、その人の顔色と脈がよくなり、楊吉老は驚いて道士を敬った。前の話も合わせれば梨の働きは小さくない。ただし食べてよいのは乳梨・鵝梨・消梨で、ほかの梨は病に効かないという。</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="17" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
@@ -16232,6 +17358,19 @@
 Shizhen connects the fruit's heart-like shape and fragrant seed with the Heart and Pericardium. Since painful, itchy sores were traditionally linked with Heart Fire, Forsythia Fruit became one of the major herbs for Heat-toxin sores and upper-body inflammatory conditions.</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>連翹
+【性味】苦、微寒。
+【毒性】無毒。
+【帰経】肺経・心経・小腸経に帰する。
+【主治】清熱解毒、消腫散結、疏散風熱。
+【名称の由来】連・異翹（『爾雅』）、旱蓮子（『薬性論』）、蘭華（『呉普本草』）、三廉・折根（『名医別録』）。根は連軺（張仲景）ともいう。
+蘇恭は実が蓮の花托に似て草の上へ突き出るため名づけられたという。寇宗奭は、特に草の上へ突き出るわけではなく、実を割ると一片ずつ羽のように並ぶからだという。李時珍は『爾雅』に「連、異翹」とあるので、もとは連、別名が異翹で、合わせて連翹になったと説く。連軺・連苕は古い本草の翹根で、別項目を統合した。旱蓮は小翹の名で、別の植物である鳢腸と同名になることもある。
+【考証】
+張元素は心経に入った熱、上焦の熱を除き、瘡を治すという三つの用途を挙げる。李杲は十二経の瘡に欠かせず、結んだものを散らすと説く。王好古は手足少陽に働き、瘡・腫瘤・しこりに効き、柴胡と似て気血に作用する違いがあるといい、牛蒡子と合わせると瘡に特によいという。李時珍は、人の心臓のように二片が合わさり、香る仁を含むことから、少陰の心と厥陰の心包の気分に働くと考える。痛み、かゆみ、瘡は心火に属するため、十二経の瘡に重要で、手足少陽と手陽明の熱にも用いる。</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="17" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
@@ -16294,6 +17433,20 @@
 Its sweet, astringent quality explains the traditional emphasis on restraining leakage rather than strongly moving or clearing.</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>蓮鬚（蓮藕）
+【性味】甘・渋、平。
+【毒性】無毒。
+【帰経】心経・腎経に帰する。
+【主治】清心益腎、渋精止血。
+【名称の由来】根は藕、実は蓮（『爾雅』）、茎と葉は荷（『説文解字』）という。
+韓保昇はいう。藕は水中に生じ、葉を荷という。『爾雅』では全体を芙蕖、茎を茄、葉を蕸、根元の地下茎を蔤、つぼみを菡萏、実を蓮、根を藕、実の中の種を菂、種の青い芯を薏と呼ぶ。邢昺は芙蕖が総称で芙蓉ともいい、江東では荷と呼ぶと注す。郭璞は蔤を泥の中の白い若い茎、蓮を花托、菂を種、薏を苦い芯とする。江東で花を芙蓉、北方で藕や蓮を荷、蜀で藕を茄というのは地方による呼び方の違いである。陸機の『詩疏』では茎が荷、開く前の花が菡萏、開いた花が芙蕖、実が蓮、その青い皮の中の白い部分や種を菂、苦い芯を薏という。
+李時珍はいう。『爾雅』、韓保昇、陸機は「荷」をそれぞれ根・葉・茎とする。茎は葉を背負うので「負荷」の意味から陸機の説がよい。「蔤」は竹の地下茎に似た若い走出茎で、節ごとに葉と花の茎を一本ずつ生じ、末端に藕を作る、花葉根実のもとである。働きを隠すので蔤と名づけた。花と葉は対になって生じるため根を藕といい、泥を耕すから「耦」に従うという説もある。茄は蔤の上に加わり、蕸は蔤から遠い。菡萏は開く前に包むこと、芙蓉は華やかに広がる姿、蓮は花と実が続いて生じること、菂は実の中に点々とある種、薏は内に苦みを秘めた芯を表す。古詩の「実を食べても芯を捨てず、苦い心に思いが残る」という句もこれをいう。
+【考証】
+李時珍はいう。古い本草に蓮鬚の項目はないが、『三因方』や固真丸・巨勝子丸などの補益の処方によく用いる。おおむね蓮子と働きは同じである。</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="17" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
@@ -16355,6 +17508,21 @@
 Classical formulas such as Qing Xin Lotus Seed Yin used it when Heart and Kidney failed to communicate, while Auspicious Lotus Pill used it to support Heart, Kidney, essence and blood.
 Older writers also praised very hard, aged 'stone lotus seeds' as longevity foods and told stories of seeds surviving for centuries.
 Claims that ancient lotus seeds could make the hair black, prevent aging or confer extraordinary endurance belong to historical longevity folklore rather than ordinary medical practice.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>蓮子（蓮藕）
+【性味】甘・渋、平。
+【毒性】無毒。
+【帰経】脾経・腎経・心経に帰する。
+【主治】補脾止瀉、止帯、益腎渋精、養心安神。
+【名称の由来】根は藕、実は蓮（『爾雅』）、茎と葉は荷（『説文解字』）という。
+韓保昇はいう。藕は水中に生じ、葉を荷という。『爾雅』では全体を芙蕖、茎を茄、葉を蕸、根元の地下茎を蔤、つぼみを菡萏、実を蓮、根を藕、実の中の種を菂、種の青い芯を薏と呼ぶ。邢昺は芙蕖が総称で芙蓉ともいい、江東では荷と呼ぶと注す。郭璞は蔤を泥の中の白い若い茎、蓮を花托、菂を種、薏を苦い芯とする。江東で花を芙蓉、北方で藕や蓮を荷、蜀で藕を茄というのは地方による呼び方の違いである。陸機の『詩疏』では茎が荷、開く前の花が菡萏、開いた花が芙蕖、実が蓮、その青い皮の中の白い部分や種を菂、苦い芯を薏という。
+李時珍はいう。『爾雅』、韓保昇、陸機は「荷」をそれぞれ根・葉・茎とする。茎は葉を背負うので「負荷」の意味から陸機の説がよい。「蔤」は竹の地下茎に似た若い走出茎で、節ごとに葉と花の茎を一本ずつ生じ、末端に藕を作る、花葉根実のもとである。働きを隠すので蔤と名づけた。花と葉は対になって生じるため根を藕といい、泥を耕すから「耦」に従うという説もある。茄は蔤の上に加わり、蕸は蔤から遠い。菡萏は開く前に包むこと、芙蓉は華やかに広がる姿、蓮は花と実が続いて生じること、菂は実の中に点々とある種、薏は内に苦みを秘めた芯を表す。古詩の「実を食べても芯を捨てず、苦い心に思いが残る」という句もこれをいう。
+【考証】
+李時珍はいう。蓮は泥の中に生じても泥に染まらず、水中にあっても沈まない。根、茎、花、実にはそれぞれ働きがある。地下茎から節ごとに茎・葉・花・藕を生じ、つぼみから蕊・花托・種・芯へと育つ。実は黄色から青、緑、黒に変わり、白い肉の中に青い芯を秘める。石蓮子は硬く長く保存でき、芯や藕からまた芽が生じる。仏家はこれをたとえに用い、医家は薬として取り入れた。甘味で穏やかに引き締め、穀物のような味を持つ脾の果実である。脾土は元気の母で、水火や木金を調える。脾の気が整えば津液と精神が養われ、長寿につながるという。心腎の不調や白い濁りに清心蓮子飲、心腎と精血を補うため瑞蓮丸が用いられる。
+陳蔵器はいう。秋を越えて黒くなったものを石蓮子といい、水に沈むが濃い塩水なら浮く。長く保存でき、食べれば髪が黒く老いないという。孟詵は、鳥や猿が実を石の穴に蓄え、三百年ものを食べれば老いず、雁が食べて山野に落とした実も長く傷まず、朝に十個食べれば体が軽くなるという。</t>
         </is>
       </c>
     </row>
@@ -16419,6 +17587,19 @@
 He therefore rejects older claims that long-term use necessarily lightens the body or promotes longevity.</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>竜胆草（竜胆）
+【性味】苦、寒。
+【毒性】無毒。
+【帰経】肝経・胆経に帰する。
+【主治】清熱燥湿、肝胆の火を瀉す。
+【名称の由来】陵游（『神農本草経』）。志という人は、葉が竜葵に似て胆のように苦いので名づけられたという。
+【考証】
+張元素はいう。竜胆は苦く寒く気味ともに濃く、沈んで下降する陰の薬で、足厥陰・少陽経の気分に働く。下半身の風湿、湿熱、臍の下から足までの腫れと痛み、寒湿による脚気を治す四つの用途がある。下降の働きは防己に似るが、酒に浸すと上へ向かう。外へは柴胡を主薬、竜胆を使薬とし、目の病にも必要だ。王好古は肝胆の気を益して火を瀉すという。
+李時珍はいう。相火が肝胆に宿るときには瀉すことが必要なので、肝胆に益するとは邪熱を除くことをいう。ただし非常に苦く寒いため、過量では胃の生発する気を傷め、かえって火邪を助ける恐れがある。黄連の長期服用が逆に火へ変じるのと同じで、『名医別録』の長く服せば体が軽くなるという説は信じ難い。</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="17" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
@@ -16475,6 +17656,19 @@
 Shizhen emphasizes the astringent principle: astringency restrains what is excessively escaping or floating.
 He cites Cheng Wuji's explanation that Fossilized Bone gathers floating upright Qi, secures the intestines and calms fright.
 It was also traditionally used for disorders associated with the Dai vessel, reflecting its strong securing and stabilizing character.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>竜骨
+【性味】甘・渋、平。
+【毒性】無毒。
+【帰経】心経・肝経・腎経に帰する。
+【主治】鎮驚安神、平肝潜陽、収斂固渋、収湿斂瘡。
+【名称の由来】李時珍は許慎の『説文解字』で「竜」の篆書が形をかたどった字であることを引く。『生肖論』では竜は耳が聞こえにくいので竜と呼ぶといい、梵語では那伽という。
+【考証】
+雷斅はいう。気が男性の腎に入るため、腎を益する薬に用いるとよい。
+李時珍はいう。渋味は脱失を止める。成無己がいうように、竜骨は浮き上がって散る正気を収め、大腸を固めて驚きを鎮める。帯脈の病にも用いる。</t>
         </is>
       </c>
     </row>
@@ -16539,6 +17733,19 @@
 Yan Yonghe's Restore the Spleen Decoction uses longan in patterns of excessive thinking and overwork that weaken the Heart and Spleen, reflecting its traditional role in nourishing blood while calming the spirit.</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>竜眼
+【性味】甘、温。
+【毒性】無毒。
+【帰経】心経・脾経に帰する。
+【主治】補益心脾、養血安神。
+【名称の由来】竜目（『呉普本草』）、円眼（俗称）、益智（『神農本草経』）、亜茘枝（『開宝本草』）、茘枝奴・驪珠・燕卵・蜜脾・鮫涙。李時珍は竜眼・竜目は形にちなみ、『呉普本草』には比目ともあるという。
+陶弘景は、広州の竜眼は益智とは別で、地元の別名だろうという。志という人は、甘味が脾へ入り知恵を養うため益智と呼び、現在の益智子とは違うという。蘇頌は茘枝の季節が終わると竜眼が熟すため南方で茘枝奴と呼び、木弾ともいう。乾燥して北方へ送られ、亜茘枝と呼ばれる。
+【考証】
+李時珍はいう。食べ物としては茘枝が重んじられるが、体を養うには竜眼がよい。茘枝は熱性で、竜眼は比較的穏やかだからである。厳用和の『済生方』にある帰脾湯は、思い悩んで心脾を傷めた場合に用い、甘味が脾へ入り知恵を養うという意味を取る。</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="17" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
@@ -16595,6 +17802,19 @@
 Shizhen cites an old preparation combining Reed Rhizome with Magnolia Bark.
 He explains Reed Rhizome's medicinal logic simply: its sweetness supports the Stomach while its cold nature clears Heat and Fire.
 This pairing made it useful in patterns of Stomach Heat with thirst, nausea or irritability, especially when Heat and Qi stagnation occurred together.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>芦根（蘆）
+【性味】甘、寒。
+【毒性】無毒。
+【帰経】肺経・胃経に帰する。
+【主治】清熱瀉火、生津止渇、除煩止嘔、利尿。
+【名称の由来】葦（音は偉）、葭（音は加。『爾雅』）。花は蓬蕽（『唐本草』）、若芽は虇（音は拳。『爾雅』）という。
+李時珍は毛萇の『詩疏』を引き、葦の芽生えを葭、穂が出る前を蘆、成長後を葦と呼ぶという。「葦」は大きい、「蘆」は黒っぽい色、「葭」は美しいという意味に由来する。
+【考証】
+李時珍は『雷公炮炙論』の序を引く。飲食を増やす際には蘆根と厚朴を同量煎じて飲むという。蘆根の甘味が胃を養い、寒性が火を下げるためである。</t>
         </is>
       </c>
     </row>
@@ -16657,6 +17877,19 @@
 Citing Su Shi, he explains deer as a Yang-associated animal and elk as Yin-associated. On that basis, deer antler was traditionally considered more suited to supporting Yang, while elk antler was considered relatively more suited to nourishing Yin.
 He notes that other authors reversed this interpretation, but favors the former view based on traditional theory and observed use.
 The entry therefore emphasizes matching the source material to the intended tonic direction rather than treating all antler products as identical.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>鹿角膠
+【性味】甘・鹹、温。
+【毒性】無毒。
+【帰経】肝経・腎経に帰する。
+【主治】温補肝腎、益精養血、止血。
+【名称の由来】鹿角膠（『神農本草経』）、粉末は鹿角霜という。甄権は白膠を黄明膠とも呼ぶというが、李時珍は黄明膠の項でこの誤りを訂正すると記す。
+【考証】
+雷斅は鹿角が麋角に勝るという。蘇頌は、今の医者は麋の若角や角を多く用い、鹿より力が強いという。
+李時珍は蘇東坡の『良方』を引く。鹿は陽の獣で陰に遭うと角を落とし、麋は陰の獣で陽に遭うと角を落とすので、陽を補うには鹿角、陰を補うには麋角がよい。単に一方が優れるとはいえない。この説は沈括の「鹿茸は陰、麋茸は陽を補う」とする説とは逆だが、働きからは蘇東坡の説が妥当で、若角の項に詳しいという。</t>
         </is>
       </c>
     </row>
@@ -16726,6 +17959,22 @@
 He repeatedly stresses pattern differentiation: Ephedra Herb is powerful and should not be used simply because fever or cough is present.</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>麻黄
+【性味】辛・苦、温。
+【毒性】無毒。
+【帰経】肺経・膀胱経に帰する。
+【主治】発汗解表、宣肺平喘、利水消腫。
+【名称の由来】竜沙（『神農本草経』）、卑相・卑塩（『名医別録』）。李時珍は名の由来ははっきりせず、味がしびれる「麻」と黄色の「黄」によるかもしれないという。張揖の『広雅』は竜沙を麻黄、狗骨を麻黄の根とするが、その区別の理由は分からない。
+【考証】
+陶弘景は麻黄が傷寒で肌を解く第一の薬という。蘇頌は、張仲景の麻黄湯・葛根湯・大小青竜湯、肺痿や気の逆上に用いる射干麻黄湯・厚朴麻黄湯などを挙げる。
+李杲はいう。軽い薬は実を除き、麻黄と葛根がその例である。六淫の邪が体表の陽分にとどまり、皮膚のきめを閉ざして営衛や気血の巡りを妨げる状態を実という。両薬は軽く澄んでこれを除く。麻黄はやや苦く茎が空洞で、陰中の陽として足太陽の寒水の経に入る。太陽経は背を通って下へ向かい寒を受けやすいため、発汗して体表の寒邪を除く。ただし汗を出しすぎると陽を失う。飲食の乱れや疲労、雑病による自汗・表虚には元気を脱落させるので禁ずる。
+王好古はいう。麻黄は衛の実、桂枝は衛の虚を治す。ともに太陽証だけでなく営衛の薬で、心は血をつかさどる営、肺は気をつかさどる衛に対応する。麻黄は手太陰肺、桂枝は手少陰心に働き、傷寒や中風での咳に用いる基本となる。
+李時珍はいう。麻黄は肺経の薬で、張仲景は傷寒で汗がなければ麻黄、汗があれば桂枝を用いた。昔の説明よりさらに考えると、津液は衛にあれば汗、営にあれば血となる。寒が営を傷つけると血の巡りが内で滞り衛へ届かず、衛気も閉じて発熱・悪寒して無汗となる。風が衛を傷つけると衛気が外へ漏れ、営を守れず、営気が虚して津液を保持できず、自汗・発熱・悪風となる。いずれも皮膚や毛から邪が入り、肺が関わる。顔の赤み、咳、痰、喘ぎ、胸の張りも肺の症状である。無汗では麻黄と甘草で営の邪を体表へ出し、杏仁で肺気を下げる。汗の後に高熱はなく喘ぐ場合には石膏、夏至以降には石膏や知母を加えて肺の火を瀉すとされ、麻黄湯は太陽の強い発汗薬でありながら肺経の鬱した火を散らす薬でもある。一方、自汗では体表が緩く肺気が虚す。桂枝と甘草で外の風邪を散らし営衛を救い、芍薬で肝木を抑えて脾を固め、生姜・大棗で脾の津液を巡らせる。下剤の後の軽い喘ぎには厚朴・杏仁、発汗後の沈遅の脈には人参、肺熱には黄芩を加えるという。桂枝湯は太陽の穏やかな解肌薬でありながら、脾を整え肺を救う薬でもある。
+少陰病で熱があり脈が沈む場合には麻黄附子細辛湯や麻黄附子甘草湯があり、少陰と太陽の表裏を考えれば、温める附子と麻黄の組み合わせは補いながら発散する。李時珍は、夏に夜通し酒を飲んだ官人の水様の下痢が数日続き、利水薬などで悪化した例を挙げる。脈は浮緩で痔からも出血し、冷たい食べ物や茶水で下の陽気が抑えられ、肝木が盛んで脾土が衰えたと判断し、上へ発散させる小続命湯一服で治した。張仲景も傷寒六、七日で強く下した後に脈が沈遅、手足が厥冷し、喉が悪く膿血を吐き下痢が続く場合、麻黄湯で肝肺を整え上へ発散させたという。同じ理を状況に応じて使うべきだと説く。</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="17" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
@@ -16791,6 +18040,21 @@
 He therefore emphasizes constitution and pattern rather than treating Ophiopogon Tuber as an all-purpose tonic.</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>麦門冬
+【性味】甘・やや苦、微寒。
+【毒性】無毒。
+【帰経】心経・肺経・胃経に帰する。
+【主治】養陰生津、潤肺清心。
+【名称の由来】虋冬（音は門。『爾雅』）、秦では羊韭、斉では愛韭、楚では馬韭、越では羊耆（『名医別録』）。禹韭・忍冬・忍凌・不死薬（『呉普本草』）、禹余粮（『名医別録』）、階前草（梅尭臣の詩）。
+陶弘景は根が大麦に似るため麦門冬という。李時珍は、麦のひげを「虋」といい、この草の根も麦に似てひげがあり、葉は韭に似て冬にも枯れないので名づけられたという。門冬は書きやすい俗字で、穀物を断つ服食にも用い、僕塁・随脂とも呼ぶ。
+【考証】
+寇宗奭はいう。麦門冬は肺熱に特によく、苦味で瀉すが収める力は弱いため、冷えの強い人には禁ずる。心肺の虚熱や虚労にも用い、地黄・阿膠・麻仁と合わせれば経絡を潤し血を養って脈と心を通し、五味子・枸杞子と合わせれば脈を生む薬となる。
+張元素はいう。肺に潜む火で脈気が絶えそうなとき、五味子と人参を加えて生脈散とし、肺の元気を補う。李杲は、六、七月に湿熱が盛んで、骨がだるく体が重い、息切れ、めまい、目の暗さ、ひどければ筋肉の萎えを生じるとき、孫思邈が生脈散で元気を補ったという。人参は熱を除き元気を養い、麦門冬は乾いた肺を潤して水の源を清め、五味子は火を瀉して肺を補い、五臓の気も益する。
+李時珍は趙継宗の『儒医精要』を引き、地黄を使薬として麦門冬を服すと髪の白化を防ぎ、髄と腎気を養い、喘ぎを鎮め、肌を潤すなどという。君薬だけではなく使薬があってこそ働く。ただし火が盛んで気力の強い人に限り、気が弱く胃の冷える人は服用してはならないという。</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="17" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
@@ -16859,6 +18123,19 @@
 Across these interpretations, Oyster Shell combines heavy settling, softening and astringent actions.</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>牡蛎
+【性味】鹹、微寒。
+【毒性】無毒。
+【帰経】肝経・胆経・腎経に帰する。
+【主治】重鎮安神、潜陽補陰、軟堅散結、収斂固渋、制酸止痛。
+【名称の由来】牡蛤（『名医別録』）、蛎蛤（『神農本草経』）、古賁（『異物志』）、蚝。
+陶弘景は左を向いたものを雄、右を向いたものを雌とする道家の説から牡蛎の名があるという。陳蔵器は、ほかの動物と異なり塩水の中で固まって動かないものに雌雄があるのか疑う。寇宗奭も『神農本草経』には左向きという説明はなく、牡丹に雌丹がないのと同様、「牡」は雄の意味ではないという。李時珍は、貝の多くは胎生または卵生だが牡蛎は化生で雄のみと考えられ、蛎・蚝は大きく粗い姿を指すという。
+【考証】
+甄権は虚して熱の多い病に地黄・小草とともに用いるという。王好古は足少陰に入り、硬いものを柔らかくすると説く。柴胡で脇の下の硬結、茶で首のしこり、大黄で腿の腫れへ導き、地黄を使薬にすれば精を養い尿を収める、腎経の血分の薬である。成無己は鹹味が胸と横隔膜の張りを消し、水気を出して硬結を柔らかくするという。張元素は水を養って陽を抑えるため、蛤や蛎が渇きを止めるという。</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="17" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
@@ -16919,6 +18196,20 @@
 Shizhen says it enters the Pericardium, Small Intestine and Bladder. Upward, it can clear Heart and Lung Heat; downward, it drains Damp-Heat through the urine.
 Its presence in Guide Out the Red Powder reflects the traditional relationship between Heart Fire and the Small Intestine.
 He also cites use for generalized painful tightness attributed to hidden Heat obstructing the channels.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>木通（通草）
+【性味】苦、寒。
+【毒性】無毒。
+【帰経】心経・小腸経・膀胱経に帰する。
+【主治】利尿通淋、清心除煩、通経下乳。
+【名称の由来】木通（陳士良）、附支（『神農本草経』）、丁翁（『呉普本草』）、万年藤（甄権）。実は燕覆（『唐本草』）という。
+李時珍は細い穴が端から端まで通るため通草といい、現在の木通に当たるという。今「通草」と呼ぶものは古い通脱木で、宋代の本草では混同されたため分けて記す。
+【考証】
+李杲は、本草の十剤で通す薬は滞りを除くとし、通草や防己を挙げる。防己は非常に苦く寒く、血中の湿熱を瀉して便通も促す。一方、通草は甘く淡く、肺の気を下へ導いて尿を出し、気の滞りを除く。肺が熱を受けて津液の変化が止まり、膀胱にも湿熱があって尿が出ない場合に用いる。胸の熱、口や舌と喉の乾き、強い渇き、尿の出にくさや閉塞、すねのだるさや足の熱などにも適する。茯苓・沢瀉・灯心草・猪苓・琥珀・瞿麦・車前子なども水湿をしみ出させて尿を出し、滞った気を除く。木通は下へ向かい、小腸の火を瀉して尿を出す力が琥珀に似る。
+李時珍はいう。木通は手厥陰の心包と手足太陽の小腸・膀胱に働く。上では心を通し肺を清め、頭痛を治して九竅を通す。下では湿熱を瀉し、排尿と排便を助け、全身のこわばる痛みを治す。『神農本草経』『名医別録』には利尿や淋の治療がなく、甄権や日華子らが詳しく述べた。心と小腸の火を瀉せば肺が邪を受けず水道が通り、津液が生じて各経の湿熱が尿とともに去る。古方の導赤散にもこの考えで入る。楊仁斎の『直指方』では、全身と胸腹に潜む熱、痛みとつり、足の冷えは伏熱が血を傷めるためで、心に属する血を巡らせるため木通を用いるという。</t>
         </is>
       </c>
     </row>
@@ -16991,6 +18282,21 @@
 Its aromatic quality therefore makes it one of the major traditional medicines for Qi constraint throughout the three burners.</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>木香
+【性味】辛・苦、温。
+【毒性】無毒。
+【帰経】脾経・胃経・大腸経・三焦経・胆経に帰する。
+【主治】行気止痛、健脾消食。
+【名称の由来】蜜香（『名医別録』）、青木香（陶弘景）、五木香（『図経本草』）、南木香（『本草綱目』）。
+李時珍はいう。木香は草で、元の名は蜜のように香る蜜香である。しかし沈香にも蜜香というものがあるため木香と呼ぶようになった。後に馬兜鈴の根が青木香と呼ばれたので、これと区別するため南木香・広木香といい、さらに別の薔薇にも木香の名があって紛らわしい。『三洞珠囊』では青木香を五香とし、一株に五根、一茎に五枝、一枝に五葉などの形から名づける。古方の五香連翹湯や古楽府の五木香もこれを指す。蘇頌は『修養書』が正月一日に五木を煮て入浴すれば老いても髪が黒いといい、道家の五香・五木も青木香とする。『金光明経』では矩琵佗香と呼ぶ。
+【考証】
+陶弘景は、大秦の人が青木香を毒性の腫れや悪気の治療に使い、煮汁での沐浴もよいという。寇宗奭は、木香は胸腹の滞った冷たい気を特によく除き、橘皮・肉豆蔲・生姜を添えると速く効くと説く。張元素は肺の滞った気も除くが、中・下焦の気の結びには檳榔を使薬とするという。朱震亨は、辛味で気を上げるため鬱して巡らない気に向くが、陰火が上る場合には火を助けるので、黄柏・知母を主にして少量を添えるべきだという。
+王好古は、本草が気の不足を補い、滞りを破り、胎を安定させ脾胃を強める一方、しこりを除くともいうのは、補薬の佐薬なら補い、瀉薬の君薬なら瀉すためだと説明する。李時珍は三焦の気分の薬で、肺に関わる上焦の鬱、脾胃に関わる中焦の滞り、排便後のしぶり・排尿障害・肝気による痛みなど下焦の閉塞を、昇降させて通すという。
+甄権は『隋書』を引き、武威の太守樊子蓋が吐谷渾への遠征の際、瘴気を防ぐため青木香を献上したと記す。蘇頌は『続伝信方』に張仲景作とされる青木香丸を挙げる。昆侖産青木香と六路訶子皮を各二十両、粉末にして砂糖で梧桐の実ほどの丸薬にし、空腹時に酒で三十丸を一日二回飲む。鄭駙馬は砂糖を蜜に替え羚羊角十二両を加えた。しかし古方と似ないので張仲景の名を冠する根拠は不明という。</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="A134" s="4" t="inlineStr">
@@ -17049,6 +18355,19 @@
 Gao summarizes four principal traditional uses: treating Wind-related rashes, Wind-Heat of the throat, dispersing toxic swelling and sores, and moving constrained Qi affecting the lower back and knees.
 Its pungent, cooling nature made it especially suited to exterior Wind-Heat with sore throat or difficult eruption of rashes.
 Because the fruit is oily, later practice also emphasized its mild bowel-moistening effect, particularly when Heat and dryness coexist.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>牛蒡子（悪実）
+【性味】辛・苦、寒。
+【毒性】無毒。
+【帰経】肺経・胃経に帰する。
+【主治】疏散風熱、宣肺透疹、解毒利咽、滑腸通便。
+【名称の由来】鼠粘・牛蒡（『名医別録』）、大力子・蒡翁菜・便牽牛（『本草綱目』）、蝙蝠刺（『斗門方』）。
+李時珍はいう。実は見た目が悪く、かぎ状のとげが多いため悪実という。根と葉は食用で牛菜とも呼び、方術家は大力と隠して呼び、民間には便牽牛、河南には夜叉頭の名がある。蘇頌は、殻のとげに鼠が触れると絡みついて取れないので鼠粘子というと説く。
+【考証】
+李杲は、風湿によるじんましん、喉の風熱、腫れや瘡の毒、腰膝に滞る気を治す四つの用途を挙げる。</t>
         </is>
       </c>
     </row>
@@ -17113,6 +18432,19 @@
 Shizhen distinguishes two broad uses. Prepared with wine, Achyranthes Root was used more for nourishing the Liver and Kidney; used fresh or raw, it was used more for moving stagnant blood.
 This explains its traditional role in lumbar and knee weakness, lower-limb wasting, and some urinary disorders.
 Historical case records also describe decoctions of the root or leaves for painful urination, blood in the urine and stone-like obstruction. These reports reflect older clinical practice rather than modern self-treatment guidance.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>牛膝
+【性味】苦・甘・酸、平。
+【毒性】無毒。
+【帰経】肝経・腎経に帰する。
+【主治】逐瘀通経、補肝腎、強筋骨、利尿通淋、血を下へ導く。
+【名称の由来】牛荎（『広雅』）、百倍（『神農本草経』）。陶弘景は、節のある茎が牛の膝に似るので名づけられたという。李時珍は百倍は滋養の力をほのめかす名で、葉が莧に似て節が対生するため山莧・対節とも呼ぶという。
+【考証】
+甄権は虚弱で痩せた患者に加えて使うという。朱震亨は牛膝が薬を下へ導くため、下半身の筋骨痛や風の病に加え、土牛膝は春夏に葉、秋冬に根を用い、葉の汁が特に速く効くという。
+李時珍はいう。足厥陰・少陰に働き、酒と合わせれば肝腎を補い、生で使えば古い瘀血を除く。腰や膝の骨痛、足の衰え、尿失禁、長引く瘧などへの働きは肝腎を補うためだ。原文の症瘕や心腹の痛みを列挙する部分は途中で別の引用に移る。陳日華の『経験方』には、長く淋疾に苦しんだ老人が牛膝の処方で治った話がある。また親族の血淋で尿中に血塊ができた際、牛膝の根を濃く煎じ一日五回飲ませると徐々に血の色が薄くなり、再発した十年後にも効いたという。『肘後方』は尿が出ず尿道がひどく痛む場合、牛膝の茎と葉を酒で煮て飲むとする。楊士瀛の『直指方』は排尿痛、血尿、砂石による張りには川牛膝一両を水二碗で一碗に煎じて温かいうちに飲むとし、十年患った女性にも効果があり、杜牛膝でもよく、麝香や乳香を加えてもよいという。</t>
         </is>
       </c>
     </row>
@@ -17179,6 +18511,20 @@
 He also records folk use of roasted glutinous rice for Cold-type diarrhea and rice cakes at night for frequent urination in older adults.</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>糯米（稲）
+【性味】甘、温。
+【毒性】無毒。
+【帰経】脾経・胃経・肺経に帰する。
+【主治】脾胃の虚寒による下痢、消渇と多尿、自汗・寝汗。
+【名称の由来】稌（音は杜）、糯（穤とも書く）。
+李時珍はいう。稲と稌は粳米と糯米の総称で、『物理論』も灌漑して栽培する穀物の総称とする。一方、本草では糯米だけを稲と呼ぶ。「稲」の字は臼の上で穀物を搗く姿を表し、「稌」は方言の音が変わったもの。粘りがあって柔らかいので糯と呼ぶ。穎という人は、糯米は筋を緩め眠気を招くという。
+【考証】
+孫思邈は、糯米は甘味で脾に属する穀物なので脾病に適するという。楊士瀛は痘疹に糯米を用いるのは、毒を解き、発酵する性質で発疹を促すためだという。
+李時珍はいう。糯米は温性で、酒に醸せば熱性が強くなり、飴に煮詰めるとさらに強いので、脾肺が虚寒の人に向く。一方、痰熱や風の病がもとからある人、脾が飲食物を運べない人は、病や積滞を生じやすい。孟詵や蘇頌が涼性・寒性としたのは誤りで、『名医別録』も中を温め便を固め、熱を増やすと記す。冷えによる下痢には炒って食べ、頻尿の老人には餅や団子にして夜食べるとよいという。痘疹への利用も脾肺を温めるためである。</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="17" customHeight="1">
       <c r="A140" s="4" t="inlineStr">
@@ -17235,6 +18581,18 @@
 Because Qi descends, Fire and phlegm also descend. This explains its use for phlegm-Heat cough and wheezing, chest and diaphragm fullness, nausea and rebellious Qi.
 Shizhen therefore calls it an important herb for phlegm and Qi and rejects the older claim that it acts the same way as Bupleurum Root.
 Their indications may overlap, but their directional tendencies and channel affinities differ.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>前胡
+【性味】苦・辛、微寒。
+【毒性】無毒。
+【帰経】肺経に帰する。
+【主治】降気化痰、散風清熱。
+【名称の由来】李時珍は、『唐韻』に湔胡と書くが名の由来は不明だという。原文では編者名の一字が欠ける。
+【考証】
+李時珍はいう。前胡は甘辛で気はやや平らか、陽中の陰として下降し、手足の太陰・陽明に働く。柴胡が純陽で上昇して少陽・厥陰に入るのとは違う。気を下げる働きに優れ、痰熱による喘ぎや咳、胸や横隔膜のつかえ、嘔吐と気の逆上を治す。気が下がれば火と痰も下がるので、古い滞りを除き新しい巡りを生む痰気の要薬である。陶弘景が柴胡と同じ働きとするのは誤りで、同じ症状に用いても作用する経と働きは異なる。</t>
         </is>
       </c>
     </row>
@@ -17301,6 +18659,20 @@
 Song records Water-and-Land Elixir, a traditional tonic pill combining Euryale Seed with Jin Ying Zi.
 Shizhen emphasizes its sweet, neutral and non-greasy quality. Because it must be chewed thoroughly, he believed it promoted the gradual circulation of fluids and nourishment.
 Its later reputation centered on strengthening the Spleen and Kidney, securing essence and chronic leakage, and serving as a gentle food-medicine suitable for prolonged use.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>芡実
+【性味】甘・渋、平。
+【毒性】無毒。
+【帰経】脾経・腎経に帰する。
+【主治】補腎固精、養肝明目。
+【名称の由来】鶏頭・雁喙（『神農本草経』）、雁頭（『古今注』）、鴻頭（韓愈）、鶏雍（『荘子』）、卯菱（『管子』）、〔原文欠字〕子（音は唯。陶弘景）、水流黄（『談圃』）。
+陶弘景は水草の実で、花が鶏冠に似るため鶏頭という。蘇頌は苞が鶏や雁の頭に似るためだという。李時珍は飢饉の食料にもなるため芡と呼ぶといい、地方によって鶏頭・雁頭・芡子と名が変わると記す。茎にも異名があるが原文では字が欠ける。別種の陸生草と混同すべきでない。
+【考証】
+陶弘景は仙方で蓮の実と合わせて食べると体によいという。蘇恭は粉にして食べれば菱より滋養があるという。蘇頌は実と種を搗き、干して再び粉にし、金桜子の煎液で丸薬にした水陸丹が下を補うという。
+李時珍は孫升の『談圃』を引き、芡は役に立たないという説がある一方、水流黄の名もあるのはなぜかと問う。噛み続ける甘く穏やかな実は、べたつかず津液を巡らせ、鉱物薬より優れるという。『淮南子』にも鶏頭がある病を治すと記すが、原文の病名は欠字である。</t>
         </is>
       </c>
     </row>
@@ -17367,6 +18739,21 @@
 Jiamo describes Notopterygium Root as a strong guiding herb for the Taiyang exterior and for pain throughout the body's joints.</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>羌活（独活・羌活）
+【性味】辛・苦、温。
+【毒性】無毒。
+【帰経】膀胱経・腎経に帰する。
+【主治】解表散寒、祛風除湿、止痛。
+【名称の由来】羌活・羌青・護羌使者（『神農本草経』）、独揺草（『名医別録』）、胡王使者（『呉普本草』）、長生草（『本草綱目』）。
+陶弘景はいう。一本の茎がまっすぐ伸び、風に揺らされないので独活という。『名医別録』は、風があっても揺れず無風でも動くため独揺草と呼ぶ。大明は、独活は羌活の母であるという。
+李時珍はいう。独活と羌活は同じ類の二種で、独活も羌の地から来たものがよい。そのため羌活・胡王使者などの名があり、川芎と撫芎、白朮と蒼朮の関係に似る。原文の説明は「使用には」で途切れている。
+【考証】
+蘇恭はいう。風を治すには独活、水湿を伴う場合には羌活を用いる。
+劉完素はいう。独活は風にも揺れず風を治し、浮萍は水に沈まず水を出す。自ら勝つ性質を利用するのだ。張元素は、風は湿に勝つため羌活は水湿を治すという。独活と細辛を合わせれば少陰の頭痛、めまいに、羌活と川芎を合わせれば太陽・少陰の頭痛、関節の滞り、督脈の病による背骨のこわばりと冷えに働く。王好古は、羌活は足太陽・厥陰・少陰の薬で、独活と別種としないが、後人は羌活の気は強く独活の気は穏やかと分けるという。強い方は足太陽の風湿による頭痛、関節痛、全身痛に欠かせない君薬である。穏やかな方は足少陰に潜む風による頭痛、両足の湿痺で動けない状態を治し、太陽の証には用いない。李時珍は両者とも風を追い湿を除き、関節を通すが、気の強弱が異なるという。『素問』には下から上るものは引いて除くとあり、二薬は苦辛で温かく、薄い味を持つ陰中の陽なので、気を上へ導いて全身へ通し、風湿を散らす。伝承では、唐の劉師貞の兄が風の病にかかり、夢で胡王使者を酒に浸して飲むよう神人に告げられたが、何か分からなかった。再び夢に母が現れ、羌活のことだと教え、服用して治った。嘉謨は、羌活は手足太陽の表裏に薬を導き、足少陰・厥陰にも入り、体表のさまざまな風邪を散らして全身の関節痛を和らげるという。</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="17" customHeight="1">
       <c r="A146" s="4" t="inlineStr">
@@ -17426,6 +18813,18 @@
 He also links it with weakness or impaired movement of the limbs and jaundice with thirst when Damp-Heat is present.
 Taiping Holy Prescriptions for Universal Relief records combinations of Gentiana Macrophylla Root with Bupleurum Root and Licorice Root for acute deficiency-Heat with body aches.
 Older pediatric formulas also used Gentiana Macrophylla Root with prepared Licorice Root, sometimes adding mint, for bone-steaming fever, reduced appetite and wasting.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>秦艽
+【性味】辛・苦、平。
+【毒性】無毒。
+【帰経】胃経・肝経・胆経に帰する。
+【主治】祛風湿、清湿熱、止痺痛、虚熱を退ける。
+【名称の由来】秦糺（『唐本草』）、秦爪（蕭炳）。蘇恭は、秦胶と書くのは俗字で、元の字「秦糺」は「糾」と同じだという。李時珍は秦の地に生え、根が絡み合ったものがよいのでこの名があるという。
+【考証】
+李時珍はいう。秦艽は手足陽明経に働き、肝胆にも入る。手足が動きにくい、黄疸、煩いや渇きに、陽明の湿熱を除くため用いる。湿があれば体の痛みと熱感、熱があれば夕方の潮熱や骨蒸が現れる。『聖恵方』は急な虚労の熱と体の痛みに秦艽・柴胡各一両、甘草五銭を粉にし、一回三銭を白湯で飲む。小児の骨蒸や潮熱、食欲低下と痩せには秦艽・炙甘草各一両から一～二銭を水で煎じ、銭乙は薄荷の葉五銭を加えたという。</t>
         </is>
       </c>
     </row>
@@ -17496,6 +18895,21 @@
 The older literature therefore presents Ginseng Root not as a general stimulant, but as a powerful tonic whose use depends on the patient's underlying deficiency pattern.</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>人参
+【性味】甘・やや苦、微温。
+【毒性】無毒。
+【帰経】脾経・肺経・心経に帰する。
+【主治】大補元気、復脈固脱、益気摂血、生津安神。
+【名称の由来】人薓（音は参。略して参）、黄参（『呉普本草』）、血参（『名医別録』）、人銜・鬼蓋（『神農本草経』）、神草・土精（『名医別録』）、地精・皺面還丹（『広雅』）、海腴。
+李時珍はいう。年を経て育った根が人の姿に似て霊力があるとされ、人薓・神草と呼ばれる。「薓」には徐々に育つ意味があり、後世は字が複雑なので星の「参」で代えた。『傷寒論』には古い字が残る。『名医別録』の人微は写し誤りである。階段状に育つので人銜、陽を避け陰に向かうので鬼蓋という。五参の中では黄色の土に属し脾胃を補って陰血を生むので黄参・血参、地の精を得るので土精・地精という。『広五行記』には、隋の文帝の時代に夜ごと人の声が聞こえ、家から一里ほどの場所で人形の根を掘り出すと声が止まった話がある。また星の光と人参の発生を結びつける書もあり、神草という名の根拠とされた。
+【考証】
+陶弘景は、人参は甘草と同様に重要な薬という。李杲は、甘温で肺の元気を補い、肺気が盛んになれば他の四臓の気も養われると説く。張仲景は発汗後に体が熱く血を失い脈が沈遅する人、下痢で体が冷たく脈が弱く血虚の人に加えた。血を失ったら気を養うのは、血が自ら生じず陽気の助けで生まれるためで、血薬だけでは足りない。『素問』も陽がなければ陰は生じず陰がなければ陽は変化できないとする。本草の十剤では人参は気、羊肉は体を補って弱りを除く。
+王好古はいう。張潔古は甘味を理由に沙参で人参を代えるが、人参は五臓の陽、沙参は五臓の陰を補うので異なる。各臓に応じた薬を添えて導く必要がある。
+言聞はいう。人参は生では涼しく、熟せば温かい。甘味は陽、やや苦い味は陰を補う。気は天に属し、味は地に属する。涼は下降し、温は上昇し、甘味は浮き、苦味は沈む。気味が薄い人参は調製によって昇降が変わる。脾土が虚して火が盛んなときは生参の涼性で火を瀉し脾を補い、脾が虚し肺が弱いときは熟参の甘温で脾を補い肺を養う。李東垣は相火が脾を攻め発熱・煩悶・喘ぎ・頭痛・渇きと強い脈を生じるとき、黄柏を人参に添えた。孫思邈は夏の熱で元気を損ない汗が多く、萎えや手足の冷えに至りそうなとき生脈散を用いた。人参の甘味で火を瀉し元気を補い、麦門冬で肺を清め水源を養い、五味子で腎精を生じて失う気を収める。これは元気を補うのであって熱火を増すのではない。白飛霞は人参膏が病後の気虚や肺虚の咳に適し、気虚に火を伴う場合は天門冬膏と合わせるという。</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="17" customHeight="1">
       <c r="A150" s="4" t="inlineStr">
@@ -17561,6 +18975,21 @@
 Overall, Cinnamon Bark is presented as the deeper, hotter form of cinnamon compared with the lighter, more exterior-acting Cinnamon Twig.</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>肉桂（桂）
+【性味】辛・甘、大熱。
+【毒性】無毒。
+【帰経】腎経・脾経・心経・肝経に帰する。
+【主治】補火助陽、引火帰元、散寒止痛、温通経脈。
+【名称の由来】李時珍は范成大の『桂海志』を引く。木の葉の中心には通常一本の筋があるが、桂には圭の形をした二本の筋があり、「圭」の字を含むという。陸佃の『埤雅』は、桂は圭を持つ使者のように諸薬を導くという。『爾雅』の「梫」はほかの木を侵す性質に由来し、『呂氏春秋』には桂枝の下に雑木は生えず、『雷公炮炙論』には桂を木の根に打つと枯れるとある。桂と牡桂には厚さや辛味の違いがあるが、『名医別録』の別項目を統合して以下で分ける。
+【考証】
+寇宗奭はいう。厚く充実し気味が強い桂は腎や下焦、薄く軽いものは頭や目の病と発散の処方に使う。『神農本草経』の菌桂は精神を養い、牡桂は関節を通す。張仲景の発汗に用いる桂枝は幹ではなく枝の皮で、軽く薄い発散力を取る。柳桂という若い細枝は上焦の薬にさらに適する。
+李時珍はいう。麻黄は皮膚と毛を通して汗を出し寒邪を散らす。桂枝は営衛へ通じ、肌を解いて風を除く。肉桂は下へ向かい火の源を養い、李杲が説く腎の乾きを辛味で潤し、皮膚のきめを開いて津液と気を巡らせる働きを持つ。『聖恵方』は桂心が心に入って血を汗や膿に変えるといい、『名医別録』も桂が血脈を通すとする。
+曾世栄は、小児の驚風や下痢に五苓散を用い、火を瀉して湿を出すといい、中の桂は肝風を抑え脾土を助けるという。『医余録』には目が赤く腫れて痛み、脾が虚して食べられず肝の脈が強い人に、涼薬では脾が弱り温薬では肝が盛んになるため、穏やかな温薬に肉桂を倍量加えて両方を治した話がある。木に桂を打つと枯れるという伝承とも合い、肝肺の気や脇の痛みへの古い記述を説明する。
+また桂は辛味で散らし子宮を通して血の滞りを破るため、『名医別録』は流産を招くとし、龐安時は炒れば胎を傷めないという。丁香と官桂が痘瘡の陥没に用いられ、温めて膿を生じさせる働きは丁香の項に詳しい。</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="17" customHeight="1">
       <c r="A152" s="4" t="inlineStr">
@@ -17624,6 +19053,21 @@
 Song also records unusual historical surgical uses of mulberry bark fiber, but these belong to anecdotal practice rather than its main medicinal role.</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>桑白皮（桑）
+【性味】甘、寒。
+【毒性】無毒。
+【帰経】肺経に帰する。
+【主治】瀉肺平喘、利水消腫。
+【名称の由来】実は椹（『集韻』）という。
+李時珍は徐鍇の『説文解字』を引き、桑の字と、東方の神木との名称や字形の関係を述べる。桑は蚕が食べる木で、神木と区別するため字形に木を加えたという。『典術』には桑は箕星の精とある。
+【考証】
+李杲はいう。桑白皮は甘味で不足した元気を固めて虚を補い、辛味で肺気の過剰を瀉して咳を止める。ただし性質が穏やか一辺倒ではなく、多用は避ける。
+李時珍はいう。桑白皮は尿を出すのに優れ、肺に水気がある場合や肺火が過剰な場合に適する。十剤に湿を除く薬として桑白皮と赤小豆を挙げる。宋の医者銭乙は、肺に熱が盛んで咳から喘ぎ、顔がむくみ発熱する場合の瀉白散に、炒った桑白皮一両、焙じた地骨皮一両、炒った甘草半両を用い、一回一～二銭と粳米百粒を煎じて食後に温かく飲ませた。桑白皮と地骨皮は火を尿へ導き、甘草は火を瀉して中を緩め、粳米は肺を清め血を養う。肺の火を瀉す処方の手本である。羅天益は、肺に潜む火を瀉すことで正気を養うという。ただし肺が虚して尿がよく出る人には適さない。
+蘇頌は、桑白皮を糸にして腹の傷から出た腸を縫い、温かい鶏血を塗った話を記す。唐の安金蔵が腹を裂いたとき、この方法で治ったという。</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="17" customHeight="1">
       <c r="A154" s="4" t="inlineStr">
@@ -17687,6 +19131,20 @@
 Later practice especially valued the leaf for Wind-Heat affecting the Lung and Liver and for dryness of the Lung with cough or irritated eyes.</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>桑葉（桑）
+【性味】甘・苦、寒。
+【毒性】無毒。
+【帰経】肺経・肝経に帰する。
+【主治】疏散風熱、清肺潤燥、平抑肝陽、清肝明目、涼血止血。
+【名称の由来】実は椹（『集韻』）という。
+李時珍は徐鍇の『説文解字』を引き、桑の字と、東方の神木との名称や字形の関係を述べる。桑は蚕が食べる木で、神木と区別するため字形に木を加えたという。『典術』には桑は箕星の精とある。
+【考証】
+蘇頌はいう。桑葉は常用もできる。仙人の服食法では四月の葉と、十月に霜を受け葉の三分の二が落ちた後に残る「神仙葉」を採り、陰干しして粉にする。丸薬や散剤、茶の代わりの煎じ汁に用いる。霜後の葉を煮た湯で手足を洗えば風による痺れに優れ、軽く炙って桑衣と煎じれば痢疾や刀傷の出血に働く。
+朱震亨は霜を受けた桑葉を粉にして米のとぎ汁で飲めば寝汗を止めるという。李時珍は手足陽明の薬で、汁を煎じて茶の代わりに飲めば消渇を止めるという。</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="A156" s="4" t="inlineStr">
@@ -17743,6 +19201,18 @@
 Its strong aroma and penetrating quality were also said to guide other medicines downward toward the lower burner.
 For this reason, some Kidney-tonifying formulas processed Amomum Fruit together with Di Huang.
 Older texts also attributed unusual abilities to Amomum Fruit in processing hard substances and alchemical preparations, though these claims belong to historical materia medica tradition.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>縮砂（砂仁）
+【性味】辛、温。
+【毒性】無毒。
+【帰経】脾経・胃経・腎経に帰する。
+【主治】化湿開胃、温脾止瀉、理気安胎。
+【名称の由来】李時珍は名の由来は詳らかでないという。蓮根の下に白いものが密に隠れることに例え、実が根元にあり仁が殻の中に隠れる姿からの名かもしれないと述べる。原文の蓮根に関する語には欠字がある。
+【考証】
+李時珍は韓氏の『医通』を引く。腎は乾燥を嫌い、辛味で潤すため、縮砂仁の辛味は腎の乾きを潤す。また土に属して脾を目覚めさせ胃を調え、諸薬を丹田へ導く。香りが強く巡り、五臓の気を調和させるので、腎を補う薬では地黄丸とともに蒸して下へ届かせる。骨を柔らかくする働きがあるとされ、草木薬や方士が煉る三黄とともに用いるが、なぜそのような作用があるのかは分からないという。</t>
         </is>
       </c>
     </row>
@@ -17808,6 +19278,20 @@
 Thus both may be called tonics, but one primarily supports Qi and Yang while the other nourishes Yin and restrains Heat.</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>沙参
+【性味】甘、微寒。
+【毒性】無毒。
+【帰経】肺経・胃経に帰する。
+【主治】養陰清肺、益胃生津、化痰益気。
+【名称の由来】白参（『呉普本草』）、知母・羊乳・鈴児草・虎鬚・苦心（『名医別録』）、羊婆奶（『本草綱目』）。苦心には文希・識美・志取の異名もある。
+陶弘景は人参・玄参・丹参・苦参と合わせて五参と呼び、形は異なっても用途が似るため「参」の名があるという。別に牡蒙という紫参もある。李時珍は、白い色で砂地に生えるため沙参、根に白い汁が多いため羊婆奶と呼ぶという。心の部分がなく味も淡いのに、苦心や知母と同じ名を持つ理由は分からず、鈴児草は花の形にちなむ。
+【考証】
+張元素は肺が冷える人には人参、肺が熱い人には甘い沙参で代えるという。王好古は沙参は甘くやや苦く、厥陰の本経と脾経の気分に働き、微苦は陰、甘は陽を補うと説く。人参は温性で五臓の陽、沙参は寒性で五臓の陰を補うため、各臓に応じた佐薬で導く必要がある。
+李時珍はいう。人参は甘苦で温かく重く充実し、主に脾胃の元気を補い、肺と腎にも益するので内傷の気虚に適する。沙参は甘淡で寒く軽く、主に肺の気を養い、脾と腎にも益するので肺が火に傷つく場合に向く。前者は陽を補って陰を生み、後者は陰を補って陽を抑える。区別すべきである。</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="17" customHeight="1">
       <c r="A160" s="4" t="inlineStr">
@@ -17870,6 +19354,19 @@
 Shizhen observes that later physicians increasingly used Sha Yuan Ji Li, now known as Flatstem Milkvetch Seed, for Kidney deficiency and tonic purposes.
 He suggests that the nourishing actions were considered broadly similar enough that the later seed became a common substitute in tonifying formulas.
 The historical entry therefore reflects a period in which thorny Ji Li and Flatstem Milkvetch Seed were not always cleanly separated in materia medica literature.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>沙苑子（白蒺藜）
+【性味】甘、温。
+【毒性】無毒。
+【帰経】肝経・腎経に帰する。
+【主治】補腎固精、養肝明目。
+【名称の由来】茨（『爾雅』）、旁通・屈人・止行・豺羽・升推（『神農本草経』）。
+陶弘景は、道端や塀に多く生え、葉が地面に広がり、小さな菱形のとげのある実を結ぶと記す。長安に多く、軍ではとげの形を鉄で作って敵の道にまく「鉄蒺藜」と呼ぶ。『易経』は蒺藜に身を置くことを傷害の象徴とし、『詩経』は塀の茨は掃えないと詠む。李時珍は「蒺」「藜」「茨」は鋭いとげがすばやく人を傷つける意味で、屈人・止行もそのための名だという。
+【考証】
+蘇頌は古方ではとげのある蒺藜を用い、風を治し目を明らかにするといい、仙方には黒白を問わず堅い実のとげを取り去って単独で服す方法がある。李時珍は、古方は補腎と風の治療に刺蒺藜を使うが、後世は沙苑蒺藜を補腎に多く使い、煮詰めて膏にもするため働きは大きく違わないだろうという。刺蒺藜を黄色く炒ってとげを除き、粉にして餅にするか蒸して食べれば飢饉の食料にもなる。原文は沙苑子と刺蒺藜の記述を一条に併記している。</t>
         </is>
       </c>
     </row>
@@ -17939,6 +19436,19 @@
 This helps explain Chinese Yam's broad role in formulas for Spleen weakness, Lung deficiency and Kidney deficiency.</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>山薬（薯蕷）
+【性味】甘、平。
+【毒性】無毒。
+【帰経】脾経・肺経・腎経に帰する。
+【主治】益気養陰、補脾肺腎、固精止帯。
+【名称の由来】藷藇（音は諸預。『山海経』）、土藷（『名医別録』）、山藷（『図経本草』）、山芋・玉延（『呉普本草』）、山薬（『本草衍義』）。
+呉普は薯薯・児草・修脆とも呼び、斉と魯では山芋、鄭と越では土薯、秦と楚では玉延という。蘇頌は、江南や福建では薯または山薯と呼び、『山海経』の薯藇と同じ植物で、表記や発音の違いは方言や伝承の訛りによるという。寇宗奭は、薯蕷は唐代宗の名「預」を避けて薯薬、宋英宗の名「署」を避けて山薬と呼ばれ、古い名が失われたので別物と誤解されないよう記す。
+【考証】
+甄権は虚して痩せた患者に加えるとよいという。孟詵は男性の陰を助け、蜜と煮る、煎じる、粉にするなどしてよく、乾燥品は薬にさらに適するという。ただし小麦粉と混ぜて作るものは気を乱すとした。李杲は手太陰に入り、張仲景の八味丸に乾燥山薬を入れるのは涼しく補うためで、乾いた皮膚も潤すという。李時珍は呉綬の説として手足太陰を補って虚熱を清めるといい、王履の説として肺を潤せばその下流の腎にも益し、八味丸が陰を養うために用いると述べる。曹毗の『杜蘭香伝』には薯蕷を食べれば霧や露の害を避けるとある。</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="17" customHeight="1">
       <c r="A164" s="4" t="inlineStr">
@@ -17998,6 +19508,19 @@
 Its sour and astringent flavor was therefore used for excessive urination, loss of essence and other deficiency patterns involving failure to secure.
 He also notes its important role in classical Kidney formulas such as Eight-Ingredient Pill.
 The herb's traditional value lies in combining gentle Liver-Kidney tonification with a securing action rather than strongly moving or draining.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>山茱萸
+【性味】酸・渋、微温。
+【毒性】無毒。
+【帰経】肝経・腎経に帰する。
+【主治】補益肝腎、収渋固脱。
+【名称の由来】蜀酸棗（『神農本草経』）、肉棗（『本草綱目』）、鬾実（『名医別録』）、鶏足・鼠矢（『呉普本草』）。
+寇宗奭は山茱萸と呉茱萸は似ず、働きも異なるので、同じ「茱萸」の名を持つ理由は分からないという。李時珍は蜀酸棗・肉棗は形にちなむ名だという。
+【考証】
+王好古はいう。滑って漏れ出るときは気が脱するため、渋味で収める。山茱萸は酸渋で尿が出すぎるのを抑え、精気を固める。張仲景が八味丸で君薬としたことからも性味が分かる。</t>
         </is>
       </c>
     </row>
@@ -18067,6 +19590,20 @@
 Shizhen therefore treats Fresh Rehmannia Root and Prepared Rehmannia Root as related but functionally distinct medicines rather than interchangeable forms.</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>生地黄（地黄）
+【性味】甘・苦、寒。
+【毒性】無毒。
+【帰経】心経・肝経・腎経に帰する。
+【主治】清熱涼血、養陰生津。
+【名称の由来】芐（音は戸）・芑（音は起。『名医別録』）、地髄（『神農本草経』）。
+大明は生の地黄を水に浸し、浮くものを天黄、半ば浮くものを人黄、沈むものを地黄とし、薬には沈むものが最良、半沈が次、浮くものは不適とする。李時珍は『爾雅』の芐が地黄で、江東の呼び名であり、沈むものが貴ばれるので字に「下」が含まれるという。
+【考証】
+王好古はいう。生地黄は手少陰と手太陽に入り、銭仲陽の導赤散では木通と合わせて心火を瀉す。ほかの薬に添えれば諸経の血熱、血尿、血便にも働く。甄権は虚して熱の多い人に加えるという。戴原礼は、陰が弱く陽と相火が盛んで陰を焼く虚火には地黄で陰を養い陽熱を退けるという。
+寇宗奭はいう。『神農本草経』には乾燥品と生品だけで、熟地黄はない。血虚の虚熱、産後の熱、老人の中焦の虚弱による乾燥熱に生品や乾燥品は冷えすぎるため、後世は蒸して干した熟品を使うようになった。李時珍は、古い「乾地黄」は陰干し・日干し・火干ししたもので、『名医別録』の「生地黄」は掘りたての鮮品で強い寒性を持つと区別する。熟地黄は後人が繰り返し蒸し干ししたもので、血を冷やす力と補う力に違いがあるため別項目にする。</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="17" customHeight="1">
       <c r="A168" s="4" t="inlineStr">
@@ -18132,6 +19669,20 @@
 Historical formulas combined ginger with tea for dysentery, with the ginger peel retained or removed according to whether Heat or Cold was believed to predominate.</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>生姜
+【性味】辛、温。
+【毒性】無毒。
+【帰経】肺経・脾経・胃経に帰する。
+【主治】解表散寒、温中止嘔、魚介の毒を解く。
+【名称の由来】李時珍は許慎の『説文解字』で姜を䕬と書き、湿を防ぐ野菜とすることを引く。王安石は多くの邪を防ぐため姜というと説く。若い芽の先が紫色のものは紫姜・子姜、古い根は母姜と呼ぶ。
+【考証】
+成無己はいう。姜の辛味と棗の甘味は脾の津液を巡らせ、営衛を調える。薬に入れるのは単なる発散のためだけではない。
+李杲はいう。生姜には半夏・厚朴の毒を抑える、風寒を散らす、大棗と合わせて脾胃の元気を養い中を温め湿を除く、芍薬と合わせて経を温め寒を散らす、という四つの用途がある。孫思邈が嘔吐の要薬とするのは、辛味で逆上して滞る気を散らすためである。生姜は肺にも胃の入口にも働く。ここでいう胃の入口は、俗にいう心窩部ではなく、喉の下で飲食物を受ける場所で、肺の経路と並ぶという。夜間は気が収まる時間なので、生姜の発散性とは合わないという説もあるが、病人では事情が異なる。乾燥生姜の粉は乾姜ほど熱くなく、生姜ほど湿らず、乾姜の代用にもなる。「寝る前は大根、起床後は生姜」という俗言は、大根が食物を消し、生姜が胃を開くことをいう。
+李時珍はいう。生姜は辛くても臭みがなく邪を除き、生でも加熱しても、酢・醤・酒粕・塩・蜜と合わせてもよい。野菜、調味料、果物、薬として役立ち、山を歩く際には口に含んで湿った霧や悪気を避けるという。蘇頌は崔元亮の『集験方』を引き、細かく切った生姜とよい茶を一、二碗分合わせて飲む姜茶が痢疾によいといい、熱の痢疾なら皮を残し、冷えの痢疾なら皮を除く。楊士瀛は生姜が陽、茶が陰を助け、悪気を散らし、湿熱や酒食、暑気による不調に赤白いずれの痢疾でも使うという。</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="17" customHeight="1">
       <c r="A170" s="4" t="inlineStr">
@@ -18194,6 +19745,22 @@
 Shizhen preserves many of these stories, including legends of adepts who lived on Acorus Rhizome for years or attained immortality. These accounts belong to religious and longevity folklore rather than ordinary medical practice.
 Su Shi praised the plant's ability to survive in clean water with little soil and kept it as an ornamental plant.
 Yang Shiying records adding small amounts of Acorus Rhizome to Spleen-tonifying formulas when severe dysentery was accompanied by refusal of food and obstruction in the chest, using its aromatic action to open the middle and restore appetite.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>石菖蒲（菖蒲）
+【性味】辛・苦、温。
+【毒性】無毒。
+【帰経】心経・胃経に帰する。
+【主治】開竅豁痰、醒神益智、化湿開胃。
+【名称の由来】昌陽（『神農本草経』）、尭韭（呉普）、水剣草（『本草綱目』）。
+李時珍は、蒲の仲間でよく繁るため菖蒲という。『呂氏春秋』は冬至から五十七日後に最初に芽を出し、その後耕作が始まると記し、昌陽の名もそこから来たという。『典術』は尭の時代に天の精が庭に降りて韭となり、陰の気を受けて菖蒲になったので尭韭と呼ぶといい、葉が剣に似るので方士は水剣と隠して呼んだ。
+【考証】
+蘇頌はいう。古方には菖蒲を単独で服す方法がある。蜀では心腹の冷えた痛みに一、二寸を砕き、呉茱萸と煎じて飲む。急な心痛には携帯したものを噛み、熱い湯や酒で飲むという。
+李時珍はいう。明の太祖に仕えた周顛仙は菖蒲を噛んで水を飲み、腹痛を防ぐと語った。菖蒲は温辛で手少陰・足厥陰に働き、心気の不足には虚した母を補い、肝の急を辛味で緩める。『道蔵経』の『菖蒲伝』には、魚の鱗のように節が密なもの一斤を水と米のとぎ汁にそれぞれ一夜浸し、皮を取り刻んで干し、粉にして糯米粥と煉蜜で梧桐の実ほどの丸薬にする方法がある。風通しのよい場所で乾かし、朝と寝る前に各三十丸を酒などで服すという。一月で消化がよくなり、二月で痰が除かれ、五年で髄が充実し白髪や歯が戻るとする伝承である。葉の青、花の赤、節の白、芯の黄、根の黒を五行に配し、風病、手足のしびれや麻痺、虚労、口・耳・目や五臓の不調、疫病、痢疾、痔や産後の血の病まで幅広く挙げる。葉敬の母や道士らが長年服して治ったという逸話もある。
+葛洪の『抱朴子』や『神仙伝』にも長年服して毛髪や歯が生え、不老になったという話がある。『神隠書』は鉢植えを机に置けば読書時の煙から目を守り、葉先の露で目を洗えば視力がよくなるとする。蘇東坡は石の上の草にはわずかな土が必要だが、石菖蒲は泥を洗い落として清水の鉢に置いても長く枯れず、節や葉が丈夫で観賞にもよいと述べる。
+楊士瀛はいう。口を閉ざして食べられない痢疾には脾虚だけでなく熱が心胸を塞ぐことがある。木香では温めすぎ、山薬では塞ぎすぎるため、参苓白朮散に石菖蒲を加え粳米の汁で飲むか、人参・茯苓・石蓮肉に少量加える。胸が開けば自然に食欲が戻る。</t>
         </is>
       </c>
     </row>
@@ -18262,6 +19829,23 @@
 White Tiger Decoction became the classic formula illustrating its use for exuberant Qi-level Heat with profuse sweating and thirst.
 Historical physicians repeatedly caution that blood deficiency, Qi deficiency and weak Stomach conditions can resemble Heat patterns but do not necessarily tolerate Gypsum.
 Shizhen recounts both successful and harmful cases to emphasize that the problem lies not in the mineral itself but in incorrect pattern identification and excessive use.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>石膏
+【性味】甘・辛、大寒。
+【毒性】無毒。
+【帰経】肺経・胃経に帰する。
+【主治】清熱瀉火、除煩止渇。
+【名称の由来】細理石（『名医別録』）、寒水石（『本草綱目』）。
+朱震亨は、焼いて細かく砕き酢で練ると炉を脂より固く密に封じられ、姿と働きから名があるという。李時珍は細かな石目から細理石、水のような強い寒性から寒水石と呼ぶが、凝水石とは同名の別物だという。
+【考証】
+成無己はいう。風は陽、寒は陰の邪で、営衛の陰陽がともに傷ついた場合には軽い薬だけでなく重い薬も合わせて散らす。大青竜湯で石膏を使薬とするのは、重い薬でも肌表へ届くためである。知母と石膏の苦甘で熱を散らすともいう。
+張元素はいう。石膏は寒性で辛淡、気味は薄いが重く沈み、下降する陰の薬で陽明経の強い熱を冷ます。頭痛・歯痛、消渇、暑気、潮熱を治すが、胃を冷やして食欲を失わせるため、腹に強い熱がなければ安易に用いない。陽明の熱で発熱と悪寒、夕方の潮熱、筋肉の強い熱、濁って赤い尿、大きな渇きと自汗、頭痛などが揃うときに白虎湯を用いる。血虚の発熱や脾胃の虚労が似た姿を示す場合、誤用すれば危険である。
+李杲はいう。石膏は足陽明の薬で、張仲景は体の熱、目の痛み、鼻の乾き、不眠に用いた。体の前面は胃の経、胸は肺に関わり、陽明の邪熱が肺を攻めるため辛寒で肺気を清める。三焦や皮膚の強い熱にも働き、速い脈が下がらない場合に用いるが、胃の弱い人には使わない。寇宗奭は、四月以降の暑さには白虎湯がよいという説も地域や年ごとの気候を考慮すべきだという。
+李時珍はいう。李杲は立夏以前に白虎湯を多く飲むと尿を抑えられなくなるといい、下降させすぎるためだとする。甄立言の五蒸湯は白虎湯に人参・茯苓・地黄・葛根を加減したもの。王燾の『外台秘要』には骨蒸や長引く咳に針を束ねたような石目の石膏一斤と粉末の甘草一両を細かく砕き、一日三～四回水で飲む処方があり、安価でも軽んじるなという。骨蒸で体内が熱く外が寒い女性を治した例もある。ただしこれは若く肺胃の火が盛んで食べられる人の場合で、年老いた人、気血が虚した人、胃が弱い人には不適だろう。
+五十歳の林という人は痰を伴う咳と発熱に石膏を一斤ほど単独で飲み、食べられず咳が増して亡くなった。これは用薬者の誤りで、石膏そのものの罪ではない。楊士瀛は炮製した石膏が瘡の広がりを収めるという。銭乙の伝記には、嘔吐と下痢の子に温薬を与え喘ぎが増したのを、内熱による病と見て石膏湯で治した話がある。また古方の寒水石は凝水石、唐宋以降の処方では今の石膏を指すことが多く、長石や方解石と混同してはならない。</t>
         </is>
       </c>
     </row>
@@ -18333,6 +19917,22 @@
 The entry also preserves dramatic old anecdotes about raw Rehmannia for severe chest or Heart pain, but these stories belong to historical case literature rather than modern treatment guidance.</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>熟地黄（地黄）
+【性味】甘、微温。
+【毒性】無毒。
+【帰経】肝経・腎経に帰する。
+【主治】補血滋陰、益精填髄。
+【名称の由来】芐（音は戸）・芑（音は起。『名医別録』）、地髄（『神農本草経』）。
+大明は生の地黄を水に浸し、浮くものを天黄、半ば浮くものを人黄、沈むものを地黄とし、薬には沈むものが最良、半沈が次、浮くものは不適とする。李時珍は『爾雅』の芐が地黄で、江東の呼び名であり、沈むものが貴ばれるので字に「下」が含まれるという。
+【考証】
+張元素はいう。生地黄は強い寒性で血を冷やし、血熱に用いる。熟地黄はやや温かく腎を補い、血の衰えに用いる。臍の下の腎経の痛みには熟地黄が欠かせない。
+王好古はいう。生地黄は心の熱や手足のほてりを治し、手足の少陰・厥陰に入って腎水を益し心血を冷やす。脈が強く実している人に適する。脈が虚す人には九度蒸した熟地黄で腎の元気を補う。張仲景の八味丸では諸薬の中心、四物湯では肝に蔵される血を治す君薬とする。
+李時珍は王碩の『易簡方』を引き、男性の陰虚には熟地黄、女性の血熱には生地黄が適するという。また生地黄は精血を生むので天門冬でその生成部位へ導き、熟地黄は精血を補うので麦門冬で補う部位へ導くとする。虞摶は、生地黄を胃気の弱い人が服すと食欲を妨げ、熟地黄を痰飲の多い人が服すと胸につかえる恐れがあるといい、生品は酒で、熟品は生姜汁で炒るとそれぞれを和らげられるという。
+蘇頌は崔元亮の『海上方』を引き、生地黄の汁を粉に混ぜる心痛の処方を紹介するが、原文の製法は途中で途切れ、二年間病を患った人が死後に腹を開かせると虫が見つかり、地黄を与えると崩れたという逸話へ移る。劉禹錫の『伝信方』にも、崔抗の娘が重い心痛で生地黄の冷たい麺を食べた後、蛙に似たものを吐き出して治った話がある。原文は「冷淘に加えてはならない」と続くところで切れている。</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="17" customHeight="1">
       <c r="A176" s="4" t="inlineStr">
@@ -18397,6 +19997,20 @@
 Zongshi likewise cautions against treating perilla tea as an everyday tonic, especially in people with cold, weak digestion and loose stools.</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>蘇葉（蘇）
+【性味】辛、温。
+【毒性】無毒。
+【帰経】肺経・脾経に帰する。
+【主治】解表散寒、行気和胃。
+【名称の由来】紫蘇（『食療本草』）、赤蘇（『肘後方』）、桂荏（『爾雅』）。李時珍は「蘇」は気血をのびやかに巡らせる名で、白蘇と区別して紫蘇と呼び、荏に似て桂のような辛味があるため桂荏とも呼ぶという。
+【考証】
+蘇頌は風毒を通して散らすなら茎だけを用い、節を除くのがさらによいという。
+李時珍はいう。紫蘇は辛味が気分、紫色が血分に入る近世の要薬である。橘皮・砂仁と合わせれば気を巡らせ胎を安定させ、藿香・烏薬なら中を温め痛みを止め、香附・麻黄なら発汗して肌を解き、川芎・当帰なら血を調え散らす。木瓜・厚朴なら湿や暑を散らして霍乱・脚気を治し、桔梗・枳殻なら横隔膜と腸を通し、杏仁・莱菔子なら痰や喘ぎを鎮める。ただし長く服せば真気を漏らす。
+寇宗奭はいう。紫蘇は香りがよくやや辛甘で散らすが、朝夕に紫蘇湯を飲み続けるのは益がない。脾胃が冷えた人には下痢を招くこともある。</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="17" customHeight="1">
       <c r="A178" s="4" t="inlineStr">
@@ -18458,6 +20072,20 @@
 Shizhen emphasizes that Sour Jujube Seed should not be understood only as a Heart herb. He places it within the Jueyin and Shaoyang systems as well, linking its sour astringency with the Liver and its sweet, moistening nature with nourishment and calming.</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>酸棗仁（酸棗）
+【性味】甘・酸、平。
+【毒性】無毒。
+【帰経】肝経・胆経・心経に帰する。
+【主治】養心補肝、寧心安神、斂汗生津。
+【名称の由来】樲（『爾雅』）、山棗（陶弘景）。
+【考証】
+蘇恭は、『神農本草経』には不眠に実を用いるとあり、仁とは書かれないが、今の処方は仁を使うという。中を補い肝を養い筋骨を強め陰気を助ける。寇宗奭も同じ違いを指摘する。
+志という人は、五代の薬の記録に、生の酸棗仁は眠気の多い人に、炒ったものは眠れない人に使うとあるという。陶弘景は食べると目が覚めるとし、古典は不眠を治すとする。果肉は酸味で眠気を覚まし、種の中の仁は不眠を治す。麻黄の茎が汗を出し根や節が止汗するのと同じである。
+李時珍はいう。酸棗の実は酸味で収めるため、肝の病や寒熱の結び、長引く痺れや下痢、臍の下の張りを治す。仁は甘く潤うので、炒ったものは胆虚による不眠、煩いや渇き、虚による汗に、生では胆熱による眠気に用いる。足厥陰・少陽に働くのに心だけの薬とみなすのは誤りだ。</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="17" customHeight="1">
       <c r="A180" s="4" t="inlineStr">
@@ -18515,6 +20143,19 @@
 Gao lists four major actions: treating Heat entering the blood chamber, removing abdominal blood stasis, relieving dry itchy skin associated with blood Heat, and moving stagnant blood in the superficial tissues.
 Cheng Wuji explains its role through the Liver's relationship with blood. When blood accumulates and stagnates, Peach Kernel's sweet quality moderates the Liver while its blood-moving action disperses stasis.
 Zhang Zhongjing's Appropriate Decoction uses Peach Kernel with strongly stasis-breaking ingredients for severe blood accumulation patterns marked by lower abdominal fullness, agitation and other signs of internal stasis.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>桃仁
+【性味】苦・甘、平。
+【毒性】小毒。
+【帰経】心経・肝経・大腸経に帰する。
+【主治】活血祛瘀、潤腸通便、止咳平喘。
+【名称の由来】李時珍は桃は早く咲き、栽培しやすく実が多いため、木と「兆」から成るという。兆は非常に多い数を表すが、音を借りた字という説もある。
+【考証】
+李杲はいう。桃仁は甘味より苦味が強く、気が薄く味が濃い。沈んで下へ向かう陰中の陽で、手足厥陰の血分に働く。苦味で滞った血を瀉し、甘味で新しい血を生むので瘀血を除く。熱が血室へ入った病、腹中の滞血、皮膚の血熱による乾燥やかゆみ、皮膚に凝った血を治す四つの用途がある。
+成無己はいう。肝は血の源で、血が集まると肝気は急になり乾く。桃仁の甘味は肝を緩め血を散らす。張仲景の抵当湯は傷寒八、九日で内に血がたまり、狂ったように熱を出し下腹が張って痛むが尿は出る場合に用いる。また汗が出るべきときに出ず、熱毒が深く入って吐血や胸中の血の結び、煩躁やうわごとを生じる場合にも用い、虻虫・水蛭・大黄と合わせる。</t>
         </is>
       </c>
     </row>
@@ -18581,6 +20222,20 @@
 Shizhen emphasizes that the root is not simply bitter and cold. It is primarily sweet, slightly bitter and slightly sour.
 The sour aspect helps generate fluids, the slight bitterness drains Fire, and the sweetness prevents excessive injury to the Stomach.
 This combination explains its traditional use for thirst, dryness and Heat without the harshness of more intensely bitter-cold medicines.</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>天花粉（栝楼）
+【性味】甘・やや苦、微寒。
+【毒性】無毒。
+【帰経】肺経・胃経に帰する。
+【主治】清熱瀉火、生津止渇、消腫排膿。
+【名称の由来】果裸（音は裸）、栝楼（『本草綱目』）、天瓜・黄瓜・沢姑（『名医別録』）、地楼（『神農本草経』）。根は白薬・天花粉（『図経本草』）、瑞雪（趙宜真）という。
+李時珍はいう。「裸」は「蓏」と同じで、許慎は木の上に実るものを果、地に生じるものを蓏という。この植物はつるが木に絡むため両方を名に含む。『詩経』に果裸の実が家の軒まで伸びるとある。栝楼は果裸の音が変わったもので、表記が重ねて変わり元の姿から離れた。昔は瓜と姑が同音だったので沢姑とも呼び、斉では形から天瓜と呼ぶ。雷斅が丸いものを栝、長いものを楼とするのはこじつけで、雌雄で分ければよい。根を粉にすると雪のように白いので天花粉といい、蘇頌の『図経』が別項目にしたのは誤りなので統合する。
+【考証】
+蘇恭は、根を白い粉にして食べると虚熱の人によいという。李杲は栝楼の根は陰性で、煩いや渇きを除き津液を巡らせ、心中の乾きを潤すという。辛酸の薬と合わせて腫れの気を導くとの記述に続くが、原文はそこで別の引用に移る。成無己は、津液の不足による渇きに、やや寒く苦い根で乾きを潤して津液を通すと説く。
+李時珍はいう。根は甘くやや苦酸、茎葉は酸味で、酸は津液を生じるので渇きを止め乾きを潤す。微苦は火を下げ、甘味は胃を傷めない。古人が苦寒とのみ記したのは味を十分に吟味していない。</t>
         </is>
       </c>
     </row>
@@ -18656,6 +20311,23 @@
 Shizhen preserves these stories but ends with a practical caution: because Asparagus Root is cold and moistening, prolonged use in people with weak, cold digestion may cause chronic loose stools.</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>天門冬
+【性味】甘・苦、寒。
+【毒性】無毒。
+【帰経】肺経・腎経に帰する。
+【主治】養陰潤燥、清肺生津。
+【名称の由来】虋冬（音は門。『爾雅』）、顛勒（『神農本草経』）、天棘（『本草綱目』）、万歳藤（『救荒本草』）。
+蘇禹錫は『爾雅』や『抱朴子』にある満冬、顛棘、地門冬、筵門冬などの名を挙げる。各山岳では淫羊藿、天門冬、管松、無不愈、百部などとも呼ぶとされるが、別に百部という草もあり、根や苗が異なり咳を治すだけで服食には向かないので区別すべきだという。李時珍は繁るつると麦門冬に似た働きから天門冬、細い棘状の葉から天棘と呼ぶと考える。万歳藤・娑羅樹の名もあり、百部と姿や肺への働きが似るため同名になる。『爾雅』で蔷蘼と虋冬を混同するのは古い書の錯簡だろうという。
+【考証】
+甄権は冷やしながら補うので、虚して熱のある人に地黄と合わせるとよいという。寇宗奭は肺熱に働くが、苦味で瀉す力が強く、寒がりの人には禁ずるという。張元素は苦味で滞血を除き甘味で元気を養い、肺を熱した血が喘ぎを招く場合に人参・黄耆を添えるとよいという。
+嘉謨はいう。天門冬と麦門冬はともに手太陰へ入り、煩いと渇きを除き、咳や痰を治す。麦門冬はさらに手少陰へ行き、心火を清め肺を守って咳を止める。天門冬は足少陰へも入り、腎を潤して元気を養い、津液不足から生じる痰を根本から解く。王好古は営衛の乾きを潤すため、両門冬・人参・五味子・枸杞子を脈を養う薬とする。
+趙継宗は、この五薬にも使薬が要り、生地黄・貝母は天門冬、地黄・車前子は麦門冬、茯苓は人参を導くという。張三豊が尚書に伝えた長生きの処方にも天門冬三斤、地黄一斤があるとするが、原文の尚書の名には欠字がある。
+蘇禹錫は『抱朴子』を引き、天門冬を蒸し煮して穀物の代わりに食べ、散剤や酒、汁を煮詰めた膏にもするといい、長く服せば力と髄が増し、松脂や蜜と合わせる方法や長寿の逸話を記す。唐慎微も『列仙伝』などの歯や髪が戻り、長年生きるという伝承を挙げ、天門冬と茯苓を等量粉にしたものを毎日方寸匕飲むという。
+李時珍はいう。天門冬は肺を清め火を下げ、水の上流を益して腎気へ通じる。滋補の処方にほかの薬と合わせれば働くが、脾胃が虚寒の人が単独で長く服せば腸が緩み、慢性の病を招く。寒く潤って大腸を通すためである。</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="17" customHeight="1">
       <c r="A186" s="4" t="inlineStr">
@@ -18721,6 +20393,19 @@
 These claims belong to historical tonic folklore, but they reflect the herb's established reputation for strengthening the Liver and Kidney, supporting essence and securing chronic leakage.</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>菟絲子（菟糸子）
+【性味】甘、温。
+【毒性】無毒。
+【帰経】肝経・腎経・脾経に帰する。
+【主治】補腎益精、養肝明目、止瀉、安胎。
+【名称の由来】菟縷・菟蔂・赤網（『名医別録』）、菟蘆（『神農本草経』）、菟丘（『広雅』）、玉女・唐蒙（『爾雅』）、火焰草・野狐糸・金線草（『本草綱目』）。
+蘇禹錫は、『呂氏春秋』『抱朴子』が菟糸の下には茯苓のような「伏菟」があり、これを抜けば菟糸が枯れると伝えるという。また初生の根が兎の形をしていたことから名づけたという説もある。陶弘景は茯苓の上に必ず菟糸が生えるわけではないという。蘇頌は、唐蒙・女蘿・菟糸を同じものとする古い書と、松蘿を女蘿とする本草の食い違いを挙げる。朱震亨は菟糸と茯苓、菟糸と松蘿を結びつけるのは誤伝だとする。李時珍は、草に絡む黄赤のつるが菟糸、松に絡む青いつるが松蘿で、古典の注釈が両者を混同したと説明する。菟糸と茯苓の伝承は茯苓の項も参照する。
+【考証】
+雷斅はいう。菟糸子は中庸の気と正陽を受けて実り、衛気を補い筋脈を助ける。蘇頌は『抱朴子』の服食法を引き、実一斗を酒一斗に浸して干し、酒がなくなるまで繰り返して粉にし、酒で二銭を一日二回飲むと記す。腰膝の風を除き目を明らかにし、長く服せば肌つやがよくなり若返るという伝承である。</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="17" customHeight="1">
       <c r="A188" s="4" t="inlineStr">
@@ -18781,6 +20466,20 @@
 Shizhen classifies Trogopterus Dung as a Liver and blood-level medicine. Because the Liver governs blood, he uses it for pain and disorders associated with blood stasis.
 He especially praises Sudden Smile Powder, a classic formula containing Trogopterus Dung for abdominal, chest, rib and lower abdominal pain attributed to blood stasis.
 The herb was also historically used in abnormal uterine bleeding, postpartum pain and other blood-stasis patterns, reflecting its combination of blood-moving and hemostatic actions.</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>五霊脂
+【性味】甘・苦・鹹、温。
+【毒性】無毒。
+【帰経】肝経に帰する。
+【主治】活血止痛、化瘀止血。
+【名称の由来】動物を鹖鴠・独舂、その糞を五霊脂という。
+李時珍は楊氏の『丹鉛録』に従い寒号虫と鹖鴠を同一視し、古書や地方によって盍旦・曷旦・䳚鴠・侃旦・渇旦・城旦・倒懸・独舂などと呼ばれるという。夜に鳴いて朝を求め、夏は毛が多く冬は裸となるため寒号と名づけられた。城旦舂という刑罰名との連想もある。糞が固まった脂に似て五行の霊気を受けるため五霊脂という。
+【考証】
+寇宗奭はいう。五霊脂は経へ薬を導き、特に肝へ速く入るが血を新たに生むわけではない。目の翳が場所を変えて現れる人に血を治す薬として用い効いた。毒蛇に噛まれて意識がぼんやりした人には、五霊脂一両と雄黄半両の粉末二銭を酒で飲ませ、残りを傷に塗り、さらに二銭を飲ませて治った例も挙げる。
+李時珍はいう。足厥陰肝経の血分に入る。肝は血をつかさどり、痛みは木に、虫は風に関わるので、血を巡らせ諸痛を止め、驚癇・瘧・痢疾・積滞・痰・疳・虫・目の血の病などを治す。失笑散は女性の心痛や血痛だけでなく、男女や年齢を問わず胸腹・脇・下腹の痛み、疝気、妊娠前後の気血の痛み、子宮出血や過多月経にも使えるという。李仲南は、子宮出血には血だけでなく風を除くためで、荊芥・防風と同じ考え方だとする。李時珍は、肝血の虚滞自体が風を生む点も考えるべきだと補う。</t>
         </is>
       </c>
     </row>
@@ -18867,6 +20566,29 @@
 The historical discussion therefore emphasizes both its strong analgesic reputation and its serious toxicity. This is not an herb for self-treatment.</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>烏頭（川烏・草烏）
+【性味】辛・苦、熱。
+【毒性】強い毒性。草烏はさらに毒性が強い。
+【帰経】心経・肝経・腎経・脾経に帰する。
+【主治】祛風除湿、温経止痛。
+【名称の由来】
+［川烏］
+李時珍はいう。最初の親根は烏の頭に似るので烏頭と呼び、そこに子のように付いて育つのが附子である。川烏と草烏、白附子は区別し、古い混同を正す。
+［草烏］
+烏喙（『神農本草経』。先の二つに分かれたもの）、草烏頭・金鴉・鴛鴦菊（『本草綱目』）、土附子（『日華子本草』）、奚毒・毒公などの異名がある。苗には茛・芨・堇・独白草、汁を煮詰めた毒には射罔の名がある。呉普は二又の形が烏のくちばしに似るという。蘇恭は二又だけを烏喙とする区別に疑問を呈し、李時珍は、草烏は野生の烏頭で竹節烏頭、淮烏頭とも呼ばれ、二又のものが烏喙・両頭尖で同じ植物に属するという。附子・天雄にも二又のものがあるが別物である。草烏の汁は鳥獣を射る毒薬に使われ、古い記録の射罔や独白草の矢毒も川烏ではなく草烏を指す。
+【考証】
+［川烏］
+寇宗奭はいう。虚寒を補うには附子、風の病には天雄を多く使い、烏頭・烏喙・附子はそれぞれに応じて用いる。李時珍は王氏の『究原方』を引く。附子は重く留まり、脾を温め寒を追う。川烏頭は軽く散り、脾を温め風を除く。寒の病には附子、風の病には川烏頭を使う。中風には最初から風薬や烏附を用いず、まず気の薬を使い、後に烏附を用いるという説もある。烏附の薬は冷まして服すのがよいという。下に陰寒があり虚陽が上へ浮く場合、冷薬では陰寒が強まり、熱薬を熱いまま飲むと体が拒む。熱薬を冷まして飲めば、飲み込んだ後で冷たさは消え、熱性が働く。これは反治の妙とされる。張仲景は寒疝に蜜で煎じた烏頭、『近効方』は喉の閉塞に蜜炙した附子を口に含む方法、朱丹溪は疝気に烏頭と梔子を用いた。李杲は陰が盛んで陽が拒まれる傷寒の患者が顔と目が赤く渇き、脈が非常に速いのに押すと散る場合、姜附湯に人参を加え、半斤を服させて発汗後に治したという。
+呉綬はいう。附子は陰証の要薬で、傷寒が三陰へ移った場合や内寒を伴い、体が熱くても脈が沈む場合に用いる。手足の冷え、腹痛、細く沈む脈、重ければ唇が青く陰嚢が縮む場合は急いで用い、陰を退け陽を戻す。近ごろは陰証を疑って使うのが遅れがちだという。内外ともに陰で陽気が急に衰えたとき、人参で元を養い、附子で経を温め寒を散らすべきだと説く。
+劉完素はいう。しびれに烏頭や附子を用いるのは強い気が道を開くためで、最初はかえってしびれが増しても、薬の気が尽き正気が巡ると治る。張元素は白朮を佐薬とした附子が寒湿を除く要薬で、湿の薬に少量加えて経へ導くといい、火の源を養い陰寒を除けば排泄も整うという。虞摶は、附子は力強く、補気薬を十二経へ導いて失われた元陽を戻し、補血薬を血分へ、発散薬を体表へ、温める薬を下焦へ導くという。
+朱震亨はいう。気虚で熱が強い場合や湿の多い肥満の人には、附子や烏頭を少量添えて薬を巡らせることがある。張仲景の八味丸で附子は少陰へ導く役であり、補う主体は地黄である。附子そのものを補薬とみなすのは誤りで、滞らず下へ走る性質で地黄の滞りを動かす。烏頭・天雄を風の治療や補薬として安易に用い、人を害した例も多い。王履はこれに対し、八味丸は陽の火の不足、銭仲陽の六味地黄丸は陰虚に用いるので、附子は陽を補う薬で、単に滞りを動かすためではないという。
+王好古は、体が冷え手足が厥冷する人以外には烏附をむやみに用いるべきでなく、附子で火を補えば水を枯らす恐れがあるという。李時珍は、烏附は有毒で重い病でなければ用いないが、補薬に少量加えて導けば速効があるという。少し飲んだだけでひどく乾燥する人もいる一方、附子湯や硫黄を数年続けた痩せて冷える王族、鹿茸・附子を服して八十余歳まで健康だった武官、毎日乾姜・附子と硫黄の丸薬を用いて九十歳まで生きた役人の話もある。ほかの人なら一粒でも害になることがあり、体質の偏りを一律には扱えない。『瑣砕録』には寒さの厳しい滑台で、住民が芋や栗のように附子を食べるとある。土地の気候によるのだろう。
+［草烏］
+李時珍はいう。草烏頭や射罔は極めて毒性が強く、栽培して加工する川烏頭や附子とは異なり、難治で急な風の病でなければ軽率に使えない。甄権が生殖の力を助け腎気の衰えを治すというのも安易に信じられない。風湿を除き、頑固な痰や瘡を毒で攻める働きはあっても、川烏・附子のように命門を補うものではない。蘄州の郝知府は風癬に草烏頭と木鼈子を過量服用し、すぐに麻痺して亡くなった。王機は、烏喙の鋭い性質が経絡や関節へすばやく達し、射罔にすれば鳥獣を殺すほどだという。楊清叟は風寒湿痺、骨の冷えた痛みや古傷、陰疽などに草烏頭と南星の粉末を等量、肉桂を少量加え、生姜の汁と温めた酒で練って外用する方法を記し、皮膚の状態に応じて働くという。</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="17" customHeight="1">
       <c r="A192" s="4" t="inlineStr">
@@ -18938,6 +20660,20 @@
 Daoist texts also claimed extraordinary longevity effects, but these belong to historical folklore rather than ordinary medical practice.</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>五味子
+【性味】酸・甘、温。
+【毒性】無毒。
+【帰経】肺経・心経・腎経に帰する。
+【主治】収斂固渋、益気生津、補腎寧心。
+【名称の由来】荎藸（音は知除。『爾雅』）、玄及・会及（『名医別録』）。蘇恭は皮と果肉は甘酸、種の中は辛苦で鹹味もあり、五味が揃うため名づけられたという。
+【考証】
+成無己は肺の気を酸味で収め、芍薬や五味子で逆上する気を収めて肺を安定させるという。李杲は肺気の不足を補い、寒による逆上には乾姜と合わせると説く。熱性の咳にも使うが、外からの邪がある場合は先に発散させないと閉じ込める恐れがある。痰には半夏、喘ぎには阿膠を添える。
+寇宗奭は、華州以西で熟した赤い実を蒸して汁を濾し、薄い膏に煮詰め、蜜を加えて保存し、肺が虚寒の人に湯で飲ませると記す。一方、多食すれば虚熱を生じるため、除熱とする書との違いに迷いがあるという。朱震亨は肺気を収めることが熱を除き腎を養うことにもつながり、食べすぎによる虚熱は急な収斂のためと説明する。夕方の咳には涼薬でなく五味子や五倍子で収め下げるという。
+孫思邈は旧暦五月・六月に五味子湯を飲み、上では肺の源を潤し下では腎を補うという。実一大合を木臼で搗き、熱湯を注いで蜜を少し加え、火のそばに置いて飲む。張元素は夏に疲労が強い場合、黄耆・人参・麦門冬と少量の黄柏を合わせて元気を補うと説く。王好古は八味丸にも用いるという。王機は北方産を津液の不足や虚労の咳に、南方産を肺の風寒に使い分ける。唐慎微は『抱朴子』の長寿の伝承も引く。</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="17" customHeight="1">
       <c r="A194" s="4" t="inlineStr">
@@ -18998,6 +20734,19 @@
 Lindera Qi-Regulating Powder uses this property to regulate Qi first, on the traditional theory that once Qi moves freely, Wind-related symptoms may also resolve.
 Four Milled Herbs Decoction combines Ginseng Root, Lindera Root, Agarwood and Bin Lang for severe Qi constraint with upward rebellion and wheezing. The formula balances descending and supporting actions.
 Lindera Root was also paired with Yi Zhi Ren in Secure the Springs Pill for frequent urination attributed to deficiency-Cold, reflecting its traditional relationship with the Kidney and Bladder.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>烏薬
+【性味】辛、温。
+【毒性】無毒。
+【帰経】肺経・脾経・腎経・膀胱経に帰する。
+【主治】行気止痛、温腎散寒。
+【名称の由来】旁其（『本草拾遺』）、鳑魮・矮樟（『本草綱目』）。李時珍は黒い色で名づけられ、葉が魚に似るため俗称があり、香りが樟に似るので南方では矮樟とも呼ぶという。原文の魚と木の俗名には欠字がある。
+【考証】
+寇宗奭は、烏薬は穏やかで気を補うより滞りを外へ出す働きが強いが、激烈ではないという。沈香とともにすりつぶして湯にし、胸腹の冷えた気に用いる。
+李時珍はいう。辛温で香りが巡り、さまざまな滞りを散らす。『和剤局方』の烏薬順気散は中風などでまず気を通し、気が順になれば風も去る。厳用和の『済生方』の四磨湯は七情の鬱結や気の逆上による喘ぎに用い、人参・烏薬・沈香・檳榔をそれぞれ濃い汁七分にすり、合わせて煎じ少しずつ飲む。『朱氏集験方』の縮泉丸は虚寒の頻尿に益智子と等量を合わせ、陽明・少陰経を通じさせる。処方は益智子の項にある。</t>
         </is>
       </c>
     </row>
@@ -19066,6 +20815,20 @@
 Gao cites Ephedra Ephedra, Prepared Aconite and Asarum Decoction as an example of using Asarum Herb when an exterior pathogen coexists with a deep Shaoyin pattern.
 Shizhen emphasizes its dispersing action in Wind-Cold, Wind-Damp headache, phlegm-fluid retention and chest Qi obstruction. It was also used for certain mouth, throat and dental disorders through the traditional principle of venting constrained Heat.
 Older texts warn strongly against excessive powdered doses, recording severe respiratory distress and death after overdose. The entry therefore treats Asarum Herb as potent and dose-sensitive, not as a casual household herb.</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>細辛
+【性味】辛、温。
+【毒性】小毒。
+【帰経】肺経・腎経・心経に帰する。
+【主治】解表散寒、祛風止痛、通竅、温肺化飲。
+【名称の由来】小辛（『神農本草経』）、少辛（『山海経』）。蘇頌は華州の真正品は根が細く非常に辛いので細辛と呼ぶという。李時珍も小辛・少辛は同じ意味だとする。
+【考証】
+寇宗奭は頭や顔の風による痛みに欠かせないという。張元素は温かく非常に辛く、上昇する陽の薬で、足厥陰・少陰の血分へ入り、手少陰へ導くという。香りと味が細やかなので少陰へ入り、独活と合わせれば少陰の頭痛に優れる。ほかの経の頭痛や風にも用い、寒や水気を散らす。成無己は辛味で水気を巡らせ乾燥を潤すという。李杲は胆気の不足や、内から表へ出る邪に用い、張仲景の麻黄附子細辛湯を例にする。
+李時珍はいう。辛温の発散性により風寒・風湿の頭痛、痰飲、胸の気滞、驚癇に用いる。口や喉、歯の病では鬱した熱を散らし、咳や気の逆上には肺、胆気の不足や目の病には肝へ働き、少陰の経や耳も通す。
+寇宗奭は華陰産以外は真正品ではないといい、粉末を単独で使う場合は一銭を超えてはならず、過量で呼吸が塞がり死んだ例があるという。毒というより量を誤る危険だとして記録した。</t>
         </is>
       </c>
     </row>
@@ -19132,6 +20895,22 @@
 Because it can move Qi throughout the San Jiao, later physicians called Cyperus Rhizome a central herb for Qi disorders and especially for gynecological patterns involving constraint and pain.</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>香附（莎根・香附子）
+【性味】辛・やや苦・やや甘、平。
+【毒性】無毒。
+【帰経】肝経・脾経・三焦経に帰する。
+【主治】疏肝解鬱、理気寛中、調経止痛。
+【名称の由来】雀頭香（『唐本草』）、草附子・水香棱・水巴戟・水莎・莎結・続根草（『図経本草』）、侯莎（『爾雅』）、夫須（『名医別録』）、地毛（『広雅』）。
+李時珍はいう。『名医別録』は莎草とだけ記し、苗か根かを指定しない。後世は根を香附子と呼んで使い、莎草という名を忘れた。草は編笠や雨具になり、水をはじくので字形にも草や沙の意が含まれる。根は連なって生じ香りの材料となるため香附子といい、古くは雀頭香と呼ぶ。葉が三棱や巴戟に似て湿地に生えるので水三棱・水巴戟の名があり、雷公頭などの俗称もある。『金光明経』には月萃哆、『記事珠』には抱霊居士とある。
+【考証】
+王好古はいう。香附は膀胱や両脇の気の滞り、動悸や息切れに働く血中の気の薬である。瘀血を除きながら、炒って黒くすれば出血や子宮出血も止める。気鬱や血の病に必要な女性の妙薬だが、多用すると気を消耗する。
+朱震亨は、若い男児の尿に浸した香附は諸々の鬱を解き、気分へ薬を導き血の生成にも役立つという。古い本草は補薬としないが、年長者に益するのは気を巡らせる中に補う働きがあるからである。
+李時珍はいう。香附は平らかで寒くなく、香りが強く巡る。辛味は散らし、微苦は下げ、微甘は調和させる。肝と三焦の気分を主として十二経にも通じ、生なら上へ胸や皮膚へ、熟せば下へ肝腎や腰足へ向かう。黒く炒れば止血する。男児の尿に浸して炒れば血分に入り虚を補い、塩水なら血分を潤し、青塩なら腎気を補い、酒なら経絡を巡らせ、酢なら積滞を消し、生姜汁なら痰飲を除く。人参・白朮と合わせて補気、当帰・川芎などと合わせて補血、木香で中焦の滞り、檀香で脾気、沈香で諸気の昇降、川芎・蒼朮で諸鬱、梔子・黄連で熱、茯神で心腎、茴香・補骨脂で気の帰元、厚朴・半夏で張り、紫蘇・葱白で外邪、三棱・莪朮でしこり、艾葉で子宮の冷えた血気に働く。気の病を総括し女性の病に重要な薬である。
+韓氏は、香附は古い滞りを除き新しい巡りを生むため、女性だけでなく男性、老人や子どもにも適すると説く。人参・黄耆を臣薬、甘草を佐薬にすれば虚弱にも使えるという。黄鶴丹は香附一斤と黄連半斤を洗い干して粉にし、水糊で梧桐の実ほどに丸める。外感には葱姜湯、内傷には米のとぎ汁、気病には木香湯、血病には酒、痰病には生姜湯、火病には白湯で飲む。青囊丸は軽く炒った香附一斤と軽く炮製した烏薬五両三銭を粉にし、水と酢で煮た粉糊で丸める。頭痛には茶、痰気には生姜湯など、証に合わせて飲むという。</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="17" customHeight="1">
       <c r="A200" s="4" t="inlineStr">
@@ -19195,6 +20974,20 @@
 The historical entry therefore treats Apricot Kernel as a useful but potentially harmful medicinal seed rather than an ordinary tonic food.</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>杏仁（杏）
+【性味】苦、温。
+【毒性】小毒。
+【帰経】肺経・大腸経に帰する。
+【主治】止咳平喘、潤腸通便。
+【名称の由来】李時珍は、篆書の「杏」は木の枝に実がある姿を表し、字形を「口」や「可」と解くのは誤りという。『江南録』には楊行密が杏を甜梅と改名したとある。
+【考証】
+張元素は、杏仁は気が薄く味が濃く、濁って沈む陰の薬で手太陰に入り、肺を潤す、食積を消す、滞った気を散らすという三つの用途があるという。
+李杲はいう。杏仁は結びを散らし乾きを潤し、肺の風熱による咳を除く。喘ぎは気の病として杏仁、狂気は血の病として桃仁を用いる。どちらも便秘を治すが、気と血を分ける。昼の排便困難には気、夜の困難には血を考え、脈が浮けば杏仁・陳皮、沈めば桃仁・陳皮を用いる。虚弱者を過度に下してはならない。肺と大腸が表裏のため陳皮を添える。王好古は麻黄湯などに杏仁を用いるのは気を巡らせ肺を瀉し肌を解くためという。
+李時珍はいう。杏仁は散らし下げるので肌を解いて風を散らし、気を下げ乾きを潤し、積滞や外傷にも用いる。瘡や虫には毒性を利用する。粉を食べて積滞した兵士に杏仁を合わせた丸薬が効いた話がある。一方、道士の伝承には毎朝杏仁七粒を口でふやかして噛み、年を経れば若返るというものや、五粒を夜明け前に水に浸して噛めば五臓を潤すというものがある。しかし李時珍は杏仁は熱性で気を下げ、長期服用には向かず、噛んで唾液とともに飲み積滞を除く範囲ならよいとする。左慈の「杏丹」で長寿になるという記述は荒唐無稽として退ける。</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="17" customHeight="1">
       <c r="A202" s="4" t="inlineStr">
@@ -19252,6 +21045,18 @@
 Shizhen records a Song-dynasty case in which powdered Chuan Dipsacus Root was added to Calm the Stomach Powder for bloody dysentery.
 The same method was later passed on during an outbreak in Kuaiji and was said to have helped both adults and children.
 The anecdote reflects the broad historical use of Dipsacus Root beyond its better-known Liver-Kidney and sinew-bone indications.</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>続断
+【性味】苦・辛、微温。
+【毒性】無毒。
+【帰経】肝経・腎経に帰する。
+【主治】肝腎の虚による子宮出血、胎漏、胎動不安。
+【名称の由来】属折・竜豆（『神農本草経』）、接骨・南草（『名医別録』）。李時珍は続断・属折・接骨はいずれも骨折をつなぐ働きに由来する名だという。
+【考証】
+李時珍はいう。宋の張叔潜が剣州の長官だった時、家人の血痢に平胃散一両と川続断の粉二銭半を合わせ、一回二銭を煎じて飲ませると治った。紹興年間に会稽で痢疾が流行した際、息子がこの処方を伝え、子どもの痢疾にも効いたという。</t>
         </is>
       </c>
     </row>
@@ -19317,6 +21122,20 @@
 Its traditional use for scrofulous nodules and swellings was likewise interpreted as dispersing Fire and Heat that had condensed into masses.</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>玄参
+【性味】甘・苦・鹹、微寒。
+【毒性】無毒。
+【帰経】肺経・胃経・腎経に帰する。
+【主治】清熱涼血、滋陰降火、解毒散結。
+【名称の由来】黒参・野脂麻（『本草綱目』）、玄台・鹿腸・鬼蔵（『呉普本草』）、重台（『神農本草経』）、正馬（『名医別録』）、逐馬（『薬性論』）、馥草（『開宝本草』）。
+李時珍は「玄」は黒い色を意味し、別名の端や鹹の由来は不明という。陶弘景は茎が人参に少し似るため参と呼び、志という人は香の調合にも使うので馥草という。
+【考証】
+張元素はいう。玄参は体の気の昇降を整える薬で、清らかで濁らず、風を治す処方にもよく入る。『活人書』は傷寒の強い陽毒で汗や下剤の後も毒が散らず、心窩部が不快で眠れず、精神が乱れる場合に用いる。胸中に漂う気や根のない火を治す重要な薬である。
+李時珍はいう。腎水が傷つき真陰が保てないと陽火が根を失って病になる。水を養って火を抑えるため玄参は地黄と似る。瘰癧のしこりを散らすのも火を散らすためで、劉守真もしこりは火の病という。</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="17" customHeight="1">
       <c r="A206" s="4" t="inlineStr">
@@ -19381,6 +21200,20 @@
 These anecdotes established its reputation as one of the most important traditional pain-relieving herbs based on moving Qi and blood rather than simply numbing sensation.</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>延胡索
+【性味】辛・苦、温。
+【毒性】無毒。
+【帰経】肝経・脾経・心経に帰する。
+【主治】活血化瘀、行気止痛。
+【名称の由来】玄胡索ともいう。王好古は、宋の真宗の名を避けて玄を延に改めたという。
+【考証】
+李珣は、腎気や産後の悪露の滞り、産後の腹痛に用い、三棱・鼈甲・大黄と合わせた散剤もよく、虫食いのあるものを粉にしたものがさらによいという。
+李時珍はいう。延胡索は苦くやや辛く温かく、手足の太陰・厥陰に入り、血中の気滞と気中の血滞を巡らせるため全身の痛みに働く。ある王妃が蕎麦を食べた後で怒り、胃と胸に耐え難い痛みを生じ、薬はすべて吐き、三日便が出なかった。『雷公炮炙論』の「心痛で死にそうなら延胡を探せ」に従い、粉末三銭を温酒で飲ませると便が出て痛みが止まった。また五十余歳の華圭が痢疾の腹痛で瀕死のとき、三銭を米のとぎ汁で飲ませると痛みが半減して回復した。『泊宅編』にも全身の激痛を中風・湿・肺気と誤診された人に、延胡索・当帰・桂心を等量粉にして温酒で三～四銭ずつ飲ませ、痛みが消えた例がある。気血を巡らせる優れた薬だという。
+趙待制は、女性の月経不順、腹のしこり、妊娠前後の病、打撲、胸腹の痛みにもすぐ効くといい、温めて散らし気を巡らせ痛みを止める働きによるとする。</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="17" customHeight="1">
       <c r="A208" s="4" t="inlineStr">
@@ -19446,6 +21279,21 @@
 Historical texts also preserve longevity and travel anecdotes involving regular consumption of Coix seed, reflecting its reputation as both food and medicine.</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>薏苡仁
+【性味】甘・淡、涼。
+【毒性】無毒。
+【帰経】脾経・胃経・肺経に帰する。
+【主治】利水滲湿、健脾止瀉、除痺排膿、解毒散結。
+【名称の由来】解蠡（音は礼。『神農本草経』）、芑実（音は起。『名医別録』）、贛米（音は感。『名医別録』）、回回米（『救荒本草』）、薏珠子（『図経本草』）。
+李時珍は名の由来は不明とし、葉が蠡の葉に似て散らばり、苗が芑黍に似るので解蠡・芑実といい、硬い実は贛米と呼ぶという。苗の異名には原文に欠字があり、回回米は西番蜀秫・草珠児ともいう。
+【考証】
+寇宗奭はいう。『神農本草経』はやや寒性で筋のけいれんを治すという。ただし熱で筋が縮み伸びない場合には薏苡を用い、寒で筋が急になる場合にはさらに冷やしてはならない。穏やかな薬なので量を増やして初めて効果が出る。朱震亨は寒で筋が急、熱で短く縮み、湿では緩んで伸びると分けるが、寒湿に熱を伴うこともあり、食生活で生じる内湿が外湿の病を招くと説く。
+李時珍はいう。薏苡仁は土に属する陽明の薬で脾胃を強める。肺は脾の子なので肺痿・肺癰にも用い、筋骨の病は陽明から治すためけいれんや風痺にも使う。土は水に勝つので下痢や水腫にも働く。小続命湯では中風の筋のけいれん、遅い言葉、弦脈に加える。『後漢書』には馬援が交趾で瘴気を防ぐため薏苡を常食した話があり、『倦遊録』には疝気で腫れた辛稼軒が東壁の黄土で炒った薏苡の膏を飲み治った話もある。
+蘇頌は心肺の処方によく入るとし、肺癰や風湿・胸痺にも使われるという。『済生方』は肺の損傷による喀血に、加熱した豚肺を刻んで薏苡の粉を付け空腹時に食べると記す。薏苡が肺を補い豚肺が薬を肺経へ導き、趙君猷も効果を見たという。</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="17" customHeight="1">
       <c r="A210" s="4" t="inlineStr">
@@ -19512,6 +21360,16 @@
 The practical emphasis remains Polygonatum Odoratum Rhizome's gentle Yin-nourishing and fluid-generating action, especially for Lung and Stomach dryness.</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>玉竹（葳蕤）
+【性味】甘味、微寒性。【毒性】無毒。【帰経】肺・胃経。
+【主治】陰を養い乾燥を潤し、津液を生じて渇きを止める。
+【名称の由来】女萎、葳蕤、委萎、萎香、玉竹、地節など。李時珍は葳蕤を葉やひげが垂れる姿に由来すると説明する。光沢のある竹に似た葉と節の多い根から、玉竹・地節の名もある。古書の異表記や異名には誤写もあるという。
+【考証】李杲は昇降の両方に働き、四肢の風邪、目の涙とただれ、男性の湿による腰痛、女性の顔の黒い斑を治すという。李時珍は柔らかく潤う甘味の薬とし、『南陽活人書』の葳蕤湯では風温による自汗、体の重さ、言葉の出にくさに主薬として使うと記す。自身も虚労による寒熱や諸虚に人参・黄耆の代わりに用い、寒にも燥にも偏らない効を評価する。陳蔵器は青粘を葳蕤と同一視し、樊阿が華佗から聞いて長く服用した伝承や、嵇紹の寒疾に効いた話を挙げる。蘇頌は同一視に慎重で、李時珍は黄精と葳蕤の別名・性味が近いため、青粘の比定には議論があるとする。
+【古典での異説】陳蔵器は『魏志・樊阿伝』の青粘を葳蕤とし、漆の葉と合わせて散剤とする古い伝承や、肌を潤し腰脚を温めるという記述を紹介する。ただし熱のある者には使わないとも記す。蘇頌は青粘を葳蕤と断定できないとし、黄精とみる説もある。李時珍は黄精と葳蕤の性味・用途が近く、青粘には黄芝と地節という両方に通じる別名があることから、古書で両者が通用した可能性を述べる。</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="17" customHeight="1">
       <c r="A212" s="4" t="inlineStr">
@@ -19573,6 +21431,15 @@
 Polygala Root was therefore used for forgetfulness, poor concentration and disturbance of the Heart-Kidney relationship.
 Older texts also record Polygala Root wine for deep sores and abscesses, interpreting the effect through its strengthening and opening qualities.
 Daoist writings credited extremely long-term use with extraordinary memory and longevity; these stories are part of historical folklore rather than clinical evidence.</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>遠志
+【性味】苦味・辛味、温性。【毒性】無毒。【帰経】心・腎・肺経。
+【主治】心を安め知恵を益し、心と腎を通じさせ、痰を除き腫れを消す。
+【名称の由来】苗は小草・細草・棘菀など。李時珍は、志を強めることから遠志と名づけられたという。『世説』の遠志と小草の逸話、『記事珠』の醒心杖という名も挙げる。
+【考証】王好古は腎経の気分の薬とする。李時珍は特に足少陰腎経に入り、志と精を益して物忘れを治すと説く。腎の精気が不足すると志が心に通じず、健忘が生じるという『霊枢』の記述を引く。陳言の遠志酒は癰疽に効くとされ、その働きも腎を補うことに由来すると考える。葛洪の『抱朴子』には陵陽子仲が二十年服用し、見た書物を忘れなくなったという伝承が載る。</t>
         </is>
       </c>
     </row>
@@ -19642,6 +21509,16 @@
 He cautions that prolonged excessive use can over-drain fluids, prevent clear Qi from rising and consume true Yin.</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>沢瀉
+【性味】甘味・淡味、寒性。【毒性】無毒。【帰経】腎・膀胱経。
+【主治】尿を出し、湿熱を清め、腎の濁りを瀉す。
+【名称の由来】水瀉、鵠瀉、及瀉、蕍、芒芋、禹孫。李時珍は沢の水を排出する意、禹が治水した故事からの名と説く。
+【考証】蘇頌は『素問』、深師方、張仲景の沢瀉湯や五苓散を挙げ、停滞した水を巡らせる要薬とする。張元素は腎経の湿と小便の淋瀝を治すというが、原文は「これらの病がない者が服むと目が…」で途切れる。寇宗奭は五苓散での利水を重視し、多服で尿が増え眼を病むとの伝えを挙げる。王好古は、停滞水を除けば目が明らかになる一方、過剰な排尿で腎気が虚すれば目がかすむと両説を説明する。王履は八味丸の沢瀉は単なる導引ではなく、補薬と組むことで腎邪を瀉し虚損を補うと論じる。李時珍は、脾胃の湿熱による頭重・目のかすみ・耳鳴りは湿を除けば改善するが、久服すれば陰と清気を損なうと戒める。地黄丸の茯苓と沢瀉は膀胱の邪気を除いて補薬を助けるために配合されるという。
+【古典での議論】寇宗奭は八味丸の沢瀉を桂・附子などを腎経へ導くためと考えたが、王履は地黄、山茱萸、茯苓、牡丹皮、附子、官桂はそれぞれすでに腎に働くため、単なる案内役ではないと反論した。李時珍も、茯苓・沢瀉が膀胱の邪気を除くことで補薬が力を発揮すると説明する。『本経』の「久服すれば目が明らかになる」と扁鵲の「多服すれば目がかすむ」は、湿を除く効果と長期の過度な利尿という条件の違いであると論じる。</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="17" customHeight="1">
       <c r="A216" s="4" t="inlineStr">
@@ -19710,6 +21587,15 @@
 Older obstetric texts sometimes used Mature Bitter Orange late in pregnancy to regulate Qi, but other physicians warned that weakening Qi could be harmful in deficient patients. The debate illustrates the importance of constitution and pattern rather than routine use.</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>枳殻（枳）
+【性味】苦味・辛味・酸味、微寒性。【毒性】無毒。【帰経】脾・胃・大腸経。
+【主治】気を巡らせ張りを消し、中焦を広げてつかえを除き、痰と食滞を消す。
+【名称の由来】枳実・枳殻。寇宗奭は同じ植物の実で、小さい枳実は作用が強く速く、大きい枳殻は穏やかで緩いと説く。張仲景は急性の病に枳実を用い、気の滞りを導く処方には枳殻を用いる。蘇恭は枳実という名に対し核や果肉を含まない用法を疑問視した。李時珍は、枳は木の名、実はその果実を指し、未熟な実は皮が厚く中が詰まり、熟した実は殻が薄く中が空くと説明する。後世に別品目としたり、名を「結実を破る」意味と解したりするのは正確とは限らない。
+【考証】張元素は気を散らし湿と痰を除き、肺から大腸へ働くが、多用すれば胸中の気を損なうため二、三服にとどめるという。原文のその後には欠落がある。李杲は気血の弱い者には気を損なうため用いないとする。王好古は枳殻は胸膈など上部の気、枳実は心腹・脾胃など下部の血に主として働くと説く。ただし双方とも気を通して痰喘・痞満・刺痛・後重を除き、実際の処方では上と下を厳密に分けない例もある。湖陽公の方では枳殻四両・甘草二両を粉末にし、毎服一銭を白湯で飲む。妊娠期に用いれば出産を容易にするという説があり、束胎丸もあるが、寇宗奭は胎児と母体の力を弱めるおそれを指摘する。李時珍は気が盛んで滞る妊婦には適しても、気虚なら避けるべきと論じる。朱震亨は、座りがちで肥満の妹の難産には気を削る処方でなく紫蘇飲に補気薬を加え、十数服で出産できた例を挙げる。</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="17" customHeight="1">
       <c r="A218" s="4" t="inlineStr">
@@ -19771,6 +21657,15 @@
 Gao also distinguishes thirst with upper-jiao Lung Heat from lower-jiao deficiency of true Water, explaining that the therapeutic approach differs according to the level of the disorder.
 Shizhen emphasizes Anemarrhena Rhizome's dual direction: upward it clears Lung Fire, while downward it nourishes Kidney Yin and relieves dryness.
 He frequently pairs it conceptually with Huang Bai, with Anemarrhena Rhizome acting more on the Qi level and Huang Bai more on the blood level of the Kidney system.</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>知母
+【性味】苦味・甘味、寒性。【毒性】無毒。【帰経】肺・胃・腎経。
+【主治】熱と火を清め、陰を養い乾燥を潤す。
+【名称の由来】連母、貨母、地参、水参、苦心、児草など。古書には欠字を含む多くの異名がある。李時珍は宿根の脇に生じる子根の形から名が転じたと説く。
+【考証】甄権は虚による口渇を伴う熱労に加えるという。李杲は足陽明・手太陰に入り、腎の根のない火を瀉し、自汗を伴う骨蒸熱、虚労熱を治し、陰の源を滋すとする。白虎湯では石膏を主とし知母の苦寒で熱を清め、甘草・粳米で急な下降を緩める。上焦の肺熱による口渇と尿閉には薄味の薬で肺火を清め、下焦の陰不足で渇きのない尿閉には黄柏・知母で腎と膀胱を助けると区別する。李時珍は知母を肺・腎の気分の薬とし、下では腎の燥を潤し上では肺火を清める。黄柏は腎の血分の薬であり、両者を併用する意味を述べる。</t>
         </is>
       </c>
     </row>
@@ -19841,6 +21736,15 @@
 The herb is therefore best understood as a strong regulator of Qi and accumulation whose overall effect depends on the surrounding formula.</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>枳実（枳）
+【性味】苦味・辛味・酸味、微寒性。【毒性】無毒。【帰経】脾・胃・大腸経。
+【主治】気を強く巡らせ積滞を消し、痰を除いて痞えを散らす。
+【名称の由来】枳実・枳殻。寇宗奭は同じ植物の実で、小さい枳実は作用が強く速く、大きい枳殻は穏やかで緩いと説く。張仲景は急性の病に枳実を用い、気の滞りを導く処方には枳殻を用いる。蘇恭は枳実という名に対し核や果肉を含まない用法を疑問視した。李時珍は、枳は木の名、実はその果実を指し、未熟な実は皮が厚く中が詰まり、熟した実は殻が薄く中が空くと説明する。後世に別品目としたり、名を「結実を破る」意味と解したりするのは正確とは限らない。
+【考証】朱震亨は痰を瀉し、気を破って通路を開く強い薬とする。張元素は心下の痞えや宿食に黄連と合わせる。李杲は蜜で炙れば水の積を破り、気を瀉して内熱を除くとし、張潔古は脾経の積血を除くという。王好古は気を益するには人参・白朮・乾姜、気の滞りを破るには大黄・牽牛子・芒硝と合わせると説く。湿には白朮、痞えには枳実が必要として枳朮丸を紹介する。張仲景の枳実白朮湯は水飲による盤のような心下の硬い腫れに用い、枳実七枚・白朮三両を水一斗で三升に煎じ三回に分けて服む。腹が柔らかくなれば消散したとする。</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="17" customHeight="1">
       <c r="A222" s="4" t="inlineStr">
@@ -19909,6 +21813,15 @@
 Gardenia Fruit also appears in traditional formulas for jaundice and dark, difficult urination when Damp-Heat is present.</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>山梔子（梔子）
+【性味】苦味、寒性。【毒性】無毒。【帰経】心・肺・三焦経。
+【主治】肺熱を清め、肌表の湿熱を散らし、血を冷やして毒を解く。
+【名称の由来】木丹、越桃、鮮支。花は薝蔔ともいう。李時珍は酒器の卮に形が似るため名づけられたと説き、花の呼び名について異説も挙げる。
+【考証】張元素は形と色から肺火を瀉すとし、心経の客熱、煩躁、上焦の虚熱、風を除く四つの働きを挙げる。朱震亨は三焦と痞塊の火を瀉し、とくに胃脘の血熱を清め、火を下げて尿とともに排すという。王好古は、張仲景が嘔吐を促す処方に用いたのは上部の邪が食を拒む場合であり、梔子自体が常に催吐薬なのではないと説く。尿への作用も肺を清めて気化を促すためとする。梔子豉湯の煩躁について、李杲は赤く苦い梔子が心に入り、黒く鹹い香豉が腎に入ると説明する。寇宗奭は傷寒の発汗・吐下の後、虚煩で眠れない場合の梔子豉湯を挙げる。胃の虚熱や心経の留熱にも用い、尿が赤く渋るときは皮を除いた煨梔子・大黄・連翹・炙甘草を等量粉末にし三銭を水煎すると記す。黄疸には茵陳・甘草・香豉と合わせ、大病後の労復にも用いる例がある。</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="17" customHeight="1">
       <c r="A224" s="4" t="inlineStr">
@@ -19963,6 +21876,15 @@
 The surviving source entry contains no separate commentary beyond the basic description.
 Its traditional medicinal identity is therefore defined mainly by its sweet, slightly cold nature and its use for Heat-phlegm, irritability and nausea or vomiting.
 Later formulas commonly rely on its gentle cooling quality when phlegm and Heat disturb the Stomach, Heart or Gallbladder.</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>竹茹（竹）
+【性味】甘味、微寒性。【毒性】無毒。【帰経】肺・胃・心・胆経。
+【主治】熱を清め痰を除き、煩わしさと嘔吐を止める。
+【名称の由来】李時珍は「竹」の字が竹の形を表すといい、『説文』の「冬に生える草」および『竹譜』の「草でも木でもなく、節を持つ植物」という説明を引く。
+【考証】原文に記載なし。</t>
         </is>
       </c>
     </row>
@@ -20028,6 +21950,15 @@
 Its light, cooling nature explains its traditional use when Heat irritates the Heart and Stomach while fluids are being consumed.</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>竹葉（竹）
+【性味】甘味・淡味、寒性。【毒性】無毒。【帰経】心・胃・小腸経。
+【主治】熱と火を清め、煩わしさを除き、津液を生じて尿を通す。
+【名称の由来】李時珍は「竹」の字が竹の形を表すといい、『説文』と『竹譜』の説明を引く。草でも木でもなく、節を持つ植物とされる。
+【考証】陶弘景は甘竹の葉が最もよいという。孟詵は薬用できる竹葉の種類を限り、淡竹を第一、甘竹を次とする。寇宗奭は竹の筍がみな微寒性なので葉も同様とし、張仲景の竹葉湯には淡竹だけを使うと記す。張元素は苦味・平性で陰の中にわずかな陽を備えるという。李杲は辛苦で寒、昇降両方に働き、新旧の風邪による煩熱を除き、喘促を止めるという。末尾は原文が途切れている。</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="17" customHeight="1">
       <c r="A228" s="4" t="inlineStr">
@@ -20084,6 +22015,15 @@
 The surviving source entry contains no separate commentary section beyond the naming explanation.
 Its medicinal identity is therefore summarized by its warm, moistening and downward-directing action on the Lung.
 Unlike strongly drying phlegm herbs, Aster Root was valued for chronic cough in which phlegm coexisted with Lung dryness or deficiency.</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>紫苑（紫菀）
+【性味】辛味・苦味、温性。【毒性】無毒。【帰経】肺経。
+【主治】肺を潤して気を下ろし、痰を除いて咳を止める。
+【名称の由来】青菀、紫蒨、返魂草、夜牽牛。李時珍は紫色で柔らかくしなやかな根から名づけられたという。『説文』には茈菀とあり、『斗門方』には返魂草とある。
+【考証】原文に記載なし。</t>
         </is>
       </c>
     </row>
@@ -21909,6 +23849,25 @@
 Platycodon Root disperses Lung Qi and guides the formula upward, also addressing chronic cough associated with Lung Deficiency.</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>参苓白朮散
+【出典】『太平恵民和剤局方』
+【効能】気を補って脾を整え、湿を排して下痢を止める
+【主治】脾虚湿盛
+【構成】
+君：人参 五銭、茯苓 五銭、白朮 五銭
+臣：山薬 五銭、蓮子 三銭、扁豆 三銭、薏苡仁 七銭
+佐：縮砂 二銭、桔梗 二銭
+使：甘草 二銭
+【配伍】
+人参・白朮・茯苓・炙甘草：四君子湯を構成し、気と脾を補って脾虚の根本に働く。
+山薬・蓮子：脾と気を補い、腸を固めて下痢を止める。
+扁豆・薏苡仁：脾を整えて湿を排す。
+縮砂：芳香で脾を働かせ、気と胃を整えて補薬による胃の重さを防ぐ。
+桔梗：肺気を巡らせ、薬の働きを上へ導き、長引く咳にも用いる。</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -21978,6 +23937,26 @@
 Prepared Licorice Root, Fresh Ginger and Jujube harmonize the Spleen and Stomach, support Qi and harmonize the ingredients.</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>藿香正気散
+【出典】『太平恵民和剤局方』
+【効能】表の寒を解き、湿を除いて中焦を整え、気を巡らせて嘔吐を鎮める
+【主治】外感風寒・内傷湿滞
+【構成】
+君：藿香 五銭
+臣：蘇葉 三銭、白芷 三銭、半夏 四銭、厚朴 四銭
+佐：白朮 四銭、蒼朮 四銭、陳皮 三銭、茯苓 五銭、大腹皮 五銭、桔梗 二銭
+使：甘草 二銭、生姜 二銭、大棗 二銭
+【配伍】
+藿香：芳香で湿を除き、胃を整えて吐き気を鎮め、表の寒も散らす。
+蘇葉・白芷：風寒を散らし、湿と濁りを除く。
+陳皮・半夏・厚朴・大腹皮：気を巡らせて湿を乾かし、腹の張りと嘔吐を和らげる。
+白朮・蒼朮・茯苓：脾を整えて湿を除き、下痢を止める。
+桔梗：肺気を巡らせ、薬を上へ導く。
+炙甘草・生姜・大棗：脾胃と気を養い、諸薬を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -22047,6 +24026,26 @@
 Jujube and prepared Licorice Root support Qi and the Spleen, harmonize the formula and help nourish blood.</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>当帰四逆湯
+【出典】『傷寒論』
+【効能】経絡を温めて寒を散らし、血を養って脈を通す
+【主治】寒凝心脈
+【構成】
+君：当帰 四銭
+臣：桂枝 三銭、白芍 三銭
+佐：細辛 一銭、木通 二銭
+使：甘草 二銭、大棗 二銭
+【配伍】
+当帰：血を養って整え、経脈に潤いを与える。
+桂枝：経脈を温め、陽気を巡らせる。
+白芍：血と陰を養い、ひきつれと痛みを緩める。
+細辛：深い寒を温めて散らす。
+木通：経脈を通し、寒邪の排出を助ける。
+大棗・炙甘草：気と脾を養い、諸薬を調和して血を補う。</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -22110,6 +24109,24 @@
 Akebia Stem clears Heart fire and promotes urination, guiding Heat out through urine.
 Bamboo Leaf clears the Heart, eases restlessness and promotes urination.
 The tip of raw Licorice Root clears Heat and soothes urinary pain while harmonizing the ingredients.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>導赤散
+【出典】『小児薬証直訣』
+【効能】心火を清め、水を巡らせて陰を養う
+【主治】心火亢盛
+【構成】
+君：生地黄 二銭、木通 二銭
+臣：竹葉 二銭
+佐：甘草 二銭
+使：
+【配伍】
+生地黄：血を冷やし、陰を養って心火を抑える。
+木通：心火を清め、利尿によって熱を排す。
+竹葉：心の熱といらだちを除き、水の排出を助ける。
+生甘草：熱を清めて痛みを和らげ、諸薬を調和させる。</t>
         </is>
       </c>
     </row>
@@ -22183,6 +24200,27 @@
 Licorice Root and Fresh Ginger harmonize the ingredients and temper the toxicity of Bile-Processed Arisaema and Pinellia Rhizome.</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>滌痰湯
+【出典】『太医院経験奇効良方大全』
+【効能】痰を除いて意識を明らかにし、気を補って正気を支える
+【主治】痰迷心竅
+【構成】
+君：半夏 二銭五分、胆南星 二銭五分
+臣：枳実 二銭、陳皮 一銭五分
+佐：竹茹 一銭、茯苓 二銭、石菖蒲 一銭、人参 一銭
+使：生姜 一銭、甘草 一銭
+【配伍】
+半夏・陳皮：湿と痰を除き、気と胃を整える。
+胆南星：熱を清めて痰を除き、半夏を助ける。
+枳実・竹茹：熱と痰を清め、気の停滞を解く。
+石菖蒲：痰を除いて意識を明らかにし、心と腎を調和させる。
+茯苓：脾を整え湿を排し、痰の生じる元を抑える。
+人参：気と正気を補う。
+甘草・生姜：諸薬と胃を整え、胆南星と半夏の毒性を和らげる。</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -22254,6 +24292,27 @@
 Prepared Licorice Root, Fresh Ginger and Jujube support the middle, harmonize the formula and temper Pinellia Rhizome.</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>養心湯
+【出典】『仁斎直指方論』
+【効能】気と血を補い、心を養って精神を落ち着かせる
+【主治】心気虚
+【構成】
+君：黄耆 五銭、人参 三銭
+臣：当帰 五銭、茯神 五銭、茯苓 五銭
+佐：酸棗仁 三銭、柏子仁 三銭、遠志 三銭、五味子 三銭、川芎 五銭、半夏 五銭、肉桂 三銭
+使：甘草 四銭、生姜 一銭、大棗 一銭
+【配伍】
+人参・黄耆：心気と元気を補う。
+当帰・川芎：血と営を養い、気血の巡りを支える。
+茯苓・茯神：脾を整え、心を鎮めて動悸を和らげる。
+酸棗仁・柏子仁・遠志・五味子：心を養い、汗を収めて精神を落ち着かせる。
+半夏：胃を整えて痰を除き、補薬による滞りを防ぐ。
+肉桂：少量で温め、心陽の働きを助ける。
+炙甘草・生姜・大棗：気と胃を養い、諸薬を調和し、半夏の毒性を和らげる。</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -22325,6 +24384,27 @@
 The envoy herb harmonizes the ingredients.</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>血府逐瘀湯
+【出典】『医林改錯』
+【効能】血を巡らせて瘀血を除き、気を通して痛みを鎮める
+【主治】心脈瘀阻
+【構成】
+君：桃仁 四銭、紅花 三銭
+臣：赤芍 二銭、川芎 二銭、牛膝 三銭
+佐：当帰 三銭、生地黄 三銭、桔梗 二銭、枳殻 三銭、柴胡 一銭
+使：甘草 二銭
+【配伍】
+桃仁・紅花：胸に滞った瘀血を動かし、刺すような痛みに働く。
+川芎・赤芍：血と気を巡らせ、胸や脇の痛みを和らげる。
+牛膝：瘀血を下へ導き、胸の滞りを除く。
+柴胡・枳殻：肝気を巡らせ、胸を開く。気の滞りが解ければ血も巡る。
+桔梗：肺気を開き、薬を胸へ導く。牛膝と上下から気血を巡らせる。
+当帰・生地黄：血を養い、瘀血を除きながら新しい血と陰を傷めない。
+甘草：諸薬を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -22396,6 +24476,27 @@
 Platycodon Root guides the formula upward toward the Heart channel.</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>天王補心丹
+【出典】『金匱要略』
+【効能】陰と血を養い、心を補って精神を落ち着かせる
+【主治】心陰虚
+【構成】
+君：生地黄 四両
+臣：天門冬 一両、麦門冬 一両、酸棗仁 一両、柏子仁 一両、当帰 一両
+佐：人参 五銭、茯苓 五銭、玄参 五銭、丹参 五銭、遠志 五銭、五味子 五銭
+使：桔梗 五銭
+【配伍】
+生地黄：多く用いて陰と血を養い、心火を清め、心と腎を補う。
+天門冬・麦門冬・玄参：陰と津液を養い、虚熱を抑えて乾燥を潤す。
+当帰・丹参：血を養って巡らせ、心を鎮める。
+人参・茯苓：気を補い、心を落ち着かせる。
+酸棗仁・柏子仁・五味子：心を養って汗を収め、精神を鎮める。
+遠志：心と腎を調和させる。
+桔梗：薬の働きを上へ導く。</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -22455,6 +24556,22 @@
 [How the ingredients work together]
 Cinnamon Twig warms Heart Yang, calms rising Qi and warms the channels and vessels.
 Prepared Licorice Root supports Qi and the middle, relaxes urgency and nourishes the Heart.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>桂枝甘草湯
+【出典】『傷寒論』
+【効能】心陽と気を温め補い、動悸を鎮める
+【主治】心陽虚
+【構成】
+君：桂枝 四銭
+臣：甘草 二銭
+佐：
+使：
+【配伍】
+桂枝：心陽を温めて巡らせ、逆上する気を下ろし、経脈を通す。
+炙甘草：気と中焦を補い、心を養って緊張を緩める。</t>
         </is>
       </c>
     </row>
@@ -22532,6 +24649,27 @@
 Jujube supports Qi and the middle and harmonizes the Spleen and Stomach.</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>黄連温胆湯
+【出典】『備急千金要方』
+【効能】熱と痰を清め、中焦と心を整える
+【主治】痰火擾心
+【構成】
+君：黄連 三銭
+臣：半夏 四銭、竹茹 五銭
+佐：陳皮 四銭、枳実 四銭、茯苓 四銭
+使：甘草 二銭、生姜 一銭、大棗 一銭
+【配伍】
+黄連：心火と湿熱を清め、痰火に働く。
+半夏：湿を乾かして痰を除く。
+竹茹：熱と痰を清め、いらだちを鎮める。
+陳皮：気を巡らせて痰を除く。
+枳実：気のつかえを解き、痰を下へ導く。
+茯苓：脾を整え湿を排し、痰の生じる元を抑える。
+甘草・生姜・大棗：諸薬と脾胃を調和し、吐き気を和らげる。</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -22603,6 +24741,27 @@
 Prepared Licorice Root, Fresh Ginger and Jujube support the middle and harmonize the ingredients, helping the Spleen and Stomach produce Qi and blood.</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>帰脾湯
+【出典】『厳氏済生方』
+【効能】気と血を補い、脾と心を養う
+【主治】心脾両虚
+【構成】
+君：黄耆 一両、人参 五銭
+臣：竜眼 五銭、白朮 五銭、当帰 五銭、酸棗仁 六銭
+佐：茯神 五銭、遠志 三銭、木香 二銭
+使：甘草 二銭、生姜 一銭、大棗 一銭
+【配伍】
+黄耆・人参：脾気を大いに補い、気から血を生み出す。
+当帰・竜眼：血と心を養い、精神を落ち着かせる。
+白朮：脾を整える。
+酸棗仁・茯神：心を鎮める。
+遠志：心と腎を調和し、精神を落ち着かせる。
+木香：気と脾を巡らせ、補薬が胃に滞るのを防ぐ。
+炙甘草・生姜・大棗：気と胃を養い、諸薬を調和して気血の生成を助ける。</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -22670,6 +24829,26 @@
 Fresh Rehmannia Root and Chinese Angelica Root nourish Yin and blood to offset the drying nature of the bitter, cooling herbs.
 Bupleurum Root frees constrained Liver Qi and guides the formula toward the Liver and Gallbladder channels.
 Raw Licorice Root clears Heat, harmonizes the formula and protects the Stomach.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>竜胆瀉肝湯
+【出典】『蘭室秘蔵』
+【効能】肝胆の強い火を清め、肝経の湿熱を排す
+【主治】肝火上炎
+【構成】
+君：竜胆草 二銭
+臣：黄芩 三銭、山梔子 三銭
+佐：沢瀉 四銭、木通 三銭、車前子 三銭、当帰 三銭、生地黄 六銭、柴胡 三銭
+使：甘草 二銭
+【配伍】
+竜胆草：強い苦寒の性質で肝胆の火と下焦の湿熱を清める。
+黄芩・山梔子：熱と湿を除き、竜胆草を助ける。
+沢瀉・木通・車前子：湿熱を尿とともに排す。
+生地黄・当帰：陰と血を養い、苦寒の薬による消耗を防ぐ。
+柴胡：肝気を巡らせ、薬を肝経へ導く。
+生甘草：熱を清め、諸薬と胃を調和させる。</t>
         </is>
       </c>
     </row>
@@ -22743,6 +24922,27 @@
 Fresh Ginger disperses Cold and harmonizes the Stomach.</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>暖肝煎
+【出典】『景岳全書』
+【効能】肝と腎を温め補い、気を巡らせて寒を散らす
+【主治】寒滞肝脈
+【構成】
+君：肉桂 一銭、茴香 二銭
+臣：当帰 二銭、枸杞子 三銭
+佐：烏薬 二銭、茯苓 二銭、沈香 一銭
+使：生姜 一銭
+【配伍】
+肉桂：腎と肝を温め、寒と痛みを除く。
+茴香：肝を温めて気を巡らせ、寒による下腹部や精巣の痛みに用いる。
+当帰・枸杞子：血と肝を養い、肝腎を補う。
+烏薬：気を巡らせて寒と痛みを除く。
+沈香：気を下ろし、肝を温めて痛みを和らげる。
+茯苓：脾を整え湿を排す。
+生姜：寒を散らし、胃を整える。</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -22811,6 +25011,26 @@
 Prepared Licorice Root harmonizes the ingredients; together with White Peony Root, it eases spasms and pain.</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>柴胡疏肝散
+【出典】『景岳全書』
+【効能】肝気の鬱滞を解き、気を巡らせて痛みを鎮める
+【主治】肝気鬱結
+【構成】
+君：柴胡 二銭
+臣：香附 一銭五分、川芎 一銭五分
+佐：陳皮 二銭、枳殻 一銭五分、白芍 一銭五分
+使：甘草 五分
+【配伍】
+柴胡：肝気の鬱滞を解き、気の流れを整える。
+香附：肝気を巡らせ、痛みを鎮める。
+川芎：気と血を巡らせ、経絡の痛みを和らげる。
+枳殻・陳皮：気の滞りを解き、胸と腹の張りを鎮める。
+白芍：肝を柔らかくし、陰と営を養って気を巡らせる薬の消耗を防ぐ。
+炙甘草：諸薬を調和し、白芍とともにひきつれと痛みを緩める。</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -22874,6 +25094,24 @@
 Chinese Angelica Root nourishes Liver blood and moves blood, providing nourishment without causing stagnation.
 White Peony Root nourishes blood and Yin, softens the Liver and nourishes the sinews.
 Sichuan Lovage Rhizome moves Qi and blood through the channels so blood can be nourished without becoming stagnant.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>四物湯
+【出典】『太平恵民和剤局方』
+【効能】血を補い、血の巡りを整える
+【主治】肝血虚
+【構成】
+君：熟地黄 四銭
+臣：当帰 三銭
+佐：白芍 三銭、川芎 二銭
+使：
+【配伍】
+熟地黄：陰と血を養い、精と髄を補う。
+当帰：血と肝を養い、血を巡らせて月経を整える。
+白芍：血と陰を養い、肝と筋を柔らかくする。
+川芎：気と血を巡らせ、補薬が滞るのを防ぐ。</t>
         </is>
       </c>
     </row>
@@ -22953,6 +25191,27 @@
 Licorice Root harmonizes the ingredients, eases spasms and tempers the stronger blood-moving herbs.</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>膈下逐瘀湯
+【出典】『医林改錯』
+【効能】血を巡らせて瘀血を除き、気を通して痛みを鎮める
+【主治】肝血瘀滞
+【構成】
+君：当帰 三銭、川芎 二銭、赤芍 二銭
+臣：桃仁 三銭、紅花 三銭、五霊脂 二銭、丹皮 二銭
+佐：香附 一銭、烏薬 二銭、枳殻 一銭、延胡索 一銭
+使：甘草 三銭
+【配伍】
+桃仁・紅花：血を巡らせ瘀血を除く。
+五霊脂：胸腹の瘀血を散らし、痛みを鎮める。
+当帰・川芎：血を養いながら巡らせる。
+赤芍・丹皮：血の熱と瘀血を除く。
+香附・烏薬・枳殻：気を巡らせ、膈下の寒と滞りを和らげる。
+延胡索：気血を巡らせて痛みを鎮める。
+甘草：諸薬を調和し、強い駆瘀の働きを緩める。</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -23018,6 +25277,25 @@
 Chinese Angelica Root nourishes blood, softens the Liver and nourishes the channels.
 Adenophora Root and Ophiopogon Tuber nourish Yin, generate fluids and moisten the Lung and Stomach.
 Sichuan Chinaberry Fruit clears Heat, moves Liver Qi and eases pain without depleting Yin.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>一貫煎
+【出典】『柳州医話』
+【効能】陰を養い、肝気を巡らせる
+【主治】肝陰虚
+【構成】
+君：生地黄 一両
+臣：枸杞子 六銭、沙参 三銭、麦門冬 三銭、当帰 三銭
+佐：川楝子 一銭五分
+使：
+【配伍】
+生地黄：多く用いて陰と血を養い、肝腎を補う。
+枸杞子：肝と腎の陰と精を養う。
+当帰：血を養い、肝と経脈を柔らかくする。
+沙参・麦門冬：陰と津液を養い、肺と胃を潤して肝を支える。
+川楝子：肝気を巡らせ、熱と痛みを除きながら陰を傷めない。</t>
         </is>
       </c>
     </row>
@@ -23091,6 +25369,26 @@
 Prepared Licorice Root and Fresh Ginger harmonize the formula, harmonize the Stomach and temper Pinellia Rhizome.</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>釣藤散
+【出典】『普済本事方』
+【効能】肝を鎮めて風を抑え、熱と痰を除き、気と陰を養う
+【主治】肝陽上亢
+【構成】
+君：釣藤鈎 三銭、菊花 三銭
+臣：防風 三銭、石膏 三銭
+佐：茯苓 三銭、半夏 三銭、陳皮 三銭、人参 三銭
+使：甘草 三銭、生姜 二銭
+【配伍】
+釣藤鈎・菊花：肝の亢ぶりと風を抑え、頭と目を清める。
+石膏：熱と火を清め、いらだちやめまいを和らげる。
+防風：風を除き、薬の働きを上へ導く。
+半夏・陳皮・茯苓：湿と痰を除き、胃を整える。
+人参：気を補い、正気を支える。
+炙甘草・生姜：諸薬と胃を調和し、吐き気を和らげる。</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -23160,6 +25458,26 @@
 Prepared Licorice Root supports Qi, harmonizes the ingredients and works with White Peony Root to ease pain.</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>逍遥散
+【出典】『太平恵民和剤局方』
+【効能】肝気の鬱滞を解き、血と脾を養う
+【主治】肝脾不和（肝鬱脾虚）
+【構成】
+君：柴胡 三銭
+臣：当帰 三銭、白芍 三銭
+佐：白朮 三銭、茯苓 三銭、生姜 一銭、薄荷 一銭
+使：甘草 一銭
+【配伍】
+柴胡：肝気の滞りを解く。
+当帰・白芍：血を養って肝を柔らかくし、鬱滞から生じる熱による陰の消耗を防ぐ。
+白朮・茯苓：脾を整えて湿を除く。
+生姜：胃と気血を整える。
+薄荷：柴胡を助け、肝の鬱滞と熱を散らす。
+炙甘草：気と中焦を補い、諸薬を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -23229,6 +25547,26 @@
 Prepared Licorice Root supports Qi, harmonizes the middle and brings the ingredients together.</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>人参蛤蚧散
+【出典】『博済方』
+【効能】肺と腎を補い、気を納めて喘ぎと咳を鎮め、痰を除く
+【主治】腎不納気
+【構成】
+君：蛤蚧 五銭、人参 四銭
+臣：知母 三銭、貝母 三銭、桑白皮 三銭
+佐：茯苓 四銭、杏仁 四銭
+使：甘草 三銭
+【配伍】
+蛤蚧：肺と腎を補い、気を納めて喘ぎと咳を鎮める。
+人参：元気と肺気を大いに補う。
+杏仁・貝母：肺を潤して痰を除き、気と咳を鎮める。
+桑白皮・知母：肺熱を清め、乾燥を潤す。
+茯苓：脾を整え湿を排し、痰の生じる元を抑える。
+炙甘草：気と中焦を養い、諸薬を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -23298,6 +25636,26 @@
 Poria strengthens the Spleen, drains Dampness and supports Chinese Yam.</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>六味地黄丸
+【出典】『小児薬証直訣』
+【効能】陰を養って腎を補う
+【主治】腎陰虚
+【構成】
+君：熟地黄 八銭
+臣：山茱萸 四銭、山薬 四銭
+佐：沢瀉 三銭、茯苓 三銭、丹皮 三銭
+使：
+【配伍】
+熟地黄：多く用いて陰と腎を養い、精と髄を補う。
+山茱萸：肝腎を補い、精を収める。
+山薬：脾と腎を補い、下焦を固める。
+沢瀉：腎に滞る濁りを排し、熟地黄の重さを和らげる。
+丹皮：虚熱を清め、血の熱を除く。
+茯苓：脾を整えて湿を排す。</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -23359,6 +25717,23 @@
 Prepared Aconite Root and Cinnamon Twig warm Kidney Yang and encourage the Kidney's Qi-transforming function.
 Prepared Rehmannia Root, Cornus Fruit and Chinese Yam nourish Kidney Yin, supporting Yang through Yin.
 Moutan Cortex, Poria and Alisma Rhizome drain turbidity, clear Heat and move fluids, balancing the rich tonics.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>金匱腎気丸
+【出典】『金匱要略』
+【効能】腎陽を温め補い、水の代謝を促す
+【主治】腎陽虚
+【構成】
+君：附子 二銭、桂枝 三銭
+臣：熟地黄 一銭、山茱萸 四銭、山薬 五銭
+佐：沢瀉 三銭、茯苓 三銭、丹皮 三銭
+使：
+【配伍】
+附子・桂枝：腎陽を温め、腎気の働きを助ける。
+熟地黄・山茱萸・山薬：陰を補い、その中から陽を養う三種の補薬。
+丹皮・茯苓・沢瀉：濁りと熱を除き、水を巡らせて補薬の滞りを防ぐ三種の瀉薬。</t>
         </is>
       </c>
     </row>
@@ -23428,6 +25803,25 @@
 White Peony Root promotes urination, softens the Liver and eases pain while balancing the drying and warming nature of Prepared Aconite Root.</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>真武湯
+【出典】『傷寒論』
+【効能】陽を温めて水を排す
+【主治】腎虚水泛
+【構成】
+君：附子 三銭
+臣：茯苓 三銭、白朮 三銭
+佐：生姜 二銭、白芍 三銭
+使：
+【配伍】
+附子：強い温熱の性質で腎陽を補い、寒を散らして水の代謝を助ける。
+茯苓：脾を整えて湿と水を排し、むくみを和らげる。
+白朮：脾を整えて湿を乾かす。
+生姜：体内の水を温めて散らし、胃を整える。
+白芍：排尿を助け、肝と筋を柔らかくして痛みを緩め、附子の強い温熱から陰を守る。</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -23495,6 +25889,25 @@
 Achyranthes Root supports the Liver and Kidney, strengthens the sinews and bones, and guides the formula downward.</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>左帰丸
+【出典】『景岳全書』
+【効能】陰と腎を補い、精と髄を養う
+【主治】腎精不足
+【構成】
+君：熟地黄 八銭
+臣：亀板膠 四銭、鹿角膠 四銭、枸杞子 四銭、菟絲子 四銭
+佐：山茱萸 四銭、山薬 四銭
+使：牛膝 三銭
+【配伍】
+熟地黄：真陰を大いに補い、精と髄を養う。
+山薬・枸杞子・山茱萸：肝腎の陰と精を養い、熟地黄を助ける。
+亀板膠・鹿角膠：精血を強く補い、陰陽をともに養う。
+菟絲子：腎と精を補う。
+牛膝：肝腎と筋骨を支え、薬の働きを下へ導く。</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -23560,6 +25973,25 @@
 Lotus Stamen helps retain essence.
 Fossilized Bone and Oyster Shell settle and astringe to help prevent leakage.
 Lotus Seed nourishes the Heart, calms the spirit, supports the Kidney and helps bind the pills.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>金鎖固精丸
+【出典】『医方集解』
+【効能】腎を補い、精と腎気を収める
+【主治】腎気不固
+【構成】
+君：沙苑子 五銭
+臣：芡実 五銭
+佐：竜骨 五銭、牡蛎 五銭、蓮鬚 三銭
+使：蓮子 三両
+【配伍】
+沙苑子：肝腎と精を穏やかに補う。
+芡実：脾と腎を補い、精気を収める。
+蓮鬚：精を収める。
+竜骨・牡蛎：鎮静と収斂の働きで漏れを防ぐ。
+蓮子：心を養って精神を落ち着かせ、腎と精を補い、丸剤をまとめる。</t>
         </is>
       </c>
     </row>
@@ -23633,6 +26065,26 @@
 Glutinous Rice strengthens the Spleen and Stomach and nourishes the developing fetus.</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>泰山磐石散
+【出典】『景岳全書』
+【効能】気と脾を補い、血を養って胎を安定させる
+【主治】妊娠
+【構成】
+君：白朮 二銭
+臣：人参 一銭、黄耆 一銭、続断 一銭、熟地黄 一銭、当帰 一銭
+佐：白芍 八分、川芎 八分、黄芩 一銭、縮砂 五分
+使：甘草 五分、糯米 五分
+【配伍】
+人参・黄耆・白朮：気血を生む脾胃を整え、胎を支える。
+当帰・熟地黄・白芍・川芎：血を養って巡らせ、妊娠を支える衝脈と任脈を補う。
+続断：肝腎を補い、胎を安定させる。
+黄芩：熱を清めて胎を守る。
+縮砂：気と胃を整え、補薬による滞りを防ぐ。
+炙甘草・糯米：気と脾胃を養い、諸薬を調和させる。</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -23700,6 +26152,25 @@
 Egg Yolk nourishes Yin, moistens Dryness and calms the Heart and spirit.</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>黄連阿膠湯
+【出典】『傷寒論』
+【効能】陰を養って火を抑え、心と腎を調和させる
+【主治】心腎不交
+【構成】
+君：黄連 四銭
+臣：黄芩 三銭、白芍 三銭
+佐：阿膠 三銭
+使：鶏子黄 一両
+【配伍】
+黄連：心火といらだちを清め、精神を落ち着かせる。
+黄芩：黄連を助けて心火を清める。
+阿膠：腎陰と血を養い、心火との均衡を整える。
+白芍：陰と営を収め、肝を柔らかくする。
+鶏子黄：陰と心を潤し、心と腎の調和を助ける。</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -23761,6 +26232,23 @@
 Raw Gypsum strongly clears intense Heat at the Yangming Qi level, easing high fever and heavy sweating.
 Anemarrhena Rhizome clears Heat, nourishes Yin and generates fluids, relieving agitation and thirst.
 Non-Glutinous Rice and prepared Licorice Root support Qi and the Stomach, temper the cooling herbs and protect body fluids.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>白虎湯
+【出典】『傷寒論』
+【効能】気分の熱を清め、津液を生む
+【主治】気分熱盛
+【構成】
+君：石膏 二両
+臣：知母 六銭
+佐：粳米 三銭
+使：甘草 二銭
+【配伍】
+生石膏：強い寒性で陽明の気分にこもる熱を清め、高熱と大量の汗を和らげる。
+知母：熱を清め、陰と津液を養い、渇きを鎮める。
+粳米・炙甘草：気と胃を養い、石膏と知母の寒性を和らげ、津液を補う。</t>
         </is>
       </c>
     </row>
@@ -39721,7 +42209,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>東璧よ、朝廷から福建への赴任を命じられた。発つ前に、お前と父上に会いに来たのだ。</t>
+          <t>東璧よ、朝廷から福建への赴任を命じられた。発つ前に、お前とお父上に会いに来たのだ。</t>
         </is>
       </c>
     </row>
@@ -51579,7 +54067,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>王様は私を心から大切にしてくれます。身請けが済んだら結婚できると二人で喜んでいたのに、おかみさんがあんな仕打ちをするなんて……</t>
+          <t>王公子は私を心から大切にしてくれます。身請けが済んだら夫婦になれると二人で喜んでいたのに、おかみさんがあんな仕打ちをするなんて……</t>
         </is>
       </c>
     </row>
@@ -53823,7 +56311,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>あなた、向こうに橋があるわ。渡って厄払いをしましょう！</t>
+          <t>奥様、向こうに橋があります。渡って厄払いをしましょう！</t>
         </is>
       </c>
     </row>

--- a/DataTables/translations_managed.xlsx
+++ b/DataTables/translations_managed.xlsx
@@ -9654,7 +9654,7 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>Medical Records</t>
+          <t>Clinical Records</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
